--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -693,14 +693,14 @@
         <v/>
       </c>
       <c r="D15" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Flat $39.99 · 5 destinations · MOST POPULAR</t>
+          <t>10GB pool · 50% carry</t>
         </is>
       </c>
     </row>
@@ -721,11 +721,11 @@
         <v>3</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>3GB pool · 30% carry</t>
+          <t>8GB pool · 70% carry · 1 oops · RECOMMENDED</t>
         </is>
       </c>
     </row>
@@ -746,11 +746,11 @@
         <v>8</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>8GB pool · 50% carry · RECOMMENDED</t>
+          <t>20GB pool · 100% carry × 2 months max · 2 oops</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>20GB pool · 80% carry · 2 oops</t>
+          <t>$299/yr · 100% carry (unlimited via annual)</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -718,14 +718,14 @@
         <v/>
       </c>
       <c r="D16" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>0.7</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>8GB pool · 70% carry · 1 oops · RECOMMENDED</t>
+          <t>15GB pool · 70% carry · 1 oops · RECOMMENDED</t>
         </is>
       </c>
     </row>
@@ -768,14 +768,14 @@
         <v/>
       </c>
       <c r="D18" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>0.8</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>$299/yr · 100% carry (unlimited via annual)</t>
+          <t>$299/yr · 12GB pool + 12GB lifetime emergency bank · 100% carry</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -661,21 +661,21 @@
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>4.99</v>
+        <v>13.68</v>
       </c>
       <c r="C14" s="11">
         <f>B14*12</f>
         <v/>
       </c>
       <c r="D14" s="12" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Avg per trip · 1GB/1-day · no carry</t>
+          <t>PAYG · avg 2.5 GB/mo @ $4.99/GB + 20% refuel attach @ $5.99</t>
         </is>
       </c>
     </row>
@@ -2996,9 +2996,8 @@
         <f>'README &amp; Assumptions'!D14</f>
         <v/>
       </c>
-      <c r="C17" s="19">
-        <f>$C$11</f>
-        <v/>
+      <c r="C17" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="D17" s="20">
         <f>B17*C17</f>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="35">
@@ -958,7 +958,7 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>0.35</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="36">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="37">
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="38">
@@ -998,7 +998,7 @@
         </is>
       </c>
       <c r="B39" s="13" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="40">
@@ -1008,7 +1008,7 @@
         </is>
       </c>
       <c r="B40" s="13" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="43">
@@ -2843,7 +2843,7 @@
         <v>0.3</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
@@ -2864,7 +2864,7 @@
         <v>0.65</v>
       </c>
       <c r="D7" s="13" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
@@ -2885,7 +2885,7 @@
         <v>0.95</v>
       </c>
       <c r="D8" s="13" t="n">
-        <v>0.5</v>
+        <v>0.65</v>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
@@ -5251,7 +5251,7 @@
         </is>
       </c>
       <c r="B6" s="29" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="C6" s="20">
         <f>IFERROR(1/B6,0)</f>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="B7" s="29" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="C7" s="20">
         <f>IFERROR(1/B7,0)</f>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="B8" s="29" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="C8" s="20">
         <f>IFERROR(1/B8,0)</f>
@@ -5308,7 +5308,7 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="C9" s="20">
         <f>IFERROR(1/B9,0)</f>
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="B10" s="29" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="C10" s="20">
         <f>IFERROR(1/B10,0)</f>
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="B11" s="29" t="n">
-        <v>0.03</v>
+        <v>0.006</v>
       </c>
       <c r="C11" s="20">
         <f>IFERROR(1/B11,0)</f>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -718,14 +718,14 @@
         <v/>
       </c>
       <c r="D16" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E16" s="13" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>15GB pool · 70% carry · 1 oops · RECOMMENDED</t>
+          <t>10GB pool · 50% carry × 2mo · lounge guides</t>
         </is>
       </c>
     </row>
@@ -743,14 +743,14 @@
         <v/>
       </c>
       <c r="D17" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="E17" s="13" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>20GB pool · 100% carry × 2 months max · 2 oops</t>
+          <t>15GB pool · 70% carry × 2mo · priority support · RECOMMENDED</t>
         </is>
       </c>
     </row>
@@ -768,14 +768,14 @@
         <v/>
       </c>
       <c r="D18" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E18" s="13" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>$299/yr · 12GB pool + 12GB lifetime emergency bank · 100% carry</t>
+          <t>25GB pool · 100% carry × 2mo · concierge layer</t>
         </is>
       </c>
     </row>
@@ -792,14 +792,14 @@
         <v>299</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>$299/yr · unlimited carry</t>
+          <t>$299/yr · 12GB monthly + 12GB lifetime emergency bank · 100% carry × 2mo · pilots only</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -2837,7 +2837,7 @@
         </is>
       </c>
       <c r="B6" s="13" t="n">
-        <v>0.4</v>
+        <v>0.25</v>
       </c>
       <c r="C6" s="13" t="n">
         <v>0.3</v>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Subscribes for peace-of-mind, barely uses pool</t>
+          <t>Crew-skewed base: fewer pure-breakage users than general travel</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="C7" s="13" t="n">
         <v>0.65</v>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Normal consumption, occasionally over</t>
+          <t>Crew-skewed base: largest cohort — normal long-haul consumption</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="C8" s="13" t="n">
         <v>0.95</v>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Power user, often refuels</t>
+          <t>Crew-skewed base: more power users (it's their job to travel)</t>
         </is>
       </c>
     </row>
@@ -5056,17 +5056,17 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Healthy SaaS (lots of light users)</t>
+          <t>Healthy SaaS (general travel — old base, upside)</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>0.05</v>
@@ -5087,17 +5087,17 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Base (current model)</t>
+          <t>Base (crew-skewed — new default)</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="13" t="n">
         <v>0.4</v>
       </c>
-      <c r="C6" s="13" t="n">
-        <v>0.35</v>
-      </c>
       <c r="D6" s="13" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>0.05</v>
@@ -5118,14 +5118,14 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Heavy crew (power users dominate)</t>
+          <t>Pure crew (power users dominate — downside)</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="D7" s="13" t="n">
         <v>0.45</v>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -10,15 +10,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README &amp; Assumptions" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Behavior" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Unit Economics" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Simulator" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +28,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="11">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -36,8 +37,11 @@
     <numFmt numFmtId="169" formatCode="$#,##0.00;[Red]-$#,##0.00"/>
     <numFmt numFmtId="170" formatCode="0&quot;x&quot;"/>
     <numFmt numFmtId="171" formatCode="$#,##0;[Red]-$#,##0"/>
+    <numFmt numFmtId="172" formatCode="&quot;$&quot;#,##0.000"/>
+    <numFmt numFmtId="173" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="174" formatCode="#,##0.00&quot; GB&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,8 +95,52 @@
       <color rgb="00595959"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="00D71921"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <color rgb="00008000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -109,6 +157,21 @@
         <fgColor rgb="00D71921"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001A1A1A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -122,7 +185,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -163,6 +226,23 @@
     <xf numFmtId="169" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="171" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="14" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="172" fontId="15" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1102,6 +1182,538 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Per-Tier Geo Mix — different tiers fly different routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Roster Bundle users fly mostly crew layover countries (Tier-A). Economy users vacation in Tier-C (Bali/Maldives).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>% Tier-A (cheap)</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>% Tier-B (medium)</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>% Tier-C (expensive)</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Effective Cost/GB</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Margin vs Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E5" s="11">
+        <f>B5*'README &amp; Assumptions'!C25+C5*'README &amp; Assumptions'!C26+D5*'README &amp; Assumptions'!C27</f>
+        <v/>
+      </c>
+      <c r="F5" s="11">
+        <f>'README &amp; Assumptions'!C29-E5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E6" s="11">
+        <f>B6*'README &amp; Assumptions'!C25+C6*'README &amp; Assumptions'!C26+D6*'README &amp; Assumptions'!C27</f>
+        <v/>
+      </c>
+      <c r="F6" s="11">
+        <f>'README &amp; Assumptions'!C29-E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E7" s="11">
+        <f>B7*'README &amp; Assumptions'!C25+C7*'README &amp; Assumptions'!C26+D7*'README &amp; Assumptions'!C27</f>
+        <v/>
+      </c>
+      <c r="F7" s="11">
+        <f>'README &amp; Assumptions'!C29-E7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E8" s="11">
+        <f>B8*'README &amp; Assumptions'!C25+C8*'README &amp; Assumptions'!C26+D8*'README &amp; Assumptions'!C27</f>
+        <v/>
+      </c>
+      <c r="F8" s="11">
+        <f>'README &amp; Assumptions'!C29-E8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C9" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D9" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E9" s="11">
+        <f>B9*'README &amp; Assumptions'!C25+C9*'README &amp; Assumptions'!C26+D9*'README &amp; Assumptions'!C27</f>
+        <v/>
+      </c>
+      <c r="F9" s="11">
+        <f>'README &amp; Assumptions'!C29-E9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="C10" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D10" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E10" s="11">
+        <f>B10*'README &amp; Assumptions'!C25+C10*'README &amp; Assumptions'!C26+D10*'README &amp; Assumptions'!C27</f>
+        <v/>
+      </c>
+      <c r="F10" s="11">
+        <f>'README &amp; Assumptions'!C29-E10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Refuel</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C11" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D11" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E11" s="11">
+        <f>B11*'README &amp; Assumptions'!C25+C11*'README &amp; Assumptions'!C26+D11*'README &amp; Assumptions'!C27</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>'README &amp; Assumptions'!C29-E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>REVISED PER-TIER GROSS MARGIN (with tier-specific geo mix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Revenue</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>GB Consumed</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>Effective $/GB</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>Adjusted COGS</t>
+        </is>
+      </c>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="G14" s="8" t="inlineStr">
+        <is>
+          <t>Margin %</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>vs Default</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="B15" s="21">
+        <f>'Per-Tier Unit Economics'!B5</f>
+        <v/>
+      </c>
+      <c r="C15" s="18">
+        <f>'Per-Tier Unit Economics'!C5</f>
+        <v/>
+      </c>
+      <c r="D15" s="21">
+        <f>E5</f>
+        <v/>
+      </c>
+      <c r="E15" s="11">
+        <f>C15*D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="22">
+        <f>B15-E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>IFERROR(F15/B15,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="31">
+        <f>F15-'Per-Tier Unit Economics'!I5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B16" s="21">
+        <f>'Per-Tier Unit Economics'!B6</f>
+        <v/>
+      </c>
+      <c r="C16" s="18">
+        <f>'Per-Tier Unit Economics'!C6</f>
+        <v/>
+      </c>
+      <c r="D16" s="21">
+        <f>E6</f>
+        <v/>
+      </c>
+      <c r="E16" s="11">
+        <f>C16*D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="22">
+        <f>B16-E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="17">
+        <f>IFERROR(F16/B16,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="31">
+        <f>F16-'Per-Tier Unit Economics'!I6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B17" s="21">
+        <f>'Per-Tier Unit Economics'!B7</f>
+        <v/>
+      </c>
+      <c r="C17" s="18">
+        <f>'Per-Tier Unit Economics'!C7</f>
+        <v/>
+      </c>
+      <c r="D17" s="21">
+        <f>E7</f>
+        <v/>
+      </c>
+      <c r="E17" s="11">
+        <f>C17*D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="22">
+        <f>B17-E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="17">
+        <f>IFERROR(F17/B17,0)</f>
+        <v/>
+      </c>
+      <c r="H17" s="31">
+        <f>F17-'Per-Tier Unit Economics'!I7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B18" s="21">
+        <f>'Per-Tier Unit Economics'!B8</f>
+        <v/>
+      </c>
+      <c r="C18" s="18">
+        <f>'Per-Tier Unit Economics'!C8</f>
+        <v/>
+      </c>
+      <c r="D18" s="21">
+        <f>E8</f>
+        <v/>
+      </c>
+      <c r="E18" s="11">
+        <f>C18*D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="22">
+        <f>B18-E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="17">
+        <f>IFERROR(F18/B18,0)</f>
+        <v/>
+      </c>
+      <c r="H18" s="31">
+        <f>F18-'Per-Tier Unit Economics'!I8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B19" s="21">
+        <f>'Per-Tier Unit Economics'!B9</f>
+        <v/>
+      </c>
+      <c r="C19" s="18">
+        <f>'Per-Tier Unit Economics'!C9</f>
+        <v/>
+      </c>
+      <c r="D19" s="21">
+        <f>E9</f>
+        <v/>
+      </c>
+      <c r="E19" s="11">
+        <f>C19*D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="22">
+        <f>B19-E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="17">
+        <f>IFERROR(F19/B19,0)</f>
+        <v/>
+      </c>
+      <c r="H19" s="31">
+        <f>F19-'Per-Tier Unit Economics'!I9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B20" s="21">
+        <f>'Per-Tier Unit Economics'!B10</f>
+        <v/>
+      </c>
+      <c r="C20" s="18">
+        <f>'Per-Tier Unit Economics'!C10</f>
+        <v/>
+      </c>
+      <c r="D20" s="21">
+        <f>E10</f>
+        <v/>
+      </c>
+      <c r="E20" s="11">
+        <f>C20*D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="22">
+        <f>B20-E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="17">
+        <f>IFERROR(F20/B20,0)</f>
+        <v/>
+      </c>
+      <c r="H20" s="31">
+        <f>F20-'Per-Tier Unit Economics'!I10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>Refuel</t>
+        </is>
+      </c>
+      <c r="B21" s="21">
+        <f>'Per-Tier Unit Economics'!B11</f>
+        <v/>
+      </c>
+      <c r="C21" s="18">
+        <f>'Per-Tier Unit Economics'!C11</f>
+        <v/>
+      </c>
+      <c r="D21" s="21">
+        <f>E11</f>
+        <v/>
+      </c>
+      <c r="E21" s="11">
+        <f>C21*D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="22">
+        <f>B21-E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="17">
+        <f>IFERROR(F21/B21,0)</f>
+        <v/>
+      </c>
+      <c r="H21" s="31">
+        <f>F21-'Per-Tier Unit Economics'!I11</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1721,7 +2333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2298,7 +2910,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3646,6 +4258,847 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>Pricing Simulator — what should we charge given Samurai wholesale costs?</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Input wholesale $/GB (top yellow cells). All tiers below recalc break-even + margin-target prices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>WHOLESALE COST SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>Blended $/GB</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Samurai actual (from rate sheet)</t>
+        </is>
+      </c>
+      <c r="B6" s="42" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Blended 30-day plan: HK/KR $0.26, UK $0.32, USA $0.35, JP $0.37, AU $0.43, UAE $1.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Samurai target (after negotiation)</t>
+        </is>
+      </c>
+      <c r="B7" s="42" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>What we ask Samurai to come down to — basis for negotiation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>eSIM Access direct (Tier-2, future)</t>
+        </is>
+      </c>
+      <c r="B8" s="42" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>True wholesale — what we get going direct at scale (5K+ activations/mo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>ACTIVE WHOLESALE COST</t>
+        </is>
+      </c>
+      <c r="B9" s="44">
+        <f>B6</f>
+        <v/>
+      </c>
+      <c r="C9" s="39" t="inlineStr">
+        <is>
+          <t>← change formula to =B7 or =B8 to test other scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>USER BEHAVIOR INPUTS (from Tab 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>% Pool consumed (weighted)</t>
+        </is>
+      </c>
+      <c r="B12" s="45">
+        <f>'User Behavior'!C11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>% Refuel attach (weighted)</t>
+        </is>
+      </c>
+      <c r="B13" s="45">
+        <f>'User Behavior'!D11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Refuel price (per 1GB top-up)</t>
+        </is>
+      </c>
+      <c r="B14" s="46">
+        <f>'README &amp; Assumptions'!B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>PER-TIER PRICING MATRIX</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="47" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B17" s="47" t="inlineStr">
+        <is>
+          <t>Pool GB</t>
+        </is>
+      </c>
+      <c r="C17" s="47" t="inlineStr">
+        <is>
+          <t>GB Used
+(consumed)</t>
+        </is>
+      </c>
+      <c r="D17" s="47" t="inlineStr">
+        <is>
+          <t>Wholesale
+COGS/user</t>
+        </is>
+      </c>
+      <c r="E17" s="47" t="inlineStr">
+        <is>
+          <t>Refuel
+revenue</t>
+        </is>
+      </c>
+      <c r="F17" s="47" t="inlineStr">
+        <is>
+          <t>Refuel
+COGS</t>
+        </is>
+      </c>
+      <c r="G17" s="47" t="inlineStr">
+        <is>
+          <t>NET COGS
+per user</t>
+        </is>
+      </c>
+      <c r="H17" s="47" t="inlineStr">
+        <is>
+          <t>Break-even
+price</t>
+        </is>
+      </c>
+      <c r="I17" s="47" t="inlineStr">
+        <is>
+          <t>30% margin
+price</t>
+        </is>
+      </c>
+      <c r="J17" s="47" t="inlineStr">
+        <is>
+          <t>50% margin
+price</t>
+        </is>
+      </c>
+      <c r="K17" s="47" t="inlineStr">
+        <is>
+          <t>70% margin
+price</t>
+        </is>
+      </c>
+      <c r="L17" s="47" t="inlineStr">
+        <is>
+          <t>Current
+retail</t>
+        </is>
+      </c>
+      <c r="M17" s="47" t="inlineStr">
+        <is>
+          <t>Current
+margin %</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>Economy (PAYG)</t>
+        </is>
+      </c>
+      <c r="B18" s="49">
+        <f>'README &amp; Assumptions'!D14</f>
+        <v/>
+      </c>
+      <c r="C18" s="50">
+        <f>B18</f>
+        <v/>
+      </c>
+      <c r="D18" s="51">
+        <f>C18*$B$9</f>
+        <v/>
+      </c>
+      <c r="E18" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="51">
+        <f>D18+F18-E18</f>
+        <v/>
+      </c>
+      <c r="H18" s="51">
+        <f>G18</f>
+        <v/>
+      </c>
+      <c r="I18" s="51">
+        <f>G18/0.7</f>
+        <v/>
+      </c>
+      <c r="J18" s="51">
+        <f>G18/0.5</f>
+        <v/>
+      </c>
+      <c r="K18" s="51">
+        <f>G18/0.3</f>
+        <v/>
+      </c>
+      <c r="L18" s="46">
+        <f>'README &amp; Assumptions'!B14</f>
+        <v/>
+      </c>
+      <c r="M18" s="52">
+        <f>IFERROR((L18-G18)/L18,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B19" s="49">
+        <f>'README &amp; Assumptions'!D15</f>
+        <v/>
+      </c>
+      <c r="C19" s="50">
+        <f>B19*$B$12</f>
+        <v/>
+      </c>
+      <c r="D19" s="51">
+        <f>C19*$B$9</f>
+        <v/>
+      </c>
+      <c r="E19" s="51">
+        <f>$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="F19" s="51">
+        <f>$B$13*1*$B$9</f>
+        <v/>
+      </c>
+      <c r="G19" s="51">
+        <f>D19+F19-E19</f>
+        <v/>
+      </c>
+      <c r="H19" s="51">
+        <f>G19</f>
+        <v/>
+      </c>
+      <c r="I19" s="51">
+        <f>G19/0.7</f>
+        <v/>
+      </c>
+      <c r="J19" s="51">
+        <f>G19/0.5</f>
+        <v/>
+      </c>
+      <c r="K19" s="51">
+        <f>G19/0.3</f>
+        <v/>
+      </c>
+      <c r="L19" s="46">
+        <f>'README &amp; Assumptions'!B15</f>
+        <v/>
+      </c>
+      <c r="M19" s="52">
+        <f>IFERROR((L19-G19)/L19,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B20" s="49">
+        <f>'README &amp; Assumptions'!D16</f>
+        <v/>
+      </c>
+      <c r="C20" s="50">
+        <f>B20*$B$12</f>
+        <v/>
+      </c>
+      <c r="D20" s="51">
+        <f>C20*$B$9</f>
+        <v/>
+      </c>
+      <c r="E20" s="51">
+        <f>$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="F20" s="51">
+        <f>$B$13*1*$B$9</f>
+        <v/>
+      </c>
+      <c r="G20" s="51">
+        <f>D20+F20-E20</f>
+        <v/>
+      </c>
+      <c r="H20" s="51">
+        <f>G20</f>
+        <v/>
+      </c>
+      <c r="I20" s="51">
+        <f>G20/0.7</f>
+        <v/>
+      </c>
+      <c r="J20" s="51">
+        <f>G20/0.5</f>
+        <v/>
+      </c>
+      <c r="K20" s="51">
+        <f>G20/0.3</f>
+        <v/>
+      </c>
+      <c r="L20" s="46">
+        <f>'README &amp; Assumptions'!B16</f>
+        <v/>
+      </c>
+      <c r="M20" s="52">
+        <f>IFERROR((L20-G20)/L20,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B21" s="49">
+        <f>'README &amp; Assumptions'!D17</f>
+        <v/>
+      </c>
+      <c r="C21" s="50">
+        <f>B21*$B$12</f>
+        <v/>
+      </c>
+      <c r="D21" s="51">
+        <f>C21*$B$9</f>
+        <v/>
+      </c>
+      <c r="E21" s="51">
+        <f>$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="F21" s="51">
+        <f>$B$13*1*$B$9</f>
+        <v/>
+      </c>
+      <c r="G21" s="51">
+        <f>D21+F21-E21</f>
+        <v/>
+      </c>
+      <c r="H21" s="51">
+        <f>G21</f>
+        <v/>
+      </c>
+      <c r="I21" s="51">
+        <f>G21/0.7</f>
+        <v/>
+      </c>
+      <c r="J21" s="51">
+        <f>G21/0.5</f>
+        <v/>
+      </c>
+      <c r="K21" s="51">
+        <f>G21/0.3</f>
+        <v/>
+      </c>
+      <c r="L21" s="46">
+        <f>'README &amp; Assumptions'!B17</f>
+        <v/>
+      </c>
+      <c r="M21" s="52">
+        <f>IFERROR((L21-G21)/L21,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B22" s="49">
+        <f>'README &amp; Assumptions'!D18</f>
+        <v/>
+      </c>
+      <c r="C22" s="50">
+        <f>B22*$B$12</f>
+        <v/>
+      </c>
+      <c r="D22" s="51">
+        <f>C22*$B$9</f>
+        <v/>
+      </c>
+      <c r="E22" s="51">
+        <f>$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="F22" s="51">
+        <f>$B$13*1*$B$9</f>
+        <v/>
+      </c>
+      <c r="G22" s="51">
+        <f>D22+F22-E22</f>
+        <v/>
+      </c>
+      <c r="H22" s="51">
+        <f>G22</f>
+        <v/>
+      </c>
+      <c r="I22" s="51">
+        <f>G22/0.7</f>
+        <v/>
+      </c>
+      <c r="J22" s="51">
+        <f>G22/0.5</f>
+        <v/>
+      </c>
+      <c r="K22" s="51">
+        <f>G22/0.3</f>
+        <v/>
+      </c>
+      <c r="L22" s="46">
+        <f>'README &amp; Assumptions'!B18</f>
+        <v/>
+      </c>
+      <c r="M22" s="52">
+        <f>IFERROR((L22-G22)/L22,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B23" s="49">
+        <f>'README &amp; Assumptions'!D19</f>
+        <v/>
+      </c>
+      <c r="C23" s="50">
+        <f>B23*$B$12</f>
+        <v/>
+      </c>
+      <c r="D23" s="51">
+        <f>C23*$B$9</f>
+        <v/>
+      </c>
+      <c r="E23" s="51">
+        <f>$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="F23" s="51">
+        <f>$B$13*1*$B$9</f>
+        <v/>
+      </c>
+      <c r="G23" s="51">
+        <f>D23+F23-E23</f>
+        <v/>
+      </c>
+      <c r="H23" s="51">
+        <f>G23</f>
+        <v/>
+      </c>
+      <c r="I23" s="51">
+        <f>G23/0.7</f>
+        <v/>
+      </c>
+      <c r="J23" s="51">
+        <f>G23/0.5</f>
+        <v/>
+      </c>
+      <c r="K23" s="51">
+        <f>G23/0.3</f>
+        <v/>
+      </c>
+      <c r="L23" s="46">
+        <f>'README &amp; Assumptions'!B19</f>
+        <v/>
+      </c>
+      <c r="M23" s="52">
+        <f>IFERROR((L23-G23)/L23,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>NEGOTIATION SUMMARY</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="41" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B27" s="41" t="inlineStr">
+        <is>
+          <t>Current retail</t>
+        </is>
+      </c>
+      <c r="C27" s="41" t="inlineStr">
+        <is>
+          <t>COGS @ Samurai actual</t>
+        </is>
+      </c>
+      <c r="D27" s="41" t="inlineStr">
+        <is>
+          <t>COGS @ Samurai target</t>
+        </is>
+      </c>
+      <c r="E27" s="41" t="inlineStr">
+        <is>
+          <t>Savings/user</t>
+        </is>
+      </c>
+      <c r="F27" s="41" t="inlineStr">
+        <is>
+          <t>At 10K users</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>Economy (PAYG)</t>
+        </is>
+      </c>
+      <c r="B28" s="46">
+        <f>'README &amp; Assumptions'!B14</f>
+        <v/>
+      </c>
+      <c r="C28" s="51">
+        <f>B18*$B$6</f>
+        <v/>
+      </c>
+      <c r="D28" s="51">
+        <f>B18*$B$7</f>
+        <v/>
+      </c>
+      <c r="E28" s="51">
+        <f>C28-D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="51">
+        <f>E28*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="48" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B29" s="46">
+        <f>'README &amp; Assumptions'!B15</f>
+        <v/>
+      </c>
+      <c r="C29" s="51">
+        <f>C19*$B$6+$B$13*1*$B$6-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="D29" s="51">
+        <f>C19*$B$7+$B$13*1*$B$7-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="E29" s="51">
+        <f>C29-D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="51">
+        <f>E29*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B30" s="46">
+        <f>'README &amp; Assumptions'!B16</f>
+        <v/>
+      </c>
+      <c r="C30" s="51">
+        <f>C20*$B$6+$B$13*1*$B$6-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="D30" s="51">
+        <f>C20*$B$7+$B$13*1*$B$7-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="E30" s="51">
+        <f>C30-D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="51">
+        <f>E30*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B31" s="46">
+        <f>'README &amp; Assumptions'!B17</f>
+        <v/>
+      </c>
+      <c r="C31" s="51">
+        <f>C21*$B$6+$B$13*1*$B$6-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="D31" s="51">
+        <f>C21*$B$7+$B$13*1*$B$7-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="E31" s="51">
+        <f>C31-D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="51">
+        <f>E31*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B32" s="46">
+        <f>'README &amp; Assumptions'!B18</f>
+        <v/>
+      </c>
+      <c r="C32" s="51">
+        <f>C22*$B$6+$B$13*1*$B$6-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="D32" s="51">
+        <f>C22*$B$7+$B$13*1*$B$7-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="E32" s="51">
+        <f>C32-D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="51">
+        <f>E32*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B33" s="46">
+        <f>'README &amp; Assumptions'!B19</f>
+        <v/>
+      </c>
+      <c r="C33" s="51">
+        <f>C23*$B$6+$B$13*1*$B$6-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="D33" s="51">
+        <f>C23*$B$7+$B$13*1*$B$7-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="E33" s="51">
+        <f>C33-D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="51">
+        <f>E33*10000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>How to use this tab</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="39" t="inlineStr">
+        <is>
+          <t>1. Yellow cells (B6, B7, B8) = your wholesale assumptions. Change to update everything below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>2. The "ACTIVE WHOLESALE" (B9) is a formula — change "=B6" to "=B7" to model the negotiation target, "=B8" for direct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>3. Behavior inputs (B12:B14) pull from Tab 2 (User Behavior) and README. Change those tabs → this updates.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>4. Tier matrix: break-even / 30% / 50% / 70% margin show what you NEED to charge at each cost basis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="inlineStr">
+        <is>
+          <t>5. Negotiation summary at bottom: if you push Samurai from $0.45 to $0.30/GB, here is the per-user savings × 10K users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>6. Compare "Current retail" (col L) vs "50% margin price" (col J). If current &lt; 50%-margin → you are underpricing.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A39:H39"/>
+    <mergeCell ref="A38:H38"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A36:H36"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="A40:H40"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3893,7 +5346,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4164,7 +5617,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4978,7 +6431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5182,7 +6635,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5786,536 +7239,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Per-Tier Geo Mix — different tiers fly different routes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Roster Bundle users fly mostly crew layover countries (Tier-A). Economy users vacation in Tier-C (Bali/Maldives).</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>% Tier-A (cheap)</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>% Tier-B (medium)</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>% Tier-C (expensive)</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Effective Cost/GB</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Margin vs Default</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E5" s="11">
-        <f>B5*'README &amp; Assumptions'!C25+C5*'README &amp; Assumptions'!C26+D5*'README &amp; Assumptions'!C27</f>
-        <v/>
-      </c>
-      <c r="F5" s="11">
-        <f>'README &amp; Assumptions'!C29-E5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Roster Bundle</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E6" s="11">
-        <f>B6*'README &amp; Assumptions'!C25+C6*'README &amp; Assumptions'!C26+D6*'README &amp; Assumptions'!C27</f>
-        <v/>
-      </c>
-      <c r="F6" s="11">
-        <f>'README &amp; Assumptions'!C29-E6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Premium Economy</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E7" s="11">
-        <f>B7*'README &amp; Assumptions'!C25+C7*'README &amp; Assumptions'!C26+D7*'README &amp; Assumptions'!C27</f>
-        <v/>
-      </c>
-      <c r="F7" s="11">
-        <f>'README &amp; Assumptions'!C29-E7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E8" s="11">
-        <f>B8*'README &amp; Assumptions'!C25+C8*'README &amp; Assumptions'!C26+D8*'README &amp; Assumptions'!C27</f>
-        <v/>
-      </c>
-      <c r="F8" s="11">
-        <f>'README &amp; Assumptions'!C29-E8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E9" s="11">
-        <f>B9*'README &amp; Assumptions'!C25+C9*'README &amp; Assumptions'!C26+D9*'README &amp; Assumptions'!C27</f>
-        <v/>
-      </c>
-      <c r="F9" s="11">
-        <f>'README &amp; Assumptions'!C29-E9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Cockpit</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D10" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E10" s="11">
-        <f>B10*'README &amp; Assumptions'!C25+C10*'README &amp; Assumptions'!C26+D10*'README &amp; Assumptions'!C27</f>
-        <v/>
-      </c>
-      <c r="F10" s="11">
-        <f>'README &amp; Assumptions'!C29-E10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Refuel</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E11" s="11">
-        <f>B11*'README &amp; Assumptions'!C25+C11*'README &amp; Assumptions'!C26+D11*'README &amp; Assumptions'!C27</f>
-        <v/>
-      </c>
-      <c r="F11" s="11">
-        <f>'README &amp; Assumptions'!C29-E11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>REVISED PER-TIER GROSS MARGIN (with tier-specific geo mix)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Revenue</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>GB Consumed</t>
-        </is>
-      </c>
-      <c r="D14" s="8" t="inlineStr">
-        <is>
-          <t>Effective $/GB</t>
-        </is>
-      </c>
-      <c r="E14" s="8" t="inlineStr">
-        <is>
-          <t>Adjusted COGS</t>
-        </is>
-      </c>
-      <c r="F14" s="8" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="G14" s="8" t="inlineStr">
-        <is>
-          <t>Margin %</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="inlineStr">
-        <is>
-          <t>vs Default</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B15" s="21">
-        <f>'Per-Tier Unit Economics'!B5</f>
-        <v/>
-      </c>
-      <c r="C15" s="18">
-        <f>'Per-Tier Unit Economics'!C5</f>
-        <v/>
-      </c>
-      <c r="D15" s="21">
-        <f>E5</f>
-        <v/>
-      </c>
-      <c r="E15" s="11">
-        <f>C15*D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="22">
-        <f>B15-E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="17">
-        <f>IFERROR(F15/B15,0)</f>
-        <v/>
-      </c>
-      <c r="H15" s="31">
-        <f>F15-'Per-Tier Unit Economics'!I5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>Roster Bundle</t>
-        </is>
-      </c>
-      <c r="B16" s="21">
-        <f>'Per-Tier Unit Economics'!B6</f>
-        <v/>
-      </c>
-      <c r="C16" s="18">
-        <f>'Per-Tier Unit Economics'!C6</f>
-        <v/>
-      </c>
-      <c r="D16" s="21">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="E16" s="11">
-        <f>C16*D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="22">
-        <f>B16-E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="17">
-        <f>IFERROR(F16/B16,0)</f>
-        <v/>
-      </c>
-      <c r="H16" s="31">
-        <f>F16-'Per-Tier Unit Economics'!I6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Premium Economy</t>
-        </is>
-      </c>
-      <c r="B17" s="21">
-        <f>'Per-Tier Unit Economics'!B7</f>
-        <v/>
-      </c>
-      <c r="C17" s="18">
-        <f>'Per-Tier Unit Economics'!C7</f>
-        <v/>
-      </c>
-      <c r="D17" s="21">
-        <f>E7</f>
-        <v/>
-      </c>
-      <c r="E17" s="11">
-        <f>C17*D17</f>
-        <v/>
-      </c>
-      <c r="F17" s="22">
-        <f>B17-E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="17">
-        <f>IFERROR(F17/B17,0)</f>
-        <v/>
-      </c>
-      <c r="H17" s="31">
-        <f>F17-'Per-Tier Unit Economics'!I7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="B18" s="21">
-        <f>'Per-Tier Unit Economics'!B8</f>
-        <v/>
-      </c>
-      <c r="C18" s="18">
-        <f>'Per-Tier Unit Economics'!C8</f>
-        <v/>
-      </c>
-      <c r="D18" s="21">
-        <f>E8</f>
-        <v/>
-      </c>
-      <c r="E18" s="11">
-        <f>C18*D18</f>
-        <v/>
-      </c>
-      <c r="F18" s="22">
-        <f>B18-E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="17">
-        <f>IFERROR(F18/B18,0)</f>
-        <v/>
-      </c>
-      <c r="H18" s="31">
-        <f>F18-'Per-Tier Unit Economics'!I8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="B19" s="21">
-        <f>'Per-Tier Unit Economics'!B9</f>
-        <v/>
-      </c>
-      <c r="C19" s="18">
-        <f>'Per-Tier Unit Economics'!C9</f>
-        <v/>
-      </c>
-      <c r="D19" s="21">
-        <f>E9</f>
-        <v/>
-      </c>
-      <c r="E19" s="11">
-        <f>C19*D19</f>
-        <v/>
-      </c>
-      <c r="F19" s="22">
-        <f>B19-E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="17">
-        <f>IFERROR(F19/B19,0)</f>
-        <v/>
-      </c>
-      <c r="H19" s="31">
-        <f>F19-'Per-Tier Unit Economics'!I9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Cockpit</t>
-        </is>
-      </c>
-      <c r="B20" s="21">
-        <f>'Per-Tier Unit Economics'!B10</f>
-        <v/>
-      </c>
-      <c r="C20" s="18">
-        <f>'Per-Tier Unit Economics'!C10</f>
-        <v/>
-      </c>
-      <c r="D20" s="21">
-        <f>E10</f>
-        <v/>
-      </c>
-      <c r="E20" s="11">
-        <f>C20*D20</f>
-        <v/>
-      </c>
-      <c r="F20" s="22">
-        <f>B20-E20</f>
-        <v/>
-      </c>
-      <c r="G20" s="17">
-        <f>IFERROR(F20/B20,0)</f>
-        <v/>
-      </c>
-      <c r="H20" s="31">
-        <f>F20-'Per-Tier Unit Economics'!I10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>Refuel</t>
-        </is>
-      </c>
-      <c r="B21" s="21">
-        <f>'Per-Tier Unit Economics'!B11</f>
-        <v/>
-      </c>
-      <c r="C21" s="18">
-        <f>'Per-Tier Unit Economics'!C11</f>
-        <v/>
-      </c>
-      <c r="D21" s="21">
-        <f>E11</f>
-        <v/>
-      </c>
-      <c r="E21" s="11">
-        <f>C21*D21</f>
-        <v/>
-      </c>
-      <c r="F21" s="22">
-        <f>B21-E21</f>
-        <v/>
-      </c>
-      <c r="G21" s="17">
-        <f>IFERROR(F21/B21,0)</f>
-        <v/>
-      </c>
-      <c r="H21" s="31">
-        <f>F21-'Per-Tier Unit Economics'!I11</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -11,15 +11,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="User Behavior" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Unit Economics" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Simulator" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economy Logic" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -28,7 +29,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="11">
+  <numFmts count="13">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -40,8 +41,10 @@
     <numFmt numFmtId="172" formatCode="&quot;$&quot;#,##0.000"/>
     <numFmt numFmtId="173" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="174" formatCode="#,##0.00&quot; GB&quot;"/>
+    <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0.00;[Red](&quot;$&quot;#,##0.00)"/>
+    <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="22">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -139,8 +142,31 @@
       <color rgb="00000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="00B07A1F"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="00D71921"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -172,6 +198,16 @@
         <fgColor rgb="00FFE0B3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -185,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -243,6 +279,28 @@
     <xf numFmtId="174" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="175" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="1" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1182,6 +1240,612 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>LTV / CAC + Per-Tier Churn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>How much can we spend to acquire each tier? LTV:CAC &gt; 3 is investable, &gt; 5 is excellent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PER-TIER MONTHLY CHURN</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Churn %</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Avg Lifetime (mo)</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C6" s="20">
+        <f>IFERROR(1/B6,0)</f>
+        <v/>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>1-month casuals, trial users</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="20">
+        <f>IFERROR(1/B7,0)</f>
+        <v/>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>Sticky once roster sync set up</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="20">
+        <f>IFERROR(1/B8,0)</f>
+        <v/>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>Light commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="C9" s="20">
+        <f>IFERROR(1/B9,0)</f>
+        <v/>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>Pool habit forms, high retention</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B10" s="29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C10" s="20">
+        <f>IFERROR(1/B10,0)</f>
+        <v/>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Power users, perks lock in</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="C11" s="20">
+        <f>IFERROR(1/B11,0)</f>
+        <v/>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Annual prepay = automatic 12-mo retention</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Refuel (add-on)</t>
+        </is>
+      </c>
+      <c r="B12" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C12" s="20">
+        <f>IFERROR(1/B12,0)</f>
+        <v/>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Per-purchase, no subscription</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>CUSTOMER ACQUISITION COST (per-channel blended avg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>% of Acquisition</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>$ CAC</t>
+        </is>
+      </c>
+      <c r="D16" s="8" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Organic / word-of-mouth</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="14" t="inlineStr">
+        <is>
+          <t>Crew network referrals — free</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Referral bonus ($5 credit)</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C18" s="28" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="14" t="inlineStr">
+        <is>
+          <t>Existing user refers</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>Paid social (IG/TikTok)</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C19" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" s="14" t="inlineStr">
+        <is>
+          <t>Cold acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>Influencer / crew creator</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Paid sponsorship to @crew_illust et al</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>BLENDED CAC</t>
+        </is>
+      </c>
+      <c r="C22" s="11">
+        <f>SUMPRODUCT(B17:B20,C17:C20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>LTV / CAC PER TIER (Gross Profit × Lifetime ÷ CAC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>Gross Profit/mo</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>Lifetime (mo)</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>LTV</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>CAC</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>LTV:CAC</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Payback (mo)</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="B27" s="21">
+        <f>'Per-Tier Unit Economics'!I5</f>
+        <v/>
+      </c>
+      <c r="C27" s="20">
+        <f>C6</f>
+        <v/>
+      </c>
+      <c r="D27" s="22">
+        <f>B27*C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="21">
+        <f>$C$22</f>
+        <v/>
+      </c>
+      <c r="F27" s="30">
+        <f>IFERROR(D27/E27,0)</f>
+        <v/>
+      </c>
+      <c r="G27" s="20">
+        <f>IFERROR(E27/B27,0)</f>
+        <v/>
+      </c>
+      <c r="H27" s="9">
+        <f>IF(F27&gt;=5,"Excellent",IF(F27&gt;=3,"Investable",IF(F27&gt;=1,"Marginal","Loss")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B28" s="21">
+        <f>'Per-Tier Unit Economics'!I6</f>
+        <v/>
+      </c>
+      <c r="C28" s="20">
+        <f>C7</f>
+        <v/>
+      </c>
+      <c r="D28" s="22">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="21">
+        <f>$C$22</f>
+        <v/>
+      </c>
+      <c r="F28" s="30">
+        <f>IFERROR(D28/E28,0)</f>
+        <v/>
+      </c>
+      <c r="G28" s="20">
+        <f>IFERROR(E28/B28,0)</f>
+        <v/>
+      </c>
+      <c r="H28" s="9">
+        <f>IF(F28&gt;=5,"Excellent",IF(F28&gt;=3,"Investable",IF(F28&gt;=1,"Marginal","Loss")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B29" s="21">
+        <f>'Per-Tier Unit Economics'!I7</f>
+        <v/>
+      </c>
+      <c r="C29" s="20">
+        <f>C8</f>
+        <v/>
+      </c>
+      <c r="D29" s="22">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="21">
+        <f>$C$22</f>
+        <v/>
+      </c>
+      <c r="F29" s="30">
+        <f>IFERROR(D29/E29,0)</f>
+        <v/>
+      </c>
+      <c r="G29" s="20">
+        <f>IFERROR(E29/B29,0)</f>
+        <v/>
+      </c>
+      <c r="H29" s="9">
+        <f>IF(F29&gt;=5,"Excellent",IF(F29&gt;=3,"Investable",IF(F29&gt;=1,"Marginal","Loss")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B30" s="21">
+        <f>'Per-Tier Unit Economics'!I8</f>
+        <v/>
+      </c>
+      <c r="C30" s="20">
+        <f>C9</f>
+        <v/>
+      </c>
+      <c r="D30" s="22">
+        <f>B30*C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="21">
+        <f>$C$22</f>
+        <v/>
+      </c>
+      <c r="F30" s="30">
+        <f>IFERROR(D30/E30,0)</f>
+        <v/>
+      </c>
+      <c r="G30" s="20">
+        <f>IFERROR(E30/B30,0)</f>
+        <v/>
+      </c>
+      <c r="H30" s="9">
+        <f>IF(F30&gt;=5,"Excellent",IF(F30&gt;=3,"Investable",IF(F30&gt;=1,"Marginal","Loss")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B31" s="21">
+        <f>'Per-Tier Unit Economics'!I9</f>
+        <v/>
+      </c>
+      <c r="C31" s="20">
+        <f>C10</f>
+        <v/>
+      </c>
+      <c r="D31" s="22">
+        <f>B31*C31</f>
+        <v/>
+      </c>
+      <c r="E31" s="21">
+        <f>$C$22</f>
+        <v/>
+      </c>
+      <c r="F31" s="30">
+        <f>IFERROR(D31/E31,0)</f>
+        <v/>
+      </c>
+      <c r="G31" s="20">
+        <f>IFERROR(E31/B31,0)</f>
+        <v/>
+      </c>
+      <c r="H31" s="9">
+        <f>IF(F31&gt;=5,"Excellent",IF(F31&gt;=3,"Investable",IF(F31&gt;=1,"Marginal","Loss")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B32" s="21">
+        <f>'Per-Tier Unit Economics'!I10</f>
+        <v/>
+      </c>
+      <c r="C32" s="20">
+        <f>C11</f>
+        <v/>
+      </c>
+      <c r="D32" s="22">
+        <f>B32*C32</f>
+        <v/>
+      </c>
+      <c r="E32" s="21">
+        <f>$C$22</f>
+        <v/>
+      </c>
+      <c r="F32" s="30">
+        <f>IFERROR(D32/E32,0)</f>
+        <v/>
+      </c>
+      <c r="G32" s="20">
+        <f>IFERROR(E32/B32,0)</f>
+        <v/>
+      </c>
+      <c r="H32" s="9">
+        <f>IF(F32&gt;=5,"Excellent",IF(F32&gt;=3,"Investable",IF(F32&gt;=1,"Marginal","Loss")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>Refuel</t>
+        </is>
+      </c>
+      <c r="B33" s="21">
+        <f>'Per-Tier Unit Economics'!I11</f>
+        <v/>
+      </c>
+      <c r="C33" s="20">
+        <f>C12</f>
+        <v/>
+      </c>
+      <c r="D33" s="22">
+        <f>B33*C33</f>
+        <v/>
+      </c>
+      <c r="E33" s="21">
+        <f>$C$22</f>
+        <v/>
+      </c>
+      <c r="F33" s="30">
+        <f>IFERROR(D33/E33,0)</f>
+        <v/>
+      </c>
+      <c r="G33" s="20">
+        <f>IFERROR(E33/B33,0)</f>
+        <v/>
+      </c>
+      <c r="H33" s="9">
+        <f>IF(F33&gt;=5,"Excellent",IF(F33&gt;=3,"Investable",IF(F33&gt;=1,"Marginal","Loss")))</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1708,7 +2372,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2333,7 +2997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2910,7 +3574,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5096,6 +5760,999 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00D71921"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F84"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>Economy Plan — math &amp; logic deep dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>PAYG top-up product. No subscription. Built for crew who refuse monthly bills + as a price anchor for subscription tiers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>1. PRODUCT DEFINITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>Economy — pay-per-trip top-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Price per top-up</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>$4.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Data per top-up</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>1 GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Validity per top-up</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>1-3 days (crew layover window)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Subscription?</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>NO — single purchase, no recurring charge</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Coverage (v1)</t>
+        </is>
+      </c>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>Flat worldwide — all Samurai eSIM countries</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Carryover</t>
+        </is>
+      </c>
+      <c r="B11" s="48" t="inlineStr">
+        <is>
+          <t>None — unused data expires with the top-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Refuel logic</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>User just buys another $4.99 top-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>2. WHOLESALE COST FLOOR (Samurai actual rate sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>1-day cost</t>
+        </is>
+      </c>
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>2-day cost</t>
+        </is>
+      </c>
+      <c r="D15" s="41" t="inlineStr">
+        <is>
+          <t>3-day cost</t>
+        </is>
+      </c>
+      <c r="E15" s="41" t="inlineStr">
+        <is>
+          <t>Avg 1-3 day</t>
+        </is>
+      </c>
+      <c r="F15" s="41" t="inlineStr">
+        <is>
+          <t>Margin @ $4.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="B16" s="54" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C16" s="54" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D16" s="54" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E16" s="55" t="n">
+        <v>0.7633333333333333</v>
+      </c>
+      <c r="F16" s="56" t="n">
+        <v>0.8470273881095524</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>Korea</t>
+        </is>
+      </c>
+      <c r="B17" s="54" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C17" s="54" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D17" s="54" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E17" s="55" t="n">
+        <v>0.7633333333333333</v>
+      </c>
+      <c r="F17" s="56" t="n">
+        <v>0.8470273881095524</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B18" s="54" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C18" s="54" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="D18" s="54" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E18" s="55" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="F18" s="56" t="n">
+        <v>0.832999331997328</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>USA</t>
+        </is>
+      </c>
+      <c r="B19" s="54" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="C19" s="54" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="D19" s="54" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E19" s="55" t="n">
+        <v>0.8166666666666668</v>
+      </c>
+      <c r="F19" s="56" t="n">
+        <v>0.8363393453573815</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C20" s="54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="D20" s="54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E20" s="55" t="n">
+        <v>0.9033333333333333</v>
+      </c>
+      <c r="F20" s="56" t="n">
+        <v>0.8189712758851035</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B21" s="54" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="C21" s="54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="D21" s="54" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="E21" s="55" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="F21" s="56" t="n">
+        <v>0.7915831663326653</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>UK</t>
+        </is>
+      </c>
+      <c r="B22" s="54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C22" s="54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="D22" s="54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E22" s="55" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="F22" s="56" t="n">
+        <v>0.7635270541082165</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>UAE</t>
+        </is>
+      </c>
+      <c r="B23" s="54" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="C23" s="54" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="D23" s="54" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="E23" s="55" t="n">
+        <v>2.153333333333333</v>
+      </c>
+      <c r="F23" s="57" t="n">
+        <v>0.5684702738810956</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="B24" s="54" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="C24" s="54" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="D24" s="54" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="E24" s="55" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="F24" s="58" t="n">
+        <v>-0.07615230460921842</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="B25" s="54" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="C25" s="54" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="D25" s="54" t="n">
+        <v>9.19</v>
+      </c>
+      <c r="E25" s="55" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="F25" s="58" t="n">
+        <v>-0.2885771543086171</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="B26" s="54" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="C26" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="D26" s="54" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="E26" s="55" t="n">
+        <v>10.00666666666667</v>
+      </c>
+      <c r="F26" s="58" t="n">
+        <v>-1.005344021376086</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>3. MARGIN MATH AT $4.99 RETAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>Avg cost</t>
+        </is>
+      </c>
+      <c r="C30" s="41" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="E30" s="41" t="inlineStr">
+        <is>
+          <t>Margin %</t>
+        </is>
+      </c>
+      <c r="F30" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t>BEST (HK/Korea 1-day)</t>
+        </is>
+      </c>
+      <c r="B31" s="59" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="C31" s="59" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D31" s="60" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="E31" s="56" t="n">
+        <v>0.8877755511022043</v>
+      </c>
+      <c r="F31" s="39" t="inlineStr">
+        <is>
+          <t>Asia layovers — bulk of crew routes</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>TYPICAL (USA/Japan/SG 2-3 day)</t>
+        </is>
+      </c>
+      <c r="B32" s="59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="59" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D32" s="60" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E32" s="56" t="n">
+        <v>0.7995991983967936</v>
+      </c>
+      <c r="F32" s="39" t="inlineStr">
+        <is>
+          <t>60% of crew trips</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>AVG (Europe/AU/UAE)</t>
+        </is>
+      </c>
+      <c r="B33" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C33" s="54" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D33" s="61" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="E33" s="57" t="n">
+        <v>0.6993987975951904</v>
+      </c>
+      <c r="F33" s="39" t="inlineStr">
+        <is>
+          <t>25% of crew trips</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="48" t="inlineStr">
+        <is>
+          <t>PAIN (India 2-3 day)</t>
+        </is>
+      </c>
+      <c r="B34" s="62" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="C34" s="62" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D34" s="63" t="n">
+        <v>-1.31</v>
+      </c>
+      <c r="E34" s="58" t="n">
+        <v>-0.2625250501002003</v>
+      </c>
+      <c r="F34" s="39" t="inlineStr">
+        <is>
+          <t>~5% of crew trips — losing money</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="48" t="inlineStr">
+        <is>
+          <t>WORST (South Africa 3-day)</t>
+        </is>
+      </c>
+      <c r="B35" s="62" t="n">
+        <v>14.56</v>
+      </c>
+      <c r="C35" s="62" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D35" s="63" t="n">
+        <v>-9.57</v>
+      </c>
+      <c r="E35" s="58" t="n">
+        <v>-1.917835671342685</v>
+      </c>
+      <c r="F35" s="39" t="inlineStr">
+        <is>
+          <t>&lt;2% of crew trips — heavy loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="40" t="inlineStr">
+        <is>
+          <t>4. STRATEGIC LOGIC — WHY $4.99 (FIVE LAYERS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>Layer 1 — Cost floor</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>Avg cost is $0.85-1.50 for 70% of crew routes. $4.99 retail = 75-85% margin. Huge cushion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Layer 2 — Market middle</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>Airalo $4.50, Roamless $4.00, Crew SIM $3-7. We sit fair-middle, not discount.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Layer 3 — Psychological</t>
+        </is>
+      </c>
+      <c r="B41" s="64" t="inlineStr">
+        <is>
+          <t>Under-$5 = impulse purchase zone. $5.99 = considered purchase zone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>Layer 4 — Upsell anchor</t>
+        </is>
+      </c>
+      <c r="B42" s="64" t="inlineStr">
+        <is>
+          <t>$4.99 × 3 top-ups = $14.97 &gt; Premium Economy $12.99 for 10 GB. Drives subscription conversion.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>Layer 5 — Crew fit</t>
+        </is>
+      </c>
+      <c r="B43" s="64" t="inlineStr">
+        <is>
+          <t>1 GB matches 1 layover. Selling 10 GB to a 1-time crew traveler feels wasteful → churn risk.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t>5. FLAT vs ZONAL — DECISION</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="65" t="inlineStr">
+        <is>
+          <t>v1 (LAUNCH): Flat $4.99 worldwide</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="66" t="inlineStr">
+        <is>
+          <t>v1.1 (3-6 months in): Add "Premium destinations $7.99-9.99" overlay for India / Africa / South America</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="39" t="inlineStr">
+        <is>
+          <t>Risk accepted: ~10% of crew trips happen in loss-making destinations (India/Brazil/Africa).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="39" t="inlineStr">
+        <is>
+          <t>At 10,000 Economy users: 500 loss-making transactions × $4 loss = -$2,000/month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="39" t="inlineStr">
+        <is>
+          <t>But 9,500 profitable transactions × $4 profit = +$38,000/month. Net positive: +$36,000/month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="39" t="inlineStr">
+        <is>
+          <t>Trade: ~$24K/year of margin headroom for marketing simplicity + faster launch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="40" t="inlineStr">
+        <is>
+          <t>6. WORKED EXAMPLE — 100 ECONOMY USERS / MONTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="39" t="inlineStr">
+        <is>
+          <t>Assumption: avg PAYG user buys 2.5 top-ups/month (typical crew layover frequency).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="48" t="inlineStr">
+        <is>
+          <t>Total top-ups bought</t>
+        </is>
+      </c>
+      <c r="B56" s="67">
+        <f>100*2.5</f>
+        <v/>
+      </c>
+      <c r="C56" s="39" t="inlineStr">
+        <is>
+          <t>250 top-ups</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="48" t="inlineStr">
+        <is>
+          <t>Revenue per top-up</t>
+        </is>
+      </c>
+      <c r="B57" s="51" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="48" t="inlineStr">
+        <is>
+          <t>Total revenue</t>
+        </is>
+      </c>
+      <c r="B58" s="51">
+        <f>B57*B56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="48" t="inlineStr">
+        <is>
+          <t>Avg wholesale cost / top-up (blended)</t>
+        </is>
+      </c>
+      <c r="B59" s="51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C59" s="39" t="inlineStr">
+        <is>
+          <t>70/20/10 mix across A/B/C zones</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="48" t="inlineStr">
+        <is>
+          <t>Total wholesale cost</t>
+        </is>
+      </c>
+      <c r="B60" s="51">
+        <f>B59*B56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="48" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B61" s="51">
+        <f>B58-B60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="48" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B62" s="52">
+        <f>B61/B58</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="48" t="inlineStr"/>
+      <c r="B63" s="48" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="48" t="inlineStr">
+        <is>
+          <t>Per-user economics:</t>
+        </is>
+      </c>
+      <c r="B64" s="48" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Revenue per Economy user / mo</t>
+        </is>
+      </c>
+      <c r="B65" s="51">
+        <f>B58/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cost per Economy user / mo</t>
+        </is>
+      </c>
+      <c r="B66" s="68">
+        <f>B60/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Profit per Economy user / mo</t>
+        </is>
+      </c>
+      <c r="B67" s="69">
+        <f>B61/100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="40" t="inlineStr">
+        <is>
+          <t>7. AT SCALE — IF 30% OF USERS ARE ECONOMY</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Total users</t>
+        </is>
+      </c>
+      <c r="B70" s="70" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C70" s="39" t="inlineStr">
+        <is>
+          <t>← editable input</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>% on Economy</t>
+        </is>
+      </c>
+      <c r="B71" s="57" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Economy users</t>
+        </is>
+      </c>
+      <c r="B72" s="71">
+        <f>B70*B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Profit per Economy user/mo</t>
+        </is>
+      </c>
+      <c r="B73" s="46">
+        <f>B67</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Total monthly Economy profit</t>
+        </is>
+      </c>
+      <c r="B74" s="72">
+        <f>B72*B73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Annual Economy profit</t>
+        </is>
+      </c>
+      <c r="B75" s="72">
+        <f>B74*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="40" t="inlineStr">
+        <is>
+          <t>8. SOURCES &amp; ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="39" t="inlineStr">
+        <is>
+          <t>• Wholesale costs: Samurai-Wifi-Wholesale-CNY.xlsx (rate sheet, sampled 2026-05-31). CNY → USD at 7.2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="39" t="inlineStr">
+        <is>
+          <t>• Competitor benchmarks: docs/downloads/competitor-pricing-research-2026-06-01.html (Airalo / Holafly / Crew SIM etc.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="39" t="inlineStr">
+        <is>
+          <t>• 2.5 top-ups/user/month: assumption based on Emirates crew layover frequency (8-12 layovers/month, ~25% PAYG use).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="39" t="inlineStr">
+        <is>
+          <t>• 70/20/10 zone mix: estimated Emirates crew layover distribution (East Asia + Europe + USA heavy).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="39" t="inlineStr">
+        <is>
+          <t>• Locked: flat $4.99 v1, zonal v1.1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="39" t="inlineStr">
+        <is>
+          <t>• See [[Pricing Simulator]] tab for cross-tier comparison.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="39" t="inlineStr">
+        <is>
+          <t>• See [[User Behavior]] tab for archetype mix that drives consumption assumptions.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A55:F55"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A52:F52"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="A78:F78"/>
+    <mergeCell ref="B41:F41"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -5346,7 +7003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5617,7 +7274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6431,7 +8088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6633,610 +8290,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>LTV / CAC + Per-Tier Churn</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>How much can we spend to acquire each tier? LTV:CAC &gt; 3 is investable, &gt; 5 is excellent.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>PER-TIER MONTHLY CHURN</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Churn %</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Avg Lifetime (mo)</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B6" s="29" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C6" s="20">
-        <f>IFERROR(1/B6,0)</f>
-        <v/>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>1-month casuals, trial users</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Roster Bundle</t>
-        </is>
-      </c>
-      <c r="B7" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C7" s="20">
-        <f>IFERROR(1/B7,0)</f>
-        <v/>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Sticky once roster sync set up</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Premium Economy</t>
-        </is>
-      </c>
-      <c r="B8" s="29" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C8" s="20">
-        <f>IFERROR(1/B8,0)</f>
-        <v/>
-      </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>Light commitment</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="B9" s="29" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="C9" s="20">
-        <f>IFERROR(1/B9,0)</f>
-        <v/>
-      </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>Pool habit forms, high retention</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="B10" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C10" s="20">
-        <f>IFERROR(1/B10,0)</f>
-        <v/>
-      </c>
-      <c r="D10" s="14" t="inlineStr">
-        <is>
-          <t>Power users, perks lock in</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Cockpit</t>
-        </is>
-      </c>
-      <c r="B11" s="29" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="C11" s="20">
-        <f>IFERROR(1/B11,0)</f>
-        <v/>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>Annual prepay = automatic 12-mo retention</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Refuel (add-on)</t>
-        </is>
-      </c>
-      <c r="B12" s="29" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C12" s="20">
-        <f>IFERROR(1/B12,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Per-purchase, no subscription</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOMER ACQUISITION COST (per-channel blended avg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>% of Acquisition</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>$ CAC</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Organic / word-of-mouth</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C17" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>Crew network referrals — free</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Referral bonus ($5 credit)</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C18" s="28" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>Existing user refers</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Paid social (IG/TikTok)</t>
-        </is>
-      </c>
-      <c r="B19" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C19" s="28" t="n">
-        <v>12</v>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>Cold acquisition</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Influencer / crew creator</t>
-        </is>
-      </c>
-      <c r="B20" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C20" s="28" t="n">
-        <v>8</v>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>Paid sponsorship to @crew_illust et al</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>BLENDED CAC</t>
-        </is>
-      </c>
-      <c r="C22" s="11">
-        <f>SUMPRODUCT(B17:B20,C17:C20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>LTV / CAC PER TIER (Gross Profit × Lifetime ÷ CAC)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Gross Profit/mo</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Lifetime (mo)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>LTV</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>CAC</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>LTV:CAC</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Payback (mo)</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B27" s="21">
-        <f>'Per-Tier Unit Economics'!I5</f>
-        <v/>
-      </c>
-      <c r="C27" s="20">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D27" s="22">
-        <f>B27*C27</f>
-        <v/>
-      </c>
-      <c r="E27" s="21">
-        <f>$C$22</f>
-        <v/>
-      </c>
-      <c r="F27" s="30">
-        <f>IFERROR(D27/E27,0)</f>
-        <v/>
-      </c>
-      <c r="G27" s="20">
-        <f>IFERROR(E27/B27,0)</f>
-        <v/>
-      </c>
-      <c r="H27" s="9">
-        <f>IF(F27&gt;=5,"Excellent",IF(F27&gt;=3,"Investable",IF(F27&gt;=1,"Marginal","Loss")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>Roster Bundle</t>
-        </is>
-      </c>
-      <c r="B28" s="21">
-        <f>'Per-Tier Unit Economics'!I6</f>
-        <v/>
-      </c>
-      <c r="C28" s="20">
-        <f>C7</f>
-        <v/>
-      </c>
-      <c r="D28" s="22">
-        <f>B28*C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="21">
-        <f>$C$22</f>
-        <v/>
-      </c>
-      <c r="F28" s="30">
-        <f>IFERROR(D28/E28,0)</f>
-        <v/>
-      </c>
-      <c r="G28" s="20">
-        <f>IFERROR(E28/B28,0)</f>
-        <v/>
-      </c>
-      <c r="H28" s="9">
-        <f>IF(F28&gt;=5,"Excellent",IF(F28&gt;=3,"Investable",IF(F28&gt;=1,"Marginal","Loss")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>Premium Economy</t>
-        </is>
-      </c>
-      <c r="B29" s="21">
-        <f>'Per-Tier Unit Economics'!I7</f>
-        <v/>
-      </c>
-      <c r="C29" s="20">
-        <f>C8</f>
-        <v/>
-      </c>
-      <c r="D29" s="22">
-        <f>B29*C29</f>
-        <v/>
-      </c>
-      <c r="E29" s="21">
-        <f>$C$22</f>
-        <v/>
-      </c>
-      <c r="F29" s="30">
-        <f>IFERROR(D29/E29,0)</f>
-        <v/>
-      </c>
-      <c r="G29" s="20">
-        <f>IFERROR(E29/B29,0)</f>
-        <v/>
-      </c>
-      <c r="H29" s="9">
-        <f>IF(F29&gt;=5,"Excellent",IF(F29&gt;=3,"Investable",IF(F29&gt;=1,"Marginal","Loss")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="B30" s="21">
-        <f>'Per-Tier Unit Economics'!I8</f>
-        <v/>
-      </c>
-      <c r="C30" s="20">
-        <f>C9</f>
-        <v/>
-      </c>
-      <c r="D30" s="22">
-        <f>B30*C30</f>
-        <v/>
-      </c>
-      <c r="E30" s="21">
-        <f>$C$22</f>
-        <v/>
-      </c>
-      <c r="F30" s="30">
-        <f>IFERROR(D30/E30,0)</f>
-        <v/>
-      </c>
-      <c r="G30" s="20">
-        <f>IFERROR(E30/B30,0)</f>
-        <v/>
-      </c>
-      <c r="H30" s="9">
-        <f>IF(F30&gt;=5,"Excellent",IF(F30&gt;=3,"Investable",IF(F30&gt;=1,"Marginal","Loss")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="B31" s="21">
-        <f>'Per-Tier Unit Economics'!I9</f>
-        <v/>
-      </c>
-      <c r="C31" s="20">
-        <f>C10</f>
-        <v/>
-      </c>
-      <c r="D31" s="22">
-        <f>B31*C31</f>
-        <v/>
-      </c>
-      <c r="E31" s="21">
-        <f>$C$22</f>
-        <v/>
-      </c>
-      <c r="F31" s="30">
-        <f>IFERROR(D31/E31,0)</f>
-        <v/>
-      </c>
-      <c r="G31" s="20">
-        <f>IFERROR(E31/B31,0)</f>
-        <v/>
-      </c>
-      <c r="H31" s="9">
-        <f>IF(F31&gt;=5,"Excellent",IF(F31&gt;=3,"Investable",IF(F31&gt;=1,"Marginal","Loss")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Cockpit</t>
-        </is>
-      </c>
-      <c r="B32" s="21">
-        <f>'Per-Tier Unit Economics'!I10</f>
-        <v/>
-      </c>
-      <c r="C32" s="20">
-        <f>C11</f>
-        <v/>
-      </c>
-      <c r="D32" s="22">
-        <f>B32*C32</f>
-        <v/>
-      </c>
-      <c r="E32" s="21">
-        <f>$C$22</f>
-        <v/>
-      </c>
-      <c r="F32" s="30">
-        <f>IFERROR(D32/E32,0)</f>
-        <v/>
-      </c>
-      <c r="G32" s="20">
-        <f>IFERROR(E32/B32,0)</f>
-        <v/>
-      </c>
-      <c r="H32" s="9">
-        <f>IF(F32&gt;=5,"Excellent",IF(F32&gt;=3,"Investable",IF(F32&gt;=1,"Marginal","Loss")))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Refuel</t>
-        </is>
-      </c>
-      <c r="B33" s="21">
-        <f>'Per-Tier Unit Economics'!I11</f>
-        <v/>
-      </c>
-      <c r="C33" s="20">
-        <f>C12</f>
-        <v/>
-      </c>
-      <c r="D33" s="22">
-        <f>B33*C33</f>
-        <v/>
-      </c>
-      <c r="E33" s="21">
-        <f>$C$22</f>
-        <v/>
-      </c>
-      <c r="F33" s="30">
-        <f>IFERROR(D33/E33,0)</f>
-        <v/>
-      </c>
-      <c r="G33" s="20">
-        <f>IFERROR(E33/B33,0)</f>
-        <v/>
-      </c>
-      <c r="H33" s="9">
-        <f>IF(F33&gt;=5,"Excellent",IF(F33&gt;=3,"Investable",IF(F33&gt;=1,"Marginal","Loss")))</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -12,15 +12,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Unit Economics" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Simulator" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economy Logic" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster Bundle Logic" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +45,7 @@
     <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0.00;[Red](&quot;$&quot;#,##0.00)"/>
     <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -165,8 +166,14 @@
       <color rgb="00D71921"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -208,6 +215,11 @@
         <fgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3CD"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -221,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -301,6 +313,15 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="15" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="15" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="22" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1240,6 +1261,210 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Behavior Sensitivity — net profit vs user behavior mix @ 1,000 users</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>How much of the 'pool unused = breakage revenue' effect changes with user behavior.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Mix Profile</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>% Light</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>% Average</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>% Heavy</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>% Churner</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Avg % Consumed</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Net</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Net Margin %</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Healthy SaaS (general travel — old base, upside)</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C5" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D5" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F5" s="17">
+        <f>B5*0.30+C5*0.65+D5*0.95+E5*0.10</f>
+        <v/>
+      </c>
+      <c r="G5" s="25">
+        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F5)-(1000*'README &amp; Assumptions'!B50)</f>
+        <v/>
+      </c>
+      <c r="H5" s="26">
+        <f>IFERROR(G5/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Base (crew-skewed — new default)</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D6" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E6" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F6" s="17">
+        <f>B6*0.30+C6*0.65+D6*0.95+E6*0.10</f>
+        <v/>
+      </c>
+      <c r="G6" s="25">
+        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F6)-(1000*'README &amp; Assumptions'!B50)</f>
+        <v/>
+      </c>
+      <c r="H6" s="26">
+        <f>IFERROR(G6/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Pure crew (power users dominate — downside)</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D7" s="13" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E7" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F7" s="17">
+        <f>B7*0.30+C7*0.65+D7*0.95+E7*0.10</f>
+        <v/>
+      </c>
+      <c r="G7" s="25">
+        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F7)-(1000*'README &amp; Assumptions'!B50)</f>
+        <v/>
+      </c>
+      <c r="H7" s="26">
+        <f>IFERROR(G7/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>High churn (bad acquisition)</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D8" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="E8" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F8" s="17">
+        <f>B8*0.30+C8*0.65+D8*0.95+E8*0.10</f>
+        <v/>
+      </c>
+      <c r="G8" s="25">
+        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F8)-(1000*'README &amp; Assumptions'!B50)</f>
+        <v/>
+      </c>
+      <c r="H8" s="26">
+        <f>IFERROR(G8/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1840,7 +2065,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2372,7 +2597,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2997,7 +3222,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3574,7 +3799,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6753,6 +6978,976 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9A03B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F77"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>Roster Bundle — math &amp; logic deep dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Pre-committed flight bundle. Upload your roster, we bundle eSIMs for each layover at a discount, auto-arm on arrival. "Save $1 per flight by bundling."</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>1. PRODUCT DEFINITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t>Roster Bundle (working name: Porter Plan)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Price formula</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t>$3.99 per flight bundled</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Monthly cap</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>$39.99 (no matter how many flights)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>What is bundled</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>A separate country-specific eSIM for each layover identified from roster</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Auto-arming</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>YES — each eSIM activates when crew lands in that city</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Discount vs PAYG</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>$1/flight saved (20% off the $4.99 Economy rate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Subscription?</t>
+        </is>
+      </c>
+      <c r="B11" s="64" t="inlineStr">
+        <is>
+          <t>Monthly recurring once enrolled — auto-renews on next roster upload</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Coverage (v1)</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>Same Samurai eSIM catalog as Economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>2. WORKED EXAMPLE — 5 FLIGHTS, MIXED ZONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>City</t>
+        </is>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>Samurai cost</t>
+        </is>
+      </c>
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>PAYG price</t>
+        </is>
+      </c>
+      <c r="D15" s="41" t="inlineStr">
+        <is>
+          <t>Bundle price</t>
+        </is>
+      </c>
+      <c r="E15" s="41" t="inlineStr">
+        <is>
+          <t>Bundle profit</t>
+        </is>
+      </c>
+      <c r="F15" s="41" t="inlineStr">
+        <is>
+          <t>Margin %</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>Tokyo</t>
+        </is>
+      </c>
+      <c r="B16" s="54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C16" s="54" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D16" s="54" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E16" s="61">
+        <f>D16-B16</f>
+        <v/>
+      </c>
+      <c r="F16" s="57">
+        <f>E16/D16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="B17" s="54" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="C17" s="54" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D17" s="54" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E17" s="61">
+        <f>D17-B17</f>
+        <v/>
+      </c>
+      <c r="F17" s="57">
+        <f>E17/D17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="B18" s="54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="C18" s="54" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D18" s="54" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E18" s="61">
+        <f>D18-B18</f>
+        <v/>
+      </c>
+      <c r="F18" s="57">
+        <f>E18/D18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>Sydney</t>
+        </is>
+      </c>
+      <c r="B19" s="54" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="C19" s="54" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D19" s="54" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E19" s="61">
+        <f>D19-B19</f>
+        <v/>
+      </c>
+      <c r="F19" s="57">
+        <f>E19/D19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>Mumbai</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="C20" s="54" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D20" s="54" t="n">
+        <v>3.99</v>
+      </c>
+      <c r="E20" s="61">
+        <f>D20-B20</f>
+        <v/>
+      </c>
+      <c r="F20" s="57">
+        <f>E20/D20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="73" t="inlineStr">
+        <is>
+          <t>TOTAL (5 flights)</t>
+        </is>
+      </c>
+      <c r="B21" s="74">
+        <f>SUM(B16:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="74">
+        <f>SUM(C16:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="74">
+        <f>SUM(D16:D20)</f>
+        <v/>
+      </c>
+      <c r="E21" s="74">
+        <f>SUM(E16:E20)</f>
+        <v/>
+      </c>
+      <c r="F21" s="75">
+        <f>E21/D21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="40" t="inlineStr">
+        <is>
+          <t>3. PAYG vs BUNDLE — THE REAL COMPARISON</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>Reality: PAYG users do not buy all 5 SIMs. They buy when they remember. Bundle captures the whole month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="41" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B25" s="41" t="inlineStr">
+        <is>
+          <t>User pays</t>
+        </is>
+      </c>
+      <c r="C25" s="41" t="inlineStr">
+        <is>
+          <t>Our cost</t>
+        </is>
+      </c>
+      <c r="D25" s="41" t="inlineStr">
+        <is>
+          <t>Profit</t>
+        </is>
+      </c>
+      <c r="E25" s="41" t="inlineStr">
+        <is>
+          <t>Margin %</t>
+        </is>
+      </c>
+      <c r="F25" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>PAYG — buys 2 of 5 flights (typical)</t>
+        </is>
+      </c>
+      <c r="B26" s="54" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="C26" s="54" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="D26" s="54" t="n">
+        <v>8.25</v>
+      </c>
+      <c r="E26" s="57" t="n">
+        <v>0.8266533066132264</v>
+      </c>
+      <c r="F26" s="39" t="inlineStr">
+        <is>
+          <t>Realistic PAYG behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="inlineStr">
+        <is>
+          <t>PAYG — buys 3 of 5 flights</t>
+        </is>
+      </c>
+      <c r="B27" s="54" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="C27" s="54" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="D27" s="54" t="n">
+        <v>11.48</v>
+      </c>
+      <c r="E27" s="57" t="n">
+        <v>0.7668670674682698</v>
+      </c>
+      <c r="F27" s="39" t="inlineStr">
+        <is>
+          <t>Slightly above-avg PAYG</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>PAYG — buys all 5 flights (rare)</t>
+        </is>
+      </c>
+      <c r="B28" s="54" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="C28" s="54" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="D28" s="54" t="n">
+        <v>15.72</v>
+      </c>
+      <c r="E28" s="57" t="n">
+        <v>0.630060120240481</v>
+      </c>
+      <c r="F28" s="39" t="inlineStr">
+        <is>
+          <t>Disciplined PAYG user</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="73" t="inlineStr">
+        <is>
+          <t>Roster Bundle — all 5 captured</t>
+        </is>
+      </c>
+      <c r="B29" s="59" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="C29" s="59" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="D29" s="76" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="E29" s="56" t="n">
+        <v>0.5373433583959899</v>
+      </c>
+      <c r="F29" s="77" t="inlineStr">
+        <is>
+          <t>Pre-committed bundle</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="40" t="inlineStr">
+        <is>
+          <t>4. PRICING TABLE — DIFFERENT FLIGHT COUNTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="41" t="inlineStr">
+        <is>
+          <t># Flights</t>
+        </is>
+      </c>
+      <c r="B33" s="41" t="inlineStr">
+        <is>
+          <t>PAYG total</t>
+        </is>
+      </c>
+      <c r="C33" s="41" t="inlineStr">
+        <is>
+          <t>Bundle price</t>
+        </is>
+      </c>
+      <c r="D33" s="41" t="inlineStr">
+        <is>
+          <t>User saves</t>
+        </is>
+      </c>
+      <c r="E33" s="41" t="inlineStr">
+        <is>
+          <t>Est. our profit</t>
+        </is>
+      </c>
+      <c r="F33" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B34" s="54" t="n">
+        <v>14.97</v>
+      </c>
+      <c r="C34" s="54" t="n">
+        <v>11.97</v>
+      </c>
+      <c r="D34" s="54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="54" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="39" t="inlineStr">
+        <is>
+          <t>Light flier — junior crew</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="78" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="79" t="n">
+        <v>24.95</v>
+      </c>
+      <c r="C35" s="79" t="n">
+        <v>19.95</v>
+      </c>
+      <c r="D35" s="79" t="n">
+        <v>5</v>
+      </c>
+      <c r="E35" s="79" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="F35" s="80" t="inlineStr">
+        <is>
+          <t>Typical Emirates crew month</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="48" t="n">
+        <v>7</v>
+      </c>
+      <c r="B36" s="54" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="C36" s="54" t="n">
+        <v>27.93</v>
+      </c>
+      <c r="D36" s="54" t="n">
+        <v>7</v>
+      </c>
+      <c r="E36" s="54" t="n">
+        <v>16</v>
+      </c>
+      <c r="F36" s="39" t="inlineStr">
+        <is>
+          <t>Above-avg flier</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="n">
+        <v>10</v>
+      </c>
+      <c r="B37" s="54" t="n">
+        <v>49.9</v>
+      </c>
+      <c r="C37" s="54" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="D37" s="54" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" s="54" t="n">
+        <v>25</v>
+      </c>
+      <c r="F37" s="39" t="inlineStr">
+        <is>
+          <t>Heavy flier — hits cap at 10</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="48" t="n">
+        <v>12</v>
+      </c>
+      <c r="B38" s="54" t="n">
+        <v>59.88</v>
+      </c>
+      <c r="C38" s="54" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="D38" s="54" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="E38" s="54" t="n">
+        <v>26</v>
+      </c>
+      <c r="F38" s="39" t="inlineStr">
+        <is>
+          <t>Max flier — bundle capped at $39.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="40" t="inlineStr">
+        <is>
+          <t>5. WHY ROSTER BUNDLE WINS (FOR US AND THE CREW)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>Reality vs theory</t>
+        </is>
+      </c>
+      <c r="B42" s="64" t="inlineStr">
+        <is>
+          <t>PAYG users buy 2-3 SIMs/month from forgetfulness. Bundle captures all 5. Revenue per user: ~$10 PAYG → $20 Bundle. ~2x revenue capture.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="43" t="inlineStr">
+        <is>
+          <t>Commitment + LTV</t>
+        </is>
+      </c>
+      <c r="B43" s="64" t="inlineStr">
+        <is>
+          <t>Bundle = monthly recurring. PAYG = ad-hoc. Bundle users stay 4-6× longer. Lower churn, higher LTV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="43" t="inlineStr">
+        <is>
+          <t>Predictable cash flow</t>
+        </is>
+      </c>
+      <c r="B44" s="64" t="inlineStr">
+        <is>
+          <t>We know in advance which SIMs to buy from Samurai → bulk-prepay negotiating leverage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>Lower support burden</t>
+        </is>
+      </c>
+      <c r="B45" s="64" t="inlineStr">
+        <is>
+          <t>Auto-arming means no "how do I install" tickets. Saves support cost.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>Unique product moat</t>
+        </is>
+      </c>
+      <c r="B46" s="64" t="inlineStr">
+        <is>
+          <t>No competitor does roster-upload-driven bundling. This is the wedge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>Crew psychology</t>
+        </is>
+      </c>
+      <c r="B47" s="64" t="inlineStr">
+        <is>
+          <t>Crew see "$1 saved per flight + zero hassle on arrival" — clear value prop. Repeatable in WhatsApp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="40" t="inlineStr">
+        <is>
+          <t>6. AT-SCALE PROFIT CALCULATOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Total users</t>
+        </is>
+      </c>
+      <c r="B51" s="70" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C51" s="39" t="inlineStr">
+        <is>
+          <t>← editable</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>% on Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B52" s="81" t="n">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Roster Bundle users</t>
+        </is>
+      </c>
+      <c r="B53" s="71">
+        <f>B51*B52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Avg flights per bundle user (Emirates baseline)</t>
+        </is>
+      </c>
+      <c r="B54" s="70" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Avg user pays (5 flights × $3.99)</t>
+        </is>
+      </c>
+      <c r="B55" s="54">
+        <f>B54*3.99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Avg our cost per bundle (5 flights, mixed zones)</t>
+        </is>
+      </c>
+      <c r="B56" s="46" t="n">
+        <v>9.23</v>
+      </c>
+      <c r="C56" s="39" t="inlineStr">
+        <is>
+          <t>← from worked example</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Profit per bundle user / month</t>
+        </is>
+      </c>
+      <c r="B57" s="68">
+        <f>B55-B56</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Total monthly profit (Roster Bundle line)</t>
+        </is>
+      </c>
+      <c r="B58" s="72">
+        <f>B53*B57</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Annual profit (Roster Bundle line)</t>
+        </is>
+      </c>
+      <c r="B59" s="72">
+        <f>B58*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="40" t="inlineStr">
+        <is>
+          <t>7. EDGE CASES TO HANDLE IN APP</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
+        <is>
+          <t>All-expensive bundle (5× Mumbai etc.)</t>
+        </is>
+      </c>
+      <c r="B62" s="64" t="inlineStr">
+        <is>
+          <t>Wholesale cost &gt; Bundle price. We lose money. Mitigation: cap bundle savings at 20% OR show user "your bundle = $X" and let them opt out. &lt;2% of crew.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="43" t="inlineStr">
+        <is>
+          <t>Schedule change mid-month</t>
+        </is>
+      </c>
+      <c r="B63" s="64" t="inlineStr">
+        <is>
+          <t>Crew gets reassigned. We pre-bought a SIM for the old city. Mitigation: pro-rate refund credit toward next month bundle.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="43" t="inlineStr">
+        <is>
+          <t>Single-flight month (vacation week)</t>
+        </is>
+      </c>
+      <c r="B64" s="64" t="inlineStr">
+        <is>
+          <t>1 flight × $3.99 = $3.99 bundle. Smaller than PAYG. Mitigation: minimum 3-flight threshold before bundle kicks in (else they fall back to PAYG).</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="43" t="inlineStr">
+        <is>
+          <t>Layover &lt; 24 hours</t>
+        </is>
+      </c>
+      <c r="B65" s="64" t="inlineStr">
+        <is>
+          <t>Some crew layovers are 8-12 hours. Do they even need data? Mitigation: app shows "skip this leg" option.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="43" t="inlineStr">
+        <is>
+          <t>Crew who do not upload roster</t>
+        </is>
+      </c>
+      <c r="B66" s="64" t="inlineStr">
+        <is>
+          <t>Without roster upload, we cannot bundle. They stay on Economy. Mitigation: manual flight builder UI (v1.1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="40" t="inlineStr">
+        <is>
+          <t>8. SOURCES &amp; ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="39" t="inlineStr">
+        <is>
+          <t>• Wholesale costs: Samurai-Wifi-Wholesale-CNY.xlsx (1 GB / 2-day plans, sampled 2026-05-31).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="39" t="inlineStr">
+        <is>
+          <t>• $3.99 / flight pricing: 20% discount from Economy $4.99 — meaningful savings, simple math.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="39" t="inlineStr">
+        <is>
+          <t>• $39.99 cap: protects heavy-flier crew (12+ flights/month) from feeling penalized.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="39" t="inlineStr">
+        <is>
+          <t>• 5-flight baseline: typical Emirates crew monthly schedule (8-12 layovers, ~5 distinct destinations).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="39" t="inlineStr">
+        <is>
+          <t>• Real PAYG behavior 2-3 of 5: estimated. Validate with crew interviews + early usage data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="39" t="inlineStr">
+        <is>
+          <t>• Bundle captures roughly 2× the per-user revenue of PAYG due to forgetfulness offset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="39" t="inlineStr">
+        <is>
+          <t>• See [[Economy Logic]] tab for the $4.99 baseline this product discounts from.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="39" t="inlineStr">
+        <is>
+          <t>• See [[Pricing Simulator]] tab for cross-tier price ladder.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="30">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="B66:F66"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="A76:F76"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="B44:F44"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B63:F63"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -7003,7 +8198,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7274,7 +8469,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8086,208 +9281,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Behavior Sensitivity — net profit vs user behavior mix @ 1,000 users</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>How much of the 'pool unused = breakage revenue' effect changes with user behavior.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Mix Profile</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>% Light</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>% Average</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>% Heavy</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>% Churner</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Avg % Consumed</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Net</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>Net Margin %</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Healthy SaaS (general travel — old base, upside)</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F5" s="17">
-        <f>B5*0.30+C5*0.65+D5*0.95+E5*0.10</f>
-        <v/>
-      </c>
-      <c r="G5" s="25">
-        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F5)-(1000*'README &amp; Assumptions'!B50)</f>
-        <v/>
-      </c>
-      <c r="H5" s="26">
-        <f>IFERROR(G5/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Base (crew-skewed — new default)</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E6" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F6" s="17">
-        <f>B6*0.30+C6*0.65+D6*0.95+E6*0.10</f>
-        <v/>
-      </c>
-      <c r="G6" s="25">
-        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F6)-(1000*'README &amp; Assumptions'!B50)</f>
-        <v/>
-      </c>
-      <c r="H6" s="26">
-        <f>IFERROR(G6/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Pure crew (power users dominate — downside)</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E7" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F7" s="17">
-        <f>B7*0.30+C7*0.65+D7*0.95+E7*0.10</f>
-        <v/>
-      </c>
-      <c r="G7" s="25">
-        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F7)-(1000*'README &amp; Assumptions'!B50)</f>
-        <v/>
-      </c>
-      <c r="H7" s="26">
-        <f>IFERROR(G7/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>High churn (bad acquisition)</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F8" s="17">
-        <f>B8*0.30+C8*0.65+D8*0.95+E8*0.10</f>
-        <v/>
-      </c>
-      <c r="G8" s="25">
-        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F8)-(1000*'README &amp; Assumptions'!B50)</f>
-        <v/>
-      </c>
-      <c r="H8" s="26">
-        <f>IFERROR(G8/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -13,15 +13,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Simulator" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economy Logic" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster Bundle Logic" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premium Economy Logic" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="16" state="visible" r:id="rId16"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -233,7 +234,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -322,6 +323,12 @@
     <xf numFmtId="173" fontId="0" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="14" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="19" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="19" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="22" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -870,7 +877,7 @@
         </is>
       </c>
       <c r="B16" s="10" t="n">
-        <v>12.99</v>
+        <v>17.99</v>
       </c>
       <c r="C16" s="11">
         <f>B16*12</f>
@@ -884,7 +891,7 @@
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>10GB pool · 50% carry × 2mo · lounge guides</t>
+          <t>10GB pool · 50% carry × 1mo · lounge guides</t>
         </is>
       </c>
     </row>
@@ -1256,6 +1263,820 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>24-Month Rollout — Base Scenario S-curve</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Active Users</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Opex</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Net Profit</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Cumulative Profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="C5" s="24">
+        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D5" s="24">
+        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E5" s="24">
+        <f>B5*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F5" s="25">
+        <f>C5-D5-E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="25">
+        <f>F5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" s="24">
+        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D6" s="24">
+        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E6" s="24">
+        <f>B6*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F6" s="25">
+        <f>C6-D6-E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="25">
+        <f>G5+F6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>130</v>
+      </c>
+      <c r="C7" s="24">
+        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D7" s="24">
+        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E7" s="24">
+        <f>B7*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F7" s="25">
+        <f>C7-D7-E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="25">
+        <f>G6+F7</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="C8" s="24">
+        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
+        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E8" s="24">
+        <f>B8*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F8" s="25">
+        <f>C8-D8-E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="25">
+        <f>G7+F8</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="n">
+        <v>300</v>
+      </c>
+      <c r="C9" s="24">
+        <f>B9*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D9" s="24">
+        <f>B9*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E9" s="24">
+        <f>B9*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F9" s="25">
+        <f>C9-D9-E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="25">
+        <f>G8+F9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n">
+        <v>450</v>
+      </c>
+      <c r="C10" s="24">
+        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D10" s="24">
+        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E10" s="24">
+        <f>B10*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F10" s="25">
+        <f>C10-D10-E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="25">
+        <f>G9+F10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="n">
+        <v>650</v>
+      </c>
+      <c r="C11" s="24">
+        <f>B11*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D11" s="24">
+        <f>B11*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E11" s="24">
+        <f>B11*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F11" s="25">
+        <f>C11-D11-E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="25">
+        <f>G10+F11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="n">
+        <v>900</v>
+      </c>
+      <c r="C12" s="24">
+        <f>B12*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>B12*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E12" s="24">
+        <f>B12*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F12" s="25">
+        <f>C12-D12-E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="25">
+        <f>G11+F12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="n">
+        <v>1200</v>
+      </c>
+      <c r="C13" s="24">
+        <f>B13*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>B13*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E13" s="24">
+        <f>B13*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F13" s="25">
+        <f>C13-D13-E13</f>
+        <v/>
+      </c>
+      <c r="G13" s="25">
+        <f>G12+F13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C14" s="24">
+        <f>B14*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>B14*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E14" s="24">
+        <f>B14*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F14" s="25">
+        <f>C14-D14-E14</f>
+        <v/>
+      </c>
+      <c r="G14" s="25">
+        <f>G13+F14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C15" s="24">
+        <f>B15*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D15" s="24">
+        <f>B15*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E15" s="24">
+        <f>B15*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F15" s="25">
+        <f>C15-D15-E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="25">
+        <f>G14+F15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="n">
+        <v>2100</v>
+      </c>
+      <c r="C16" s="24">
+        <f>B16*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D16" s="24">
+        <f>B16*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E16" s="24">
+        <f>B16*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F16" s="25">
+        <f>C16-D16-E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="25">
+        <f>G15+F16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>M13</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="n">
+        <v>2400</v>
+      </c>
+      <c r="C17" s="24">
+        <f>B17*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D17" s="24">
+        <f>B17*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E17" s="24">
+        <f>B17*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F17" s="25">
+        <f>C17-D17-E17</f>
+        <v/>
+      </c>
+      <c r="G17" s="25">
+        <f>G16+F17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>M14</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C18" s="24">
+        <f>B18*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D18" s="24">
+        <f>B18*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E18" s="24">
+        <f>B18*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F18" s="25">
+        <f>C18-D18-E18</f>
+        <v/>
+      </c>
+      <c r="G18" s="25">
+        <f>G17+F18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>M15</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C19" s="24">
+        <f>B19*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D19" s="24">
+        <f>B19*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E19" s="24">
+        <f>B19*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F19" s="25">
+        <f>C19-D19-E19</f>
+        <v/>
+      </c>
+      <c r="G19" s="25">
+        <f>G18+F19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>M16</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="n">
+        <v>3300</v>
+      </c>
+      <c r="C20" s="24">
+        <f>B20*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D20" s="24">
+        <f>B20*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E20" s="24">
+        <f>B20*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F20" s="25">
+        <f>C20-D20-E20</f>
+        <v/>
+      </c>
+      <c r="G20" s="25">
+        <f>G19+F20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>M17</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="n">
+        <v>3600</v>
+      </c>
+      <c r="C21" s="24">
+        <f>B21*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D21" s="24">
+        <f>B21*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E21" s="24">
+        <f>B21*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F21" s="25">
+        <f>C21-D21-E21</f>
+        <v/>
+      </c>
+      <c r="G21" s="25">
+        <f>G20+F21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>M18</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="n">
+        <v>3900</v>
+      </c>
+      <c r="C22" s="24">
+        <f>B22*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D22" s="24">
+        <f>B22*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E22" s="24">
+        <f>B22*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F22" s="25">
+        <f>C22-D22-E22</f>
+        <v/>
+      </c>
+      <c r="G22" s="25">
+        <f>G21+F22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>M19</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>4200</v>
+      </c>
+      <c r="C23" s="24">
+        <f>B23*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D23" s="24">
+        <f>B23*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E23" s="24">
+        <f>B23*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F23" s="25">
+        <f>C23-D23-E23</f>
+        <v/>
+      </c>
+      <c r="G23" s="25">
+        <f>G22+F23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>M20</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="n">
+        <v>4500</v>
+      </c>
+      <c r="C24" s="24">
+        <f>B24*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D24" s="24">
+        <f>B24*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E24" s="24">
+        <f>B24*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F24" s="25">
+        <f>C24-D24-E24</f>
+        <v/>
+      </c>
+      <c r="G24" s="25">
+        <f>G23+F24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>M21</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C25" s="24">
+        <f>B25*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D25" s="24">
+        <f>B25*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E25" s="24">
+        <f>B25*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F25" s="25">
+        <f>C25-D25-E25</f>
+        <v/>
+      </c>
+      <c r="G25" s="25">
+        <f>G24+F25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>M22</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="n">
+        <v>4850</v>
+      </c>
+      <c r="C26" s="24">
+        <f>B26*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D26" s="24">
+        <f>B26*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E26" s="24">
+        <f>B26*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F26" s="25">
+        <f>C26-D26-E26</f>
+        <v/>
+      </c>
+      <c r="G26" s="25">
+        <f>G25+F26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>M23</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="n">
+        <v>4950</v>
+      </c>
+      <c r="C27" s="24">
+        <f>B27*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D27" s="24">
+        <f>B27*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E27" s="24">
+        <f>B27*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F27" s="25">
+        <f>C27-D27-E27</f>
+        <v/>
+      </c>
+      <c r="G27" s="25">
+        <f>G26+F27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>M24</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C28" s="24">
+        <f>B28*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D28" s="24">
+        <f>B28*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E28" s="24">
+        <f>B28*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="F28" s="25">
+        <f>C28-D28-E28</f>
+        <v/>
+      </c>
+      <c r="G28" s="25">
+        <f>G27+F28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>24-MO TOTAL</t>
+        </is>
+      </c>
+      <c r="C29" s="25">
+        <f>SUM(C5:C28)</f>
+        <v/>
+      </c>
+      <c r="D29" s="25">
+        <f>SUM(D5:D28)</f>
+        <v/>
+      </c>
+      <c r="E29" s="25">
+        <f>SUM(E5:E28)</f>
+        <v/>
+      </c>
+      <c r="F29" s="25">
+        <f>SUM(F5:F28)</f>
+        <v/>
+      </c>
+      <c r="G29" s="25">
+        <f>G28</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1459,7 +2280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2065,7 +2886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2597,7 +3418,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3222,7 +4043,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3799,7 +4620,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7948,6 +8769,910 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002D7A4F"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F74"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>Premium Economy — math &amp; logic deep dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Global pool subscription for crew without rosters. 1-GB-at-a-time UX (manual refill) maximizes breakage transparently.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>1. PRODUCT DEFINITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t>$17.99 / month</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t>10 GB (global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Carryover</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>50% × 1 month (unused half rolls forward)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>Any country on supplier network</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>UX — active data</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>1 GB at a time visible in app</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>UX — refill</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>Manual "Refill from pool" button (visible, not hidden)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>UX — reminder</t>
+        </is>
+      </c>
+      <c r="B11" s="64" t="inlineStr">
+        <is>
+          <t>Day-25 push: "You have X GB unused — refill?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Auto-arming</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>NO — manual eSIM install required</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Refuel ($5.99 / 1 GB)</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>Available even with full pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Best for</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>Reserve crew, irregular schedules, tourists who skip Roster Bundle</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>2. PER-USER MONTHLY MATH (with 1-GB refill friction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>Revenue per subscriber / mo</t>
+        </is>
+      </c>
+      <c r="B18" s="54" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>Locked retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>GB Consumed (40% friction-adjusted)</t>
+        </is>
+      </c>
+      <c r="B19" s="82" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>Vs 62.5% if auto-deducted</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>Wholesale cost / GB (blended Samurai)</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>Cheap+medium zone weighted</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>Wholesale COGS / user</t>
+        </is>
+      </c>
+      <c r="B21" s="54">
+        <f>B19*B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="39">
+        <f>GB Consumed × cost/GB</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>GB Carryover (next month bank)</t>
+        </is>
+      </c>
+      <c r="B22" s="82">
+        <f>(10-B19)*0.5</f>
+        <v/>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>50% of unused rolls forward</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>GB Breakage (gone)</t>
+        </is>
+      </c>
+      <c r="B23" s="82">
+        <f>(10-B19)*0.5</f>
+        <v/>
+      </c>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>50% expires — pure profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>Gross profit from subscription</t>
+        </is>
+      </c>
+      <c r="B24" s="54">
+        <f>B18-B21</f>
+        <v/>
+      </c>
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>Revenue − COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B25" s="26">
+        <f>B24/B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="inlineStr">
+        <is>
+          <t>Refuel attach %</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C27" s="39" t="inlineStr">
+        <is>
+          <t>Lower than 34% — pool not empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>Refuel revenue / user</t>
+        </is>
+      </c>
+      <c r="B28" s="54">
+        <f>B27*5.99</f>
+        <v/>
+      </c>
+      <c r="C28" s="39" t="inlineStr">
+        <is>
+          <t>$5.99 per 1 GB top-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="48" t="inlineStr">
+        <is>
+          <t>Refuel COGS / user</t>
+        </is>
+      </c>
+      <c r="B29" s="54">
+        <f>B27*B20</f>
+        <v/>
+      </c>
+      <c r="C29" s="39" t="inlineStr">
+        <is>
+          <t>1 GB × wholesale</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t>Refuel net profit</t>
+        </is>
+      </c>
+      <c r="B30" s="54">
+        <f>B28-B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL profit per Premium user / mo</t>
+        </is>
+      </c>
+      <c r="B32" s="83">
+        <f>B24+B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL all-in margin %</t>
+        </is>
+      </c>
+      <c r="B33" s="84">
+        <f>B32/(B18+B28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="40" t="inlineStr">
+        <is>
+          <t>3. WITH vs WITHOUT THE 1-GB REFILL FRICTION</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>Consumption %</t>
+        </is>
+      </c>
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>COGS/user</t>
+        </is>
+      </c>
+      <c r="D36" s="41" t="inlineStr">
+        <is>
+          <t>Profit/user</t>
+        </is>
+      </c>
+      <c r="E36" s="41" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="F36" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="inlineStr">
+        <is>
+          <t>Without friction (auto-deduct full pool)</t>
+        </is>
+      </c>
+      <c r="B37" s="48" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="C37" s="61" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="D37" s="61" t="n">
+        <v>10.49</v>
+      </c>
+      <c r="E37" s="48" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="F37" s="39" t="inlineStr">
+        <is>
+          <t>Standard SaaS</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="85" t="inlineStr">
+        <is>
+          <t>With 1-GB refill friction (locked design)</t>
+        </is>
+      </c>
+      <c r="B38" s="85" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="C38" s="60" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="D38" s="60" t="n">
+        <v>13.19</v>
+      </c>
+      <c r="E38" s="85" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="F38" s="77" t="inlineStr">
+        <is>
+          <t>Friction = breakage = margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="inlineStr">
+        <is>
+          <t>Delta per user / month</t>
+        </is>
+      </c>
+      <c r="B39" s="48" t="inlineStr"/>
+      <c r="C39" s="61" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="D39" s="61" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E39" s="48" t="inlineStr">
+        <is>
+          <t>+15pts</t>
+        </is>
+      </c>
+      <c r="F39" s="39" t="inlineStr">
+        <is>
+          <t>Pure breakage profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="40" t="inlineStr">
+        <is>
+          <t>4. AT SCALE (Premium Economy = 13% of users per Tab 1 mix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="41" t="inlineStr">
+        <is>
+          <t>Total users</t>
+        </is>
+      </c>
+      <c r="B42" s="41" t="inlineStr">
+        <is>
+          <t>Premium users (13%)</t>
+        </is>
+      </c>
+      <c r="C42" s="41" t="inlineStr">
+        <is>
+          <t>Monthly profit</t>
+        </is>
+      </c>
+      <c r="D42" s="41" t="inlineStr">
+        <is>
+          <t>Annual profit</t>
+        </is>
+      </c>
+      <c r="E42" s="41" t="inlineStr">
+        <is>
+          <t>Extra from friction</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B43" s="71" t="n">
+        <v>130</v>
+      </c>
+      <c r="C43" s="86" t="n">
+        <v>1839.5</v>
+      </c>
+      <c r="D43" s="86" t="n">
+        <v>22074</v>
+      </c>
+      <c r="E43" s="86" t="n">
+        <v>4212</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="71" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B44" s="71" t="n">
+        <v>650</v>
+      </c>
+      <c r="C44" s="86" t="n">
+        <v>9197.5</v>
+      </c>
+      <c r="D44" s="86" t="n">
+        <v>110370</v>
+      </c>
+      <c r="E44" s="86" t="n">
+        <v>21060</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="71" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B45" s="71" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C45" s="86" t="n">
+        <v>18395</v>
+      </c>
+      <c r="D45" s="86" t="n">
+        <v>220740</v>
+      </c>
+      <c r="E45" s="86" t="n">
+        <v>42120.00000000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="71" t="n">
+        <v>50000</v>
+      </c>
+      <c r="B46" s="71" t="n">
+        <v>6500</v>
+      </c>
+      <c r="C46" s="86" t="n">
+        <v>91975</v>
+      </c>
+      <c r="D46" s="86" t="n">
+        <v>1103700</v>
+      </c>
+      <c r="E46" s="86" t="n">
+        <v>210600</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="71" t="n">
+        <v>100000</v>
+      </c>
+      <c r="B47" s="71" t="n">
+        <v>13000</v>
+      </c>
+      <c r="C47" s="87" t="n">
+        <v>183950</v>
+      </c>
+      <c r="D47" s="87" t="n">
+        <v>2207400</v>
+      </c>
+      <c r="E47" s="87" t="n">
+        <v>421200</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="40" t="inlineStr">
+        <is>
+          <t>5. WHY $17.99 STILL FEELS FAIR TO THE CREW</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="41" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B51" s="41" t="inlineStr">
+        <is>
+          <t>10 GB equivalent</t>
+        </is>
+      </c>
+      <c r="C51" s="41" t="inlineStr">
+        <is>
+          <t>Vs Premium $17.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="48" t="inlineStr">
+        <is>
+          <t>Economy PAYG (10 × $4.99)</t>
+        </is>
+      </c>
+      <c r="B52" s="48" t="inlineStr">
+        <is>
+          <t>$49.90</t>
+        </is>
+      </c>
+      <c r="C52" s="39" t="inlineStr">
+        <is>
+          <t>Premium saves $32</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="48" t="inlineStr">
+        <is>
+          <t>Airalo Global 10 GB / 30d</t>
+        </is>
+      </c>
+      <c r="B53" s="48" t="inlineStr">
+        <is>
+          <t>$26-35</t>
+        </is>
+      </c>
+      <c r="C53" s="39" t="inlineStr">
+        <is>
+          <t>Premium 30-50% cheaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="48" t="inlineStr">
+        <is>
+          <t>Holafly Global unlimited (30d)</t>
+        </is>
+      </c>
+      <c r="B54" s="48" t="inlineStr">
+        <is>
+          <t>$49.90</t>
+        </is>
+      </c>
+      <c r="C54" s="39" t="inlineStr">
+        <is>
+          <t>Premium 64% cheaper, but capped</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="48" t="inlineStr">
+        <is>
+          <t>Saily Ultra 30 GB / 30d</t>
+        </is>
+      </c>
+      <c r="B55" s="48" t="inlineStr">
+        <is>
+          <t>$59.99</t>
+        </is>
+      </c>
+      <c r="C55" s="39" t="inlineStr">
+        <is>
+          <t>Different tier — Saily targets heavy travelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="48" t="inlineStr">
+        <is>
+          <t>Roster Bundle (5 flights, auto-arm)</t>
+        </is>
+      </c>
+      <c r="B56" s="48" t="inlineStr">
+        <is>
+          <t>$19.95</t>
+        </is>
+      </c>
+      <c r="C56" s="39" t="inlineStr">
+        <is>
+          <t>Premium $2 cheaper, no auto-arm tradeoff</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="40" t="inlineStr">
+        <is>
+          <t>6. UX MECHANICS &amp; TRANSPARENCY POLICY</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="43" t="inlineStr">
+        <is>
+          <t>Pool visibility</t>
+        </is>
+      </c>
+      <c r="B60" s="64" t="inlineStr">
+        <is>
+          <t>User ALWAYS sees full 10 GB pool — never hidden</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="43" t="inlineStr">
+        <is>
+          <t>Active data display</t>
+        </is>
+      </c>
+      <c r="B61" s="64" t="inlineStr">
+        <is>
+          <t>Default 1 GB. Refill button visible at all times.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
+        <is>
+          <t>Refill action</t>
+        </is>
+      </c>
+      <c r="B62" s="64" t="inlineStr">
+        <is>
+          <t>One tap. No friction beyond the explicit action.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="43" t="inlineStr">
+        <is>
+          <t>Day-25 reminder</t>
+        </is>
+      </c>
+      <c r="B63" s="64" t="inlineStr">
+        <is>
+          <t>Push: "You have X GB unused. Refill for upcoming trips?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="43" t="inlineStr">
+        <is>
+          <t>Carryover transparency</t>
+        </is>
+      </c>
+      <c r="B64" s="64" t="inlineStr">
+        <is>
+          <t>App shows: "Y GB will carry to next month, Z GB expires."</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="43" t="inlineStr">
+        <is>
+          <t>Locked policy</t>
+        </is>
+      </c>
+      <c r="B65" s="64" t="inlineStr">
+        <is>
+          <t>We do NOT hide anything. Breakage we earn = forgetfulness, NOT deception.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="40" t="inlineStr">
+        <is>
+          <t>7. SOURCES &amp; ASSUMPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="39" t="inlineStr">
+        <is>
+          <t>• Price $17.99: chosen to sit $2 below Roster Bundle ($19.95) — preserves Roster as the wedge tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="39" t="inlineStr">
+        <is>
+          <t>• 40% consumption: estimated friction-adjusted rate. Validate post-launch with usage telemetry.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="39" t="inlineStr">
+        <is>
+          <t>• $1.20 blended wholesale: Samurai global-pool estimate; will sharpen after first month of real data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="39" t="inlineStr">
+        <is>
+          <t>• 20% refuel attach: lower than blended 34% — Premium users have pool buffer, less urgency.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="39" t="inlineStr">
+        <is>
+          <t>• Crew interviews + WhatsApp validation queued for Akito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="39" t="inlineStr">
+        <is>
+          <t>• See [[Economy Logic]] and [[Roster Bundle Logic]] for tier comparisons.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="39" t="inlineStr">
+        <is>
+          <t>• See [[Pricing Simulator]] tab for cross-tier price ladder.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A71:F71"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B61:F61"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="A72:F72"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B65:F65"/>
+    <mergeCell ref="A73:F73"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="A69:F69"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -8198,7 +9923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -8467,818 +10192,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>24-Month Rollout — Base Scenario S-curve</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Active Users</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>COGS</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Opex</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Net Profit</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Cumulative Profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="C5" s="24">
-        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24">
-        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E5" s="24">
-        <f>B5*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F5" s="25">
-        <f>C5-D5-E5</f>
-        <v/>
-      </c>
-      <c r="G5" s="25">
-        <f>F5</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="n">
-        <v>80</v>
-      </c>
-      <c r="C6" s="24">
-        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24">
-        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E6" s="24">
-        <f>B6*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F6" s="25">
-        <f>C6-D6-E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="25">
-        <f>G5+F6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="n">
-        <v>130</v>
-      </c>
-      <c r="C7" s="24">
-        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24">
-        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E7" s="24">
-        <f>B7*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F7" s="25">
-        <f>C7-D7-E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="25">
-        <f>G6+F7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="C8" s="24">
-        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D8" s="24">
-        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E8" s="24">
-        <f>B8*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F8" s="25">
-        <f>C8-D8-E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="25">
-        <f>G7+F8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B9" s="23" t="n">
-        <v>300</v>
-      </c>
-      <c r="C9" s="24">
-        <f>B9*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D9" s="24">
-        <f>B9*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E9" s="24">
-        <f>B9*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F9" s="25">
-        <f>C9-D9-E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="25">
-        <f>G8+F9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B10" s="23" t="n">
-        <v>450</v>
-      </c>
-      <c r="C10" s="24">
-        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D10" s="24">
-        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E10" s="24">
-        <f>B10*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F10" s="25">
-        <f>C10-D10-E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="25">
-        <f>G9+F10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>M7</t>
-        </is>
-      </c>
-      <c r="B11" s="23" t="n">
-        <v>650</v>
-      </c>
-      <c r="C11" s="24">
-        <f>B11*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D11" s="24">
-        <f>B11*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E11" s="24">
-        <f>B11*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F11" s="25">
-        <f>C11-D11-E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="25">
-        <f>G10+F11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="B12" s="23" t="n">
-        <v>900</v>
-      </c>
-      <c r="C12" s="24">
-        <f>B12*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>B12*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E12" s="24">
-        <f>B12*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F12" s="25">
-        <f>C12-D12-E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="25">
-        <f>G11+F12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
-      </c>
-      <c r="B13" s="23" t="n">
-        <v>1200</v>
-      </c>
-      <c r="C13" s="24">
-        <f>B13*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>B13*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E13" s="24">
-        <f>B13*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F13" s="25">
-        <f>C13-D13-E13</f>
-        <v/>
-      </c>
-      <c r="G13" s="25">
-        <f>G12+F13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="B14" s="23" t="n">
-        <v>1500</v>
-      </c>
-      <c r="C14" s="24">
-        <f>B14*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D14" s="24">
-        <f>B14*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E14" s="24">
-        <f>B14*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F14" s="25">
-        <f>C14-D14-E14</f>
-        <v/>
-      </c>
-      <c r="G14" s="25">
-        <f>G13+F14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="B15" s="23" t="n">
-        <v>1800</v>
-      </c>
-      <c r="C15" s="24">
-        <f>B15*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D15" s="24">
-        <f>B15*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E15" s="24">
-        <f>B15*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F15" s="25">
-        <f>C15-D15-E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="25">
-        <f>G14+F15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="B16" s="23" t="n">
-        <v>2100</v>
-      </c>
-      <c r="C16" s="24">
-        <f>B16*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D16" s="24">
-        <f>B16*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E16" s="24">
-        <f>B16*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F16" s="25">
-        <f>C16-D16-E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="25">
-        <f>G15+F16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>M13</t>
-        </is>
-      </c>
-      <c r="B17" s="23" t="n">
-        <v>2400</v>
-      </c>
-      <c r="C17" s="24">
-        <f>B17*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D17" s="24">
-        <f>B17*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E17" s="24">
-        <f>B17*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F17" s="25">
-        <f>C17-D17-E17</f>
-        <v/>
-      </c>
-      <c r="G17" s="25">
-        <f>G16+F17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>M14</t>
-        </is>
-      </c>
-      <c r="B18" s="23" t="n">
-        <v>2700</v>
-      </c>
-      <c r="C18" s="24">
-        <f>B18*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D18" s="24">
-        <f>B18*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E18" s="24">
-        <f>B18*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F18" s="25">
-        <f>C18-D18-E18</f>
-        <v/>
-      </c>
-      <c r="G18" s="25">
-        <f>G17+F18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>M15</t>
-        </is>
-      </c>
-      <c r="B19" s="23" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C19" s="24">
-        <f>B19*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D19" s="24">
-        <f>B19*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E19" s="24">
-        <f>B19*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F19" s="25">
-        <f>C19-D19-E19</f>
-        <v/>
-      </c>
-      <c r="G19" s="25">
-        <f>G18+F19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>M16</t>
-        </is>
-      </c>
-      <c r="B20" s="23" t="n">
-        <v>3300</v>
-      </c>
-      <c r="C20" s="24">
-        <f>B20*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D20" s="24">
-        <f>B20*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E20" s="24">
-        <f>B20*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F20" s="25">
-        <f>C20-D20-E20</f>
-        <v/>
-      </c>
-      <c r="G20" s="25">
-        <f>G19+F20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>M17</t>
-        </is>
-      </c>
-      <c r="B21" s="23" t="n">
-        <v>3600</v>
-      </c>
-      <c r="C21" s="24">
-        <f>B21*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D21" s="24">
-        <f>B21*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E21" s="24">
-        <f>B21*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F21" s="25">
-        <f>C21-D21-E21</f>
-        <v/>
-      </c>
-      <c r="G21" s="25">
-        <f>G20+F21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>M18</t>
-        </is>
-      </c>
-      <c r="B22" s="23" t="n">
-        <v>3900</v>
-      </c>
-      <c r="C22" s="24">
-        <f>B22*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D22" s="24">
-        <f>B22*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E22" s="24">
-        <f>B22*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F22" s="25">
-        <f>C22-D22-E22</f>
-        <v/>
-      </c>
-      <c r="G22" s="25">
-        <f>G21+F22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>M19</t>
-        </is>
-      </c>
-      <c r="B23" s="23" t="n">
-        <v>4200</v>
-      </c>
-      <c r="C23" s="24">
-        <f>B23*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D23" s="24">
-        <f>B23*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E23" s="24">
-        <f>B23*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F23" s="25">
-        <f>C23-D23-E23</f>
-        <v/>
-      </c>
-      <c r="G23" s="25">
-        <f>G22+F23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>M20</t>
-        </is>
-      </c>
-      <c r="B24" s="23" t="n">
-        <v>4500</v>
-      </c>
-      <c r="C24" s="24">
-        <f>B24*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D24" s="24">
-        <f>B24*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E24" s="24">
-        <f>B24*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F24" s="25">
-        <f>C24-D24-E24</f>
-        <v/>
-      </c>
-      <c r="G24" s="25">
-        <f>G23+F24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>M21</t>
-        </is>
-      </c>
-      <c r="B25" s="23" t="n">
-        <v>4700</v>
-      </c>
-      <c r="C25" s="24">
-        <f>B25*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D25" s="24">
-        <f>B25*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E25" s="24">
-        <f>B25*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F25" s="25">
-        <f>C25-D25-E25</f>
-        <v/>
-      </c>
-      <c r="G25" s="25">
-        <f>G24+F25</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>M22</t>
-        </is>
-      </c>
-      <c r="B26" s="23" t="n">
-        <v>4850</v>
-      </c>
-      <c r="C26" s="24">
-        <f>B26*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D26" s="24">
-        <f>B26*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E26" s="24">
-        <f>B26*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F26" s="25">
-        <f>C26-D26-E26</f>
-        <v/>
-      </c>
-      <c r="G26" s="25">
-        <f>G25+F26</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>M23</t>
-        </is>
-      </c>
-      <c r="B27" s="23" t="n">
-        <v>4950</v>
-      </c>
-      <c r="C27" s="24">
-        <f>B27*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D27" s="24">
-        <f>B27*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E27" s="24">
-        <f>B27*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F27" s="25">
-        <f>C27-D27-E27</f>
-        <v/>
-      </c>
-      <c r="G27" s="25">
-        <f>G26+F27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>M24</t>
-        </is>
-      </c>
-      <c r="B28" s="23" t="n">
-        <v>5000</v>
-      </c>
-      <c r="C28" s="24">
-        <f>B28*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D28" s="24">
-        <f>B28*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E28" s="24">
-        <f>B28*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="F28" s="25">
-        <f>C28-D28-E28</f>
-        <v/>
-      </c>
-      <c r="G28" s="25">
-        <f>G27+F28</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>24-MO TOTAL</t>
-        </is>
-      </c>
-      <c r="C29" s="25">
-        <f>SUM(C5:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="25">
-        <f>SUM(D5:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="25">
-        <f>SUM(E5:E28)</f>
-        <v/>
-      </c>
-      <c r="F29" s="25">
-        <f>SUM(F5:F28)</f>
-        <v/>
-      </c>
-      <c r="G29" s="25">
-        <f>G28</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -14,15 +14,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economy Logic" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster Bundle Logic" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premium Economy Logic" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business Logic" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="17" state="visible" r:id="rId17"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -902,7 +903,7 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>24.99</v>
+        <v>29.99</v>
       </c>
       <c r="C17" s="11">
         <f>B17*12</f>
@@ -916,7 +917,7 @@
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>15GB pool · 70% carry × 2mo · priority support · RECOMMENDED</t>
+          <t>15GB pool · 70% carry × 1mo · priority support · RECOMMENDED</t>
         </is>
       </c>
     </row>
@@ -1263,6 +1264,277 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Supply Procurement Options — same volume, 3 supply chains</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Compare current Samurai pay-per-order vs. bulk-prepay vs. eSIM Access direct at 1,000 users.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>OPTIONS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Cost Modifier</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>Breakage Cost</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>Platform Fee/mo</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>A. Samurai pay-per-order</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="14" t="inlineStr">
+        <is>
+          <t>Current model: COGS = consumed only, no upfront commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>B. Samurai bulk prepay -10%</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C7" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>10% discount but pre-buy 100% of pool, 15% breakage on unused inventory</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>C. eSIM Access direct -40%</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E8" s="14" t="inlineStr">
+        <is>
+          <t>Bypass Samurai, save 40% but $5K/mo platform commitment</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>COMPARISON @ 1,000 active users</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Option</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Revenue</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>Effective COGS</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>Platform Fee</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Net Profit</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>Net Margin %</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>Annual Net</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>A. Samurai pay-per-order</t>
+        </is>
+      </c>
+      <c r="B12" s="24">
+        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C12" s="24">
+        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)*B6</f>
+        <v/>
+      </c>
+      <c r="D12" s="24">
+        <f>D6</f>
+        <v/>
+      </c>
+      <c r="E12" s="25">
+        <f>B12-C12-D12-(1000*'README &amp; Assumptions'!B50)</f>
+        <v/>
+      </c>
+      <c r="F12" s="17">
+        <f>IFERROR(E12/B12,0)</f>
+        <v/>
+      </c>
+      <c r="G12" s="25">
+        <f>E12*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>B. Samurai bulk prepay -10%</t>
+        </is>
+      </c>
+      <c r="B13" s="24">
+        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C13" s="24">
+        <f>1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*B7</f>
+        <v/>
+      </c>
+      <c r="D13" s="24">
+        <f>D7</f>
+        <v/>
+      </c>
+      <c r="E13" s="25">
+        <f>B13-C13-D13-(1000*'README &amp; Assumptions'!B50)</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>IFERROR(E13/B13,0)</f>
+        <v/>
+      </c>
+      <c r="G13" s="25">
+        <f>E13*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>C. eSIM Access direct -40%</t>
+        </is>
+      </c>
+      <c r="B14" s="24">
+        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
+        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)*B8</f>
+        <v/>
+      </c>
+      <c r="D14" s="24">
+        <f>D8</f>
+        <v/>
+      </c>
+      <c r="E14" s="25">
+        <f>B14-C14-D14-(1000*'README &amp; Assumptions'!B50)</f>
+        <v/>
+      </c>
+      <c r="F14" s="17">
+        <f>IFERROR(E14/B14,0)</f>
+        <v/>
+      </c>
+      <c r="G14" s="25">
+        <f>E14*12</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2076,7 +2348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2280,7 +2552,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2886,7 +3158,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3418,7 +3690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4043,7 +4315,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4620,7 +4892,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9070,7 +9342,6 @@
     </row>
     <row r="26">
       <c r="A26" s="48" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="48" t="inlineStr">
@@ -9132,7 +9403,6 @@
     </row>
     <row r="31">
       <c r="A31" s="48" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="48" t="inlineStr">
@@ -9673,6 +9943,853 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="002A4A8A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F64"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>Business — math &amp; logic deep dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>The RECOMMENDED tier. 15 GB pool subscription for senior/regular crew. Best per-GB value across the ladder.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>1. PRODUCT DEFINITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>$29.99 / month (locked 2026-06-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>15 GB (global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Carryover</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>70% × 1 month (matches Premium for consistency)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>Same 1-GB refill mechanic as Premium. Refill button visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Day-25 reminder</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>Yes — same transparency policy</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>Global pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Auto-arming</t>
+        </is>
+      </c>
+      <c r="B11" s="48" t="inlineStr">
+        <is>
+          <t>NO — manual install (Roster Bundle is the auto-arm tier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Perks</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>Priority support + crew recs unlocked</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Tier flag</t>
+        </is>
+      </c>
+      <c r="B13" s="48" t="inlineStr">
+        <is>
+          <t>RECOMMENDED on price card</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="B14" s="48" t="inlineStr">
+        <is>
+          <t>Senior crew, full-rota crew, frequent travelers</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>2. PER-USER MONTHLY MATH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>Subscription revenue</t>
+        </is>
+      </c>
+      <c r="B18" s="54" t="n">
+        <v>29.99</v>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>Locked retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>GB Consumed (45% friction-adjusted)</t>
+        </is>
+      </c>
+      <c r="B19" s="82" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>Higher than Premium 40% — heavier users</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>Wholesale cost / GB blended</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>Same blended rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>Wholesale COGS / user</t>
+        </is>
+      </c>
+      <c r="B21" s="54">
+        <f>B19*B20</f>
+        <v/>
+      </c>
+      <c r="C21" s="39">
+        <f>GB × $/GB</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>GB Carryover (next month)</t>
+        </is>
+      </c>
+      <c r="B22" s="82">
+        <f>(15-B19)*0.7</f>
+        <v/>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>70% of unused rolls</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>GB Breakage</t>
+        </is>
+      </c>
+      <c r="B23" s="82">
+        <f>(15-B19)*0.3</f>
+        <v/>
+      </c>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>30% expires immediately</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>Gross profit subscription</t>
+        </is>
+      </c>
+      <c r="B24" s="54">
+        <f>B18-B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B25" s="26">
+        <f>B24/B18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="inlineStr">
+        <is>
+          <t>Refuel attach %</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C27" s="39" t="inlineStr">
+        <is>
+          <t>Slightly higher than Premium</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>Refuel revenue</t>
+        </is>
+      </c>
+      <c r="B28" s="54">
+        <f>B27*5.99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="48" t="inlineStr">
+        <is>
+          <t>Refuel COGS</t>
+        </is>
+      </c>
+      <c r="B29" s="54">
+        <f>B27*B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t>Refuel net</t>
+        </is>
+      </c>
+      <c r="B30" s="54">
+        <f>B28-B29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL profit per Business user / mo</t>
+        </is>
+      </c>
+      <c r="B32" s="83">
+        <f>B24+B30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL all-in margin</t>
+        </is>
+      </c>
+      <c r="B33" s="84">
+        <f>B32/(B18+B28)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="40" t="inlineStr">
+        <is>
+          <t>3. UPGRADE STORY (Premium $17.99 → Business $29.99)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="41" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B36" s="41" t="inlineStr">
+        <is>
+          <t>Premium</t>
+        </is>
+      </c>
+      <c r="C36" s="41" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="D36" s="41" t="inlineStr">
+        <is>
+          <t>Delta</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="48" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B37" s="48" t="inlineStr">
+        <is>
+          <t>$17.99</t>
+        </is>
+      </c>
+      <c r="C37" s="48" t="inlineStr">
+        <is>
+          <t>$29.99</t>
+        </is>
+      </c>
+      <c r="D37" s="48" t="inlineStr">
+        <is>
+          <t>+$12</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="48" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B38" s="48" t="inlineStr">
+        <is>
+          <t>10 GB</t>
+        </is>
+      </c>
+      <c r="C38" s="48" t="inlineStr">
+        <is>
+          <t>15 GB</t>
+        </is>
+      </c>
+      <c r="D38" s="48" t="inlineStr">
+        <is>
+          <t>+50% pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="inlineStr">
+        <is>
+          <t>Per-GB</t>
+        </is>
+      </c>
+      <c r="B39" s="48" t="inlineStr">
+        <is>
+          <t>$1.80</t>
+        </is>
+      </c>
+      <c r="C39" s="48" t="inlineStr">
+        <is>
+          <t>$2.00</t>
+        </is>
+      </c>
+      <c r="D39" s="48" t="inlineStr">
+        <is>
+          <t>+11¢/GB (still under Airalo)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="48" t="inlineStr">
+        <is>
+          <t>Carryover</t>
+        </is>
+      </c>
+      <c r="B40" s="48" t="inlineStr">
+        <is>
+          <t>50% × 1mo</t>
+        </is>
+      </c>
+      <c r="C40" s="48" t="inlineStr">
+        <is>
+          <t>70% × 1mo</t>
+        </is>
+      </c>
+      <c r="D40" s="48" t="inlineStr">
+        <is>
+          <t>+20pts retention</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="48" t="inlineStr">
+        <is>
+          <t>Perks</t>
+        </is>
+      </c>
+      <c r="B41" s="48" t="inlineStr">
+        <is>
+          <t>Lounge guides</t>
+        </is>
+      </c>
+      <c r="C41" s="48" t="inlineStr">
+        <is>
+          <t>+Priority support, +Crew recs</t>
+        </is>
+      </c>
+      <c r="D41" s="48" t="inlineStr">
+        <is>
+          <t>Real upgrade</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="40" t="inlineStr">
+        <is>
+          <t>4. AT SCALE (Business = 8% of users per Tab 1 mix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="41" t="inlineStr">
+        <is>
+          <t>Total users</t>
+        </is>
+      </c>
+      <c r="B44" s="41" t="inlineStr">
+        <is>
+          <t>Business users (8%)</t>
+        </is>
+      </c>
+      <c r="C44" s="41" t="inlineStr">
+        <is>
+          <t>Monthly profit</t>
+        </is>
+      </c>
+      <c r="D44" s="41" t="inlineStr">
+        <is>
+          <t>Annual profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B45" s="71" t="n">
+        <v>80</v>
+      </c>
+      <c r="C45" s="86" t="n">
+        <v>1847.2</v>
+      </c>
+      <c r="D45" s="86" t="n">
+        <v>22166.4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="71" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B46" s="71" t="n">
+        <v>400</v>
+      </c>
+      <c r="C46" s="86" t="n">
+        <v>9236</v>
+      </c>
+      <c r="D46" s="86" t="n">
+        <v>110832</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="71" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B47" s="71" t="n">
+        <v>800</v>
+      </c>
+      <c r="C47" s="86" t="n">
+        <v>18472</v>
+      </c>
+      <c r="D47" s="86" t="n">
+        <v>221664</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="71" t="n">
+        <v>50000</v>
+      </c>
+      <c r="B48" s="71" t="n">
+        <v>4000</v>
+      </c>
+      <c r="C48" s="86" t="n">
+        <v>92360</v>
+      </c>
+      <c r="D48" s="86" t="n">
+        <v>1108320</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="71" t="n">
+        <v>100000</v>
+      </c>
+      <c r="B49" s="71" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C49" s="87" t="n">
+        <v>184720</v>
+      </c>
+      <c r="D49" s="87" t="n">
+        <v>2216640</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="40" t="inlineStr">
+        <is>
+          <t>5. WHY $29.99 IS THE RIGHT PRICE</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="41" t="inlineStr">
+        <is>
+          <t>Competitor</t>
+        </is>
+      </c>
+      <c r="B53" s="41" t="inlineStr">
+        <is>
+          <t>Plan</t>
+        </is>
+      </c>
+      <c r="C53" s="41" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="D53" s="41" t="inlineStr">
+        <is>
+          <t>Per-GB</t>
+        </is>
+      </c>
+      <c r="E53" s="41" t="inlineStr">
+        <is>
+          <t>Vs Peanut Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="48" t="inlineStr">
+        <is>
+          <t>Airalo</t>
+        </is>
+      </c>
+      <c r="B54" s="48" t="inlineStr">
+        <is>
+          <t>Global 20 GB / 30d</t>
+        </is>
+      </c>
+      <c r="C54" s="48" t="inlineStr">
+        <is>
+          <t>$50</t>
+        </is>
+      </c>
+      <c r="D54" s="48" t="inlineStr">
+        <is>
+          <t>$2.50</t>
+        </is>
+      </c>
+      <c r="E54" s="48" t="inlineStr">
+        <is>
+          <t>We are 40% cheaper</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="48" t="inlineStr">
+        <is>
+          <t>Saily</t>
+        </is>
+      </c>
+      <c r="B55" s="48" t="inlineStr">
+        <is>
+          <t>Standard 10 GB / 30d</t>
+        </is>
+      </c>
+      <c r="C55" s="48" t="inlineStr">
+        <is>
+          <t>$30-35</t>
+        </is>
+      </c>
+      <c r="D55" s="48" t="inlineStr">
+        <is>
+          <t>$3.00</t>
+        </is>
+      </c>
+      <c r="E55" s="48" t="inlineStr">
+        <is>
+          <t>We give 5 more GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="48" t="inlineStr">
+        <is>
+          <t>Holafly</t>
+        </is>
+      </c>
+      <c r="B56" s="48" t="inlineStr">
+        <is>
+          <t>Global unlimited 15d</t>
+        </is>
+      </c>
+      <c r="C56" s="48" t="inlineStr">
+        <is>
+          <t>$40</t>
+        </is>
+      </c>
+      <c r="D56" s="48" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E56" s="48" t="inlineStr">
+        <is>
+          <t>We have predictable usage</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="48" t="inlineStr">
+        <is>
+          <t>Roster Bundle (Peanut)</t>
+        </is>
+      </c>
+      <c r="B57" s="48" t="inlineStr">
+        <is>
+          <t>7 flights bundled</t>
+        </is>
+      </c>
+      <c r="C57" s="48" t="inlineStr">
+        <is>
+          <t>$27.93</t>
+        </is>
+      </c>
+      <c r="D57" s="48" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="E57" s="48" t="inlineStr">
+        <is>
+          <t>Different model — auto-arm</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="48" t="inlineStr">
+        <is>
+          <t>Crew SIM</t>
+        </is>
+      </c>
+      <c r="B58" s="48" t="inlineStr">
+        <is>
+          <t>PAYG per country</t>
+        </is>
+      </c>
+      <c r="C58" s="48" t="inlineStr">
+        <is>
+          <t>$3-7/GB</t>
+        </is>
+      </c>
+      <c r="D58" s="48" t="inlineStr">
+        <is>
+          <t>varies</t>
+        </is>
+      </c>
+      <c r="E58" s="48" t="inlineStr">
+        <is>
+          <t>We bundle 15 GB for $29.99</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="40" t="inlineStr">
+        <is>
+          <t>6. DECISION LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Price locked at $29.99 (up from $24.99 placeholder)</t>
+        </is>
+      </c>
+      <c r="B62" s="64" t="inlineStr">
+        <is>
+          <t>Balraj decision. Premium-to-Business ladder gap of $12 = meaningful upgrade signal. Market room (Airalo $50) supports it. Revisit at month 6 with usage data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Carry-over locked at 70% × 1 month (down from × 2)</t>
+        </is>
+      </c>
+      <c r="B63" s="64" t="inlineStr">
+        <is>
+          <t>Consistent with Premium Economy. Shorter carry = more breakage = higher margin.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: 1-GB refill UX locked (same as Premium)</t>
+        </is>
+      </c>
+      <c r="B64" s="64" t="inlineStr">
+        <is>
+          <t>Transparent. Pool always visible. Day-25 reminder. Breakage = honest forgetfulness only.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="15">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B62:F62"/>
+    <mergeCell ref="B64:F64"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B63:F63"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B13:F13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -9921,275 +11038,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Supply Procurement Options — same volume, 3 supply chains</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Compare current Samurai pay-per-order vs. bulk-prepay vs. eSIM Access direct at 1,000 users.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>OPTIONS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Option</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Cost Modifier</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>Breakage Cost</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Platform Fee/mo</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>A. Samurai pay-per-order</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Current model: COGS = consumed only, no upfront commitment</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>B. Samurai bulk prepay -10%</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D7" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>10% discount but pre-buy 100% of pool, 15% breakage on unused inventory</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>C. eSIM Access direct -40%</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>5000</v>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Bypass Samurai, save 40% but $5K/mo platform commitment</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>COMPARISON @ 1,000 active users</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>Option</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Revenue</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>Effective COGS</t>
-        </is>
-      </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>Platform Fee</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>Net Profit</t>
-        </is>
-      </c>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>Net Margin %</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>Annual Net</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>A. Samurai pay-per-order</t>
-        </is>
-      </c>
-      <c r="B12" s="24">
-        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C12" s="24">
-        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)*B6</f>
-        <v/>
-      </c>
-      <c r="D12" s="24">
-        <f>D6</f>
-        <v/>
-      </c>
-      <c r="E12" s="25">
-        <f>B12-C12-D12-(1000*'README &amp; Assumptions'!B50)</f>
-        <v/>
-      </c>
-      <c r="F12" s="17">
-        <f>IFERROR(E12/B12,0)</f>
-        <v/>
-      </c>
-      <c r="G12" s="25">
-        <f>E12*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>B. Samurai bulk prepay -10%</t>
-        </is>
-      </c>
-      <c r="B13" s="24">
-        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C13" s="24">
-        <f>1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*B7</f>
-        <v/>
-      </c>
-      <c r="D13" s="24">
-        <f>D7</f>
-        <v/>
-      </c>
-      <c r="E13" s="25">
-        <f>B13-C13-D13-(1000*'README &amp; Assumptions'!B50)</f>
-        <v/>
-      </c>
-      <c r="F13" s="17">
-        <f>IFERROR(E13/B13,0)</f>
-        <v/>
-      </c>
-      <c r="G13" s="25">
-        <f>E13*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>C. eSIM Access direct -40%</t>
-        </is>
-      </c>
-      <c r="B14" s="24">
-        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C14" s="24">
-        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)*B8</f>
-        <v/>
-      </c>
-      <c r="D14" s="24">
-        <f>D8</f>
-        <v/>
-      </c>
-      <c r="E14" s="25">
-        <f>B14-C14-D14-(1000*'README &amp; Assumptions'!B50)</f>
-        <v/>
-      </c>
-      <c r="F14" s="17">
-        <f>IFERROR(E14/B14,0)</f>
-        <v/>
-      </c>
-      <c r="G14" s="25">
-        <f>E14*12</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -15,15 +15,17 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roster Bundle Logic" sheetId="6" state="visible" r:id="rId6"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Premium Economy Logic" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business Logic" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First Logic" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First Suite Logic" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -695,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -928,240 +930,260 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>49.99</v>
+        <v>39.99</v>
       </c>
       <c r="C18" s="11">
         <f>B18*12</f>
         <v/>
       </c>
       <c r="D18" s="12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>25GB pool · 100% carry × 2mo · concierge layer</t>
+          <t>20GB pool · 100% carry × 2mo · concierge layer</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Cockpit Annual</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>24.92</v>
-      </c>
-      <c r="C19" s="10" t="n">
-        <v>299</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="E19" s="13" t="n">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>First Suite</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="C19">
+        <f>B19*12</f>
+        <v/>
+      </c>
+      <c r="D19" t="n">
+        <v>30</v>
+      </c>
+      <c r="E19" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="14" t="inlineStr">
-        <is>
-          <t>$299/yr · 12GB monthly + 12GB lifetime emergency bank · 100% carry × 2mo · pilots only</t>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>30GB pool · 100% carry × 2mo · concierge layer · top of ladder</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
+          <t>Cockpit Annual</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>299</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="E20" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>$299/yr · 12GB monthly + 12GB lifetime emergency bank · 100% carry × 2mo · pilots only</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
           <t>Refuel (add-on)</t>
         </is>
       </c>
-      <c r="B20" s="10" t="n">
+      <c r="B21" s="10" t="n">
         <v>5.99</v>
       </c>
-      <c r="C20" s="11">
+      <c r="C21" s="11">
         <f>B20*12</f>
         <v/>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D21" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E21" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="14" t="inlineStr">
+      <c r="F21" s="14" t="inlineStr">
         <is>
           <t>Avg top-up</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>GEO COST BUCKETS (1GB / 1-day eSIM wholesale)</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C25" s="8" t="inlineStr">
         <is>
           <t>Cost USD</t>
         </is>
       </c>
-      <c r="D24" s="8" t="inlineStr">
+      <c r="D25" s="8" t="inlineStr">
         <is>
           <t>% Mix</t>
         </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>Tier-A (cheap)</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>JP, UK, SG, MY, HK, KR, US</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="D25" s="13" t="n">
-        <v>0.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Tier-B (medium)</t>
+          <t>Tier-A (cheap)</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>CA, AU, NZ, VN, UAE</t>
+          <t>JP, UK, SG, MY, HK, KR, US</t>
         </is>
       </c>
       <c r="C26" s="10" t="n">
-        <v>1.5</v>
+        <v>0.97</v>
       </c>
       <c r="D26" s="13" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
+          <t>Tier-B (medium)</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>CA, AU, NZ, VN, UAE</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="D27" s="13" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
           <t>Tier-C (expensive)</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B28" s="14" t="inlineStr">
         <is>
           <t>IN, BR, SA, ZA</t>
         </is>
       </c>
-      <c r="C27" s="10" t="n">
+      <c r="C28" s="10" t="n">
         <v>5.8</v>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D28" s="13" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>BLENDED COST / GB</t>
         </is>
       </c>
-      <c r="C29" s="11">
+      <c r="C30" s="11">
         <f>SUMPRODUCT(C25:C27,D25:D27)</f>
         <v/>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>CABIN-CLASS MIX (% of paying users in each tier)</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B34" s="15" t="inlineStr">
         <is>
           <t>% Users</t>
         </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B34" s="13" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>Roster Bundle</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Premium Economy</t>
+          <t>Roster Bundle</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Premium Economy</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>First</t>
         </is>
       </c>
       <c r="B39" s="13" t="n">
@@ -1169,91 +1191,113 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>First Suite</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B41" s="13" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
         <is>
           <t>Refuel attach</t>
         </is>
       </c>
-      <c r="B40" s="13" t="n">
+      <c r="B42" s="13" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>OPERATING COST / USER / MONTH</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B44" s="15" t="inlineStr">
+      <c r="B46" s="15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Cloud / API per user</t>
-        </is>
-      </c>
-      <c r="B45" s="10" t="n">
-        <v>0.15</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Payment processing (2.9% + $0.30)</t>
-        </is>
-      </c>
-      <c r="B46" s="10" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Customer support amortized</t>
+          <t>Cloud / API per user</t>
         </is>
       </c>
       <c r="B47" s="10" t="n">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SMS / OTP / verification</t>
+          <t>Payment processing (2.9% + $0.30)</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>0.05</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>Customer support amortized</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SMS / OTP / verification</t>
+        </is>
+      </c>
+      <c r="B50" s="10" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>Hosting + dev tools amortized</t>
         </is>
       </c>
-      <c r="B49" s="10" t="n">
+      <c r="B51" s="10" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="9" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>TOTAL OPEX</t>
         </is>
       </c>
-      <c r="B50" s="11">
+      <c r="B52" s="11">
         <f>SUM(B45:B49)</f>
         <v/>
       </c>
@@ -1264,6 +1308,721 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>First Suite — math &amp; logic deep dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Top of the ladder. 30 GB / $49.99. Best per-GB on the entire price card. Concierge + everything.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>1. PRODUCT DEFINITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>$49.99 / month (locked 2026-06-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>30 GB (global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Carryover</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>100% × 2 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>1-GB refill mechanic — same as Premium/Business/First</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>Global pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Auto-arming</t>
+        </is>
+      </c>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>NO — manual install</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Perks</t>
+        </is>
+      </c>
+      <c r="B11" s="48" t="inlineStr">
+        <is>
+          <t>Concierge support + crew recs + priority + status badge</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>Heaviest travelers, top purser, lead crew, frequent fliers</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Strategic role</t>
+        </is>
+      </c>
+      <c r="B13" s="48" t="inlineStr">
+        <is>
+          <t>Best per-GB on the ladder. The anchor product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="40" t="inlineStr">
+        <is>
+          <t>2. PER-USER MONTHLY MATH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="41" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B17" s="41" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C17" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>Subscription revenue</t>
+        </is>
+      </c>
+      <c r="B18" s="54" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>Locked retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>GB Consumed (80% friction + 20% capped at need)</t>
+        </is>
+      </c>
+      <c r="B19" s="82" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>Similar to First — friction is the limiter</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>Wholesale cost / GB</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>Wholesale COGS</t>
+        </is>
+      </c>
+      <c r="B21" s="54">
+        <f>B14*B15</f>
+        <v/>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>13.2 × $1.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>GB Carryover bank</t>
+        </is>
+      </c>
+      <c r="B22" s="82">
+        <f>(30-B14)*1.0</f>
+        <v/>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>100% rolls, lasts 2 months — biggest bank on ladder</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>Refuel attach</t>
+        </is>
+      </c>
+      <c r="B23" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>Lower — pool rarely runs out</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>Refuel revenue</t>
+        </is>
+      </c>
+      <c r="B24" s="54">
+        <f>B18*5.99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t>Refuel COGS</t>
+        </is>
+      </c>
+      <c r="B25" s="54">
+        <f>B18*B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL profit per user / mo</t>
+        </is>
+      </c>
+      <c r="B26" s="83" t="n">
+        <v>35.11</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL margin</t>
+        </is>
+      </c>
+      <c r="B27" s="84" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="40" t="inlineStr">
+        <is>
+          <t>3. AT SCALE (2% of users)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>Total users</t>
+        </is>
+      </c>
+      <c r="B31" s="41" t="inlineStr">
+        <is>
+          <t>First Suite users</t>
+        </is>
+      </c>
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>Monthly profit</t>
+        </is>
+      </c>
+      <c r="D31" s="41" t="inlineStr">
+        <is>
+          <t>Annual profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B32" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="C32" s="86" t="n">
+        <v>702.2</v>
+      </c>
+      <c r="D32" s="86" t="n">
+        <v>8426.400000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="71" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B33" s="71" t="n">
+        <v>100</v>
+      </c>
+      <c r="C33" s="86" t="n">
+        <v>3511</v>
+      </c>
+      <c r="D33" s="86" t="n">
+        <v>42132</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="71" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B34" s="71" t="n">
+        <v>200</v>
+      </c>
+      <c r="C34" s="86" t="n">
+        <v>7022</v>
+      </c>
+      <c r="D34" s="86" t="n">
+        <v>84264</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="71" t="n">
+        <v>50000</v>
+      </c>
+      <c r="B35" s="71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C35" s="86" t="n">
+        <v>35110</v>
+      </c>
+      <c r="D35" s="86" t="n">
+        <v>421320</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="71" t="n">
+        <v>100000</v>
+      </c>
+      <c r="B36" s="71" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C36" s="87" t="n">
+        <v>70220</v>
+      </c>
+      <c r="D36" s="87" t="n">
+        <v>842640</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="40" t="inlineStr">
+        <is>
+          <t>4. DECISION LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: First Suite split from First</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>Created as the top-of-ladder product. 30 GB / $49.99 = $1.67/GB = best per-GB on entire price card.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: 100% × 2 months carryover</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>Longest carry bank on the ladder. Premium differentiator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Per-GB anchor strategy</t>
+        </is>
+      </c>
+      <c r="B41" s="64" t="inlineStr">
+        <is>
+          <t>At $1.67/GB, undercuts Business ($2.00/GB) on unit price → creates upgrade pull. Volume amortizes higher COGS.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B13:F13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Monthly P&amp;L across 4 scale scenarios</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Active Users</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Revenue</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Monthly COGS</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Gross Profit</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Opex</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Net Profit</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Net Margin %</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Annual Net</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Conservative</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="C5" s="24">
+        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D5" s="24">
+        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E5" s="25">
+        <f>C5-D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="26">
+        <f>IFERROR(E5/C5,0)</f>
+        <v/>
+      </c>
+      <c r="G5" s="27">
+        <f>B5*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="H5" s="25">
+        <f>E5-G5</f>
+        <v/>
+      </c>
+      <c r="I5" s="26">
+        <f>IFERROR(H5/C5,0)</f>
+        <v/>
+      </c>
+      <c r="J5" s="25">
+        <f>H5*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Base</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C6" s="24">
+        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D6" s="24">
+        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E6" s="25">
+        <f>C6-D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="26">
+        <f>IFERROR(E6/C6,0)</f>
+        <v/>
+      </c>
+      <c r="G6" s="27">
+        <f>B6*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="H6" s="25">
+        <f>E6-G6</f>
+        <v/>
+      </c>
+      <c r="I6" s="26">
+        <f>IFERROR(H6/C6,0)</f>
+        <v/>
+      </c>
+      <c r="J6" s="25">
+        <f>H6*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Aggressive</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C7" s="24">
+        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D7" s="24">
+        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E7" s="25">
+        <f>C7-D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="26">
+        <f>IFERROR(E7/C7,0)</f>
+        <v/>
+      </c>
+      <c r="G7" s="27">
+        <f>B7*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="H7" s="25">
+        <f>E7-G7</f>
+        <v/>
+      </c>
+      <c r="I7" s="26">
+        <f>IFERROR(H7/C7,0)</f>
+        <v/>
+      </c>
+      <c r="J7" s="25">
+        <f>H7*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Hockey Stick</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C8" s="24">
+        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="D8" s="24">
+        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="E8" s="25">
+        <f>C8-D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="26">
+        <f>IFERROR(E8/C8,0)</f>
+        <v/>
+      </c>
+      <c r="G8" s="27">
+        <f>B8*'README &amp; Assumptions'!B50</f>
+        <v/>
+      </c>
+      <c r="H8" s="25">
+        <f>E8-G8</f>
+        <v/>
+      </c>
+      <c r="I8" s="26">
+        <f>IFERROR(H8/C8,0)</f>
+        <v/>
+      </c>
+      <c r="J8" s="25">
+        <f>H8*12</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1534,7 +2293,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2348,7 +3107,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2552,7 +3311,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3158,7 +3917,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3690,7 +4449,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4315,7 +5074,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4892,7 +5651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10239,7 +10998,6 @@
     </row>
     <row r="26">
       <c r="A26" s="48" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="48" t="inlineStr">
@@ -10291,7 +11049,6 @@
     </row>
     <row r="31">
       <c r="A31" s="48" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="48" t="inlineStr">
@@ -10777,8 +11534,8 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B63:F63"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="B63:F63"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B13:F13"/>
@@ -10793,249 +11550,455 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Monthly P&amp;L across 4 scale scenarios</t>
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>First — math &amp; logic deep dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Top tier for senior crew. 20 GB / $39.99. 100% × 2mo carryover. Concierge support.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Scenario</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Active Users</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Revenue</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Monthly COGS</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Gross Profit</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>Gross Margin %</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Opex</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Net Profit</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>Net Margin %</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>Annual Net</t>
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>1. PRODUCT DEFINITION</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Conservative</t>
-        </is>
-      </c>
-      <c r="B5" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="C5" s="24">
-        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D5" s="24">
-        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E5" s="25">
-        <f>C5-D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="26">
-        <f>IFERROR(E5/C5,0)</f>
-        <v/>
-      </c>
-      <c r="G5" s="27">
-        <f>B5*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="H5" s="25">
-        <f>E5-G5</f>
-        <v/>
-      </c>
-      <c r="I5" s="26">
-        <f>IFERROR(H5/C5,0)</f>
-        <v/>
-      </c>
-      <c r="J5" s="25">
-        <f>H5*12</f>
-        <v/>
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B5" s="48" t="inlineStr">
+        <is>
+          <t>$39.99 / month (locked 2026-06-01)</t>
+        </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Base</t>
-        </is>
-      </c>
-      <c r="B6" s="23" t="n">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B6" s="48" t="inlineStr">
+        <is>
+          <t>20 GB (global)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Carryover</t>
+        </is>
+      </c>
+      <c r="B7" s="48" t="inlineStr">
+        <is>
+          <t>100% × 2 months (premium differentiator)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B8" s="48" t="inlineStr">
+        <is>
+          <t>1-GB refill mechanic — same as Premium/Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B9" s="48" t="inlineStr">
+        <is>
+          <t>Global pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Auto-arming</t>
+        </is>
+      </c>
+      <c r="B10" s="48" t="inlineStr">
+        <is>
+          <t>NO — manual install (Roster Bundle is auto-arm tier)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Perks</t>
+        </is>
+      </c>
+      <c r="B11" s="48" t="inlineStr">
+        <is>
+          <t>Priority support + crew recs + concierge layer</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="B12" s="48" t="inlineStr">
+        <is>
+          <t>Senior crew, purser-grade, frequent long-haul</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="40" t="inlineStr">
+        <is>
+          <t>2. PER-USER MONTHLY MATH</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="41" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B16" s="41" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C16" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>Subscription revenue</t>
+        </is>
+      </c>
+      <c r="B17" s="54" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>Locked retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>GB Consumed (80% friction + 20% pool-capped)</t>
+        </is>
+      </c>
+      <c r="B18" s="82" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="C18" s="39" t="inlineStr">
+        <is>
+          <t>Heavier users than Business</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>Wholesale cost / GB</t>
+        </is>
+      </c>
+      <c r="B19" s="54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C19" s="39" t="inlineStr">
+        <is>
+          <t>Same blended rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>Wholesale COGS</t>
+        </is>
+      </c>
+      <c r="B20" s="54">
+        <f>B14*B15</f>
+        <v/>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>13.6 × $1.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>GB Carryover bank</t>
+        </is>
+      </c>
+      <c r="B21" s="82">
+        <f>(20-B14)*1.0</f>
+        <v/>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>100% rolls, lasts 2 months</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>Refuel attach</t>
+        </is>
+      </c>
+      <c r="B22" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>Higher than 30% — pool fills faster</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>Refuel revenue</t>
+        </is>
+      </c>
+      <c r="B23" s="54">
+        <f>B18*5.99</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>Refuel COGS</t>
+        </is>
+      </c>
+      <c r="B24" s="54">
+        <f>B18*B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL profit per user / mo</t>
+        </is>
+      </c>
+      <c r="B25" s="83" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="C25" s="39" t="inlineStr">
+        <is>
+          <t>Locked in working math</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL margin</t>
+        </is>
+      </c>
+      <c r="B26" s="84" t="n">
+        <v>0.605</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="40" t="inlineStr">
+        <is>
+          <t>3. AT SCALE (3% of users)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="41" t="inlineStr">
+        <is>
+          <t>Total users</t>
+        </is>
+      </c>
+      <c r="B30" s="41" t="inlineStr">
+        <is>
+          <t>First users</t>
+        </is>
+      </c>
+      <c r="C30" s="41" t="inlineStr">
+        <is>
+          <t>Monthly profit</t>
+        </is>
+      </c>
+      <c r="D30" s="41" t="inlineStr">
+        <is>
+          <t>Annual profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="71" t="n">
         <v>1000</v>
       </c>
-      <c r="C6" s="24">
-        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D6" s="24">
-        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E6" s="25">
-        <f>C6-D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="26">
-        <f>IFERROR(E6/C6,0)</f>
-        <v/>
-      </c>
-      <c r="G6" s="27">
-        <f>B6*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="H6" s="25">
-        <f>E6-G6</f>
-        <v/>
-      </c>
-      <c r="I6" s="26">
-        <f>IFERROR(H6/C6,0)</f>
-        <v/>
-      </c>
-      <c r="J6" s="25">
-        <f>H6*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Aggressive</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="n">
+      <c r="B31" s="71" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" s="86" t="n">
+        <v>767.7</v>
+      </c>
+      <c r="D31" s="86" t="n">
+        <v>9212.400000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="71" t="n">
         <v>5000</v>
       </c>
-      <c r="C7" s="24">
-        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D7" s="24">
-        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E7" s="25">
-        <f>C7-D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="26">
-        <f>IFERROR(E7/C7,0)</f>
-        <v/>
-      </c>
-      <c r="G7" s="27">
-        <f>B7*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="H7" s="25">
-        <f>E7-G7</f>
-        <v/>
-      </c>
-      <c r="I7" s="26">
-        <f>IFERROR(H7/C7,0)</f>
-        <v/>
-      </c>
-      <c r="J7" s="25">
-        <f>H7*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Hockey Stick</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="n">
-        <v>20000</v>
-      </c>
-      <c r="C8" s="24">
-        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="D8" s="24">
-        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="E8" s="25">
-        <f>C8-D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="26">
-        <f>IFERROR(E8/C8,0)</f>
-        <v/>
-      </c>
-      <c r="G8" s="27">
-        <f>B8*'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="H8" s="25">
-        <f>E8-G8</f>
-        <v/>
-      </c>
-      <c r="I8" s="26">
-        <f>IFERROR(H8/C8,0)</f>
-        <v/>
-      </c>
-      <c r="J8" s="25">
-        <f>H8*12</f>
-        <v/>
+      <c r="B32" s="71" t="n">
+        <v>150</v>
+      </c>
+      <c r="C32" s="86" t="n">
+        <v>3838.5</v>
+      </c>
+      <c r="D32" s="86" t="n">
+        <v>46062</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="71" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B33" s="71" t="n">
+        <v>300</v>
+      </c>
+      <c r="C33" s="86" t="n">
+        <v>7677</v>
+      </c>
+      <c r="D33" s="86" t="n">
+        <v>92124</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="71" t="n">
+        <v>50000</v>
+      </c>
+      <c r="B34" s="71" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C34" s="86" t="n">
+        <v>38385</v>
+      </c>
+      <c r="D34" s="86" t="n">
+        <v>460620</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="71" t="n">
+        <v>100000</v>
+      </c>
+      <c r="B35" s="71" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C35" s="87" t="n">
+        <v>76770</v>
+      </c>
+      <c r="D35" s="87" t="n">
+        <v>921240</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t>4. DECISION LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Two-option First (First + First Suite)</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>Locked: $39.99/20GB + $49.99/30GB. Captures buyers who think Business is too small but Suite is too much. Mirrors Emirates First / First Suite cabin naming.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: 100% × 2 months carryover</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>Longer bank than Premium/Business (1 month). The carryover length is the premium differentiator.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: 1-GB refill UX</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>Consistent with Premium/Business. Transparent pool visibility.</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B9:F9"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -49,7 +49,7 @@
     <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0.00;[Red](&quot;$&quot;#,##0.00)"/>
     <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="26">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -176,6 +176,21 @@
       <color rgb="00008000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00B07A1F"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <i val="1"/>
+      <color rgb="00666666"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -237,7 +252,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -332,6 +347,9 @@
     <xf numFmtId="0" fontId="17" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="22" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -698,7 +716,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -937,14 +955,14 @@
         <v/>
       </c>
       <c r="D18" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>1</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>20GB pool · 100% carry × 2mo · concierge layer</t>
+          <t>25GB pool · 100% carry × 2mo · concierge layer</t>
         </is>
       </c>
     </row>
@@ -962,14 +980,14 @@
         <v/>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>30GB pool · 100% carry × 2mo · concierge layer · top of ladder</t>
+          <t>40GB pool · 100% carry × 2mo · concierge + status badge · top of ladder</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1022,7 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
       <c r="C21" s="11">
         <f>B20*12</f>
@@ -1018,12 +1036,22 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Avg top-up</t>
-        </is>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23"/>
+          <t>Avg top-up · matched to Economy price · only refuel option for subscribers</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="88" t="inlineStr">
+        <is>
+          <t>⚠ Economy backdoor closure</t>
+        </is>
+      </c>
+      <c r="B22" s="89" t="inlineStr">
+        <is>
+          <t>Economy product hidden from active subscribers in app. Subscribers only see refuel option ($4.99). Closes the backdoor where subscribers could buy cheaper Economy top-ups.</t>
+        </is>
+      </c>
+    </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -1107,7 +1135,6 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
@@ -1119,8 +1146,6 @@
         <v/>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32"/>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
@@ -1220,8 +1245,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="43"/>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
@@ -1313,8 +1336,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1338,6 +1361,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
@@ -1365,7 +1389,7 @@
       </c>
       <c r="B6" s="48" t="inlineStr">
         <is>
-          <t>30 GB (global)</t>
+          <t>40 GB (global) — locked 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -1453,6 +1477,8 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="40" t="inlineStr">
         <is>
@@ -1540,7 +1566,7 @@
         </is>
       </c>
       <c r="B22" s="82">
-        <f>(30-B14)*1.0</f>
+        <f>(40-B14)*1.0</f>
         <v/>
       </c>
       <c r="C22" s="39" t="inlineStr">
@@ -1606,6 +1632,8 @@
         <v>0.6860000000000001</v>
       </c>
     </row>
+    <row r="28"/>
+    <row r="29"/>
     <row r="30">
       <c r="A30" s="40" t="inlineStr">
         <is>
@@ -1705,6 +1733,7 @@
         <v>842640</v>
       </c>
     </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="40" t="inlineStr">
         <is>
@@ -1745,6 +1774,18 @@
       <c r="B41" s="64" t="inlineStr">
         <is>
           <t>At $1.67/GB, undercuts Business ($2.00/GB) on unit price → creates upgrade pull. Volume amortizes higher COGS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01 (LOCKED): Pool bumped 30 → 40 GB</t>
+        </is>
+      </c>
+      <c r="B42" s="90" t="inlineStr">
+        <is>
+          <t>Same $49.99 price. $1.25/GB = best per-GB on entire ladder. Anchor product.</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1817,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -2029,7 +2070,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -2300,7 +2341,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3114,7 +3155,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -3318,7 +3359,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -3924,7 +3965,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -4456,7 +4497,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -5081,7 +5122,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -5658,7 +5699,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -6125,7 +6166,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -6539,7 +6580,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -7000,7 +7041,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -7842,7 +7883,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F84"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -8835,7 +8876,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F77"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -9805,7 +9846,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F74"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -10707,7 +10748,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F64"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -11550,8 +11591,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:F41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -11575,6 +11616,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
@@ -11602,7 +11644,7 @@
       </c>
       <c r="B6" s="48" t="inlineStr">
         <is>
-          <t>20 GB (global)</t>
+          <t>25 GB (global) — locked 2026-06-01</t>
         </is>
       </c>
     </row>
@@ -11678,6 +11720,8 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="40" t="inlineStr">
         <is>
@@ -11770,7 +11814,7 @@
         </is>
       </c>
       <c r="B21" s="82">
-        <f>(20-B14)*1.0</f>
+        <f>(25-B14)*1.0</f>
         <v/>
       </c>
       <c r="C21" s="39" t="inlineStr">
@@ -11841,6 +11885,8 @@
         <v>0.605</v>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="40" t="inlineStr">
         <is>
@@ -11940,6 +11986,7 @@
         <v>921240</v>
       </c>
     </row>
+    <row r="36"/>
     <row r="37">
       <c r="A37" s="40" t="inlineStr">
         <is>
@@ -11980,6 +12027,18 @@
       <c r="B40" s="64" t="inlineStr">
         <is>
           <t>Consistent with Premium/Business. Transparent pool visibility.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01 (LOCKED): Pool bumped 20 → 25 GB</t>
+        </is>
+      </c>
+      <c r="B41" s="90" t="inlineStr">
+        <is>
+          <t>Same $39.99 price. Pool expansion is free to us (1-GB friction caps consumption at ~13-14 GB regardless of pool). Better value perception, same margin.</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -17,15 +17,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Business Logic" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First Logic" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First Suite Logic" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cockpit Logic" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,7 +35,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="13">
+  <numFmts count="14">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -48,6 +49,7 @@
     <numFmt numFmtId="174" formatCode="#,##0.00&quot; GB&quot;"/>
     <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0.00;[Red](&quot;$&quot;#,##0.00)"/>
     <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0"/>
+    <numFmt numFmtId="177" formatCode="#,##0.0&quot; GB&quot;"/>
   </numFmts>
   <fonts count="26">
     <font>
@@ -252,7 +254,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -350,6 +352,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -716,7 +719,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F52"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -994,7 +997,7 @@
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Cockpit Annual</t>
+          <t>Cockpit (annual)</t>
         </is>
       </c>
       <c r="B20" s="10" t="n">
@@ -1011,7 +1014,7 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>$299/yr · 12GB monthly + 12GB lifetime emergency bank · 100% carry × 2mo · pilots only</t>
+          <t>$299/yr · 12GB monthly · 12GB emergency bank (refreshes annually) · 100% × 2mo carry · 1-yr lock</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1340,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -1361,7 +1364,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
@@ -1477,8 +1479,6 @@
         </is>
       </c>
     </row>
-    <row r="14"/>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="40" t="inlineStr">
         <is>
@@ -1632,8 +1632,6 @@
         <v>0.6860000000000001</v>
       </c>
     </row>
-    <row r="28"/>
-    <row r="29"/>
     <row r="30">
       <c r="A30" s="40" t="inlineStr">
         <is>
@@ -1733,7 +1731,6 @@
         <v>842640</v>
       </c>
     </row>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="40" t="inlineStr">
         <is>
@@ -1813,11 +1810,738 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="006B3FA0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>Cockpit — math &amp; logic deep dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>"You be the pilot" — annual lockin tier. Pay once, fly anywhere for a year. Schedule changes? Doesn't matter. Set it for a year, stop thinking about it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>1. PRODUCT DEFINITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t>$299 / year (annual prepay only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Monthly equivalent</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t>$24.92 (for ladder display only — no monthly billing option)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Monthly pool</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>12 GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Carryover</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>100% × 2 months on monthly pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Emergency bank</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>12 GB lifetime — REFRESHES ANNUALLY (locked: Option A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Emergency usage</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>Tap anytime for diverted flights, weather delays, mech delays</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>UX</t>
+        </is>
+      </c>
+      <c r="B11" s="64" t="inlineStr">
+        <is>
+          <t>1-GB refill mechanic — same as Premium/Business/First</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>Global pool — works in any country</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>Auto-arming</t>
+        </is>
+      </c>
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>NO — Roster Bundle is the auto-arm product. Cockpit is pool-only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>Lockin</t>
+        </is>
+      </c>
+      <c r="B14" s="64" t="inlineStr">
+        <is>
+          <t>12 months. No mid-year cancellation or refunds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t>Persona</t>
+        </is>
+      </c>
+      <c r="B15" s="64" t="inlineStr">
+        <is>
+          <t>"I want one decision per year and zero plan management." Power users, frequent travelers, schedule-volatile crew.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>Value prop</t>
+        </is>
+      </c>
+      <c r="B16" s="64" t="inlineStr">
+        <is>
+          <t>"Set it for a year. Forget about it. Whatever happens to your schedule, you're covered."</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="40" t="inlineStr">
+        <is>
+          <t>2. PER-USER ANNUAL ECONOMICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B19" s="41" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C19" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr">
+        <is>
+          <t>Annual revenue (prepaid upfront)</t>
+        </is>
+      </c>
+      <c r="B20" s="54" t="n">
+        <v>299</v>
+      </c>
+      <c r="C20" s="39" t="inlineStr">
+        <is>
+          <t>Locked retail</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>Annual pool capacity (12 GB × 12 mo)</t>
+        </is>
+      </c>
+      <c r="B21" s="91" t="n">
+        <v>144</v>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>144 GB monthly pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>Annual emergency bank</t>
+        </is>
+      </c>
+      <c r="B22" s="91" t="n">
+        <v>12</v>
+      </c>
+      <c r="C22" s="39" t="inlineStr">
+        <is>
+          <t>Refreshes Jan 1 each subscription year</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>Total annual data ceiling</t>
+        </is>
+      </c>
+      <c r="B23" s="91">
+        <f>B21+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="39" t="inlineStr">
+        <is>
+          <t>156 GB if fully utilized</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="48" t="inlineStr">
+        <is>
+          <t>Effective per-GB rate (at full use)</t>
+        </is>
+      </c>
+      <c r="B24" s="54">
+        <f>B20/B23</f>
+        <v/>
+      </c>
+      <c r="C24" s="39" t="inlineStr">
+        <is>
+          <t>$/GB if user maxed everything</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="48" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="48" t="inlineStr">
+        <is>
+          <t>GB consumed per month (60% friction)</t>
+        </is>
+      </c>
+      <c r="B26" s="91" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="C26" s="39" t="inlineStr">
+        <is>
+          <t>Same friction model as First</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="48" t="inlineStr">
+        <is>
+          <t>Wholesale cost / GB blended</t>
+        </is>
+      </c>
+      <c r="B27" s="54" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="48" t="inlineStr">
+        <is>
+          <t>Monthly wholesale COGS</t>
+        </is>
+      </c>
+      <c r="B28" s="54">
+        <f>B26*B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="48" t="inlineStr">
+        <is>
+          <t>Annual base COGS (12 months)</t>
+        </is>
+      </c>
+      <c r="B29" s="54">
+        <f>B28*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="48" t="inlineStr">
+        <is>
+          <t>Emergency bank usage (20% avg)</t>
+        </is>
+      </c>
+      <c r="B30" s="91" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="C30" s="39" t="inlineStr">
+        <is>
+          <t>20% of users tap emergency</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="48" t="inlineStr">
+        <is>
+          <t>Emergency COGS / user / year</t>
+        </is>
+      </c>
+      <c r="B31" s="54">
+        <f>B30*B27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="48" t="inlineStr">
+        <is>
+          <t>TOTAL annual COGS per Cockpit user</t>
+        </is>
+      </c>
+      <c r="B32" s="54">
+        <f>B29+B31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="48" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="48" t="inlineStr">
+        <is>
+          <t>ANNUAL PROFIT PER USER</t>
+        </is>
+      </c>
+      <c r="B34" s="83">
+        <f>B20-B32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="48" t="inlineStr">
+        <is>
+          <t>ANNUAL MARGIN</t>
+        </is>
+      </c>
+      <c r="B35" s="84">
+        <f>B34/B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t>3. BACKDOOR EXPLOIT CHECK (5 scenarios tested)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="41" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B38" s="41" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t>Result</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="48" t="n">
+        <v>1</v>
+      </c>
+      <c r="B39" s="48" t="inlineStr">
+        <is>
+          <t>Cockpit user buys Economy ($4.99/GB) instead of refuel</t>
+        </is>
+      </c>
+      <c r="C39" s="48" t="inlineStr">
+        <is>
+          <t>SAFE — Economy blocked for subscribers</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="48" t="n">
+        <v>2</v>
+      </c>
+      <c r="B40" s="48" t="inlineStr">
+        <is>
+          <t>Business users downgrade to Cockpit ($1.92 vs $2.00/GB)</t>
+        </is>
+      </c>
+      <c r="C40" s="48" t="inlineStr">
+        <is>
+          <t>SAFE — annual lockin + emergency bank differentiates</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="48" t="n">
+        <v>3</v>
+      </c>
+      <c r="B41" s="48" t="inlineStr">
+        <is>
+          <t>Refuel ($4.99/GB) used vs pool ($1.92/GB) — backdoor?</t>
+        </is>
+      </c>
+      <c r="C41" s="48" t="inlineStr">
+        <is>
+          <t>SAFE — refuel costs more, no advantage</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="48" t="n">
+        <v>4</v>
+      </c>
+      <c r="B42" s="48" t="inlineStr">
+        <is>
+          <t>Roster heavy user shifts to Cockpit (lose auto-arming)</t>
+        </is>
+      </c>
+      <c r="C42" s="48" t="inlineStr">
+        <is>
+          <t>FAIR TRADEOFF — Roster $480/yr vs Cockpit $299/yr — different products</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="48" t="n">
+        <v>5</v>
+      </c>
+      <c r="B43" s="48" t="inlineStr">
+        <is>
+          <t>Premium ($216/yr, 120GB) vs Cockpit ($299/yr, 156GB + emergency)</t>
+        </is>
+      </c>
+      <c r="C43" s="48" t="inlineStr">
+        <is>
+          <t>SAFE — Cockpit costs $83 more for emergency bank + lockin</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="40" t="inlineStr">
+        <is>
+          <t>4. AT SCALE (Cockpit = 3% of user base)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="41" t="inlineStr">
+        <is>
+          <t>Total users</t>
+        </is>
+      </c>
+      <c r="B46" s="41" t="inlineStr">
+        <is>
+          <t>Cockpit (3%)</t>
+        </is>
+      </c>
+      <c r="C46" s="41" t="inlineStr">
+        <is>
+          <t>Annual revenue (prepaid)</t>
+        </is>
+      </c>
+      <c r="D46" s="41" t="inlineStr">
+        <is>
+          <t>Annual profit</t>
+        </is>
+      </c>
+      <c r="E46" s="41" t="inlineStr">
+        <is>
+          <t>Cash flow benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B47" s="71" t="n">
+        <v>30</v>
+      </c>
+      <c r="C47" s="86" t="n">
+        <v>8970</v>
+      </c>
+      <c r="D47" s="86" t="n">
+        <v>5773.2</v>
+      </c>
+      <c r="E47" s="86" t="n">
+        <v>8970</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="71" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B48" s="71" t="n">
+        <v>150</v>
+      </c>
+      <c r="C48" s="86" t="n">
+        <v>44850</v>
+      </c>
+      <c r="D48" s="86" t="n">
+        <v>28866</v>
+      </c>
+      <c r="E48" s="86" t="n">
+        <v>44850</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="71" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B49" s="71" t="n">
+        <v>300</v>
+      </c>
+      <c r="C49" s="86" t="n">
+        <v>89700</v>
+      </c>
+      <c r="D49" s="86" t="n">
+        <v>57732</v>
+      </c>
+      <c r="E49" s="86" t="n">
+        <v>89700</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="71" t="n">
+        <v>50000</v>
+      </c>
+      <c r="B50" s="71" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C50" s="86" t="n">
+        <v>448500</v>
+      </c>
+      <c r="D50" s="86" t="n">
+        <v>288660</v>
+      </c>
+      <c r="E50" s="86" t="n">
+        <v>448500</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="71" t="n">
+        <v>100000</v>
+      </c>
+      <c r="B51" s="71" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C51" s="87" t="n">
+        <v>897000</v>
+      </c>
+      <c r="D51" s="87" t="n">
+        <v>577320</v>
+      </c>
+      <c r="E51" s="87" t="n">
+        <v>897000</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="40" t="inlineStr">
+        <is>
+          <t>5. DECISION LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Price locked at $299/year</t>
+        </is>
+      </c>
+      <c r="B55" s="64" t="inlineStr">
+        <is>
+          <t>Annual prepay only. 17% discount vs Business monthly. Reframe: not pilots-only, but "you be the pilot of your year." Set it once.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Pool locked at 12 GB / month</t>
+        </is>
+      </c>
+      <c r="B56" s="64" t="inlineStr">
+        <is>
+          <t>Smaller than First (25 GB) intentionally. Cockpit value is the annual peace-of-mind + emergency bank, not pool size.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Carryover 100% × 2 months</t>
+        </is>
+      </c>
+      <c r="B57" s="64" t="inlineStr">
+        <is>
+          <t>Same as First/Suite — top-tier carry policy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Emergency bank 12 GB ANNUAL REFRESH (Option A)</t>
+        </is>
+      </c>
+      <c r="B58" s="64" t="inlineStr">
+        <is>
+          <t>Bank refreshes Jan 1 each year. Creates renewal incentive. ~$2.88/user/year cost vs huge perceived value.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Annual lockin, no monthly option</t>
+        </is>
+      </c>
+      <c r="B59" s="64" t="inlineStr">
+        <is>
+          <t>Annual commitment is the deal. No partial refunds, no mid-year tier swaps.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Backdoor audit passed</t>
+        </is>
+      </c>
+      <c r="B60" s="64" t="inlineStr">
+        <is>
+          <t>All 5 exploit paths checked. No advantage to gaming Cockpit vs other tiers.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B40"/>
+    <mergeCell ref="B16:F16"/>
+    <mergeCell ref="B59:F59"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B58:F58"/>
+    <mergeCell ref="B41"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B60:F60"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B43"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="B39"/>
+    <mergeCell ref="B42"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B5:F5"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -2063,14 +2787,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -2334,14 +3058,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -3148,14 +3872,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -3352,14 +4076,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -3958,14 +4682,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -4490,14 +5214,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -5115,14 +5839,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
@@ -5684,473 +6408,6 @@
       </c>
       <c r="G30" s="35">
         <f>F30-E30</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Cash vs Accrual + Refuel Sensitivity + Failed-eSIM Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>REFUEL ATTACH RATE SENSITIVITY (@ 1,000 users)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Refuel Attach %</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Refuel Revenue</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Refuel COGS</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>Net Refuel Profit</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>Net Margin Impact</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B5" s="24">
-        <f>1000*5.99*A5</f>
-        <v/>
-      </c>
-      <c r="C5" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A5</f>
-        <v/>
-      </c>
-      <c r="D5" s="25">
-        <f>B5-C5</f>
-        <v/>
-      </c>
-      <c r="E5" s="36">
-        <f>D5-($D$7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="B6" s="24">
-        <f>1000*5.99*A6</f>
-        <v/>
-      </c>
-      <c r="C6" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A6</f>
-        <v/>
-      </c>
-      <c r="D6" s="25">
-        <f>B6-C6</f>
-        <v/>
-      </c>
-      <c r="E6" s="36">
-        <f>D6-($D$7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="B7" s="24">
-        <f>1000*5.99*A7</f>
-        <v/>
-      </c>
-      <c r="C7" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A7</f>
-        <v/>
-      </c>
-      <c r="D7" s="25">
-        <f>B7-C7</f>
-        <v/>
-      </c>
-      <c r="E7" s="36">
-        <f>D7-($D$7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="B8" s="24">
-        <f>1000*5.99*A8</f>
-        <v/>
-      </c>
-      <c r="C8" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A8</f>
-        <v/>
-      </c>
-      <c r="D8" s="25">
-        <f>B8-C8</f>
-        <v/>
-      </c>
-      <c r="E8" s="36">
-        <f>D8-($D$7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="B9" s="24">
-        <f>1000*5.99*A9</f>
-        <v/>
-      </c>
-      <c r="C9" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A9</f>
-        <v/>
-      </c>
-      <c r="D9" s="25">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-      <c r="E9" s="36">
-        <f>D9-($D$7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="B10" s="24">
-        <f>1000*5.99*A10</f>
-        <v/>
-      </c>
-      <c r="C10" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A10</f>
-        <v/>
-      </c>
-      <c r="D10" s="25">
-        <f>B10-C10</f>
-        <v/>
-      </c>
-      <c r="E10" s="36">
-        <f>D10-($D$7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>FAILED-eSIM COST</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>For every failed activation: refund + 2GB goodwill + reissue cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Failure Rate</t>
-        </is>
-      </c>
-      <c r="B15" s="8" t="inlineStr">
-        <is>
-          <t>Cost per Failed Activation</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>Failed/mo @ 1K users</t>
-        </is>
-      </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Cost</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>Annual Cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="29" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="B16" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C16" s="37">
-        <f>1000*A16*3</f>
-        <v/>
-      </c>
-      <c r="D16" s="25">
-        <f>C16*B16</f>
-        <v/>
-      </c>
-      <c r="E16" s="25">
-        <f>D16*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="29" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="B17" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" s="37">
-        <f>1000*A17*3</f>
-        <v/>
-      </c>
-      <c r="D17" s="25">
-        <f>C17*B17</f>
-        <v/>
-      </c>
-      <c r="E17" s="25">
-        <f>D17*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="B18" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C18" s="37">
-        <f>1000*A18*3</f>
-        <v/>
-      </c>
-      <c r="D18" s="25">
-        <f>C18*B18</f>
-        <v/>
-      </c>
-      <c r="E18" s="25">
-        <f>D18*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="29" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="B19" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C19" s="37">
-        <f>1000*A19*3</f>
-        <v/>
-      </c>
-      <c r="D19" s="25">
-        <f>C19*B19</f>
-        <v/>
-      </c>
-      <c r="E19" s="25">
-        <f>D19*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="29" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="B20" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="C20" s="37">
-        <f>1000*A20*3</f>
-        <v/>
-      </c>
-      <c r="D20" s="25">
-        <f>C20*B20</f>
-        <v/>
-      </c>
-      <c r="E20" s="25">
-        <f>D20*12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>COCKPIT ANNUAL CASH ADVANTAGE</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>$299 collected upfront vs $24.92/mo over 12 months. The cashflow boost matters for runway.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Cockpit Users</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Monthly Sub Recognized</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Upfront Cash</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Cash Boost vs Monthly</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="B26" s="24">
-        <f>A26*24.92</f>
-        <v/>
-      </c>
-      <c r="C26" s="25">
-        <f>A26*299</f>
-        <v/>
-      </c>
-      <c r="D26" s="24">
-        <f>C26-(B26*12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="23" t="n">
-        <v>50</v>
-      </c>
-      <c r="B27" s="24">
-        <f>A27*24.92</f>
-        <v/>
-      </c>
-      <c r="C27" s="25">
-        <f>A27*299</f>
-        <v/>
-      </c>
-      <c r="D27" s="24">
-        <f>C27-(B27*12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="23" t="n">
-        <v>100</v>
-      </c>
-      <c r="B28" s="24">
-        <f>A28*24.92</f>
-        <v/>
-      </c>
-      <c r="C28" s="25">
-        <f>A28*299</f>
-        <v/>
-      </c>
-      <c r="D28" s="24">
-        <f>C28-(B28*12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="23" t="n">
-        <v>200</v>
-      </c>
-      <c r="B29" s="24">
-        <f>A29*24.92</f>
-        <v/>
-      </c>
-      <c r="C29" s="25">
-        <f>A29*299</f>
-        <v/>
-      </c>
-      <c r="D29" s="24">
-        <f>C29-(B29*12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="23" t="n">
-        <v>500</v>
-      </c>
-      <c r="B30" s="24">
-        <f>A30*24.92</f>
-        <v/>
-      </c>
-      <c r="C30" s="25">
-        <f>A30*299</f>
-        <v/>
-      </c>
-      <c r="D30" s="24">
-        <f>C30-(B30*12)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="23" t="n">
-        <v>1000</v>
-      </c>
-      <c r="B31" s="24">
-        <f>A31*24.92</f>
-        <v/>
-      </c>
-      <c r="C31" s="25">
-        <f>A31*299</f>
-        <v/>
-      </c>
-      <c r="D31" s="24">
-        <f>C31-(B31*12)</f>
         <v/>
       </c>
     </row>
@@ -6166,7 +6423,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F23"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -6565,6 +6822,473 @@
       </c>
       <c r="F23" s="20">
         <f>(B23-D23)*(1-'README &amp; Assumptions'!E20)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Cash vs Accrual + Refuel Sensitivity + Failed-eSIM Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>REFUEL ATTACH RATE SENSITIVITY (@ 1,000 users)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Refuel Attach %</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Refuel Revenue</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Refuel COGS</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Net Refuel Profit</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Net Margin Impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B5" s="24">
+        <f>1000*5.99*A5</f>
+        <v/>
+      </c>
+      <c r="C5" s="24">
+        <f>1000*'README &amp; Assumptions'!C29*A5</f>
+        <v/>
+      </c>
+      <c r="D5" s="25">
+        <f>B5-C5</f>
+        <v/>
+      </c>
+      <c r="E5" s="36">
+        <f>D5-($D$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B6" s="24">
+        <f>1000*5.99*A6</f>
+        <v/>
+      </c>
+      <c r="C6" s="24">
+        <f>1000*'README &amp; Assumptions'!C29*A6</f>
+        <v/>
+      </c>
+      <c r="D6" s="25">
+        <f>B6-C6</f>
+        <v/>
+      </c>
+      <c r="E6" s="36">
+        <f>D6-($D$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="B7" s="24">
+        <f>1000*5.99*A7</f>
+        <v/>
+      </c>
+      <c r="C7" s="24">
+        <f>1000*'README &amp; Assumptions'!C29*A7</f>
+        <v/>
+      </c>
+      <c r="D7" s="25">
+        <f>B7-C7</f>
+        <v/>
+      </c>
+      <c r="E7" s="36">
+        <f>D7-($D$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="B8" s="24">
+        <f>1000*5.99*A8</f>
+        <v/>
+      </c>
+      <c r="C8" s="24">
+        <f>1000*'README &amp; Assumptions'!C29*A8</f>
+        <v/>
+      </c>
+      <c r="D8" s="25">
+        <f>B8-C8</f>
+        <v/>
+      </c>
+      <c r="E8" s="36">
+        <f>D8-($D$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="B9" s="24">
+        <f>1000*5.99*A9</f>
+        <v/>
+      </c>
+      <c r="C9" s="24">
+        <f>1000*'README &amp; Assumptions'!C29*A9</f>
+        <v/>
+      </c>
+      <c r="D9" s="25">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+      <c r="E9" s="36">
+        <f>D9-($D$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="B10" s="24">
+        <f>1000*5.99*A10</f>
+        <v/>
+      </c>
+      <c r="C10" s="24">
+        <f>1000*'README &amp; Assumptions'!C29*A10</f>
+        <v/>
+      </c>
+      <c r="D10" s="25">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+      <c r="E10" s="36">
+        <f>D10-($D$7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>FAILED-eSIM COST</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>For every failed activation: refund + 2GB goodwill + reissue cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Failure Rate</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>Cost per Failed Activation</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>Failed/mo @ 1K users</t>
+        </is>
+      </c>
+      <c r="D15" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Cost</t>
+        </is>
+      </c>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>Annual Cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="B16" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="37">
+        <f>1000*A16*3</f>
+        <v/>
+      </c>
+      <c r="D16" s="25">
+        <f>C16*B16</f>
+        <v/>
+      </c>
+      <c r="E16" s="25">
+        <f>D16*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="B17" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="37">
+        <f>1000*A17*3</f>
+        <v/>
+      </c>
+      <c r="D17" s="25">
+        <f>C17*B17</f>
+        <v/>
+      </c>
+      <c r="E17" s="25">
+        <f>D17*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C18" s="37">
+        <f>1000*A18*3</f>
+        <v/>
+      </c>
+      <c r="D18" s="25">
+        <f>C18*B18</f>
+        <v/>
+      </c>
+      <c r="E18" s="25">
+        <f>D18*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C19" s="37">
+        <f>1000*A19*3</f>
+        <v/>
+      </c>
+      <c r="D19" s="25">
+        <f>C19*B19</f>
+        <v/>
+      </c>
+      <c r="E19" s="25">
+        <f>D19*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="B20" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="C20" s="37">
+        <f>1000*A20*3</f>
+        <v/>
+      </c>
+      <c r="D20" s="25">
+        <f>C20*B20</f>
+        <v/>
+      </c>
+      <c r="E20" s="25">
+        <f>D20*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>COCKPIT ANNUAL CASH ADVANTAGE</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
+        <is>
+          <t>$299 collected upfront vs $24.92/mo over 12 months. The cashflow boost matters for runway.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Cockpit Users</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Monthly Sub Recognized</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="inlineStr">
+        <is>
+          <t>Upfront Cash</t>
+        </is>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Cash Boost vs Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B26" s="24">
+        <f>A26*24.92</f>
+        <v/>
+      </c>
+      <c r="C26" s="25">
+        <f>A26*299</f>
+        <v/>
+      </c>
+      <c r="D26" s="24">
+        <f>C26-(B26*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="23" t="n">
+        <v>50</v>
+      </c>
+      <c r="B27" s="24">
+        <f>A27*24.92</f>
+        <v/>
+      </c>
+      <c r="C27" s="25">
+        <f>A27*299</f>
+        <v/>
+      </c>
+      <c r="D27" s="24">
+        <f>C27-(B27*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="23" t="n">
+        <v>100</v>
+      </c>
+      <c r="B28" s="24">
+        <f>A28*24.92</f>
+        <v/>
+      </c>
+      <c r="C28" s="25">
+        <f>A28*299</f>
+        <v/>
+      </c>
+      <c r="D28" s="24">
+        <f>C28-(B28*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="23" t="n">
+        <v>200</v>
+      </c>
+      <c r="B29" s="24">
+        <f>A29*24.92</f>
+        <v/>
+      </c>
+      <c r="C29" s="25">
+        <f>A29*299</f>
+        <v/>
+      </c>
+      <c r="D29" s="24">
+        <f>C29-(B29*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="23" t="n">
+        <v>500</v>
+      </c>
+      <c r="B30" s="24">
+        <f>A30*24.92</f>
+        <v/>
+      </c>
+      <c r="C30" s="25">
+        <f>A30*299</f>
+        <v/>
+      </c>
+      <c r="D30" s="24">
+        <f>C30-(B30*12)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="23" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B31" s="24">
+        <f>A31*24.92</f>
+        <v/>
+      </c>
+      <c r="C31" s="25">
+        <f>A31*299</f>
+        <v/>
+      </c>
+      <c r="D31" s="24">
+        <f>C31-(B31*12)</f>
         <v/>
       </c>
     </row>
@@ -6580,7 +7304,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
@@ -7041,7 +7765,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
@@ -7883,7 +8607,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F84"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -8876,7 +9600,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F77"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
@@ -9846,7 +10570,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F74"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -10748,7 +11472,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F64"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -11592,7 +12316,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:F41"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
@@ -11616,7 +12340,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
@@ -11720,8 +12443,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="40" t="inlineStr">
         <is>
@@ -11885,8 +12606,6 @@
         <v>0.605</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="40" t="inlineStr">
         <is>
@@ -11986,7 +12705,6 @@
         <v>921240</v>
       </c>
     </row>
-    <row r="36"/>
     <row r="37">
       <c r="A37" s="40" t="inlineStr">
         <is>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -51,7 +51,7 @@
     <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="177" formatCode="#,##0.0&quot; GB&quot;"/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -193,6 +193,12 @@
       <name val="Helvetica Neue"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <i val="1"/>
+      <color rgb="00B07A1F"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -254,7 +260,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -353,6 +359,9 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -718,7 +727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -847,25 +856,25 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>Economy (pay-per-trip)</t>
+          <t>Economy (PAYG)</t>
         </is>
       </c>
       <c r="B14" s="10" t="n">
-        <v>13.68</v>
+        <v>4.99</v>
       </c>
       <c r="C14" s="11">
         <f>B14*12</f>
         <v/>
       </c>
       <c r="D14" s="12" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>PAYG · avg 2.5 GB/mo @ $4.99/GB + 20% refuel attach @ $5.99</t>
+          <t>$4.99 per 1 GB top-up · no subscription · blocked for active subscribers</t>
         </is>
       </c>
     </row>
@@ -876,21 +885,21 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>39.99</v>
+        <v>19.95</v>
       </c>
       <c r="C15" s="11">
         <f>B15*12</f>
         <v/>
       </c>
       <c r="D15" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E15" s="13" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>10GB pool · 50% carry</t>
+          <t>$3.99 per flight · cap $39.99/mo · auto-arms eSIM at each layover · roster upload required</t>
         </is>
       </c>
     </row>
@@ -1063,272 +1072,280 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="92" t="inlineStr">
+        <is>
+          <t>⚠ COSTS are real Samurai data. MIX % (60/25/15) is placeholder — awaiting Akito crew roster validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
         <is>
           <t>Bucket</t>
         </is>
       </c>
-      <c r="B25" s="8" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Cost USD</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
+      <c r="C26" s="8" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
         <is>
           <t>% Mix</t>
         </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Tier-A (cheap)</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>JP, UK, SG, MY, HK, KR, US</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="D26" s="13" t="n">
-        <v>0.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Tier-B (medium)</t>
+          <t>Tier-A (cheap)</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>CA, AU, NZ, VN, UAE</t>
+          <t>JP, UK, SG, MY, HK, KR, US</t>
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>0.25</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
+          <t>Tier-B (medium)</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>CA, AU, NZ, VN, UAE</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D28" s="13" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
           <t>Tier-C (expensive)</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B29" s="14" t="inlineStr">
         <is>
           <t>IN, BR, SA, ZA</t>
         </is>
       </c>
-      <c r="C28" s="10" t="n">
+      <c r="C29" s="10" t="n">
         <v>5.8</v>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D29" s="13" t="n">
         <v>0.15</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>BLENDED COST / GB</t>
         </is>
       </c>
-      <c r="C30" s="11">
+      <c r="C31" s="11">
         <f>SUMPRODUCT(C25:C27,D25:D27)</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>CABIN-CLASS MIX (% of paying users in each tier)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B35" s="15" t="inlineStr">
         <is>
           <t>% Users</t>
         </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B35" s="13" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Roster Bundle</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="B36" s="13" t="n">
-        <v>0.18</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="9" t="inlineStr">
         <is>
-          <t>Premium Economy</t>
+          <t>Roster Bundle</t>
         </is>
       </c>
       <c r="B37" s="13" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="9" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Premium Economy</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
         <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B39" s="13" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
           <t>First</t>
         </is>
       </c>
-      <c r="B39" s="13" t="n">
+      <c r="B40" s="13" t="n">
         <v>0.03</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>First Suite</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="B41" t="n">
         <v>0.02</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="9" t="inlineStr">
-        <is>
-          <t>Cockpit</t>
-        </is>
-      </c>
-      <c r="B41" s="13" t="n">
-        <v>0.03</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
           <t>Refuel attach</t>
         </is>
       </c>
-      <c r="B42" s="13" t="n">
+      <c r="B43" s="13" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
         <is>
           <t>OPERATING COST / USER / MONTH</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B46" s="15" t="inlineStr">
+      <c r="B47" s="15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Cloud / API per user</t>
-        </is>
-      </c>
-      <c r="B47" s="10" t="n">
-        <v>0.15</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Payment processing (2.9% + $0.30)</t>
+          <t>Cloud / API per user</t>
         </is>
       </c>
       <c r="B48" s="10" t="n">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Customer support amortized</t>
+          <t>Payment processing (2.9% + $0.30)</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SMS / OTP / verification</t>
+          <t>Customer support amortized</t>
         </is>
       </c>
       <c r="B50" s="10" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>SMS / OTP / verification</t>
+        </is>
+      </c>
+      <c r="B51" s="10" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>Hosting + dev tools amortized</t>
         </is>
       </c>
-      <c r="B51" s="10" t="n">
+      <c r="B52" s="10" t="n">
         <v>0.1</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="9" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>TOTAL OPEX</t>
         </is>
       </c>
-      <c r="B52" s="11">
+      <c r="B53" s="11">
         <f>SUM(B45:B49)</f>
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A25:D25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2093,7 +2110,6 @@
     </row>
     <row r="25">
       <c r="A25" s="48" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="48" t="inlineStr">
@@ -2181,7 +2197,6 @@
     </row>
     <row r="33">
       <c r="A33" s="48" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="48" t="inlineStr">
@@ -3878,7 +3893,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -4071,7 +4086,268 @@
         <v/>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="40" t="inlineStr">
+        <is>
+          <t>CABIN-CLASS MIX SENSITIVITY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="39" t="inlineStr">
+        <is>
+          <t>These mix % are educated guesses (not hard data for eSIM-for-crew). This stress-test shows what happens to blended ARPU under different assumptions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="41" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="inlineStr">
+        <is>
+          <t>Econ %</t>
+        </is>
+      </c>
+      <c r="C14" s="41" t="inlineStr">
+        <is>
+          <t>Roster %</t>
+        </is>
+      </c>
+      <c r="D14" s="41" t="inlineStr">
+        <is>
+          <t>Prem %</t>
+        </is>
+      </c>
+      <c r="E14" s="41" t="inlineStr">
+        <is>
+          <t>Biz %</t>
+        </is>
+      </c>
+      <c r="F14" s="41" t="inlineStr">
+        <is>
+          <t>First %</t>
+        </is>
+      </c>
+      <c r="G14" s="41" t="inlineStr">
+        <is>
+          <t>Suite %</t>
+        </is>
+      </c>
+      <c r="H14" s="41" t="inlineStr">
+        <is>
+          <t>Cockpit %</t>
+        </is>
+      </c>
+      <c r="I14" s="41" t="inlineStr">
+        <is>
+          <t>Blended ARPU</t>
+        </is>
+      </c>
+      <c r="J14" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="90" t="inlineStr">
+        <is>
+          <t>Pessimistic (low conversion)</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="C15" s="57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D15" s="57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="E15" s="57" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F15" s="57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G15" s="57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H15" s="57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I15" s="54" t="n">
+        <v>15.1679</v>
+      </c>
+      <c r="J15" s="39" t="inlineStr">
+        <is>
+          <t>Most users stay PAYG. Worst case for ARPU.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="90" t="inlineStr">
+        <is>
+          <t>Early-stage (months 1-6)</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C16" s="57" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D16" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E16" s="57" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F16" s="57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G16" s="57" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="H16" s="57" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I16" s="54" t="n">
+        <v>14.55265</v>
+      </c>
+      <c r="J16" s="39" t="inlineStr">
+        <is>
+          <t>Realistic launch period — heavy Economy mix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="93" t="inlineStr">
+        <is>
+          <t>Base / current model</t>
+        </is>
+      </c>
+      <c r="B17" s="56" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C17" s="56" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D17" s="56" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E17" s="56" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F17" s="56" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G17" s="56" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H17" s="56" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I17" s="59" t="n">
+        <v>17.516</v>
+      </c>
+      <c r="J17" s="77" t="inlineStr">
+        <is>
+          <t>Steady-state guess. CURRENT MODEL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="90" t="inlineStr">
+        <is>
+          <t>Optimistic (high conversion)</t>
+        </is>
+      </c>
+      <c r="B18" s="57" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C18" s="57" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D18" s="57" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="E18" s="57" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F18" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G18" s="57" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H18" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I18" s="54" t="n">
+        <v>20.3392</v>
+      </c>
+      <c r="J18" s="39" t="inlineStr">
+        <is>
+          <t>Strong subscription uptake.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="90" t="inlineStr">
+        <is>
+          <t>Subscription-heavy (year 2+)</t>
+        </is>
+      </c>
+      <c r="B19" s="57" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C19" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D19" s="57" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E19" s="57" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F19" s="57" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G19" s="57" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H19" s="57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I19" s="54" t="n">
+        <v>21.4755</v>
+      </c>
+      <c r="J19" s="39" t="inlineStr">
+        <is>
+          <t>Mature population after Cockpit/First grow.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="94" t="inlineStr">
+        <is>
+          <t>BLENDED ARPU RANGE</t>
+        </is>
+      </c>
+      <c r="I21" s="94" t="inlineStr">
+        <is>
+          <t>$14.55 – $21.48</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A12:H12"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -35,7 +35,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="14">
+  <numFmts count="16">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -50,8 +50,10 @@
     <numFmt numFmtId="175" formatCode="&quot;$&quot;#,##0.00;[Red](&quot;$&quot;#,##0.00)"/>
     <numFmt numFmtId="176" formatCode="&quot;$&quot;#,##0"/>
     <numFmt numFmtId="177" formatCode="#,##0.0&quot; GB&quot;"/>
+    <numFmt numFmtId="178" formatCode="#,##0&quot; users&quot;"/>
+    <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0&quot; /mo&quot;"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="29">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -199,6 +201,17 @@
       <color rgb="00B07A1F"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <i val="1"/>
+      <color rgb="00D71921"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -260,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -362,6 +375,10 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="25" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -727,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1262,6 +1279,8 @@
         <v>0.3</v>
       </c>
     </row>
+    <row r="44"/>
+    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -1294,11 +1313,11 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Payment processing (2.9% + $0.30)</t>
+          <t>Payment processing (Stripe 2.9% + $0.30, mixed IAP)</t>
         </is>
       </c>
       <c r="B49" s="10" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="50">
@@ -1340,6 +1359,142 @@
       <c r="B53" s="11">
         <f>SUM(B45:B49)</f>
         <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="94" t="inlineStr">
+        <is>
+          <t>PAYMENT PROCESSING — 3 SCENARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr">
+        <is>
+          <t>$/user/mo</t>
+        </is>
+      </c>
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>Total OPEX</t>
+        </is>
+      </c>
+      <c r="D56" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="90" t="inlineStr">
+        <is>
+          <t>Optimistic — Stripe only (web-first)</t>
+        </is>
+      </c>
+      <c r="B57" s="54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" s="54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="D57" s="39" t="inlineStr">
+        <is>
+          <t>iOS users routed to web checkout via Universal Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="93" t="inlineStr">
+        <is>
+          <t>Realistic — Mixed Stripe + some Apple IAP</t>
+        </is>
+      </c>
+      <c r="B58" s="59" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C58" s="59" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="D58" s="77" t="inlineStr">
+        <is>
+          <t>CURRENT MODEL VALUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="90" t="inlineStr">
+        <is>
+          <t>Conservative — Apple IAP heavy</t>
+        </is>
+      </c>
+      <c r="B59" s="54" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C59" s="54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D59" s="39" t="inlineStr">
+        <is>
+          <t>Use this for investor pitches — protects against bad iOS routing</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="95" t="inlineStr">
+        <is>
+          <t>At 100K users / month:</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Optimistic ($1.00/user)</t>
+        </is>
+      </c>
+      <c r="B62" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C62" s="97" t="n">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Realistic ($1.20/user)</t>
+        </is>
+      </c>
+      <c r="B63" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C63" s="97" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Conservative ($1.50/user)</t>
+        </is>
+      </c>
+      <c r="B64" s="96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C64" s="97" t="n">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Range / month: $50K — $80K — $120K</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -1279,8 +1279,6 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
@@ -6853,7 +6851,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7029,6 +7027,13 @@
         <v/>
       </c>
     </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>% Consumed (per-tier friction-adjusted)</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
@@ -7104,9 +7109,8 @@
         <f>'README &amp; Assumptions'!D15</f>
         <v/>
       </c>
-      <c r="C18" s="19">
-        <f>$C$11</f>
-        <v/>
+      <c r="C18" s="19" t="n">
+        <v>1</v>
       </c>
       <c r="D18" s="20">
         <f>B18*C18</f>
@@ -7131,9 +7135,8 @@
         <f>'README &amp; Assumptions'!D16</f>
         <v/>
       </c>
-      <c r="C19" s="19">
-        <f>$C$11</f>
-        <v/>
+      <c r="C19" s="19" t="n">
+        <v>0.4</v>
       </c>
       <c r="D19" s="20">
         <f>B19*C19</f>
@@ -7158,9 +7161,8 @@
         <f>'README &amp; Assumptions'!D17</f>
         <v/>
       </c>
-      <c r="C20" s="19">
-        <f>$C$11</f>
-        <v/>
+      <c r="C20" s="19" t="n">
+        <v>0.45</v>
       </c>
       <c r="D20" s="20">
         <f>B20*C20</f>
@@ -7185,9 +7187,8 @@
         <f>'README &amp; Assumptions'!D18</f>
         <v/>
       </c>
-      <c r="C21" s="19">
-        <f>$C$11</f>
-        <v/>
+      <c r="C21" s="19" t="n">
+        <v>0.54</v>
       </c>
       <c r="D21" s="20">
         <f>B21*C21</f>
@@ -7203,28 +7204,27 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>Cockpit</t>
-        </is>
-      </c>
-      <c r="B22" s="18">
+      <c r="A22" s="90" t="inlineStr">
+        <is>
+          <t>First Suite</t>
+        </is>
+      </c>
+      <c r="B22">
         <f>'README &amp; Assumptions'!D19</f>
         <v/>
       </c>
-      <c r="C22" s="19">
-        <f>$C$11</f>
-        <v/>
-      </c>
-      <c r="D22" s="20">
+      <c r="C22" s="26" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D22">
         <f>B22*C22</f>
         <v/>
       </c>
-      <c r="E22" s="20">
+      <c r="E22">
         <f>(B22-D22)*'README &amp; Assumptions'!E19</f>
         <v/>
       </c>
-      <c r="F22" s="20">
+      <c r="F22">
         <f>(B22-D22)*(1-'README &amp; Assumptions'!E19)</f>
         <v/>
       </c>
@@ -7232,19 +7232,18 @@
     <row r="23">
       <c r="A23" s="9" t="inlineStr">
         <is>
-          <t>Refuel attach</t>
+          <t>Cockpit</t>
         </is>
       </c>
       <c r="B23" s="18">
         <f>'README &amp; Assumptions'!D20</f>
         <v/>
       </c>
-      <c r="C23" s="19">
-        <f>$C$11</f>
-        <v/>
+      <c r="C23" s="19" t="n">
+        <v>0.6</v>
       </c>
       <c r="D23" s="20">
-        <f>B23*C23</f>
+        <f>B22*C22</f>
         <v/>
       </c>
       <c r="E23" s="20">
@@ -7256,7 +7255,43 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Refuel attach</t>
+        </is>
+      </c>
+      <c r="B24" s="18">
+        <f>'README &amp; Assumptions'!D21</f>
+        <v/>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="20">
+        <f>B23*C23</f>
+        <v/>
+      </c>
+      <c r="E24" s="20">
+        <f>(B24-D24)*'README &amp; Assumptions'!E21</f>
+        <v/>
+      </c>
+      <c r="F24" s="20">
+        <f>(B24-D24)*(1-'README &amp; Assumptions'!E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>ℹ Per-tier consumption rates above OVERRIDE the weighted average from archetypes (rows 6-9). 1-GB refill UX changes behavior per tier.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -18,15 +18,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First Logic" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First Suite Logic" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cockpit Logic" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refuel Logic" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -273,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -379,6 +380,8 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="22" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2705,6 +2708,508 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00C9A03B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="53" t="inlineStr">
+        <is>
+          <t>Refuel (add-on) — math &amp; logic deep dive</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>Subscriber-only 1 GB top-up. Matches Economy price ($4.99) to close the subscriber backdoor. Same product, different audience.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="40" t="inlineStr">
+        <is>
+          <t>1. PRODUCT DEFINITION</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="B5" s="64" t="inlineStr">
+        <is>
+          <t>$4.99 per 1 GB top-up (dropped from $5.99 — matched to Economy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="B6" s="64" t="inlineStr">
+        <is>
+          <t>1 GB per refuel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t>Available to</t>
+        </is>
+      </c>
+      <c r="B7" s="64" t="inlineStr">
+        <is>
+          <t>Active subscribers ONLY (Economy is the non-subscriber alternative)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t>Carry</t>
+        </is>
+      </c>
+      <c r="B8" s="64" t="inlineStr">
+        <is>
+          <t>None — refuel data is consumed in the active billing period</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Use case</t>
+        </is>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>User runs out of monthly pool, taps "Refuel" button in app, adds 1 GB instantly</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>Subscription?</t>
+        </is>
+      </c>
+      <c r="B10" s="64" t="inlineStr">
+        <is>
+          <t>No — pure single-purchase top-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Strategic role</t>
+        </is>
+      </c>
+      <c r="B11" s="64" t="inlineStr">
+        <is>
+          <t>Closes the subscriber backdoor (else they'd buy cheaper Economy top-ups)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B12" s="64" t="inlineStr">
+        <is>
+          <t>LOCKED 2026-06-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>2. PER-PURCHASE ECONOMICS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>Line</t>
+        </is>
+      </c>
+      <c r="B15" s="41" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C15" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="48" t="inlineStr">
+        <is>
+          <t>Retail price</t>
+        </is>
+      </c>
+      <c r="B16" s="54" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="C16" s="39" t="inlineStr">
+        <is>
+          <t>Locked, matched to Economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="48" t="inlineStr">
+        <is>
+          <t>Wholesale COGS (1 GB × $1.20 blended)</t>
+        </is>
+      </c>
+      <c r="B17" s="54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C17" s="39" t="inlineStr">
+        <is>
+          <t>Blended Samurai rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="48" t="inlineStr">
+        <is>
+          <t>Gross profit per refuel</t>
+        </is>
+      </c>
+      <c r="B18" s="68">
+        <f>B16-B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="48" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B19" s="26">
+        <f>B18/B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="48" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>Stripe fee per transaction (2.9% + $0.30)</t>
+        </is>
+      </c>
+      <c r="B21" s="54">
+        <f>B16*0.029+0.3</f>
+        <v/>
+      </c>
+      <c r="C21" s="39" t="inlineStr">
+        <is>
+          <t>Direct cost per top-up</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="48" t="inlineStr">
+        <is>
+          <t>Net profit per refuel</t>
+        </is>
+      </c>
+      <c r="B22" s="83">
+        <f>B18-B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="48" t="inlineStr">
+        <is>
+          <t>Net margin %</t>
+        </is>
+      </c>
+      <c r="B23" s="26">
+        <f>B22/B16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="40" t="inlineStr">
+        <is>
+          <t>3. AT-SCALE — REFUEL REVENUE LINE</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="39" t="inlineStr">
+        <is>
+          <t>Refuel attach assumption: ~30% of subscribers refuel each month (varies by tier — Premium 20%, Business 25%, First 40%, Suite 20%, Cockpit 15%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>Total users</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>Active subscribers (~47%)</t>
+        </is>
+      </c>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>Refuels/mo (30% attach)</t>
+        </is>
+      </c>
+      <c r="D29" s="41" t="inlineStr">
+        <is>
+          <t>Monthly net profit</t>
+        </is>
+      </c>
+      <c r="E29" s="41" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B30" s="71" t="n">
+        <v>470</v>
+      </c>
+      <c r="C30" s="71" t="n">
+        <v>141</v>
+      </c>
+      <c r="D30" s="86" t="n">
+        <v>451.2</v>
+      </c>
+      <c r="E30" s="86" t="n">
+        <v>5414.400000000001</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="71" t="n">
+        <v>5000</v>
+      </c>
+      <c r="B31" s="71" t="n">
+        <v>2350</v>
+      </c>
+      <c r="C31" s="71" t="n">
+        <v>705</v>
+      </c>
+      <c r="D31" s="86" t="n">
+        <v>2256</v>
+      </c>
+      <c r="E31" s="86" t="n">
+        <v>27072</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="71" t="n">
+        <v>10000</v>
+      </c>
+      <c r="B32" s="71" t="n">
+        <v>4700</v>
+      </c>
+      <c r="C32" s="71" t="n">
+        <v>1410</v>
+      </c>
+      <c r="D32" s="86" t="n">
+        <v>4512</v>
+      </c>
+      <c r="E32" s="86" t="n">
+        <v>54144</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="71" t="n">
+        <v>50000</v>
+      </c>
+      <c r="B33" s="71" t="n">
+        <v>23500</v>
+      </c>
+      <c r="C33" s="71" t="n">
+        <v>7050</v>
+      </c>
+      <c r="D33" s="86" t="n">
+        <v>22560</v>
+      </c>
+      <c r="E33" s="86" t="n">
+        <v>270720</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="71" t="n">
+        <v>100000</v>
+      </c>
+      <c r="B34" s="71" t="n">
+        <v>47000</v>
+      </c>
+      <c r="C34" s="100" t="n">
+        <v>14100</v>
+      </c>
+      <c r="D34" s="87" t="n">
+        <v>45120</v>
+      </c>
+      <c r="E34" s="87" t="n">
+        <v>541440</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="40" t="inlineStr">
+        <is>
+          <t>4. STRATEGIC ROLE</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="43" t="inlineStr">
+        <is>
+          <t>Backdoor closure</t>
+        </is>
+      </c>
+      <c r="B38" s="64" t="inlineStr">
+        <is>
+          <t>Originally refuel was $5.99 — subscribers got penalized vs $4.99 Economy. Dropped to $4.99 to remove the unfair "subscriber tax." Now subscribers see only Refuel option in app, Economy is hidden.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t>Safety valve for overconsumers</t>
+        </is>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>Heavy users (especially First and Business) hit pool limits → refuel keeps them paying instead of churning to a bigger tier mid-month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="43" t="inlineStr">
+        <is>
+          <t>Predictable margin</t>
+        </is>
+      </c>
+      <c r="B40" s="64" t="inlineStr">
+        <is>
+          <t>76% gross margin on every refuel. High-value transaction with zero acquisition cost (already a subscriber).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="43" t="inlineStr">
+        <is>
+          <t>Mostly passive revenue</t>
+        </is>
+      </c>
+      <c r="B41" s="64" t="inlineStr">
+        <is>
+          <t>No marketing required. Users self-serve when they need it. Pure UX-driven.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="40" t="inlineStr">
+        <is>
+          <t>5. DECISION LOG</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Price dropped $5.99 → $4.99</t>
+        </is>
+      </c>
+      <c r="B45" s="64" t="inlineStr">
+        <is>
+          <t>Match to Economy price. Removes subscriber tax. Closes backdoor where subscribers could buy cheaper Economy.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: Blocked Economy for active subscribers</t>
+        </is>
+      </c>
+      <c r="B46" s="64" t="inlineStr">
+        <is>
+          <t>In-app logic hides Economy product from subscribers. Only Refuel option visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="43" t="inlineStr">
+        <is>
+          <t>2026-06-01: No carryover</t>
+        </is>
+      </c>
+      <c r="B47" s="64" t="inlineStr">
+        <is>
+          <t>Refuel data must be used in current billing cycle. Aligns with single-purchase model.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B39:F39"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B11:F11"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B9:F9"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -2955,7 +3460,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3226,7 +3731,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4040,7 +4545,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4505,7 +5010,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5111,7 +5616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5643,7 +6148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6268,7 +6773,893 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>Tab 2 — User Behavior</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>PURPOSE: Predicts how much data crew will actually USE (not buy). Drives COGS in every other tab. Most leveraged tab in the workbook.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="94" t="inlineStr">
+        <is>
+          <t>1. BEHAVIOR ARCHETYPES — who our paying users are</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="39" t="inlineStr">
+        <is>
+          <t>ABOUT THIS SECTION: Every paying crew member falls into one of 4 user types. These define a CONCEPTUAL MODEL of who buys our product. Crew-skewed (25/40/30/5) — we adjusted from general travel (40/35/20/5) because crew fly 8-12x/month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="41" t="inlineStr">
+        <is>
+          <t>Archetype</t>
+        </is>
+      </c>
+      <c r="B7" s="41" t="inlineStr">
+        <is>
+          <t>% of Users</t>
+        </is>
+      </c>
+      <c r="C7" s="41" t="inlineStr">
+        <is>
+          <t>% Pool Consumed</t>
+        </is>
+      </c>
+      <c r="D7" s="41" t="inlineStr">
+        <is>
+          <t>Refuel Attach</t>
+        </is>
+      </c>
+      <c r="E7" s="41" t="inlineStr">
+        <is>
+          <t>Mental Picture</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="90" t="inlineStr">
+        <is>
+          <t>Light user</t>
+        </is>
+      </c>
+      <c r="B8" s="81" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C8" s="81" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D8" s="81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" s="39" t="inlineStr">
+        <is>
+          <t>"Subscribed Premium just in case." Pool mostly unused. Pure breakage gold.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="90" t="inlineStr">
+        <is>
+          <t>Average user</t>
+        </is>
+      </c>
+      <c r="B9" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C9" s="81" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="D9" s="81" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E9" s="39" t="inlineStr">
+        <is>
+          <t>Default crew. Eats most of pool. Refuels ~1 month in 3.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="90" t="inlineStr">
+        <is>
+          <t>Heavy user</t>
+        </is>
+      </c>
+      <c r="B10" s="81" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C10" s="81" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="D10" s="81" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E10" s="39" t="inlineStr">
+        <is>
+          <t>Long-haul + connectivity dependent. Almost full consumption, often refuels.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="90" t="inlineStr">
+        <is>
+          <t>Churner</t>
+        </is>
+      </c>
+      <c r="B11" s="81" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C11" s="81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D11" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="39" t="inlineStr">
+        <is>
+          <t>Tries one month, cancels. Single-month pure breakage.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B12" s="57">
+        <f>SUM(B8:B11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVG % POOL CONSUMED</t>
+        </is>
+      </c>
+      <c r="C13" s="26">
+        <f>SUMPRODUCT(B8:B11,C8:C11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVG REFUEL ATTACH</t>
+        </is>
+      </c>
+      <c r="D14" s="26">
+        <f>SUMPRODUCT(B8:B11,D8:D11)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="92" t="inlineStr">
+        <is>
+          <t>⚠ ESTIMATE: Archetype mix and consumption % are educated guesses based on general SaaS benchmarks. NOT validated for crew-specific eSIM. Akito to validate via 20-30 crew interviews this week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t>2. PER-TIER CONSUMPTION — what the model actually USES for COGS</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="39" t="inlineStr">
+        <is>
+          <t>ABOUT THIS SECTION: After we locked the 1-GB refill UX, the single archetype weighted average no longer reflects reality. Each tier has its own consumption % based on friction-capped usage (~13 GB max per user regardless of pool size). These per-tier rates OVERRIDE Section 1's weighted average.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="41" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B20" s="41" t="inlineStr">
+        <is>
+          <t>Pool GB</t>
+        </is>
+      </c>
+      <c r="C20" s="41" t="inlineStr">
+        <is>
+          <t>% Consumed</t>
+        </is>
+      </c>
+      <c r="D20" s="41" t="inlineStr">
+        <is>
+          <t>GB Consumed</t>
+        </is>
+      </c>
+      <c r="E20" s="41" t="inlineStr">
+        <is>
+          <t>GB Carries</t>
+        </is>
+      </c>
+      <c r="F20" s="41" t="inlineStr">
+        <is>
+          <t>GB Breakage</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="90" t="inlineStr">
+        <is>
+          <t>Economy (PAYG)</t>
+        </is>
+      </c>
+      <c r="B21" s="99">
+        <f>'README &amp; Assumptions'!D14</f>
+        <v/>
+      </c>
+      <c r="C21" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="82">
+        <f>B21*C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="82">
+        <f>(B21-D21)*'README &amp; Assumptions'!E14</f>
+        <v/>
+      </c>
+      <c r="F21" s="82">
+        <f>(B21-D21)*(1-'README &amp; Assumptions'!E14)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="90" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B22" s="99">
+        <f>'README &amp; Assumptions'!D15</f>
+        <v/>
+      </c>
+      <c r="C22" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="82">
+        <f>B22*C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="82">
+        <f>(B22-D22)*'README &amp; Assumptions'!E15</f>
+        <v/>
+      </c>
+      <c r="F22" s="82">
+        <f>(B22-D22)*(1-'README &amp; Assumptions'!E15)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="90" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B23" s="99">
+        <f>'README &amp; Assumptions'!D16</f>
+        <v/>
+      </c>
+      <c r="C23" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D23" s="82">
+        <f>B23*C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="82">
+        <f>(B23-D23)*'README &amp; Assumptions'!E16</f>
+        <v/>
+      </c>
+      <c r="F23" s="82">
+        <f>(B23-D23)*(1-'README &amp; Assumptions'!E16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="90" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B24" s="99">
+        <f>'README &amp; Assumptions'!D17</f>
+        <v/>
+      </c>
+      <c r="C24" s="81" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D24" s="82">
+        <f>B24*C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="82">
+        <f>(B24-D24)*'README &amp; Assumptions'!E17</f>
+        <v/>
+      </c>
+      <c r="F24" s="82">
+        <f>(B24-D24)*(1-'README &amp; Assumptions'!E17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="90" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="90" t="inlineStr">
+        <is>
+          <t>First Suite</t>
+        </is>
+      </c>
+      <c r="B26" s="99">
+        <f>'README &amp; Assumptions'!D19</f>
+        <v/>
+      </c>
+      <c r="C26" s="81" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="D26" s="82">
+        <f>B26*C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="82">
+        <f>(B26-D26)*'README &amp; Assumptions'!E19</f>
+        <v/>
+      </c>
+      <c r="F26" s="82">
+        <f>(B26-D26)*(1-'README &amp; Assumptions'!E19)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="90" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B27" s="99">
+        <f>'README &amp; Assumptions'!D20</f>
+        <v/>
+      </c>
+      <c r="C27" s="81" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D27" s="82">
+        <f>B27*C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="82">
+        <f>(B27-D27)*'README &amp; Assumptions'!E20</f>
+        <v/>
+      </c>
+      <c r="F27" s="82">
+        <f>(B27-D27)*(1-'README &amp; Assumptions'!E20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="90" t="inlineStr">
+        <is>
+          <t>Refuel</t>
+        </is>
+      </c>
+      <c r="B28" s="99">
+        <f>'README &amp; Assumptions'!D21</f>
+        <v/>
+      </c>
+      <c r="C28" s="81" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" s="82">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="82">
+        <f>(B28-D28)*'README &amp; Assumptions'!E21</f>
+        <v/>
+      </c>
+      <c r="F28" s="82">
+        <f>(B28-D28)*(1-'README &amp; Assumptions'!E21)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="92" t="inlineStr">
+        <is>
+          <t>⚠ ESTIMATE: Per-tier consumption rates (40/45/54/33/60) are MY ESTIMATES based on the 1-GB friction logic. Real consumption could land 30-70%. App analytics months 1-3 post-launch will replace these with measured values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="94" t="inlineStr">
+        <is>
+          <t>3. THE KEY INSIGHT — pool expansion is essentially FREE to us</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="39" t="inlineStr">
+        <is>
+          <t>Because 1-GB friction caps consumption at ~13 GB regardless of pool size, going from First (25 GB) to First Suite (40 GB) costs us nothing in COGS but doubles the perceived value. This is why First Suite at $1.25/GB is the anchor product — best per-GB on the ladder, same cost to us.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B35" s="41" t="inlineStr">
+        <is>
+          <t>Pool</t>
+        </is>
+      </c>
+      <c r="C35" s="41" t="inlineStr">
+        <is>
+          <t>GB Consumed (friction-capped)</t>
+        </is>
+      </c>
+      <c r="D35" s="41" t="inlineStr">
+        <is>
+          <t>Per-GB price</t>
+        </is>
+      </c>
+      <c r="E35" s="41" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="90" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B36" s="90" t="inlineStr">
+        <is>
+          <t>10 GB</t>
+        </is>
+      </c>
+      <c r="C36" s="90" t="inlineStr">
+        <is>
+          <t>4 GB</t>
+        </is>
+      </c>
+      <c r="D36" s="90" t="inlineStr">
+        <is>
+          <t>$1.80</t>
+        </is>
+      </c>
+      <c r="E36" s="39" t="inlineStr">
+        <is>
+          <t>Small pool — friction matters most</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="90" t="inlineStr">
+        <is>
+          <t>Business ⭐</t>
+        </is>
+      </c>
+      <c r="B37" s="90" t="inlineStr">
+        <is>
+          <t>15 GB</t>
+        </is>
+      </c>
+      <c r="C37" s="90" t="inlineStr">
+        <is>
+          <t>6.75 GB</t>
+        </is>
+      </c>
+      <c r="D37" s="90" t="inlineStr">
+        <is>
+          <t>$2.00</t>
+        </is>
+      </c>
+      <c r="E37" s="39" t="inlineStr">
+        <is>
+          <t>Recommended tier — peak per-GB</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="90" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B38" s="90" t="inlineStr">
+        <is>
+          <t>25 GB</t>
+        </is>
+      </c>
+      <c r="C38" s="90" t="inlineStr">
+        <is>
+          <t>13.5 GB</t>
+        </is>
+      </c>
+      <c r="D38" s="90" t="inlineStr">
+        <is>
+          <t>$1.60</t>
+        </is>
+      </c>
+      <c r="E38" s="39" t="inlineStr">
+        <is>
+          <t>Heavy users near friction cap</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="90" t="inlineStr">
+        <is>
+          <t>First Suite ⭐</t>
+        </is>
+      </c>
+      <c r="B39" s="90" t="inlineStr">
+        <is>
+          <t>40 GB</t>
+        </is>
+      </c>
+      <c r="C39" s="90" t="inlineStr">
+        <is>
+          <t>13.2 GB</t>
+        </is>
+      </c>
+      <c r="D39" s="90" t="inlineStr">
+        <is>
+          <t>$1.25</t>
+        </is>
+      </c>
+      <c r="E39" s="39" t="inlineStr">
+        <is>
+          <t>ANCHOR PRODUCT — same cost, better marketing</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="90" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B40" s="90" t="inlineStr">
+        <is>
+          <t>12 GB</t>
+        </is>
+      </c>
+      <c r="C40" s="90" t="inlineStr">
+        <is>
+          <t>7.2 GB</t>
+        </is>
+      </c>
+      <c r="D40" s="90" t="inlineStr">
+        <is>
+          <t>$1.92</t>
+        </is>
+      </c>
+      <c r="E40" s="39" t="inlineStr">
+        <is>
+          <t>Pool tight, friction less constraining</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="94" t="inlineStr">
+        <is>
+          <t>4. HOW THIS TAB FEEDS THE MODEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>Tab 2 outputs go into 7+ downstream tabs. Change ANY number here, the whole workbook recalculates. A small mistake here cascades everywhere — that's why we validate carefully.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>Downstream tab</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t>What it does with Tab 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="90" t="inlineStr">
+        <is>
+          <t>Tab 3 — Per-Tier Unit Economics</t>
+        </is>
+      </c>
+      <c r="B46" s="90" t="inlineStr">
+        <is>
+          <t>Uses GB Consumed → COGS per user → Gross margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="90" t="inlineStr">
+        <is>
+          <t>Tab 4 — Pricing Simulator</t>
+        </is>
+      </c>
+      <c r="B47" s="90" t="inlineStr">
+        <is>
+          <t>Uses behavior inputs → break-even / margin-target retail prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="90" t="inlineStr">
+        <is>
+          <t>Tab 5 — Volume Scenarios</t>
+        </is>
+      </c>
+      <c r="B48" s="90" t="inlineStr">
+        <is>
+          <t>Per-user × user counts → 1K/5K/10K/100K P&amp;L</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="90" t="inlineStr">
+        <is>
+          <t>Tab 7 — Behavior Sensitivity</t>
+        </is>
+      </c>
+      <c r="B49" s="90" t="inlineStr">
+        <is>
+          <t>Stress-tests by shifting archetype mix</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="90" t="inlineStr">
+        <is>
+          <t>Tab 8 — LTV-CAC + Churn</t>
+        </is>
+      </c>
+      <c r="B50" s="90" t="inlineStr">
+        <is>
+          <t>Consumption + churn → lifetime value</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="90" t="inlineStr">
+        <is>
+          <t>Tab 10 — Carryover Liability</t>
+        </is>
+      </c>
+      <c r="B51" s="90" t="inlineStr">
+        <is>
+          <t>GB Carries → deferred revenue + aging schedule</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="90" t="inlineStr">
+        <is>
+          <t>Tab 11 — Strategic Scenarios</t>
+        </is>
+      </c>
+      <c r="B52" s="90" t="inlineStr">
+        <is>
+          <t>Supplier path comparisons under behavioral assumptions</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="90" t="inlineStr">
+        <is>
+          <t>Per-plan Logic tabs</t>
+        </is>
+      </c>
+      <c r="B53" s="90" t="inlineStr">
+        <is>
+          <t>Each plan's deep-dive economics</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="94" t="inlineStr">
+        <is>
+          <t>5. VALIDATION QUEUE — what needs to be tested with real data</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="41" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B56" s="41" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="90" t="inlineStr">
+        <is>
+          <t>Validate archetype mix (25/40/30/5) with crew interviews</t>
+        </is>
+      </c>
+      <c r="B57" s="90" t="inlineStr">
+        <is>
+          <t>Akito</t>
+        </is>
+      </c>
+      <c r="C57" s="90" t="inlineStr">
+        <is>
+          <t>This week</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="90" t="inlineStr">
+        <is>
+          <t>Validate consumption per archetype (30/65/95/10)</t>
+        </is>
+      </c>
+      <c r="B58" s="90" t="inlineStr">
+        <is>
+          <t>Akito</t>
+        </is>
+      </c>
+      <c r="C58" s="90" t="inlineStr">
+        <is>
+          <t>Same crew interviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="90" t="inlineStr">
+        <is>
+          <t>Validate refuel attach per archetype (10/30/65/0%)</t>
+        </is>
+      </c>
+      <c r="B59" s="90" t="inlineStr">
+        <is>
+          <t>Akito</t>
+        </is>
+      </c>
+      <c r="C59" s="90" t="inlineStr">
+        <is>
+          <t>Same crew interviews</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="90" t="inlineStr">
+        <is>
+          <t>Validate per-tier consumption rates (40/45/54/33/60)</t>
+        </is>
+      </c>
+      <c r="B60" s="90" t="inlineStr">
+        <is>
+          <t>App analytics</t>
+        </is>
+      </c>
+      <c r="C60" s="90" t="inlineStr">
+        <is>
+          <t>Months 1-3 post-launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="90" t="inlineStr">
+        <is>
+          <t>Fix refuel attach to use per-tier rates (currently archetype-driven)</t>
+        </is>
+      </c>
+      <c r="B61" s="90" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="C61" s="90" t="inlineStr">
+        <is>
+          <t>Next pass</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="90" t="inlineStr">
+        <is>
+          <t>Document Economy/Roster "100% consumption" model abstraction</t>
+        </is>
+      </c>
+      <c r="B62" s="90" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="C62" s="90" t="inlineStr">
+        <is>
+          <t>Next blueprint</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B53:F53"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="B47:F47"/>
+    <mergeCell ref="B48:F48"/>
+    <mergeCell ref="B52:F52"/>
+    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B46:F46"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="B50:F50"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A43:F43"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6845,458 +8236,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>User Behavior Profiles — % of pool consumed by user type</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>For each tier, model 4 user types. % of pool consumed determines COGS in pay-per-order model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>BEHAVIOR PROFILES (apply to all tiers)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Profile</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>% of Users</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>% of Pool Consumed</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>Refuel Attach Rate</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Light user</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="C6" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="D6" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="E6" s="14" t="inlineStr">
-        <is>
-          <t>Crew-skewed base: fewer pure-breakage users than general travel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Average user</t>
-        </is>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="C7" s="13" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="D7" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>Crew-skewed base: largest cohort — normal long-haul consumption</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Heavy user</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C8" s="13" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="D8" s="13" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E8" s="14" t="inlineStr">
-        <is>
-          <t>Crew-skewed base: more power users (it's their job to travel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Churner</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="14" t="inlineStr">
-        <is>
-          <t>Tries one month, cancels — pure breakage</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B10" s="16">
-        <f>SUM(B6:B9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVG % POOL CONSUMED</t>
-        </is>
-      </c>
-      <c r="C11" s="17">
-        <f>SUMPRODUCT(B6:B9,C6:C9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>WEIGHTED AVG REFUEL ATTACH</t>
-        </is>
-      </c>
-      <c r="D12" s="17">
-        <f>SUMPRODUCT(B6:B9,D6:D9)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>% Consumed (per-tier friction-adjusted)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>EXPECTED GB CONSUMED PER USER PER MONTH (by tier)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>Pool GB</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>% Consumed</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>GB Consumed</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>GB Unused (carries)</t>
-        </is>
-      </c>
-      <c r="F16" s="8" t="inlineStr">
-        <is>
-          <t>GB Truly Unused (breakage)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B17" s="18">
-        <f>'README &amp; Assumptions'!D14</f>
-        <v/>
-      </c>
-      <c r="C17" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" s="20">
-        <f>B17*C17</f>
-        <v/>
-      </c>
-      <c r="E17" s="20">
-        <f>(B17-D17)*'README &amp; Assumptions'!E14</f>
-        <v/>
-      </c>
-      <c r="F17" s="20">
-        <f>(B17-D17)*(1-'README &amp; Assumptions'!E14)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Roster Bundle</t>
-        </is>
-      </c>
-      <c r="B18" s="18">
-        <f>'README &amp; Assumptions'!D15</f>
-        <v/>
-      </c>
-      <c r="C18" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="20">
-        <f>B18*C18</f>
-        <v/>
-      </c>
-      <c r="E18" s="20">
-        <f>(B18-D18)*'README &amp; Assumptions'!E15</f>
-        <v/>
-      </c>
-      <c r="F18" s="20">
-        <f>(B18-D18)*(1-'README &amp; Assumptions'!E15)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Premium Economy</t>
-        </is>
-      </c>
-      <c r="B19" s="18">
-        <f>'README &amp; Assumptions'!D16</f>
-        <v/>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D19" s="20">
-        <f>B19*C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="20">
-        <f>(B19-D19)*'README &amp; Assumptions'!E16</f>
-        <v/>
-      </c>
-      <c r="F19" s="20">
-        <f>(B19-D19)*(1-'README &amp; Assumptions'!E16)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="B20" s="18">
-        <f>'README &amp; Assumptions'!D17</f>
-        <v/>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="D20" s="20">
-        <f>B20*C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="20">
-        <f>(B20-D20)*'README &amp; Assumptions'!E17</f>
-        <v/>
-      </c>
-      <c r="F20" s="20">
-        <f>(B20-D20)*(1-'README &amp; Assumptions'!E17)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="B21" s="18">
-        <f>'README &amp; Assumptions'!D18</f>
-        <v/>
-      </c>
-      <c r="C21" s="19" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="D21" s="20">
-        <f>B21*C21</f>
-        <v/>
-      </c>
-      <c r="E21" s="20">
-        <f>(B21-D21)*'README &amp; Assumptions'!E18</f>
-        <v/>
-      </c>
-      <c r="F21" s="20">
-        <f>(B21-D21)*(1-'README &amp; Assumptions'!E18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="90" t="inlineStr">
-        <is>
-          <t>First Suite</t>
-        </is>
-      </c>
-      <c r="B22">
-        <f>'README &amp; Assumptions'!D19</f>
-        <v/>
-      </c>
-      <c r="C22" s="26" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="D22">
-        <f>B22*C22</f>
-        <v/>
-      </c>
-      <c r="E22">
-        <f>(B22-D22)*'README &amp; Assumptions'!E19</f>
-        <v/>
-      </c>
-      <c r="F22">
-        <f>(B22-D22)*(1-'README &amp; Assumptions'!E19)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>Cockpit</t>
-        </is>
-      </c>
-      <c r="B23" s="18">
-        <f>'README &amp; Assumptions'!D20</f>
-        <v/>
-      </c>
-      <c r="C23" s="19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="D23" s="20">
-        <f>B22*C22</f>
-        <v/>
-      </c>
-      <c r="E23" s="20">
-        <f>(B23-D23)*'README &amp; Assumptions'!E20</f>
-        <v/>
-      </c>
-      <c r="F23" s="20">
-        <f>(B23-D23)*(1-'README &amp; Assumptions'!E20)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>Refuel attach</t>
-        </is>
-      </c>
-      <c r="B24" s="18">
-        <f>'README &amp; Assumptions'!D21</f>
-        <v/>
-      </c>
-      <c r="C24" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" s="20">
-        <f>B23*C23</f>
-        <v/>
-      </c>
-      <c r="E24" s="20">
-        <f>(B24-D24)*'README &amp; Assumptions'!E21</f>
-        <v/>
-      </c>
-      <c r="F24" s="20">
-        <f>(B24-D24)*(1-'README &amp; Assumptions'!E21)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="39" t="inlineStr">
-        <is>
-          <t>ℹ Per-tier consumption rates above OVERRIDE the weighted average from archetypes (rows 6-9). 1-GB refill UX changes behavior per tier.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A25:F25"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -274,7 +274,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -382,6 +382,10 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="22" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="16" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="16" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2918,7 +2922,6 @@
     </row>
     <row r="20">
       <c r="A20" s="48" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="48" t="inlineStr">
@@ -7643,7 +7646,7 @@
     <mergeCell ref="B47:F47"/>
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B52:F52"/>
-    <mergeCell ref="B49:F49"/>
+    <mergeCell ref="A43:F43"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="B51:F51"/>
@@ -7653,7 +7656,7 @@
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="B49:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8709,457 +8712,783 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Per-Tier Unit Economics (PAY-PER-ORDER model)</t>
+      <c r="A1" s="38" t="inlineStr">
+        <is>
+          <t>Tab 3 — Per-Tier Unit Economics</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>COGS = actual GB consumed × wholesale cost. Unused GB that breaks is pure breakage revenue.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>PURPOSE: For each tier, compute revenue, COGS, refuel income, gross margin, and net margin (after OPEX). Single-user view.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="39" t="inlineStr">
+        <is>
+          <t>Pulls prices from README (rows 14-21), GB Consumed from Tab 2 (rows 21-28), blended wholesale cost from README C31, OPEX from README B53.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="94" t="inlineStr">
+        <is>
+          <t>1. PER-TIER UNIT ECONOMICS — single subscriber per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="50" customHeight="1">
+      <c r="A7" s="47" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B7" s="47" t="inlineStr">
         <is>
           <t>Monthly Revenue</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C7" s="47" t="inlineStr">
         <is>
           <t>GB Consumed</t>
         </is>
       </c>
-      <c r="D4" s="8" t="inlineStr">
+      <c r="D7" s="47" t="inlineStr">
         <is>
           <t>Wholesale $/GB</t>
         </is>
       </c>
-      <c r="E4" s="8" t="inlineStr">
+      <c r="E7" s="47" t="inlineStr">
         <is>
           <t>eSIM COGS</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="F7" s="47" t="inlineStr">
+        <is>
+          <t>Refuel Attach %</t>
+        </is>
+      </c>
+      <c r="G7" s="47" t="inlineStr">
         <is>
           <t>Refuel Revenue</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="H7" s="47" t="inlineStr">
         <is>
           <t>Refuel COGS</t>
         </is>
       </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>Refund Cost</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="I7" s="47" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="J7" s="47" t="inlineStr">
+        <is>
+          <t>Total COGS</t>
+        </is>
+      </c>
+      <c r="K7" s="47" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="L7" s="47" t="inlineStr">
         <is>
           <t>Gross Margin %</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>After Opex</t>
-        </is>
-      </c>
-      <c r="L4" s="8" t="inlineStr">
-        <is>
-          <t>Net Margin %</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B5" s="21">
-        <f>'README &amp; Assumptions'!B13</f>
-        <v/>
-      </c>
-      <c r="C5" s="18">
-        <f>'User Behavior'!D17</f>
-        <v/>
-      </c>
-      <c r="D5" s="21">
-        <f>'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-      <c r="E5" s="11">
-        <f>C5*D5</f>
-        <v/>
-      </c>
-      <c r="F5" s="11">
-        <f>5.99*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="G5" s="11">
-        <f>D5*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="H5" s="11">
-        <f>2.50*0.5*SUMPRODUCT('User Behavior'!B6:B9,'User Behavior'!C6:C9)/1</f>
-        <v/>
-      </c>
-      <c r="I5" s="22">
-        <f>B5+F5-E5-G5-H5</f>
-        <v/>
-      </c>
-      <c r="J5" s="17">
-        <f>IFERROR(I5/(B5+F5),0)</f>
-        <v/>
-      </c>
-      <c r="K5" s="22">
-        <f>I5-'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="L5" s="17">
-        <f>IFERROR(K5/(B5+F5),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="M7" s="47" t="inlineStr">
+        <is>
+          <t>Net Margin (after OPEX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="90" t="inlineStr">
+        <is>
+          <t>Economy (PAYG)</t>
+        </is>
+      </c>
+      <c r="B8" s="46">
+        <f>'README &amp; Assumptions'!B14</f>
+        <v/>
+      </c>
+      <c r="C8" s="49">
+        <f>'User Behavior'!D21</f>
+        <v/>
+      </c>
+      <c r="D8" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E8" s="54">
+        <f>C8*D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="54">
+        <f>F8*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H8" s="54">
+        <f>F8*1*D8</f>
+        <v/>
+      </c>
+      <c r="I8" s="54">
+        <f>B8+G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="54">
+        <f>E8+H8</f>
+        <v/>
+      </c>
+      <c r="K8" s="54">
+        <f>I8-J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="26">
+        <f>IFERROR(K8/I8,0)</f>
+        <v/>
+      </c>
+      <c r="M8" s="26">
+        <f>IFERROR((K8-'README &amp; Assumptions'!B53)/I8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="90" t="inlineStr">
         <is>
           <t>Roster Bundle</t>
         </is>
       </c>
-      <c r="B6" s="21">
-        <f>'README &amp; Assumptions'!B14</f>
-        <v/>
-      </c>
-      <c r="C6" s="18">
-        <f>'User Behavior'!D18</f>
-        <v/>
-      </c>
-      <c r="D6" s="21">
-        <f>'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-      <c r="E6" s="11">
-        <f>C6*D6</f>
-        <v/>
-      </c>
-      <c r="F6" s="11">
-        <f>5.99*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="G6" s="11">
-        <f>D6*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="H6" s="11">
-        <f>2.50*0.5*SUMPRODUCT('User Behavior'!B6:B9,'User Behavior'!C6:C9)/1</f>
-        <v/>
-      </c>
-      <c r="I6" s="22">
-        <f>B6+F6-E6-G6-H6</f>
-        <v/>
-      </c>
-      <c r="J6" s="17">
-        <f>IFERROR(I6/(B6+F6),0)</f>
-        <v/>
-      </c>
-      <c r="K6" s="22">
-        <f>I6-'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="L6" s="17">
-        <f>IFERROR(K6/(B6+F6),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="B9" s="46">
+        <f>'README &amp; Assumptions'!B15</f>
+        <v/>
+      </c>
+      <c r="C9" s="49">
+        <f>'User Behavior'!D22</f>
+        <v/>
+      </c>
+      <c r="D9" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E9" s="54">
+        <f>C9*D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="54">
+        <f>F9*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H9" s="54">
+        <f>F9*1*D9</f>
+        <v/>
+      </c>
+      <c r="I9" s="54">
+        <f>B9+G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="54">
+        <f>E9+H9</f>
+        <v/>
+      </c>
+      <c r="K9" s="54">
+        <f>I9-J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="26">
+        <f>IFERROR(K9/I9,0)</f>
+        <v/>
+      </c>
+      <c r="M9" s="26">
+        <f>IFERROR((K9-'README &amp; Assumptions'!B53)/I9,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="90" t="inlineStr">
         <is>
           <t>Premium Economy</t>
         </is>
       </c>
-      <c r="B7" s="21">
-        <f>'README &amp; Assumptions'!B15</f>
-        <v/>
-      </c>
-      <c r="C7" s="18">
-        <f>'User Behavior'!D19</f>
-        <v/>
-      </c>
-      <c r="D7" s="21">
-        <f>'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-      <c r="E7" s="11">
-        <f>C7*D7</f>
-        <v/>
-      </c>
-      <c r="F7" s="11">
-        <f>5.99*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="G7" s="11">
-        <f>D7*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="H7" s="11">
-        <f>2.50*0.5*SUMPRODUCT('User Behavior'!B6:B9,'User Behavior'!C6:C9)/1</f>
-        <v/>
-      </c>
-      <c r="I7" s="22">
-        <f>B7+F7-E7-G7-H7</f>
-        <v/>
-      </c>
-      <c r="J7" s="17">
-        <f>IFERROR(I7/(B7+F7),0)</f>
-        <v/>
-      </c>
-      <c r="K7" s="22">
-        <f>I7-'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="L7" s="17">
-        <f>IFERROR(K7/(B7+F7),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="B10" s="46">
+        <f>'README &amp; Assumptions'!B16</f>
+        <v/>
+      </c>
+      <c r="C10" s="49">
+        <f>'User Behavior'!D23</f>
+        <v/>
+      </c>
+      <c r="D10" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E10" s="54">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="81" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="54">
+        <f>F10*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H10" s="54">
+        <f>F10*1*D10</f>
+        <v/>
+      </c>
+      <c r="I10" s="54">
+        <f>B10+G10</f>
+        <v/>
+      </c>
+      <c r="J10" s="54">
+        <f>E10+H10</f>
+        <v/>
+      </c>
+      <c r="K10" s="54">
+        <f>I10-J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="26">
+        <f>IFERROR(K10/I10,0)</f>
+        <v/>
+      </c>
+      <c r="M10" s="26">
+        <f>IFERROR((K10-'README &amp; Assumptions'!B53)/I10,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="93" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="B8" s="21">
-        <f>'README &amp; Assumptions'!B16</f>
-        <v/>
-      </c>
-      <c r="C8" s="18">
-        <f>'User Behavior'!D20</f>
-        <v/>
-      </c>
-      <c r="D8" s="21">
-        <f>'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-      <c r="E8" s="11">
-        <f>C8*D8</f>
-        <v/>
-      </c>
-      <c r="F8" s="11">
-        <f>5.99*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="G8" s="11">
-        <f>D8*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="H8" s="11">
-        <f>2.50*0.5*SUMPRODUCT('User Behavior'!B6:B9,'User Behavior'!C6:C9)/1</f>
-        <v/>
-      </c>
-      <c r="I8" s="22">
-        <f>B8+F8-E8-G8-H8</f>
-        <v/>
-      </c>
-      <c r="J8" s="17">
-        <f>IFERROR(I8/(B8+F8),0)</f>
-        <v/>
-      </c>
-      <c r="K8" s="22">
-        <f>I8-'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="L8" s="17">
-        <f>IFERROR(K8/(B8+F8),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="B11" s="101">
+        <f>'README &amp; Assumptions'!B17</f>
+        <v/>
+      </c>
+      <c r="C11" s="102">
+        <f>'User Behavior'!D24</f>
+        <v/>
+      </c>
+      <c r="D11" s="101">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E11" s="59">
+        <f>C11*D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="103" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G11" s="59">
+        <f>F11*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H11" s="59">
+        <f>F11*1*D11</f>
+        <v/>
+      </c>
+      <c r="I11" s="59">
+        <f>B11+G11</f>
+        <v/>
+      </c>
+      <c r="J11" s="59">
+        <f>E11+H11</f>
+        <v/>
+      </c>
+      <c r="K11" s="59">
+        <f>I11-J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="104">
+        <f>IFERROR(K11/I11,0)</f>
+        <v/>
+      </c>
+      <c r="M11" s="104">
+        <f>IFERROR((K11-'README &amp; Assumptions'!B53)/I11,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="90" t="inlineStr">
         <is>
           <t>First</t>
         </is>
       </c>
-      <c r="B9" s="21">
-        <f>'README &amp; Assumptions'!B17</f>
-        <v/>
-      </c>
-      <c r="C9" s="18">
-        <f>'User Behavior'!D21</f>
-        <v/>
-      </c>
-      <c r="D9" s="21">
-        <f>'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-      <c r="E9" s="11">
-        <f>C9*D9</f>
-        <v/>
-      </c>
-      <c r="F9" s="11">
-        <f>5.99*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="G9" s="11">
-        <f>D9*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="H9" s="11">
-        <f>2.50*0.5*SUMPRODUCT('User Behavior'!B6:B9,'User Behavior'!C6:C9)/1</f>
-        <v/>
-      </c>
-      <c r="I9" s="22">
-        <f>B9+F9-E9-G9-H9</f>
-        <v/>
-      </c>
-      <c r="J9" s="17">
-        <f>IFERROR(I9/(B9+F9),0)</f>
-        <v/>
-      </c>
-      <c r="K9" s="22">
-        <f>I9-'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="L9" s="17">
-        <f>IFERROR(K9/(B9+F9),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>Cockpit</t>
-        </is>
-      </c>
-      <c r="B10" s="21">
+      <c r="B12" s="46">
         <f>'README &amp; Assumptions'!B18</f>
         <v/>
       </c>
-      <c r="C10" s="18">
-        <f>'User Behavior'!D22</f>
-        <v/>
-      </c>
-      <c r="D10" s="21">
-        <f>'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-      <c r="E10" s="11">
-        <f>C10*D10</f>
-        <v/>
-      </c>
-      <c r="F10" s="11">
-        <f>5.99*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="G10" s="11">
-        <f>D10*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="H10" s="11">
-        <f>2.50*0.5*SUMPRODUCT('User Behavior'!B6:B9,'User Behavior'!C6:C9)/1</f>
-        <v/>
-      </c>
-      <c r="I10" s="22">
-        <f>B10+F10-E10-G10-H10</f>
-        <v/>
-      </c>
-      <c r="J10" s="17">
-        <f>IFERROR(I10/(B10+F10),0)</f>
-        <v/>
-      </c>
-      <c r="K10" s="22">
-        <f>I10-'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="L10" s="17">
-        <f>IFERROR(K10/(B10+F10),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Refuel attach</t>
-        </is>
-      </c>
-      <c r="B11" s="21">
+      <c r="C12" s="49">
+        <f>'User Behavior'!D25</f>
+        <v/>
+      </c>
+      <c r="D12" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E12" s="54">
+        <f>C12*D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G12" s="54">
+        <f>F12*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H12" s="54">
+        <f>F12*1*D12</f>
+        <v/>
+      </c>
+      <c r="I12" s="54">
+        <f>B12+G12</f>
+        <v/>
+      </c>
+      <c r="J12" s="54">
+        <f>E12+H12</f>
+        <v/>
+      </c>
+      <c r="K12" s="54">
+        <f>I12-J12</f>
+        <v/>
+      </c>
+      <c r="L12" s="26">
+        <f>IFERROR(K12/I12,0)</f>
+        <v/>
+      </c>
+      <c r="M12" s="26">
+        <f>IFERROR((K12-'README &amp; Assumptions'!B53)/I12,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="90" t="inlineStr">
+        <is>
+          <t>First Suite</t>
+        </is>
+      </c>
+      <c r="B13" s="46">
         <f>'README &amp; Assumptions'!B19</f>
         <v/>
       </c>
-      <c r="C11" s="18">
-        <f>'User Behavior'!D23</f>
-        <v/>
-      </c>
-      <c r="D11" s="21">
-        <f>'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-      <c r="E11" s="11">
-        <f>C11*D11</f>
-        <v/>
-      </c>
-      <c r="F11" s="11">
-        <f>5.99*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="G11" s="11">
-        <f>D11*'User Behavior'!D12</f>
-        <v/>
-      </c>
-      <c r="H11" s="11">
-        <f>2.50*0.5*SUMPRODUCT('User Behavior'!B6:B9,'User Behavior'!C6:C9)/1</f>
-        <v/>
-      </c>
-      <c r="I11" s="22">
-        <f>B11+F11-E11-G11-H11</f>
-        <v/>
-      </c>
-      <c r="J11" s="17">
-        <f>IFERROR(I11/(B11+F11),0)</f>
-        <v/>
-      </c>
-      <c r="K11" s="22">
-        <f>I11-'README &amp; Assumptions'!B50</f>
-        <v/>
-      </c>
-      <c r="L11" s="17">
-        <f>IFERROR(K11/(B11+F11),0)</f>
-        <v/>
+      <c r="C13" s="49">
+        <f>'User Behavior'!D26</f>
+        <v/>
+      </c>
+      <c r="D13" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E13" s="54">
+        <f>C13*D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="81" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="54">
+        <f>F13*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H13" s="54">
+        <f>F13*1*D13</f>
+        <v/>
+      </c>
+      <c r="I13" s="54">
+        <f>B13+G13</f>
+        <v/>
+      </c>
+      <c r="J13" s="54">
+        <f>E13+H13</f>
+        <v/>
+      </c>
+      <c r="K13" s="54">
+        <f>I13-J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="26">
+        <f>IFERROR(K13/I13,0)</f>
+        <v/>
+      </c>
+      <c r="M13" s="26">
+        <f>IFERROR((K13-'README &amp; Assumptions'!B53)/I13,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="90" t="inlineStr">
+        <is>
+          <t>Cockpit (annual)</t>
+        </is>
+      </c>
+      <c r="B14" s="46">
+        <f>'README &amp; Assumptions'!B20</f>
+        <v/>
+      </c>
+      <c r="C14" s="49">
+        <f>'User Behavior'!D27</f>
+        <v/>
+      </c>
+      <c r="D14" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E14" s="54">
+        <f>C14*D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="81" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G14" s="54">
+        <f>F14*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H14" s="54">
+        <f>F14*1*D14</f>
+        <v/>
+      </c>
+      <c r="I14" s="54">
+        <f>B14+G14</f>
+        <v/>
+      </c>
+      <c r="J14" s="54">
+        <f>E14+H14</f>
+        <v/>
+      </c>
+      <c r="K14" s="54">
+        <f>I14-J14</f>
+        <v/>
+      </c>
+      <c r="L14" s="26">
+        <f>IFERROR(K14/I14,0)</f>
+        <v/>
+      </c>
+      <c r="M14" s="26">
+        <f>IFERROR((K14-'README &amp; Assumptions'!B53)/I14,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="39" t="inlineStr">
+        <is>
+          <t>⚠ Cockpit revenue here shows monthly equivalent ($24.92), not the annual $299 prepay. Cockpit ROI is best understood in Cockpit Logic tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="94" t="inlineStr">
+        <is>
+          <t>2. HOW TO READ THIS TAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="95" t="inlineStr">
+        <is>
+          <t>Monthly Revenue</t>
+        </is>
+      </c>
+      <c r="B19" s="90" t="inlineStr">
+        <is>
+          <t>What user pays us per month for their subscription/PAYG plan</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="95" t="inlineStr">
+        <is>
+          <t>GB Consumed</t>
+        </is>
+      </c>
+      <c r="B20" s="90" t="inlineStr">
+        <is>
+          <t>How much data they actually USE (from Tab 2 per-tier rates, friction-adjusted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="95" t="inlineStr">
+        <is>
+          <t>Wholesale $/GB</t>
+        </is>
+      </c>
+      <c r="B21" s="90" t="inlineStr">
+        <is>
+          <t>What we pay Samurai per GB consumed (blended Tier-A/B/C cost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="95" t="inlineStr">
+        <is>
+          <t>eSIM COGS</t>
+        </is>
+      </c>
+      <c r="B22" s="90" t="inlineStr">
+        <is>
+          <t>GB consumed × wholesale $/GB = what we owe Samurai for this user</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="95" t="inlineStr">
+        <is>
+          <t>Refuel Revenue + COGS</t>
+        </is>
+      </c>
+      <c r="B23" s="90" t="inlineStr">
+        <is>
+          <t>Some % of users top up. They pay $4.99 per 1 GB, we pay ~$0.85-$1.40 wholesale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="95" t="inlineStr">
+        <is>
+          <t>Total Revenue / COGS</t>
+        </is>
+      </c>
+      <c r="B24" s="90" t="inlineStr">
+        <is>
+          <t>Sum of base + refuel</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="95" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="B25" s="90" t="inlineStr">
+        <is>
+          <t>Total Revenue - Total COGS (before operating costs)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="95" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="B26" s="90" t="inlineStr">
+        <is>
+          <t>Industry-standard profitability indicator. Target: 60-80%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="95" t="inlineStr">
+        <is>
+          <t>Net Margin (after OPEX)</t>
+        </is>
+      </c>
+      <c r="B27" s="90" t="inlineStr">
+        <is>
+          <t>Gross Profit minus $1.80/user OPEX (cloud, payments, support, SMS, hosting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="94" t="inlineStr">
+        <is>
+          <t>3. SOURCES &amp; CONFIDENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="41" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B31" s="41" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C31" s="41" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="90" t="inlineStr">
+        <is>
+          <t>Retail prices</t>
+        </is>
+      </c>
+      <c r="B32" s="90" t="inlineStr">
+        <is>
+          <t>Locked decisions 2026-06-01 (Tab 1 Section 2)</t>
+        </is>
+      </c>
+      <c r="C32" s="90" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="90" t="inlineStr">
+        <is>
+          <t>GB Consumed</t>
+        </is>
+      </c>
+      <c r="B33" s="90" t="inlineStr">
+        <is>
+          <t>Per-tier rates from Tab 2 (40/45/54/33/60%)</t>
+        </is>
+      </c>
+      <c r="C33" s="90" t="inlineStr">
+        <is>
+          <t>MEDIUM (estimates)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="90" t="inlineStr">
+        <is>
+          <t>Wholesale $/GB</t>
+        </is>
+      </c>
+      <c r="B34" s="90" t="inlineStr">
+        <is>
+          <t>Real Samurai rate sheet, weighted by 60/25/15 country mix</t>
+        </is>
+      </c>
+      <c r="C34" s="90" t="inlineStr">
+        <is>
+          <t>MEDIUM (mix is placeholder)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="90" t="inlineStr">
+        <is>
+          <t>Refuel attach %</t>
+        </is>
+      </c>
+      <c r="B35" s="90" t="inlineStr">
+        <is>
+          <t>MY ESTIMATE per tier (10-40%)</t>
+        </is>
+      </c>
+      <c r="C35" s="90" t="inlineStr">
+        <is>
+          <t>LOW (needs validation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="90" t="inlineStr">
+        <is>
+          <t>OPEX $1.80/user</t>
+        </is>
+      </c>
+      <c r="B36" s="90" t="inlineStr">
+        <is>
+          <t>Tab 1 Section 5 — payment processing $1.20 + others</t>
+        </is>
+      </c>
+      <c r="C36" s="90" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="94" t="inlineStr">
+        <is>
+          <t>4. VALIDATION QUEUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="39" t="inlineStr">
+        <is>
+          <t>• Per-tier refuel attach rates (10/20/25/40/20/15%) — validate via app analytics post-launch</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="39" t="inlineStr">
+        <is>
+          <t>• Wholesale country mix (60/25/15) — Akito to validate via 5-10 sample crew rosters</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="39" t="inlineStr">
+        <is>
+          <t>• Per-tier consumption rates inherited from Tab 2 (same validation as Tab 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>• Sensitivity test: what happens if Premium consumption is 50% instead of 40%?</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="B24:M24"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B25:M25"/>
+    <mergeCell ref="B19:M19"/>
+    <mergeCell ref="B20:M20"/>
+    <mergeCell ref="B21:M21"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="A40:M40"/>
+    <mergeCell ref="B22:M22"/>
+    <mergeCell ref="A3:M3"/>
+    <mergeCell ref="B26:M26"/>
+    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="A43:M43"/>
+    <mergeCell ref="A16:M16"/>
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A42:M42"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -19,15 +19,16 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="First Suite Logic" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cockpit Logic" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Refuel Logic" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Costs &amp; Burn" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Volume Scenarios" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Procurement Options" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="24-Month Rollout" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Behavior Sensitivity" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LTV-CAC + Churn" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per-Tier Geo Mix" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Carryover Liability" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Strategic Scenarios" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash + Sensitivity" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -36,7 +37,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="16">
+  <numFmts count="17">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -53,8 +54,9 @@
     <numFmt numFmtId="177" formatCode="#,##0.0&quot; GB&quot;"/>
     <numFmt numFmtId="178" formatCode="#,##0&quot; users&quot;"/>
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0&quot; /mo&quot;"/>
+    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00&quot; /user/mo&quot;"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="34">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -213,8 +215,37 @@
       <color rgb="00D71921"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="002B2B2B"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <i val="1"/>
+      <color rgb="006B6B6B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="00D71921"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="006B6B6B"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -261,8 +292,23 @@
         <fgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002B2B2B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF4B8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F7F7F7"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -270,11 +316,69 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="120">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -386,6 +490,43 @@
     <xf numFmtId="174" fontId="16" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="9" fontId="14" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="173" fontId="32" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="32" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="27" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3216,6 +3357,1018 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:E59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="105" t="inlineStr">
+        <is>
+          <t>Costs &amp; Burn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="106" t="inlineStr">
+        <is>
+          <t>Single source of truth for all Peanut eSIM costs — variable per-user, fixed monthly burn, marketing, one-time, and what still needs validation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="107" t="inlineStr">
+        <is>
+          <t>Section 1 — Per-user variable costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="108" t="inlineStr">
+        <is>
+          <t>Cost line</t>
+        </is>
+      </c>
+      <c r="B5" s="108" t="inlineStr">
+        <is>
+          <t>Current estimate ($/user/mo)</t>
+        </is>
+      </c>
+      <c r="C5" s="108" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="D5" s="108" t="inlineStr">
+        <is>
+          <t>Confidence</t>
+        </is>
+      </c>
+      <c r="E5" s="108" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="109" t="inlineStr">
+        <is>
+          <t>Payment processing (Stripe 2.9% + $0.30 weighted)</t>
+        </is>
+      </c>
+      <c r="B6" s="110" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="C6" s="109" t="inlineStr">
+        <is>
+          <t>Tab 1 Section 5 — 3-scenario locked at realistic</t>
+        </is>
+      </c>
+      <c r="D6" s="109" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E6" s="111" t="inlineStr">
+        <is>
+          <t>Range $1.00-$1.50 depending on iOS routing</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="109" t="inlineStr">
+        <is>
+          <t>Apple App Store fees (if iOS in-app)</t>
+        </is>
+      </c>
+      <c r="B7" s="112" t="inlineStr">
+        <is>
+          <t>included in payment processing</t>
+        </is>
+      </c>
+      <c r="C7" s="109" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="109" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E7" s="111" t="inlineStr">
+        <is>
+          <t>30% IAP charges, mixed in payment processing</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="109" t="inlineStr">
+        <is>
+          <t>Customer support amortized</t>
+        </is>
+      </c>
+      <c r="B8" s="110" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C8" s="109" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="D8" s="109" t="inlineStr">
+        <is>
+          <t>Low — phase-dependent</t>
+        </is>
+      </c>
+      <c r="E8" s="111" t="inlineStr">
+        <is>
+          <t>Pre-launch much higher, mature lower</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="109" t="inlineStr">
+        <is>
+          <t>Cloud / API per user</t>
+        </is>
+      </c>
+      <c r="B9" s="110" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C9" s="109" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="D9" s="109" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E9" s="111" t="inlineStr">
+        <is>
+          <t>Firebase, API gateway</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="109" t="inlineStr">
+        <is>
+          <t>SMS / OTP / verification</t>
+        </is>
+      </c>
+      <c r="B10" s="110" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C10" s="109" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="D10" s="109" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E10" s="111" t="inlineStr">
+        <is>
+          <t>Twilio rates</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="109" t="inlineStr">
+        <is>
+          <t>Hosting + dev tools amortized</t>
+        </is>
+      </c>
+      <c r="B11" s="110" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C11" s="109" t="inlineStr">
+        <is>
+          <t>Placeholder</t>
+        </is>
+      </c>
+      <c r="D11" s="109" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E11" s="111" t="inlineStr">
+        <is>
+          <t>GitHub, monitoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="109" t="inlineStr">
+        <is>
+          <t>FX conversion fees</t>
+        </is>
+      </c>
+      <c r="B12" s="110" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C12" s="109" t="inlineStr">
+        <is>
+          <t>Estimate</t>
+        </is>
+      </c>
+      <c r="D12" s="109" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E12" s="111" t="inlineStr">
+        <is>
+          <t>Stripe FX ~1% on cross-currency</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="109" t="inlineStr">
+        <is>
+          <t>Refund cost (avg per user)</t>
+        </is>
+      </c>
+      <c r="B13" s="110" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C13" s="109" t="inlineStr">
+        <is>
+          <t>Estimate (~2% of revenue refunded)</t>
+        </is>
+      </c>
+      <c r="D13" s="109" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E13" s="111" t="inlineStr">
+        <is>
+          <t>Industry standard 2-3%</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="113" t="inlineStr">
+        <is>
+          <t>TOTAL per-user variable</t>
+        </is>
+      </c>
+      <c r="B14" s="114">
+        <f>SUM(B6,B8,B9,B10,B11,B12,B13)</f>
+        <v/>
+      </c>
+      <c r="C14" s="113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E14" s="115" t="inlineStr">
+        <is>
+          <t>(formula =SUM above) — quoted $2.20/user/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="107" t="inlineStr">
+        <is>
+          <t>Section 2 — Fixed monthly burn</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="108" t="inlineStr">
+        <is>
+          <t>Cost line</t>
+        </is>
+      </c>
+      <c r="B17" s="108" t="inlineStr">
+        <is>
+          <t>Pre-launch</t>
+        </is>
+      </c>
+      <c r="C17" s="108" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+      <c r="D17" s="108" t="inlineStr">
+        <is>
+          <t>Mature</t>
+        </is>
+      </c>
+      <c r="E17" s="108" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="109" t="inlineStr">
+        <is>
+          <t>Founder salaries (Balraj + Akito)</t>
+        </is>
+      </c>
+      <c r="B18" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="116" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D18" s="116" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E18" s="111" t="inlineStr">
+        <is>
+          <t>Bootstrap pre-launch, modest salary post-launch, market rate at scale</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="109" t="inlineStr">
+        <is>
+          <t>Legal / accounting</t>
+        </is>
+      </c>
+      <c r="B19" s="116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C19" s="116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D19" s="116" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E19" s="111" t="inlineStr">
+        <is>
+          <t>Required from LLC formation</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="109" t="inlineStr">
+        <is>
+          <t>Insurance (E&amp;O, cyber, liability)</t>
+        </is>
+      </c>
+      <c r="B20" s="116" t="n">
+        <v>400</v>
+      </c>
+      <c r="C20" s="116" t="n">
+        <v>400</v>
+      </c>
+      <c r="D20" s="116" t="n">
+        <v>400</v>
+      </c>
+      <c r="E20" s="111" t="inlineStr">
+        <is>
+          <t>Annual ~$5K spread monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="109" t="inlineStr">
+        <is>
+          <t>Office / co-working</t>
+        </is>
+      </c>
+      <c r="B21" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="111" t="inlineStr">
+        <is>
+          <t>Remote-first</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="109" t="inlineStr">
+        <is>
+          <t>Software stack (Slack, Notion, Figma, etc.)</t>
+        </is>
+      </c>
+      <c r="B22" s="116" t="n">
+        <v>300</v>
+      </c>
+      <c r="C22" s="116" t="n">
+        <v>300</v>
+      </c>
+      <c r="D22" s="116" t="n">
+        <v>300</v>
+      </c>
+      <c r="E22" s="111" t="inlineStr">
+        <is>
+          <t>Founder tools</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="109" t="inlineStr">
+        <is>
+          <t>Domain + DNS</t>
+        </is>
+      </c>
+      <c r="B23" s="116" t="n">
+        <v>5</v>
+      </c>
+      <c r="C23" s="116" t="n">
+        <v>5</v>
+      </c>
+      <c r="D23" s="116" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" s="111" t="inlineStr">
+        <is>
+          <t>moonlight.ventures + others amortized</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="109" t="inlineStr">
+        <is>
+          <t>Apple Developer Program</t>
+        </is>
+      </c>
+      <c r="B24" s="116" t="n">
+        <v>8</v>
+      </c>
+      <c r="C24" s="116" t="n">
+        <v>8</v>
+      </c>
+      <c r="D24" s="116" t="n">
+        <v>8</v>
+      </c>
+      <c r="E24" s="111" t="inlineStr">
+        <is>
+          <t>$99/year ÷ 12</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="113" t="inlineStr">
+        <is>
+          <t>TOTAL fixed monthly burn (pre-launch)</t>
+        </is>
+      </c>
+      <c r="B25" s="117">
+        <f>SUM(B18:B24)</f>
+        <v/>
+      </c>
+      <c r="C25" s="113" t="inlineStr"/>
+      <c r="D25" s="113" t="inlineStr"/>
+      <c r="E25" s="115" t="inlineStr">
+        <is>
+          <t>(sum) — quoted $1,713</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="113" t="inlineStr">
+        <is>
+          <t>TOTAL fixed monthly burn (early)</t>
+        </is>
+      </c>
+      <c r="B26" s="113" t="inlineStr"/>
+      <c r="C26" s="117">
+        <f>SUM(C18:C24)</f>
+        <v/>
+      </c>
+      <c r="D26" s="113" t="inlineStr"/>
+      <c r="E26" s="115" t="inlineStr">
+        <is>
+          <t>(with founder pay) — quoted $11,713</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="113" t="inlineStr">
+        <is>
+          <t>TOTAL fixed monthly burn (mature)</t>
+        </is>
+      </c>
+      <c r="B27" s="113" t="inlineStr"/>
+      <c r="C27" s="113" t="inlineStr"/>
+      <c r="D27" s="117">
+        <f>SUM(D18:D24)</f>
+        <v/>
+      </c>
+      <c r="E27" s="115" t="inlineStr">
+        <is>
+          <t>(full salaries) — quoted $26,713</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="107" t="inlineStr">
+        <is>
+          <t>Section 3 — Variable scaling costs (marketing &amp; growth)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="108" t="inlineStr">
+        <is>
+          <t>Cost line</t>
+        </is>
+      </c>
+      <c r="B30" s="108" t="inlineStr">
+        <is>
+          <t>Pre-launch</t>
+        </is>
+      </c>
+      <c r="C30" s="108" t="inlineStr">
+        <is>
+          <t>Early</t>
+        </is>
+      </c>
+      <c r="D30" s="108" t="inlineStr">
+        <is>
+          <t>Growth</t>
+        </is>
+      </c>
+      <c r="E30" s="108" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="109" t="inlineStr">
+        <is>
+          <t>Crew WhatsApp acquisition (Akito's network)</t>
+        </is>
+      </c>
+      <c r="B31" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="111" t="inlineStr">
+        <is>
+          <t>Free organic — the wedge</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="109" t="inlineStr">
+        <is>
+          <t>Referral incentives ($5 credit per referral)</t>
+        </is>
+      </c>
+      <c r="B32" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C32" s="116" t="n">
+        <v>500</v>
+      </c>
+      <c r="D32" s="116" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="111" t="inlineStr">
+        <is>
+          <t>Scale with user growth</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="109" t="inlineStr">
+        <is>
+          <t>Paid social (Instagram crew creators)</t>
+        </is>
+      </c>
+      <c r="B33" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="116" t="n">
+        <v>500</v>
+      </c>
+      <c r="D33" s="116" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E33" s="111" t="inlineStr">
+        <is>
+          <t>Phase 2 onwards</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="109" t="inlineStr">
+        <is>
+          <t>Content marketing (Akito blog/JP content)</t>
+        </is>
+      </c>
+      <c r="B34" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="111" t="inlineStr">
+        <is>
+          <t>Time-based, no $ cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="109" t="inlineStr">
+        <is>
+          <t>Beta crew gifts/swag</t>
+        </is>
+      </c>
+      <c r="B35" s="116" t="n">
+        <v>200</v>
+      </c>
+      <c r="C35" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="111" t="inlineStr">
+        <is>
+          <t>One-time ($200) — placed in pre-launch column</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="109" t="inlineStr">
+        <is>
+          <t>Crew interview compensation</t>
+        </is>
+      </c>
+      <c r="B36" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="111" t="inlineStr">
+        <is>
+          <t>$50 × 20-30 crew, one-time — see Section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="109" t="inlineStr">
+        <is>
+          <t>Conferences / events</t>
+        </is>
+      </c>
+      <c r="B37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="116" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E37" s="111" t="inlineStr">
+        <is>
+          <t>Year 2+ when we have product</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="113" t="inlineStr">
+        <is>
+          <t>TOTAL marketing (early stage)</t>
+        </is>
+      </c>
+      <c r="B38" s="113" t="inlineStr"/>
+      <c r="C38" s="117">
+        <f>SUM(C31:C37)</f>
+        <v/>
+      </c>
+      <c r="D38" s="113" t="inlineStr"/>
+      <c r="E38" s="115" t="inlineStr">
+        <is>
+          <t>(sum) — quoted $1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="113" t="inlineStr">
+        <is>
+          <t>TOTAL marketing (growth stage)</t>
+        </is>
+      </c>
+      <c r="B39" s="113" t="inlineStr"/>
+      <c r="C39" s="113" t="inlineStr"/>
+      <c r="D39" s="117">
+        <f>SUM(D31:D37)</f>
+        <v/>
+      </c>
+      <c r="E39" s="115" t="inlineStr">
+        <is>
+          <t>(sum) — quoted $10,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="107" t="inlineStr">
+        <is>
+          <t>Section 4 — One-time costs</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="108" t="inlineStr">
+        <is>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B42" s="108" t="inlineStr">
+        <is>
+          <t>Amount</t>
+        </is>
+      </c>
+      <c r="C42" s="108" t="inlineStr">
+        <is>
+          <t>When</t>
+        </is>
+      </c>
+      <c r="D42" s="108" t="inlineStr"/>
+      <c r="E42" s="108" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="109" t="inlineStr">
+        <is>
+          <t>Delaware LLC filing</t>
+        </is>
+      </c>
+      <c r="B43" s="116" t="n">
+        <v>90</v>
+      </c>
+      <c r="C43" s="111" t="inlineStr">
+        <is>
+          <t>This week</t>
+        </is>
+      </c>
+      <c r="D43" s="109" t="inlineStr"/>
+      <c r="E43" s="109" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="109" t="inlineStr">
+        <is>
+          <t>Trademark Class 35 search</t>
+        </is>
+      </c>
+      <c r="B44" s="116" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C44" s="111" t="inlineStr">
+        <is>
+          <t>Before public launch</t>
+        </is>
+      </c>
+      <c r="D44" s="109" t="inlineStr"/>
+      <c r="E44" s="109" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="109" t="inlineStr">
+        <is>
+          <t>Trademark Class 9/38 filing</t>
+        </is>
+      </c>
+      <c r="B45" s="116" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C45" s="111" t="inlineStr">
+        <is>
+          <t>Before public launch</t>
+        </is>
+      </c>
+      <c r="D45" s="109" t="inlineStr"/>
+      <c r="E45" s="109" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="109" t="inlineStr">
+        <is>
+          <t>moonlight.ventures domain (5 years)</t>
+        </is>
+      </c>
+      <c r="B46" s="116" t="n">
+        <v>125</v>
+      </c>
+      <c r="C46" s="111" t="inlineStr">
+        <is>
+          <t>This week</t>
+        </is>
+      </c>
+      <c r="D46" s="109" t="inlineStr"/>
+      <c r="E46" s="109" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="109" t="inlineStr">
+        <is>
+          <t>Initial Apple Developer enrollment</t>
+        </is>
+      </c>
+      <c r="B47" s="116" t="n">
+        <v>99</v>
+      </c>
+      <c r="C47" s="111" t="inlineStr">
+        <is>
+          <t>LLC formation prereq</t>
+        </is>
+      </c>
+      <c r="D47" s="109" t="inlineStr"/>
+      <c r="E47" s="109" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="109" t="inlineStr">
+        <is>
+          <t>Mercury bank setup</t>
+        </is>
+      </c>
+      <c r="B48" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="111" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="D48" s="109" t="inlineStr"/>
+      <c r="E48" s="109" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="109" t="inlineStr">
+        <is>
+          <t>Initial Samurai onboarding fees</t>
+        </is>
+      </c>
+      <c r="B49" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C49" s="111" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D49" s="109" t="inlineStr"/>
+      <c r="E49" s="109" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="113" t="inlineStr">
+        <is>
+          <t>TOTAL one-time</t>
+        </is>
+      </c>
+      <c r="B50" s="117">
+        <f>SUM(B43:B49)</f>
+        <v/>
+      </c>
+      <c r="C50" s="115" t="inlineStr">
+        <is>
+          <t>(sum) — quoted $3,314</t>
+        </is>
+      </c>
+      <c r="D50" s="113" t="inlineStr"/>
+      <c r="E50" s="113" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="107" t="inlineStr">
+        <is>
+          <t>Section 5 — Validation queue</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="108" t="inlineStr">
+        <is>
+          <t>Open validation item</t>
+        </is>
+      </c>
+      <c r="B53" s="118" t="n"/>
+      <c r="C53" s="118" t="n"/>
+      <c r="D53" s="118" t="n"/>
+      <c r="E53" s="119" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="112" t="inlineStr">
+        <is>
+          <t>☐  Validate Stripe payment processing actual rate post-launch</t>
+        </is>
+      </c>
+      <c r="B54" s="118" t="n"/>
+      <c r="C54" s="118" t="n"/>
+      <c r="D54" s="118" t="n"/>
+      <c r="E54" s="119" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="112" t="inlineStr">
+        <is>
+          <t>☐  Validate customer support cost as we hire</t>
+        </is>
+      </c>
+      <c r="B55" s="118" t="n"/>
+      <c r="C55" s="118" t="n"/>
+      <c r="D55" s="118" t="n"/>
+      <c r="E55" s="119" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="112" t="inlineStr">
+        <is>
+          <t>☐  Validate refund cost from real data months 1-3</t>
+        </is>
+      </c>
+      <c r="B56" s="118" t="n"/>
+      <c r="C56" s="118" t="n"/>
+      <c r="D56" s="118" t="n"/>
+      <c r="E56" s="119" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="112" t="inlineStr">
+        <is>
+          <t>☐  Validate FX fee impact on non-USD purchases</t>
+        </is>
+      </c>
+      <c r="B57" s="118" t="n"/>
+      <c r="C57" s="118" t="n"/>
+      <c r="D57" s="118" t="n"/>
+      <c r="E57" s="119" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="112" t="inlineStr">
+        <is>
+          <t>☐  Validate marketing CAC after first campaign</t>
+        </is>
+      </c>
+      <c r="B58" s="118" t="n"/>
+      <c r="C58" s="118" t="n"/>
+      <c r="D58" s="118" t="n"/>
+      <c r="E58" s="119" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="112" t="inlineStr">
+        <is>
+          <t>☐  Validate insurance quote (currently estimate)</t>
+        </is>
+      </c>
+      <c r="B59" s="118" t="n"/>
+      <c r="C59" s="118" t="n"/>
+      <c r="D59" s="118" t="n"/>
+      <c r="E59" s="119" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A53:E53"/>
+    <mergeCell ref="A55:E55"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A57:E57"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A52:E52"/>
+    <mergeCell ref="A54:E54"/>
+    <mergeCell ref="A41:E41"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A56:E56"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3463,7 +4616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3734,7 +4887,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4548,7 +5701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5013,7 +6166,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5619,7 +6772,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6143,631 +7296,6 @@
       </c>
       <c r="H21" s="31">
         <f>F21-'Per-Tier Unit Economics'!I11</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G30"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Carryover Liability — GB you owe users</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Premium/Business/First/Cockpit carry unused GB. At any month you have $ liability if everyone redeems together.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>PER-TIER CARRYOVER (per user per month)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>GB Pool</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr">
-        <is>
-          <t>% Consumed</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>GB Unused</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>Carry %</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>GB Carried/mo</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>$ Liability per user</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B6" s="18">
-        <f>'README &amp; Assumptions'!D14</f>
-        <v/>
-      </c>
-      <c r="C6" s="19">
-        <f>'User Behavior'!C11</f>
-        <v/>
-      </c>
-      <c r="D6" s="20">
-        <f>B6*(1-C6)</f>
-        <v/>
-      </c>
-      <c r="E6" s="32">
-        <f>'README &amp; Assumptions'!E14</f>
-        <v/>
-      </c>
-      <c r="F6" s="20">
-        <f>D6*E6</f>
-        <v/>
-      </c>
-      <c r="G6" s="22">
-        <f>F6*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>Roster Bundle</t>
-        </is>
-      </c>
-      <c r="B7" s="18">
-        <f>'README &amp; Assumptions'!D15</f>
-        <v/>
-      </c>
-      <c r="C7" s="19">
-        <f>'User Behavior'!C11</f>
-        <v/>
-      </c>
-      <c r="D7" s="20">
-        <f>B7*(1-C7)</f>
-        <v/>
-      </c>
-      <c r="E7" s="32">
-        <f>'README &amp; Assumptions'!E15</f>
-        <v/>
-      </c>
-      <c r="F7" s="20">
-        <f>D7*E7</f>
-        <v/>
-      </c>
-      <c r="G7" s="22">
-        <f>F7*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>Premium Economy</t>
-        </is>
-      </c>
-      <c r="B8" s="18">
-        <f>'README &amp; Assumptions'!D16</f>
-        <v/>
-      </c>
-      <c r="C8" s="19">
-        <f>'User Behavior'!C11</f>
-        <v/>
-      </c>
-      <c r="D8" s="20">
-        <f>B8*(1-C8)</f>
-        <v/>
-      </c>
-      <c r="E8" s="32">
-        <f>'README &amp; Assumptions'!E16</f>
-        <v/>
-      </c>
-      <c r="F8" s="20">
-        <f>D8*E8</f>
-        <v/>
-      </c>
-      <c r="G8" s="22">
-        <f>F8*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="B9" s="18">
-        <f>'README &amp; Assumptions'!D17</f>
-        <v/>
-      </c>
-      <c r="C9" s="19">
-        <f>'User Behavior'!C11</f>
-        <v/>
-      </c>
-      <c r="D9" s="20">
-        <f>B9*(1-C9)</f>
-        <v/>
-      </c>
-      <c r="E9" s="32">
-        <f>'README &amp; Assumptions'!E17</f>
-        <v/>
-      </c>
-      <c r="F9" s="20">
-        <f>D9*E9</f>
-        <v/>
-      </c>
-      <c r="G9" s="22">
-        <f>F9*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="B10" s="18">
-        <f>'README &amp; Assumptions'!D18</f>
-        <v/>
-      </c>
-      <c r="C10" s="19">
-        <f>'User Behavior'!C11</f>
-        <v/>
-      </c>
-      <c r="D10" s="20">
-        <f>B10*(1-C10)</f>
-        <v/>
-      </c>
-      <c r="E10" s="32">
-        <f>'README &amp; Assumptions'!E18</f>
-        <v/>
-      </c>
-      <c r="F10" s="20">
-        <f>D10*E10</f>
-        <v/>
-      </c>
-      <c r="G10" s="22">
-        <f>F10*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>Cockpit</t>
-        </is>
-      </c>
-      <c r="B11" s="18">
-        <f>'README &amp; Assumptions'!D19</f>
-        <v/>
-      </c>
-      <c r="C11" s="19">
-        <f>'User Behavior'!C11</f>
-        <v/>
-      </c>
-      <c r="D11" s="20">
-        <f>B11*(1-C11)</f>
-        <v/>
-      </c>
-      <c r="E11" s="32">
-        <f>'README &amp; Assumptions'!E19</f>
-        <v/>
-      </c>
-      <c r="F11" s="20">
-        <f>D11*E11</f>
-        <v/>
-      </c>
-      <c r="G11" s="22">
-        <f>F11*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>Refuel</t>
-        </is>
-      </c>
-      <c r="B12" s="18">
-        <f>'README &amp; Assumptions'!D20</f>
-        <v/>
-      </c>
-      <c r="C12" s="19">
-        <f>'User Behavior'!C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="20">
-        <f>B12*(1-C12)</f>
-        <v/>
-      </c>
-      <c r="E12" s="32">
-        <f>'README &amp; Assumptions'!E20</f>
-        <v/>
-      </c>
-      <c r="F12" s="20">
-        <f>D12*E12</f>
-        <v/>
-      </c>
-      <c r="G12" s="22">
-        <f>F12*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>CUMULATIVE LIABILITY OVER 12 MONTHS (at base 1,000 users, default mix)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Assumes 20%/mo redemption rate. Net accrual = carried - redeemed each month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="B17" s="8" t="inlineStr">
-        <is>
-          <t>New Carryover</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>Redeemed</t>
-        </is>
-      </c>
-      <c r="D17" s="8" t="inlineStr">
-        <is>
-          <t>Net Balance</t>
-        </is>
-      </c>
-      <c r="E17" s="8" t="inlineStr">
-        <is>
-          <t>$ Value @ blended cost</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Redemption rate</t>
-        </is>
-      </c>
-      <c r="B18" s="13" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>M1</t>
-        </is>
-      </c>
-      <c r="B19" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C19" s="20">
-        <f>0</f>
-        <v/>
-      </c>
-      <c r="D19" s="33">
-        <f>B19-C19</f>
-        <v/>
-      </c>
-      <c r="E19" s="25">
-        <f>D19*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>M2</t>
-        </is>
-      </c>
-      <c r="B20" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C20" s="20">
-        <f>D19*$B$18</f>
-        <v/>
-      </c>
-      <c r="D20" s="33">
-        <f>D19+B20-C20</f>
-        <v/>
-      </c>
-      <c r="E20" s="25">
-        <f>D20*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>M3</t>
-        </is>
-      </c>
-      <c r="B21" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C21" s="20">
-        <f>D20*$B$18</f>
-        <v/>
-      </c>
-      <c r="D21" s="33">
-        <f>D20+B21-C21</f>
-        <v/>
-      </c>
-      <c r="E21" s="25">
-        <f>D21*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>M4</t>
-        </is>
-      </c>
-      <c r="B22" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C22" s="20">
-        <f>D21*$B$18</f>
-        <v/>
-      </c>
-      <c r="D22" s="33">
-        <f>D21+B22-C22</f>
-        <v/>
-      </c>
-      <c r="E22" s="25">
-        <f>D22*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>M5</t>
-        </is>
-      </c>
-      <c r="B23" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C23" s="20">
-        <f>D22*$B$18</f>
-        <v/>
-      </c>
-      <c r="D23" s="33">
-        <f>D22+B23-C23</f>
-        <v/>
-      </c>
-      <c r="E23" s="25">
-        <f>D23*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>M6</t>
-        </is>
-      </c>
-      <c r="B24" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C24" s="20">
-        <f>D23*$B$18</f>
-        <v/>
-      </c>
-      <c r="D24" s="33">
-        <f>D23+B24-C24</f>
-        <v/>
-      </c>
-      <c r="E24" s="25">
-        <f>D24*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>M7</t>
-        </is>
-      </c>
-      <c r="B25" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C25" s="20">
-        <f>D24*$B$18</f>
-        <v/>
-      </c>
-      <c r="D25" s="33">
-        <f>D24+B25-C25</f>
-        <v/>
-      </c>
-      <c r="E25" s="25">
-        <f>D25*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>M8</t>
-        </is>
-      </c>
-      <c r="B26" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C26" s="20">
-        <f>D25*$B$18</f>
-        <v/>
-      </c>
-      <c r="D26" s="33">
-        <f>D25+B26-C26</f>
-        <v/>
-      </c>
-      <c r="E26" s="25">
-        <f>D26*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>M9</t>
-        </is>
-      </c>
-      <c r="B27" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C27" s="20">
-        <f>D26*$B$18</f>
-        <v/>
-      </c>
-      <c r="D27" s="33">
-        <f>D26+B27-C27</f>
-        <v/>
-      </c>
-      <c r="E27" s="25">
-        <f>D27*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>M10</t>
-        </is>
-      </c>
-      <c r="B28" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C28" s="20">
-        <f>D27*$B$18</f>
-        <v/>
-      </c>
-      <c r="D28" s="33">
-        <f>D27+B28-C28</f>
-        <v/>
-      </c>
-      <c r="E28" s="25">
-        <f>D28*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>M11</t>
-        </is>
-      </c>
-      <c r="B29" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C29" s="20">
-        <f>D28*$B$18</f>
-        <v/>
-      </c>
-      <c r="D29" s="33">
-        <f>D28+B29-C29</f>
-        <v/>
-      </c>
-      <c r="E29" s="25">
-        <f>D29*'README &amp; Assumptions'!C29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>M12</t>
-        </is>
-      </c>
-      <c r="B30" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C30" s="20">
-        <f>D29*$B$18</f>
-        <v/>
-      </c>
-      <c r="D30" s="33">
-        <f>D29+B30-C30</f>
-        <v/>
-      </c>
-      <c r="E30" s="25">
-        <f>D30*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
     </row>
@@ -7671,6 +8199,631 @@
   <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Carryover Liability — GB you owe users</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>Premium/Business/First/Cockpit carry unused GB. At any month you have $ liability if everyone redeems together.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PER-TIER CARRYOVER (per user per month)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>GB Pool</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr">
+        <is>
+          <t>% Consumed</t>
+        </is>
+      </c>
+      <c r="D5" s="8" t="inlineStr">
+        <is>
+          <t>GB Unused</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>Carry %</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>GB Carried/mo</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
+        <is>
+          <t>$ Liability per user</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="B6" s="18">
+        <f>'README &amp; Assumptions'!D14</f>
+        <v/>
+      </c>
+      <c r="C6" s="19">
+        <f>'User Behavior'!C11</f>
+        <v/>
+      </c>
+      <c r="D6" s="20">
+        <f>B6*(1-C6)</f>
+        <v/>
+      </c>
+      <c r="E6" s="32">
+        <f>'README &amp; Assumptions'!E14</f>
+        <v/>
+      </c>
+      <c r="F6" s="20">
+        <f>D6*E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="22">
+        <f>F6*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B7" s="18">
+        <f>'README &amp; Assumptions'!D15</f>
+        <v/>
+      </c>
+      <c r="C7" s="19">
+        <f>'User Behavior'!C11</f>
+        <v/>
+      </c>
+      <c r="D7" s="20">
+        <f>B7*(1-C7)</f>
+        <v/>
+      </c>
+      <c r="E7" s="32">
+        <f>'README &amp; Assumptions'!E15</f>
+        <v/>
+      </c>
+      <c r="F7" s="20">
+        <f>D7*E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="22">
+        <f>F7*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B8" s="18">
+        <f>'README &amp; Assumptions'!D16</f>
+        <v/>
+      </c>
+      <c r="C8" s="19">
+        <f>'User Behavior'!C11</f>
+        <v/>
+      </c>
+      <c r="D8" s="20">
+        <f>B8*(1-C8)</f>
+        <v/>
+      </c>
+      <c r="E8" s="32">
+        <f>'README &amp; Assumptions'!E16</f>
+        <v/>
+      </c>
+      <c r="F8" s="20">
+        <f>D8*E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="22">
+        <f>F8*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B9" s="18">
+        <f>'README &amp; Assumptions'!D17</f>
+        <v/>
+      </c>
+      <c r="C9" s="19">
+        <f>'User Behavior'!C11</f>
+        <v/>
+      </c>
+      <c r="D9" s="20">
+        <f>B9*(1-C9)</f>
+        <v/>
+      </c>
+      <c r="E9" s="32">
+        <f>'README &amp; Assumptions'!E17</f>
+        <v/>
+      </c>
+      <c r="F9" s="20">
+        <f>D9*E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="22">
+        <f>F9*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B10" s="18">
+        <f>'README &amp; Assumptions'!D18</f>
+        <v/>
+      </c>
+      <c r="C10" s="19">
+        <f>'User Behavior'!C11</f>
+        <v/>
+      </c>
+      <c r="D10" s="20">
+        <f>B10*(1-C10)</f>
+        <v/>
+      </c>
+      <c r="E10" s="32">
+        <f>'README &amp; Assumptions'!E18</f>
+        <v/>
+      </c>
+      <c r="F10" s="20">
+        <f>D10*E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="22">
+        <f>F10*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B11" s="18">
+        <f>'README &amp; Assumptions'!D19</f>
+        <v/>
+      </c>
+      <c r="C11" s="19">
+        <f>'User Behavior'!C11</f>
+        <v/>
+      </c>
+      <c r="D11" s="20">
+        <f>B11*(1-C11)</f>
+        <v/>
+      </c>
+      <c r="E11" s="32">
+        <f>'README &amp; Assumptions'!E19</f>
+        <v/>
+      </c>
+      <c r="F11" s="20">
+        <f>D11*E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="22">
+        <f>F11*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>Refuel</t>
+        </is>
+      </c>
+      <c r="B12" s="18">
+        <f>'README &amp; Assumptions'!D20</f>
+        <v/>
+      </c>
+      <c r="C12" s="19">
+        <f>'User Behavior'!C11</f>
+        <v/>
+      </c>
+      <c r="D12" s="20">
+        <f>B12*(1-C12)</f>
+        <v/>
+      </c>
+      <c r="E12" s="32">
+        <f>'README &amp; Assumptions'!E20</f>
+        <v/>
+      </c>
+      <c r="F12" s="20">
+        <f>D12*E12</f>
+        <v/>
+      </c>
+      <c r="G12" s="22">
+        <f>F12*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>CUMULATIVE LIABILITY OVER 12 MONTHS (at base 1,000 users, default mix)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Assumes 20%/mo redemption rate. Net accrual = carried - redeemed each month.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Month</t>
+        </is>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>New Carryover</t>
+        </is>
+      </c>
+      <c r="C17" s="8" t="inlineStr">
+        <is>
+          <t>Redeemed</t>
+        </is>
+      </c>
+      <c r="D17" s="8" t="inlineStr">
+        <is>
+          <t>Net Balance</t>
+        </is>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>$ Value @ blended cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>Redemption rate</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>M1</t>
+        </is>
+      </c>
+      <c r="B19" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C19" s="20">
+        <f>0</f>
+        <v/>
+      </c>
+      <c r="D19" s="33">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+      <c r="E19" s="25">
+        <f>D19*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>M2</t>
+        </is>
+      </c>
+      <c r="B20" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C20" s="20">
+        <f>D19*$B$18</f>
+        <v/>
+      </c>
+      <c r="D20" s="33">
+        <f>D19+B20-C20</f>
+        <v/>
+      </c>
+      <c r="E20" s="25">
+        <f>D20*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="9" t="inlineStr">
+        <is>
+          <t>M3</t>
+        </is>
+      </c>
+      <c r="B21" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C21" s="20">
+        <f>D20*$B$18</f>
+        <v/>
+      </c>
+      <c r="D21" s="33">
+        <f>D20+B21-C21</f>
+        <v/>
+      </c>
+      <c r="E21" s="25">
+        <f>D21*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>M4</t>
+        </is>
+      </c>
+      <c r="B22" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C22" s="20">
+        <f>D21*$B$18</f>
+        <v/>
+      </c>
+      <c r="D22" s="33">
+        <f>D21+B22-C22</f>
+        <v/>
+      </c>
+      <c r="E22" s="25">
+        <f>D22*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>M5</t>
+        </is>
+      </c>
+      <c r="B23" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C23" s="20">
+        <f>D22*$B$18</f>
+        <v/>
+      </c>
+      <c r="D23" s="33">
+        <f>D22+B23-C23</f>
+        <v/>
+      </c>
+      <c r="E23" s="25">
+        <f>D23*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>M6</t>
+        </is>
+      </c>
+      <c r="B24" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C24" s="20">
+        <f>D23*$B$18</f>
+        <v/>
+      </c>
+      <c r="D24" s="33">
+        <f>D23+B24-C24</f>
+        <v/>
+      </c>
+      <c r="E24" s="25">
+        <f>D24*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>M7</t>
+        </is>
+      </c>
+      <c r="B25" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C25" s="20">
+        <f>D24*$B$18</f>
+        <v/>
+      </c>
+      <c r="D25" s="33">
+        <f>D24+B25-C25</f>
+        <v/>
+      </c>
+      <c r="E25" s="25">
+        <f>D25*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>M8</t>
+        </is>
+      </c>
+      <c r="B26" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C26" s="20">
+        <f>D25*$B$18</f>
+        <v/>
+      </c>
+      <c r="D26" s="33">
+        <f>D25+B26-C26</f>
+        <v/>
+      </c>
+      <c r="E26" s="25">
+        <f>D26*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>M9</t>
+        </is>
+      </c>
+      <c r="B27" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C27" s="20">
+        <f>D26*$B$18</f>
+        <v/>
+      </c>
+      <c r="D27" s="33">
+        <f>D26+B27-C27</f>
+        <v/>
+      </c>
+      <c r="E27" s="25">
+        <f>D27*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>M10</t>
+        </is>
+      </c>
+      <c r="B28" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C28" s="20">
+        <f>D27*$B$18</f>
+        <v/>
+      </c>
+      <c r="D28" s="33">
+        <f>D27+B28-C28</f>
+        <v/>
+      </c>
+      <c r="E28" s="25">
+        <f>D28*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>M11</t>
+        </is>
+      </c>
+      <c r="B29" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C29" s="20">
+        <f>D28*$B$18</f>
+        <v/>
+      </c>
+      <c r="D29" s="33">
+        <f>D28+B29-C29</f>
+        <v/>
+      </c>
+      <c r="E29" s="25">
+        <f>D29*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>M12</t>
+        </is>
+      </c>
+      <c r="B30" s="20">
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <v/>
+      </c>
+      <c r="C30" s="20">
+        <f>D29*$B$18</f>
+        <v/>
+      </c>
+      <c r="D30" s="33">
+        <f>D29+B30-C30</f>
+        <v/>
+      </c>
+      <c r="E30" s="25">
+        <f>D30*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G30"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
@@ -8239,7 +9392,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9477,15 +10630,15 @@
     <mergeCell ref="B19:M19"/>
     <mergeCell ref="B20:M20"/>
     <mergeCell ref="B21:M21"/>
+    <mergeCell ref="A16:M16"/>
     <mergeCell ref="B23:M23"/>
     <mergeCell ref="A40:M40"/>
     <mergeCell ref="B22:M22"/>
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="B26:M26"/>
     <mergeCell ref="B27:M27"/>
+    <mergeCell ref="A43:M43"/>
     <mergeCell ref="A41:M41"/>
-    <mergeCell ref="A43:M43"/>
-    <mergeCell ref="A16:M16"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A42:M42"/>
   </mergeCells>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -1229,6 +1229,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -1239,7 +1240,7 @@
     <row r="25">
       <c r="A25" s="92" t="inlineStr">
         <is>
-          <t>⚠ COSTS are real Samurai data. MIX % (60/25/15) is placeholder — awaiting Akito crew roster validation.</t>
+          <t>⚠ MIX UPDATED 2026-06-01: 75/20/5 (Emirates-crew realistic) replaces 60/25/15 placeholder. Blended drops $2.13 → $1.34/GB. Akito to validate via crew roster samples.</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1279,7 @@
         <v>1.4</v>
       </c>
       <c r="D27" s="13" t="n">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="28">
@@ -1296,7 +1297,7 @@
         <v>8.5</v>
       </c>
       <c r="D28" s="13" t="n">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="29">
@@ -1314,7 +1315,7 @@
         <v>5.8</v>
       </c>
       <c r="D29" s="13" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="31">
@@ -4347,8 +4348,8 @@
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A16:E16"/>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -1229,7 +1229,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
@@ -1255,8 +1254,10 @@
           <t>Description</t>
         </is>
       </c>
-      <c r="C26" s="8" t="n">
-        <v>0.85</v>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>$/GB</t>
+        </is>
       </c>
       <c r="D26" s="8" t="inlineStr">
         <is>
@@ -1276,7 +1277,7 @@
         </is>
       </c>
       <c r="C27" s="10" t="n">
-        <v>1.4</v>
+        <v>0.85</v>
       </c>
       <c r="D27" s="13" t="n">
         <v>0.75</v>
@@ -1294,7 +1295,7 @@
         </is>
       </c>
       <c r="C28" s="10" t="n">
-        <v>8.5</v>
+        <v>1.4</v>
       </c>
       <c r="D28" s="13" t="n">
         <v>0.2</v>
@@ -1312,7 +1313,7 @@
         </is>
       </c>
       <c r="C29" s="10" t="n">
-        <v>5.8</v>
+        <v>8.5</v>
       </c>
       <c r="D29" s="13" t="n">
         <v>0.05</v>
@@ -1325,7 +1326,7 @@
         </is>
       </c>
       <c r="C31" s="11">
-        <f>SUMPRODUCT(C25:C27,D25:D27)</f>
+        <f>SUMPRODUCT(C27:C29,D27:D29)</f>
         <v/>
       </c>
     </row>
@@ -1859,7 +1860,7 @@
         </is>
       </c>
       <c r="B20" s="54" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="21">
@@ -1874,7 +1875,7 @@
       </c>
       <c r="C21" s="39" t="inlineStr">
         <is>
-          <t>13.2 × $1.20</t>
+          <t>13.2 × $1.34</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2436,7 @@
         </is>
       </c>
       <c r="B27" s="54" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="28">
@@ -3028,15 +3029,15 @@
     <row r="17">
       <c r="A17" s="48" t="inlineStr">
         <is>
-          <t>Wholesale COGS (1 GB × $1.20 blended)</t>
+          <t>Wholesale COGS (1 GB × $1.34 blended)</t>
         </is>
       </c>
       <c r="B17" s="54" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="C17" s="39" t="inlineStr">
         <is>
-          <t>Blended Samurai rate</t>
+          <t>Blended rate (75/20/5 mix, updated 2026-06-01)</t>
         </is>
       </c>
     </row>
@@ -10545,7 +10546,7 @@
       </c>
       <c r="B34" s="90" t="inlineStr">
         <is>
-          <t>Real Samurai rate sheet, weighted by 60/25/15 country mix</t>
+          <t>Real wholesale rate sheet, weighted by 75/20/5 country mix (updated 2026-06-01)</t>
         </is>
       </c>
       <c r="C34" s="90" t="inlineStr">
@@ -10605,7 +10606,7 @@
     <row r="41">
       <c r="A41" s="39" t="inlineStr">
         <is>
-          <t>• Wholesale country mix (60/25/15) — Akito to validate via 5-10 sample crew rosters</t>
+          <t>• Wholesale country mix updated to 75/20/5 on 2026-06-01 (Emirates-realistic). Validate via 5-10 sample crew rosters.</t>
         </is>
       </c>
     </row>
@@ -12237,11 +12238,11 @@
         </is>
       </c>
       <c r="B59" s="51" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="C59" s="39" t="inlineStr">
         <is>
-          <t>70/20/10 mix across A/B/C zones</t>
+          <t>75/20/5 Emirates-realistic mix (updated 2026-06-01)</t>
         </is>
       </c>
     </row>
@@ -13671,7 +13672,7 @@
         </is>
       </c>
       <c r="B20" s="54" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
@@ -14289,7 +14290,7 @@
     <row r="70">
       <c r="A70" s="39" t="inlineStr">
         <is>
-          <t>• $1.20 blended wholesale: Samurai global-pool estimate; will sharpen after first month of real data.</t>
+          <t>• $1.34 blended wholesale: weighted across 75/20/5 Tier-A/B/C mix (updated 2026-06-01, was $1.20 at old 60/25/15).</t>
         </is>
       </c>
     </row>
@@ -14573,11 +14574,11 @@
         </is>
       </c>
       <c r="B20" s="54" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
-          <t>Same blended rate</t>
+          <t>Same blended rate (75/20/5 mix, updated 2026-06-01)</t>
         </is>
       </c>
     </row>
@@ -15393,11 +15394,11 @@
         </is>
       </c>
       <c r="B19" s="54" t="n">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="C19" s="39" t="inlineStr">
         <is>
-          <t>Same blended rate</t>
+          <t>Same blended rate (75/20/5 mix, updated 2026-06-01)</t>
         </is>
       </c>
     </row>
@@ -15413,7 +15414,7 @@
       </c>
       <c r="C20" s="39" t="inlineStr">
         <is>
-          <t>13.6 × $1.20</t>
+          <t>13.6 × $1.34</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -1870,7 +1870,7 @@
         </is>
       </c>
       <c r="B21" s="54">
-        <f>B14*B15</f>
+        <f>B19*B20</f>
         <v/>
       </c>
       <c r="C21" s="39" t="inlineStr">
@@ -1886,7 +1886,7 @@
         </is>
       </c>
       <c r="B22" s="82">
-        <f>(40-B14)*1.0</f>
+        <f>(40-B19)*1.0</f>
         <v/>
       </c>
       <c r="C22" s="39" t="inlineStr">
@@ -1917,7 +1917,7 @@
         </is>
       </c>
       <c r="B24" s="54">
-        <f>B18*5.99</f>
+        <f>B23*4.99</f>
         <v/>
       </c>
     </row>
@@ -1928,7 +1928,7 @@
         </is>
       </c>
       <c r="B25" s="54">
-        <f>B18*B15</f>
+        <f>B23*B20</f>
         <v/>
       </c>
     </row>
@@ -1938,8 +1938,9 @@
           <t>TOTAL profit per user / mo</t>
         </is>
       </c>
-      <c r="B26" s="83" t="n">
-        <v>35.11</v>
+      <c r="B26" s="83">
+        <f>B18-B21+B24-B25</f>
+        <v/>
       </c>
     </row>
     <row r="27">
@@ -1948,8 +1949,9 @@
           <t>TOTAL margin</t>
         </is>
       </c>
-      <c r="B27" s="84" t="n">
-        <v>0.6860000000000001</v>
+      <c r="B27" s="84">
+        <f>B26/(B18+B24)</f>
+        <v/>
       </c>
     </row>
     <row r="30">
@@ -1989,10 +1991,10 @@
         <v>20</v>
       </c>
       <c r="C32" s="86" t="n">
-        <v>702.2</v>
+        <v>660.6400000000001</v>
       </c>
       <c r="D32" s="86" t="n">
-        <v>8426.400000000001</v>
+        <v>7927.680000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2003,10 +2005,10 @@
         <v>100</v>
       </c>
       <c r="C33" s="86" t="n">
-        <v>3511</v>
+        <v>3303.2</v>
       </c>
       <c r="D33" s="86" t="n">
-        <v>42132</v>
+        <v>39638.4</v>
       </c>
     </row>
     <row r="34">
@@ -2017,10 +2019,10 @@
         <v>200</v>
       </c>
       <c r="C34" s="86" t="n">
-        <v>7022</v>
+        <v>6606.400000000001</v>
       </c>
       <c r="D34" s="86" t="n">
-        <v>84264</v>
+        <v>79276.8</v>
       </c>
     </row>
     <row r="35">
@@ -2031,10 +2033,10 @@
         <v>1000</v>
       </c>
       <c r="C35" s="86" t="n">
-        <v>35110</v>
+        <v>33032</v>
       </c>
       <c r="D35" s="86" t="n">
-        <v>421320</v>
+        <v>396384</v>
       </c>
     </row>
     <row r="36">
@@ -2045,10 +2047,10 @@
         <v>2000</v>
       </c>
       <c r="C36" s="87" t="n">
-        <v>70220</v>
+        <v>66064</v>
       </c>
       <c r="D36" s="87" t="n">
-        <v>842640</v>
+        <v>792768</v>
       </c>
     </row>
     <row r="38">
@@ -15409,7 +15411,7 @@
         </is>
       </c>
       <c r="B20" s="54">
-        <f>B14*B15</f>
+        <f>B18*B19</f>
         <v/>
       </c>
       <c r="C20" s="39" t="inlineStr">
@@ -15425,7 +15427,7 @@
         </is>
       </c>
       <c r="B21" s="82">
-        <f>(25-B14)*1.0</f>
+        <f>(25-B18)*1.0</f>
         <v/>
       </c>
       <c r="C21" s="39" t="inlineStr">
@@ -15456,7 +15458,7 @@
         </is>
       </c>
       <c r="B23" s="54">
-        <f>B18*5.99</f>
+        <f>B22*4.99</f>
         <v/>
       </c>
     </row>
@@ -15467,7 +15469,7 @@
         </is>
       </c>
       <c r="B24" s="54">
-        <f>B18*B15</f>
+        <f>B22*B19</f>
         <v/>
       </c>
     </row>
@@ -15477,8 +15479,9 @@
           <t>TOTAL profit per user / mo</t>
         </is>
       </c>
-      <c r="B25" s="83" t="n">
-        <v>25.59</v>
+      <c r="B25" s="83">
+        <f>B17-B20+B23-B24</f>
+        <v/>
       </c>
       <c r="C25" s="39" t="inlineStr">
         <is>
@@ -15492,8 +15495,9 @@
           <t>TOTAL margin</t>
         </is>
       </c>
-      <c r="B26" s="84" t="n">
-        <v>0.605</v>
+      <c r="B26" s="84">
+        <f>B25/(B17+B23)</f>
+        <v/>
       </c>
     </row>
     <row r="29">
@@ -15533,10 +15537,10 @@
         <v>30</v>
       </c>
       <c r="C31" s="86" t="n">
-        <v>767.7</v>
+        <v>696.78</v>
       </c>
       <c r="D31" s="86" t="n">
-        <v>9212.400000000001</v>
+        <v>8361.360000000001</v>
       </c>
     </row>
     <row r="32">
@@ -15547,10 +15551,10 @@
         <v>150</v>
       </c>
       <c r="C32" s="86" t="n">
-        <v>3838.5</v>
+        <v>3483.9</v>
       </c>
       <c r="D32" s="86" t="n">
-        <v>46062</v>
+        <v>41806.8</v>
       </c>
     </row>
     <row r="33">
@@ -15561,10 +15565,10 @@
         <v>300</v>
       </c>
       <c r="C33" s="86" t="n">
-        <v>7677</v>
+        <v>6967.799999999999</v>
       </c>
       <c r="D33" s="86" t="n">
-        <v>92124</v>
+        <v>83613.59999999999</v>
       </c>
     </row>
     <row r="34">
@@ -15575,10 +15579,10 @@
         <v>1500</v>
       </c>
       <c r="C34" s="86" t="n">
-        <v>38385</v>
+        <v>34839</v>
       </c>
       <c r="D34" s="86" t="n">
-        <v>460620</v>
+        <v>418068</v>
       </c>
     </row>
     <row r="35">
@@ -15589,10 +15593,10 @@
         <v>3000</v>
       </c>
       <c r="C35" s="87" t="n">
-        <v>76770</v>
+        <v>69678</v>
       </c>
       <c r="D35" s="87" t="n">
-        <v>921240</v>
+        <v>836136</v>
       </c>
     </row>
     <row r="37">

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -56,7 +56,7 @@
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0&quot; /mo&quot;"/>
     <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00&quot; /user/mo&quot;"/>
   </numFmts>
-  <fonts count="34">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -244,6 +244,12 @@
       <color rgb="006B6B6B"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <color rgb="00D71921"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -378,7 +384,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="121">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -527,6 +533,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9869,7 +9876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9908,741 +9915,897 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="94" t="inlineStr">
+        <is>
+          <t>🗺 TAB 3 BITES MAP — what each part of this tab covers</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="94" t="inlineStr">
-        <is>
-          <t>1. PER-TIER UNIT ECONOMICS — single subscriber per month</t>
+      <c r="A5" s="41" t="inlineStr">
+        <is>
+          <t>Bite #</t>
+        </is>
+      </c>
+      <c r="B5" s="41" t="inlineStr">
+        <is>
+          <t>Topic</t>
+        </is>
+      </c>
+      <c r="C5" s="41" t="inlineStr">
+        <is>
+          <t>Where to look</t>
+        </is>
+      </c>
+      <c r="D5" s="41" t="inlineStr">
+        <is>
+          <t>Key takeaway</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="120" t="inlineStr">
+        <is>
+          <t>Bite 1</t>
+        </is>
+      </c>
+      <c r="B6" s="90" t="inlineStr">
+        <is>
+          <t>What Tab 3 does</t>
+        </is>
+      </c>
+      <c r="C6" s="39" t="inlineStr">
+        <is>
+          <t>Read rows 1-3 (title + purpose)</t>
+        </is>
+      </c>
+      <c r="D6" s="90" t="inlineStr">
+        <is>
+          <t>Per-USER economics — not total revenue</t>
         </is>
       </c>
     </row>
     <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="47" t="inlineStr">
+      <c r="A7" s="120" t="inlineStr">
+        <is>
+          <t>Bite 2</t>
+        </is>
+      </c>
+      <c r="B7" s="90" t="inlineStr">
+        <is>
+          <t>The 13 columns explained</t>
+        </is>
+      </c>
+      <c r="C7" s="39" t="inlineStr">
+        <is>
+          <t>Columns A-M, headers in row 17</t>
+        </is>
+      </c>
+      <c r="D7" s="90" t="inlineStr">
+        <is>
+          <t>Group 1 = inputs, Group 2 = eSIM math, Group 3 = profit math</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="120" t="inlineStr">
+        <is>
+          <t>Bite 3</t>
+        </is>
+      </c>
+      <c r="B8" s="90" t="inlineStr">
+        <is>
+          <t>Per-tier profit numbers</t>
+        </is>
+      </c>
+      <c r="C8" s="39" t="inlineStr">
+        <is>
+          <t>Data rows 18-24 (Economy → Cockpit)</t>
+        </is>
+      </c>
+      <c r="D8" s="90" t="inlineStr">
+        <is>
+          <t>Business 71% margin / First Suite $33 highest absolute profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="120" t="inlineStr">
+        <is>
+          <t>Bite 4</t>
+        </is>
+      </c>
+      <c r="B9" s="90" t="inlineStr">
+        <is>
+          <t>Strategic insights</t>
+        </is>
+      </c>
+      <c r="C9" s="39" t="inlineStr">
+        <is>
+          <t>Read the whole data table 18-24</t>
+        </is>
+      </c>
+      <c r="D9" s="90" t="inlineStr">
+        <is>
+          <t>First Suite is hero / Business is RECOMMENDED / First lowest margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="120" t="inlineStr">
+        <is>
+          <t>Bite 5</t>
+        </is>
+      </c>
+      <c r="B10" s="90" t="inlineStr">
+        <is>
+          <t>How Tab 3 feeds downstream</t>
+        </is>
+      </c>
+      <c r="C10" s="39" t="inlineStr">
+        <is>
+          <t>See "Sources" section + cross-tab references</t>
+        </is>
+      </c>
+      <c r="D10" s="90" t="inlineStr">
+        <is>
+          <t>Per-user × user count → Tab 5/6/8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="94" t="inlineStr">
+        <is>
+          <t>1. PER-TIER UNIT ECONOMICS (Bites 2-4) — single subscriber per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="47" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B7" s="47" t="inlineStr">
+      <c r="B17" s="47" t="inlineStr">
         <is>
           <t>Monthly Revenue</t>
         </is>
       </c>
-      <c r="C7" s="47" t="inlineStr">
+      <c r="C17" s="47" t="inlineStr">
         <is>
           <t>GB Consumed</t>
         </is>
       </c>
-      <c r="D7" s="47" t="inlineStr">
+      <c r="D17" s="47" t="inlineStr">
         <is>
           <t>Wholesale $/GB</t>
         </is>
       </c>
-      <c r="E7" s="47" t="inlineStr">
+      <c r="E17" s="47" t="inlineStr">
         <is>
           <t>eSIM COGS</t>
         </is>
       </c>
-      <c r="F7" s="47" t="inlineStr">
+      <c r="F17" s="47" t="inlineStr">
         <is>
           <t>Refuel Attach %</t>
         </is>
       </c>
-      <c r="G7" s="47" t="inlineStr">
+      <c r="G17" s="47" t="inlineStr">
         <is>
           <t>Refuel Revenue</t>
         </is>
       </c>
-      <c r="H7" s="47" t="inlineStr">
+      <c r="H17" s="47" t="inlineStr">
         <is>
           <t>Refuel COGS</t>
         </is>
       </c>
-      <c r="I7" s="47" t="inlineStr">
+      <c r="I17" s="47" t="inlineStr">
         <is>
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="J7" s="47" t="inlineStr">
+      <c r="J17" s="47" t="inlineStr">
         <is>
           <t>Total COGS</t>
         </is>
       </c>
-      <c r="K7" s="47" t="inlineStr">
+      <c r="K17" s="47" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="L7" s="47" t="inlineStr">
+      <c r="L17" s="47" t="inlineStr">
         <is>
           <t>Gross Margin %</t>
         </is>
       </c>
-      <c r="M7" s="47" t="inlineStr">
+      <c r="M17" s="47" t="inlineStr">
         <is>
           <t>Net Margin (after OPEX)</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="90" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="90" t="inlineStr">
         <is>
           <t>Economy (PAYG)</t>
         </is>
       </c>
-      <c r="B8" s="46">
+      <c r="B18" s="46">
         <f>'README &amp; Assumptions'!B14</f>
         <v/>
       </c>
-      <c r="C8" s="49">
+      <c r="C18" s="49">
         <f>'User Behavior'!D21</f>
         <v/>
       </c>
-      <c r="D8" s="46">
+      <c r="D18" s="46">
         <f>'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
-      <c r="E8" s="54">
+      <c r="E18" s="54">
         <f>C8*D8</f>
         <v/>
       </c>
-      <c r="F8" s="81" t="n">
+      <c r="F18" s="81" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="54">
+      <c r="G18" s="54">
         <f>F8*'README &amp; Assumptions'!B21</f>
         <v/>
       </c>
-      <c r="H8" s="54">
+      <c r="H18" s="54">
         <f>F8*1*D8</f>
         <v/>
       </c>
-      <c r="I8" s="54">
+      <c r="I18" s="54">
         <f>B8+G8</f>
         <v/>
       </c>
-      <c r="J8" s="54">
+      <c r="J18" s="54">
         <f>E8+H8</f>
         <v/>
       </c>
-      <c r="K8" s="54">
+      <c r="K18" s="54">
         <f>I8-J8</f>
         <v/>
       </c>
-      <c r="L8" s="26">
+      <c r="L18" s="26">
         <f>IFERROR(K8/I8,0)</f>
         <v/>
       </c>
-      <c r="M8" s="26">
+      <c r="M18" s="26">
         <f>IFERROR((K8-'README &amp; Assumptions'!B53)/I8,0)</f>
         <v/>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="90" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="90" t="inlineStr">
         <is>
           <t>Roster Bundle</t>
         </is>
       </c>
-      <c r="B9" s="46">
+      <c r="B19" s="46">
         <f>'README &amp; Assumptions'!B15</f>
         <v/>
       </c>
-      <c r="C9" s="49">
+      <c r="C19" s="49">
         <f>'User Behavior'!D22</f>
         <v/>
       </c>
-      <c r="D9" s="46">
+      <c r="D19" s="46">
         <f>'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
-      <c r="E9" s="54">
+      <c r="E19" s="54">
         <f>C9*D9</f>
         <v/>
       </c>
-      <c r="F9" s="81" t="n">
+      <c r="F19" s="81" t="n">
         <v>0.1</v>
       </c>
-      <c r="G9" s="54">
+      <c r="G19" s="54">
         <f>F9*'README &amp; Assumptions'!B21</f>
         <v/>
       </c>
-      <c r="H9" s="54">
+      <c r="H19" s="54">
         <f>F9*1*D9</f>
         <v/>
       </c>
-      <c r="I9" s="54">
+      <c r="I19" s="54">
         <f>B9+G9</f>
         <v/>
       </c>
-      <c r="J9" s="54">
+      <c r="J19" s="54">
         <f>E9+H9</f>
         <v/>
       </c>
-      <c r="K9" s="54">
+      <c r="K19" s="54">
         <f>I9-J9</f>
         <v/>
       </c>
-      <c r="L9" s="26">
+      <c r="L19" s="26">
         <f>IFERROR(K9/I9,0)</f>
         <v/>
       </c>
-      <c r="M9" s="26">
+      <c r="M19" s="26">
         <f>IFERROR((K9-'README &amp; Assumptions'!B53)/I9,0)</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="90" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="90" t="inlineStr">
         <is>
           <t>Premium Economy</t>
         </is>
       </c>
-      <c r="B10" s="46">
+      <c r="B20" s="46">
         <f>'README &amp; Assumptions'!B16</f>
         <v/>
       </c>
-      <c r="C10" s="49">
+      <c r="C20" s="49">
         <f>'User Behavior'!D23</f>
         <v/>
       </c>
-      <c r="D10" s="46">
+      <c r="D20" s="46">
         <f>'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
-      <c r="E10" s="54">
+      <c r="E20" s="54">
         <f>C10*D10</f>
         <v/>
       </c>
-      <c r="F10" s="81" t="n">
+      <c r="F20" s="81" t="n">
         <v>0.2</v>
       </c>
-      <c r="G10" s="54">
+      <c r="G20" s="54">
         <f>F10*'README &amp; Assumptions'!B21</f>
         <v/>
       </c>
-      <c r="H10" s="54">
+      <c r="H20" s="54">
         <f>F10*1*D10</f>
         <v/>
       </c>
-      <c r="I10" s="54">
+      <c r="I20" s="54">
         <f>B10+G10</f>
         <v/>
       </c>
-      <c r="J10" s="54">
+      <c r="J20" s="54">
         <f>E10+H10</f>
         <v/>
       </c>
-      <c r="K10" s="54">
+      <c r="K20" s="54">
         <f>I10-J10</f>
         <v/>
       </c>
-      <c r="L10" s="26">
+      <c r="L20" s="26">
         <f>IFERROR(K10/I10,0)</f>
         <v/>
       </c>
-      <c r="M10" s="26">
+      <c r="M20" s="26">
         <f>IFERROR((K10-'README &amp; Assumptions'!B53)/I10,0)</f>
         <v/>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="93" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="93" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="B11" s="101">
+      <c r="B21" s="101">
         <f>'README &amp; Assumptions'!B17</f>
         <v/>
       </c>
-      <c r="C11" s="102">
+      <c r="C21" s="102">
         <f>'User Behavior'!D24</f>
         <v/>
       </c>
-      <c r="D11" s="101">
+      <c r="D21" s="101">
         <f>'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
-      <c r="E11" s="59">
+      <c r="E21" s="59">
         <f>C11*D11</f>
         <v/>
       </c>
-      <c r="F11" s="103" t="n">
+      <c r="F21" s="103" t="n">
         <v>0.25</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G21" s="59">
         <f>F11*'README &amp; Assumptions'!B21</f>
         <v/>
       </c>
-      <c r="H11" s="59">
+      <c r="H21" s="59">
         <f>F11*1*D11</f>
         <v/>
       </c>
-      <c r="I11" s="59">
+      <c r="I21" s="59">
         <f>B11+G11</f>
         <v/>
       </c>
-      <c r="J11" s="59">
+      <c r="J21" s="59">
         <f>E11+H11</f>
         <v/>
       </c>
-      <c r="K11" s="59">
+      <c r="K21" s="59">
         <f>I11-J11</f>
         <v/>
       </c>
-      <c r="L11" s="104">
+      <c r="L21" s="104">
         <f>IFERROR(K11/I11,0)</f>
         <v/>
       </c>
-      <c r="M11" s="104">
+      <c r="M21" s="104">
         <f>IFERROR((K11-'README &amp; Assumptions'!B53)/I11,0)</f>
         <v/>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="90" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="90" t="inlineStr">
         <is>
           <t>First</t>
         </is>
       </c>
-      <c r="B12" s="46">
+      <c r="B22" s="46">
         <f>'README &amp; Assumptions'!B18</f>
         <v/>
       </c>
-      <c r="C12" s="49">
+      <c r="C22" s="49">
         <f>'User Behavior'!D25</f>
         <v/>
       </c>
-      <c r="D12" s="46">
+      <c r="D22" s="46">
         <f>'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
-      <c r="E12" s="54">
+      <c r="E22" s="54">
         <f>C12*D12</f>
         <v/>
       </c>
-      <c r="F12" s="81" t="n">
+      <c r="F22" s="81" t="n">
         <v>0.4</v>
       </c>
-      <c r="G12" s="54">
+      <c r="G22" s="54">
         <f>F12*'README &amp; Assumptions'!B21</f>
         <v/>
       </c>
-      <c r="H12" s="54">
+      <c r="H22" s="54">
         <f>F12*1*D12</f>
         <v/>
       </c>
-      <c r="I12" s="54">
+      <c r="I22" s="54">
         <f>B12+G12</f>
         <v/>
       </c>
-      <c r="J12" s="54">
+      <c r="J22" s="54">
         <f>E12+H12</f>
         <v/>
       </c>
-      <c r="K12" s="54">
+      <c r="K22" s="54">
         <f>I12-J12</f>
         <v/>
       </c>
-      <c r="L12" s="26">
+      <c r="L22" s="26">
         <f>IFERROR(K12/I12,0)</f>
         <v/>
       </c>
-      <c r="M12" s="26">
+      <c r="M22" s="26">
         <f>IFERROR((K12-'README &amp; Assumptions'!B53)/I12,0)</f>
         <v/>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="90" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="90" t="inlineStr">
         <is>
           <t>First Suite</t>
         </is>
       </c>
-      <c r="B13" s="46">
+      <c r="B23" s="46">
         <f>'README &amp; Assumptions'!B19</f>
         <v/>
       </c>
-      <c r="C13" s="49">
+      <c r="C23" s="49">
         <f>'User Behavior'!D26</f>
         <v/>
       </c>
-      <c r="D13" s="46">
+      <c r="D23" s="46">
         <f>'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
-      <c r="E13" s="54">
+      <c r="E23" s="54">
         <f>C13*D13</f>
         <v/>
       </c>
-      <c r="F13" s="81" t="n">
+      <c r="F23" s="81" t="n">
         <v>0.2</v>
       </c>
-      <c r="G13" s="54">
+      <c r="G23" s="54">
         <f>F13*'README &amp; Assumptions'!B21</f>
         <v/>
       </c>
-      <c r="H13" s="54">
+      <c r="H23" s="54">
         <f>F13*1*D13</f>
         <v/>
       </c>
-      <c r="I13" s="54">
+      <c r="I23" s="54">
         <f>B13+G13</f>
         <v/>
       </c>
-      <c r="J13" s="54">
+      <c r="J23" s="54">
         <f>E13+H13</f>
         <v/>
       </c>
-      <c r="K13" s="54">
+      <c r="K23" s="54">
         <f>I13-J13</f>
         <v/>
       </c>
-      <c r="L13" s="26">
+      <c r="L23" s="26">
         <f>IFERROR(K13/I13,0)</f>
         <v/>
       </c>
-      <c r="M13" s="26">
+      <c r="M23" s="26">
         <f>IFERROR((K13-'README &amp; Assumptions'!B53)/I13,0)</f>
         <v/>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="90" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="90" t="inlineStr">
         <is>
           <t>Cockpit (annual)</t>
         </is>
       </c>
-      <c r="B14" s="46">
+      <c r="B24" s="46">
         <f>'README &amp; Assumptions'!B20</f>
         <v/>
       </c>
-      <c r="C14" s="49">
+      <c r="C24" s="49">
         <f>'User Behavior'!D27</f>
         <v/>
       </c>
-      <c r="D14" s="46">
+      <c r="D24" s="46">
         <f>'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
-      <c r="E14" s="54">
+      <c r="E24" s="54">
         <f>C14*D14</f>
         <v/>
       </c>
-      <c r="F14" s="81" t="n">
+      <c r="F24" s="81" t="n">
         <v>0.15</v>
       </c>
-      <c r="G14" s="54">
+      <c r="G24" s="54">
         <f>F14*'README &amp; Assumptions'!B21</f>
         <v/>
       </c>
-      <c r="H14" s="54">
+      <c r="H24" s="54">
         <f>F14*1*D14</f>
         <v/>
       </c>
-      <c r="I14" s="54">
+      <c r="I24" s="54">
         <f>B14+G14</f>
         <v/>
       </c>
-      <c r="J14" s="54">
+      <c r="J24" s="54">
         <f>E14+H14</f>
         <v/>
       </c>
-      <c r="K14" s="54">
+      <c r="K24" s="54">
         <f>I14-J14</f>
         <v/>
       </c>
-      <c r="L14" s="26">
+      <c r="L24" s="26">
         <f>IFERROR(K14/I14,0)</f>
         <v/>
       </c>
-      <c r="M14" s="26">
+      <c r="M24" s="26">
         <f>IFERROR((K14-'README &amp; Assumptions'!B53)/I14,0)</f>
         <v/>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="39" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="39" t="inlineStr">
         <is>
           <t>⚠ Cockpit revenue here shows monthly equivalent ($24.92), not the annual $299 prepay. Cockpit ROI is best understood in Cockpit Logic tab.</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="94" t="inlineStr">
-        <is>
-          <t>2. HOW TO READ THIS TAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="95" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>2. HOW TO READ THIS TAB (Bite 2 — column-by-column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="95" t="inlineStr">
         <is>
           <t>Monthly Revenue</t>
         </is>
       </c>
-      <c r="B19" s="90" t="inlineStr">
+      <c r="B29" s="90" t="inlineStr">
         <is>
           <t>What user pays us per month for their subscription/PAYG plan</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="95" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="95" t="inlineStr">
         <is>
           <t>GB Consumed</t>
         </is>
       </c>
-      <c r="B20" s="90" t="inlineStr">
+      <c r="B30" s="90" t="inlineStr">
         <is>
           <t>How much data they actually USE (from Tab 2 per-tier rates, friction-adjusted)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="95" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="95" t="inlineStr">
         <is>
           <t>Wholesale $/GB</t>
         </is>
       </c>
-      <c r="B21" s="90" t="inlineStr">
+      <c r="B31" s="90" t="inlineStr">
         <is>
           <t>What we pay Samurai per GB consumed (blended Tier-A/B/C cost)</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="95" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="95" t="inlineStr">
         <is>
           <t>eSIM COGS</t>
         </is>
       </c>
-      <c r="B22" s="90" t="inlineStr">
+      <c r="B32" s="90" t="inlineStr">
         <is>
           <t>GB consumed × wholesale $/GB = what we owe Samurai for this user</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="95" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="95" t="inlineStr">
         <is>
           <t>Refuel Revenue + COGS</t>
         </is>
       </c>
-      <c r="B23" s="90" t="inlineStr">
+      <c r="B33" s="90" t="inlineStr">
         <is>
           <t>Some % of users top up. They pay $4.99 per 1 GB, we pay ~$0.85-$1.40 wholesale.</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="95" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="95" t="inlineStr">
         <is>
           <t>Total Revenue / COGS</t>
         </is>
       </c>
-      <c r="B24" s="90" t="inlineStr">
+      <c r="B34" s="90" t="inlineStr">
         <is>
           <t>Sum of base + refuel</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="95" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="95" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B25" s="90" t="inlineStr">
+      <c r="B35" s="90" t="inlineStr">
         <is>
           <t>Total Revenue - Total COGS (before operating costs)</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="95" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="95" t="inlineStr">
         <is>
           <t>Gross Margin %</t>
         </is>
       </c>
-      <c r="B26" s="90" t="inlineStr">
+      <c r="B36" s="90" t="inlineStr">
         <is>
           <t>Industry-standard profitability indicator. Target: 60-80%.</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="95" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="95" t="inlineStr">
         <is>
           <t>Net Margin (after OPEX)</t>
         </is>
       </c>
-      <c r="B27" s="90" t="inlineStr">
+      <c r="B37" s="90" t="inlineStr">
         <is>
           <t>Gross Profit minus $1.80/user OPEX (cloud, payments, support, SMS, hosting)</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="94" t="inlineStr">
-        <is>
-          <t>3. SOURCES &amp; CONFIDENCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="41" t="inlineStr">
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="94" t="inlineStr">
+        <is>
+          <t>3. SOURCES &amp; CONFIDENCE (Bite 5 — what feeds this tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="41" t="inlineStr">
         <is>
           <t>Component</t>
         </is>
       </c>
-      <c r="B31" s="41" t="inlineStr">
+      <c r="B41" s="41" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C31" s="41" t="inlineStr">
+      <c r="C41" s="41" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="90" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="90" t="inlineStr">
         <is>
           <t>Retail prices</t>
         </is>
       </c>
-      <c r="B32" s="90" t="inlineStr">
+      <c r="B42" s="90" t="inlineStr">
         <is>
           <t>Locked decisions 2026-06-01 (Tab 1 Section 2)</t>
         </is>
       </c>
-      <c r="C32" s="90" t="inlineStr">
+      <c r="C42" s="90" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="90" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="90" t="inlineStr">
         <is>
           <t>GB Consumed</t>
         </is>
       </c>
-      <c r="B33" s="90" t="inlineStr">
+      <c r="B43" s="90" t="inlineStr">
         <is>
           <t>Per-tier rates from Tab 2 (40/45/54/33/60%)</t>
         </is>
       </c>
-      <c r="C33" s="90" t="inlineStr">
+      <c r="C43" s="90" t="inlineStr">
         <is>
           <t>MEDIUM (estimates)</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="90" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="90" t="inlineStr">
         <is>
           <t>Wholesale $/GB</t>
         </is>
       </c>
-      <c r="B34" s="90" t="inlineStr">
+      <c r="B44" s="90" t="inlineStr">
         <is>
           <t>Real wholesale rate sheet, weighted by 75/20/5 country mix (updated 2026-06-01)</t>
         </is>
       </c>
-      <c r="C34" s="90" t="inlineStr">
+      <c r="C44" s="90" t="inlineStr">
         <is>
           <t>MEDIUM (mix is placeholder)</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="90" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="90" t="inlineStr">
         <is>
           <t>Refuel attach %</t>
         </is>
       </c>
-      <c r="B35" s="90" t="inlineStr">
+      <c r="B45" s="90" t="inlineStr">
         <is>
           <t>MY ESTIMATE per tier (10-40%)</t>
         </is>
       </c>
-      <c r="C35" s="90" t="inlineStr">
+      <c r="C45" s="90" t="inlineStr">
         <is>
           <t>LOW (needs validation)</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="90" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="90" t="inlineStr">
         <is>
           <t>OPEX $1.80/user</t>
         </is>
       </c>
-      <c r="B36" s="90" t="inlineStr">
+      <c r="B46" s="90" t="inlineStr">
         <is>
           <t>Tab 1 Section 5 — payment processing $1.20 + others</t>
         </is>
       </c>
-      <c r="C36" s="90" t="inlineStr">
+      <c r="C46" s="90" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="94" t="inlineStr">
-        <is>
-          <t>4. VALIDATION QUEUE</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="94" t="inlineStr">
+        <is>
+          <t>4. VALIDATION QUEUE (open items)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="39" t="inlineStr">
         <is>
           <t>• Per-tier refuel attach rates (10/20/25/40/20/15%) — validate via app analytics post-launch</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="39" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="39" t="inlineStr">
         <is>
           <t>• Wholesale country mix updated to 75/20/5 on 2026-06-01 (Emirates-realistic). Validate via 5-10 sample crew rosters.</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="39" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="39" t="inlineStr">
         <is>
           <t>• Per-tier consumption rates inherited from Tab 2 (same validation as Tab 2)</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="39" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="39" t="inlineStr">
         <is>
           <t>• Sensitivity test: what happens if Premium consumption is 50% instead of 40%?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="23">
+    <mergeCell ref="D9:M9"/>
+    <mergeCell ref="B23:M23"/>
+    <mergeCell ref="A4:M4"/>
+    <mergeCell ref="D8:M8"/>
+    <mergeCell ref="A43:M43"/>
+    <mergeCell ref="B19:M19"/>
+    <mergeCell ref="A40:M40"/>
+    <mergeCell ref="D10:M10"/>
     <mergeCell ref="B24:M24"/>
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="B20:M20"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="B26:M26"/>
+    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="A16:M16"/>
     <mergeCell ref="B25:M25"/>
-    <mergeCell ref="B19:M19"/>
-    <mergeCell ref="B20:M20"/>
-    <mergeCell ref="B21:M21"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="B23:M23"/>
-    <mergeCell ref="A40:M40"/>
     <mergeCell ref="B22:M22"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="B26:M26"/>
+    <mergeCell ref="D7:M7"/>
     <mergeCell ref="B27:M27"/>
-    <mergeCell ref="A43:M43"/>
-    <mergeCell ref="A41:M41"/>
+    <mergeCell ref="B21:M21"/>
     <mergeCell ref="A2:M2"/>
     <mergeCell ref="A42:M42"/>
   </mergeCells>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -251,7 +251,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="19">
     <fill>
       <patternFill/>
     </fill>
@@ -311,6 +311,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F7F7F7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002A4A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00B07A1F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D7A4F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005C7CB8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D8A547"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="005BAA82"/>
       </patternFill>
     </fill>
   </fills>
@@ -384,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="121">
+  <cellXfs count="127">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -534,6 +564,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -9876,7 +9924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M53"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9915,876 +9963,467 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="94" t="inlineStr">
-        <is>
-          <t>🗺 TAB 3 BITES MAP — what each part of this tab covers</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="41" t="inlineStr">
-        <is>
-          <t>Bite #</t>
-        </is>
-      </c>
-      <c r="B5" s="41" t="inlineStr">
-        <is>
-          <t>Topic</t>
-        </is>
-      </c>
-      <c r="C5" s="41" t="inlineStr">
-        <is>
-          <t>Where to look</t>
-        </is>
-      </c>
-      <c r="D5" s="41" t="inlineStr">
-        <is>
-          <t>Key takeaway</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="120" t="inlineStr">
-        <is>
-          <t>Bite 1</t>
-        </is>
-      </c>
-      <c r="B6" s="90" t="inlineStr">
-        <is>
-          <t>What Tab 3 does</t>
-        </is>
-      </c>
-      <c r="C6" s="39" t="inlineStr">
-        <is>
-          <t>Read rows 1-3 (title + purpose)</t>
-        </is>
-      </c>
-      <c r="D6" s="90" t="inlineStr">
-        <is>
-          <t>Per-USER economics — not total revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="50" customHeight="1">
-      <c r="A7" s="120" t="inlineStr">
-        <is>
-          <t>Bite 2</t>
-        </is>
-      </c>
-      <c r="B7" s="90" t="inlineStr">
-        <is>
-          <t>The 13 columns explained</t>
-        </is>
-      </c>
-      <c r="C7" s="39" t="inlineStr">
-        <is>
-          <t>Columns A-M, headers in row 17</t>
-        </is>
-      </c>
-      <c r="D7" s="90" t="inlineStr">
-        <is>
-          <t>Group 1 = inputs, Group 2 = eSIM math, Group 3 = profit math</t>
-        </is>
-      </c>
-    </row>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7" ht="50" customHeight="1"/>
     <row r="8">
-      <c r="A8" s="120" t="inlineStr">
-        <is>
-          <t>Bite 3</t>
-        </is>
-      </c>
-      <c r="B8" s="90" t="inlineStr">
-        <is>
-          <t>Per-tier profit numbers</t>
-        </is>
-      </c>
-      <c r="C8" s="39" t="inlineStr">
-        <is>
-          <t>Data rows 18-24 (Economy → Cockpit)</t>
-        </is>
-      </c>
-      <c r="D8" s="90" t="inlineStr">
-        <is>
-          <t>Business 71% margin / First Suite $33 highest absolute profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="120" t="inlineStr">
-        <is>
-          <t>Bite 4</t>
-        </is>
-      </c>
-      <c r="B9" s="90" t="inlineStr">
-        <is>
-          <t>Strategic insights</t>
-        </is>
-      </c>
-      <c r="C9" s="39" t="inlineStr">
-        <is>
-          <t>Read the whole data table 18-24</t>
-        </is>
-      </c>
-      <c r="D9" s="90" t="inlineStr">
-        <is>
-          <t>First Suite is hero / Business is RECOMMENDED / First lowest margin</t>
-        </is>
-      </c>
-    </row>
+      <c r="A8" s="94" t="inlineStr">
+        <is>
+          <t>1. PER-TIER UNIT ECONOMICS (Bites 2-4) — single subscriber per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
     <row r="10">
-      <c r="A10" s="120" t="inlineStr">
-        <is>
-          <t>Bite 5</t>
-        </is>
-      </c>
-      <c r="B10" s="90" t="inlineStr">
-        <is>
-          <t>How Tab 3 feeds downstream</t>
-        </is>
-      </c>
-      <c r="C10" s="39" t="inlineStr">
-        <is>
-          <t>See "Sources" section + cross-tab references</t>
-        </is>
-      </c>
-      <c r="D10" s="90" t="inlineStr">
-        <is>
-          <t>Per-user × user count → Tab 5/6/8</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
+      <c r="A10" s="121" t="inlineStr">
+        <is>
+          <t>GROUP 1 — INPUTS</t>
+        </is>
+      </c>
+      <c r="E10" s="122" t="inlineStr">
+        <is>
+          <t>GROUP 2 — eSIM MATH</t>
+        </is>
+      </c>
+      <c r="I10" s="123" t="inlineStr">
+        <is>
+          <t>GROUP 3 — PROFIT MATH</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="124" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B11" s="124" t="inlineStr">
+        <is>
+          <t>Monthly Revenue</t>
+        </is>
+      </c>
+      <c r="C11" s="124" t="inlineStr">
+        <is>
+          <t>GB Consumed</t>
+        </is>
+      </c>
+      <c r="D11" s="124" t="inlineStr">
+        <is>
+          <t>Wholesale $/GB</t>
+        </is>
+      </c>
+      <c r="E11" s="125" t="inlineStr">
+        <is>
+          <t>eSIM COGS</t>
+        </is>
+      </c>
+      <c r="F11" s="125" t="inlineStr">
+        <is>
+          <t>Refuel Attach %</t>
+        </is>
+      </c>
+      <c r="G11" s="125" t="inlineStr">
+        <is>
+          <t>Refuel Revenue</t>
+        </is>
+      </c>
+      <c r="H11" s="125" t="inlineStr">
+        <is>
+          <t>Refuel COGS</t>
+        </is>
+      </c>
+      <c r="I11" s="126" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="J11" s="126" t="inlineStr">
+        <is>
+          <t>Total COGS</t>
+        </is>
+      </c>
+      <c r="K11" s="126" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="L11" s="126" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="M11" s="126" t="inlineStr">
+        <is>
+          <t>Net Margin (after OPEX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="90" t="inlineStr">
+        <is>
+          <t>Economy (PAYG)</t>
+        </is>
+      </c>
+      <c r="B12" s="46">
+        <f>'README &amp; Assumptions'!B14</f>
+        <v/>
+      </c>
+      <c r="C12" s="49">
+        <f>'User Behavior'!D21</f>
+        <v/>
+      </c>
+      <c r="D12" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E12" s="54">
+        <f>C8*D8</f>
+        <v/>
+      </c>
+      <c r="F12" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="54">
+        <f>F8*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H12" s="54">
+        <f>F8*1*D8</f>
+        <v/>
+      </c>
+      <c r="I12" s="54">
+        <f>B8+G8</f>
+        <v/>
+      </c>
+      <c r="J12" s="54">
+        <f>E8+H8</f>
+        <v/>
+      </c>
+      <c r="K12" s="54">
+        <f>I8-J8</f>
+        <v/>
+      </c>
+      <c r="L12" s="26">
+        <f>IFERROR(K8/I8,0)</f>
+        <v/>
+      </c>
+      <c r="M12" s="26">
+        <f>IFERROR((K8-'README &amp; Assumptions'!B53)/I8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="90" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B13" s="46">
+        <f>'README &amp; Assumptions'!B15</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="90" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B14" s="46">
+        <f>'README &amp; Assumptions'!B16</f>
+        <v/>
+      </c>
+    </row>
     <row r="15">
-      <c r="A15" s="94" t="inlineStr">
-        <is>
-          <t>1. PER-TIER UNIT ECONOMICS (Bites 2-4) — single subscriber per month</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+      <c r="A15" s="93" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B15" s="101">
+        <f>'README &amp; Assumptions'!B17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="90" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B16" s="46">
+        <f>'README &amp; Assumptions'!B18</f>
+        <v/>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="47" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B17" s="47" t="inlineStr">
-        <is>
-          <t>Monthly Revenue</t>
-        </is>
-      </c>
-      <c r="C17" s="47" t="inlineStr">
-        <is>
-          <t>GB Consumed</t>
-        </is>
-      </c>
-      <c r="D17" s="47" t="inlineStr">
-        <is>
-          <t>Wholesale $/GB</t>
-        </is>
-      </c>
-      <c r="E17" s="47" t="inlineStr">
-        <is>
-          <t>eSIM COGS</t>
-        </is>
-      </c>
-      <c r="F17" s="47" t="inlineStr">
-        <is>
-          <t>Refuel Attach %</t>
-        </is>
-      </c>
-      <c r="G17" s="47" t="inlineStr">
-        <is>
-          <t>Refuel Revenue</t>
-        </is>
-      </c>
-      <c r="H17" s="47" t="inlineStr">
-        <is>
-          <t>Refuel COGS</t>
-        </is>
-      </c>
-      <c r="I17" s="47" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="J17" s="47" t="inlineStr">
-        <is>
-          <t>Total COGS</t>
-        </is>
-      </c>
-      <c r="K17" s="47" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="L17" s="47" t="inlineStr">
-        <is>
-          <t>Gross Margin %</t>
-        </is>
-      </c>
-      <c r="M17" s="47" t="inlineStr">
-        <is>
-          <t>Net Margin (after OPEX)</t>
-        </is>
+      <c r="A17" s="90" t="inlineStr">
+        <is>
+          <t>First Suite</t>
+        </is>
+      </c>
+      <c r="B17" s="46">
+        <f>'README &amp; Assumptions'!B19</f>
+        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="90" t="inlineStr">
         <is>
-          <t>Economy (PAYG)</t>
+          <t>Cockpit (annual)</t>
         </is>
       </c>
       <c r="B18" s="46">
-        <f>'README &amp; Assumptions'!B14</f>
-        <v/>
-      </c>
-      <c r="C18" s="49">
-        <f>'User Behavior'!D21</f>
-        <v/>
-      </c>
-      <c r="D18" s="46">
-        <f>'README &amp; Assumptions'!C31</f>
-        <v/>
-      </c>
-      <c r="E18" s="54">
-        <f>C8*D8</f>
-        <v/>
-      </c>
-      <c r="F18" s="81" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="54">
-        <f>F8*'README &amp; Assumptions'!B21</f>
-        <v/>
-      </c>
-      <c r="H18" s="54">
-        <f>F8*1*D8</f>
-        <v/>
-      </c>
-      <c r="I18" s="54">
-        <f>B8+G8</f>
-        <v/>
-      </c>
-      <c r="J18" s="54">
-        <f>E8+H8</f>
-        <v/>
-      </c>
-      <c r="K18" s="54">
-        <f>I8-J8</f>
-        <v/>
-      </c>
-      <c r="L18" s="26">
-        <f>IFERROR(K8/I8,0)</f>
-        <v/>
-      </c>
-      <c r="M18" s="26">
-        <f>IFERROR((K8-'README &amp; Assumptions'!B53)/I8,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="90" t="inlineStr">
-        <is>
-          <t>Roster Bundle</t>
-        </is>
-      </c>
-      <c r="B19" s="46">
-        <f>'README &amp; Assumptions'!B15</f>
-        <v/>
-      </c>
-      <c r="C19" s="49">
-        <f>'User Behavior'!D22</f>
-        <v/>
-      </c>
-      <c r="D19" s="46">
-        <f>'README &amp; Assumptions'!C31</f>
-        <v/>
-      </c>
-      <c r="E19" s="54">
-        <f>C9*D9</f>
-        <v/>
-      </c>
-      <c r="F19" s="81" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G19" s="54">
-        <f>F9*'README &amp; Assumptions'!B21</f>
-        <v/>
-      </c>
-      <c r="H19" s="54">
-        <f>F9*1*D9</f>
-        <v/>
-      </c>
-      <c r="I19" s="54">
-        <f>B9+G9</f>
-        <v/>
-      </c>
-      <c r="J19" s="54">
-        <f>E9+H9</f>
-        <v/>
-      </c>
-      <c r="K19" s="54">
-        <f>I9-J9</f>
-        <v/>
-      </c>
-      <c r="L19" s="26">
-        <f>IFERROR(K9/I9,0)</f>
-        <v/>
-      </c>
-      <c r="M19" s="26">
-        <f>IFERROR((K9-'README &amp; Assumptions'!B53)/I9,0)</f>
-        <v/>
-      </c>
-    </row>
+        <f>'README &amp; Assumptions'!B20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="90" t="inlineStr">
-        <is>
-          <t>Premium Economy</t>
-        </is>
-      </c>
-      <c r="B20" s="46">
-        <f>'README &amp; Assumptions'!B16</f>
-        <v/>
-      </c>
-      <c r="C20" s="49">
-        <f>'User Behavior'!D23</f>
-        <v/>
-      </c>
-      <c r="D20" s="46">
-        <f>'README &amp; Assumptions'!C31</f>
-        <v/>
-      </c>
-      <c r="E20" s="54">
-        <f>C10*D10</f>
-        <v/>
-      </c>
-      <c r="F20" s="81" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G20" s="54">
-        <f>F10*'README &amp; Assumptions'!B21</f>
-        <v/>
-      </c>
-      <c r="H20" s="54">
-        <f>F10*1*D10</f>
-        <v/>
-      </c>
-      <c r="I20" s="54">
-        <f>B10+G10</f>
-        <v/>
-      </c>
-      <c r="J20" s="54">
-        <f>E10+H10</f>
-        <v/>
-      </c>
-      <c r="K20" s="54">
-        <f>I10-J10</f>
-        <v/>
-      </c>
-      <c r="L20" s="26">
-        <f>IFERROR(K10/I10,0)</f>
-        <v/>
-      </c>
-      <c r="M20" s="26">
-        <f>IFERROR((K10-'README &amp; Assumptions'!B53)/I10,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="93" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="B21" s="101">
-        <f>'README &amp; Assumptions'!B17</f>
-        <v/>
-      </c>
-      <c r="C21" s="102">
-        <f>'User Behavior'!D24</f>
-        <v/>
-      </c>
-      <c r="D21" s="101">
-        <f>'README &amp; Assumptions'!C31</f>
-        <v/>
-      </c>
-      <c r="E21" s="59">
-        <f>C11*D11</f>
-        <v/>
-      </c>
-      <c r="F21" s="103" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G21" s="59">
-        <f>F11*'README &amp; Assumptions'!B21</f>
-        <v/>
-      </c>
-      <c r="H21" s="59">
-        <f>F11*1*D11</f>
-        <v/>
-      </c>
-      <c r="I21" s="59">
-        <f>B11+G11</f>
-        <v/>
-      </c>
-      <c r="J21" s="59">
-        <f>E11+H11</f>
-        <v/>
-      </c>
-      <c r="K21" s="59">
-        <f>I11-J11</f>
-        <v/>
-      </c>
-      <c r="L21" s="104">
-        <f>IFERROR(K11/I11,0)</f>
-        <v/>
-      </c>
-      <c r="M21" s="104">
-        <f>IFERROR((K11-'README &amp; Assumptions'!B53)/I11,0)</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A20" s="39" t="inlineStr">
+        <is>
+          <t>⚠ Cockpit revenue here shows monthly equivalent ($24.92), not the annual $299 prepay. Cockpit ROI is best understood in Cockpit Logic tab.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" s="90" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="B22" s="46">
-        <f>'README &amp; Assumptions'!B18</f>
-        <v/>
-      </c>
-      <c r="C22" s="49">
-        <f>'User Behavior'!D25</f>
-        <v/>
-      </c>
-      <c r="D22" s="46">
-        <f>'README &amp; Assumptions'!C31</f>
-        <v/>
-      </c>
-      <c r="E22" s="54">
-        <f>C12*D12</f>
-        <v/>
-      </c>
-      <c r="F22" s="81" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G22" s="54">
-        <f>F12*'README &amp; Assumptions'!B21</f>
-        <v/>
-      </c>
-      <c r="H22" s="54">
-        <f>F12*1*D12</f>
-        <v/>
-      </c>
-      <c r="I22" s="54">
-        <f>B12+G12</f>
-        <v/>
-      </c>
-      <c r="J22" s="54">
-        <f>E12+H12</f>
-        <v/>
-      </c>
-      <c r="K22" s="54">
-        <f>I12-J12</f>
-        <v/>
-      </c>
-      <c r="L22" s="26">
-        <f>IFERROR(K12/I12,0)</f>
-        <v/>
-      </c>
-      <c r="M22" s="26">
-        <f>IFERROR((K12-'README &amp; Assumptions'!B53)/I12,0)</f>
-        <v/>
+      <c r="A22" s="94" t="inlineStr">
+        <is>
+          <t>2. HOW TO READ THIS TAB (Bite 2 — column-by-column)</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="90" t="inlineStr">
-        <is>
-          <t>First Suite</t>
-        </is>
-      </c>
-      <c r="B23" s="46">
-        <f>'README &amp; Assumptions'!B19</f>
-        <v/>
-      </c>
-      <c r="C23" s="49">
-        <f>'User Behavior'!D26</f>
-        <v/>
-      </c>
-      <c r="D23" s="46">
-        <f>'README &amp; Assumptions'!C31</f>
-        <v/>
-      </c>
-      <c r="E23" s="54">
-        <f>C13*D13</f>
-        <v/>
-      </c>
-      <c r="F23" s="81" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="G23" s="54">
-        <f>F13*'README &amp; Assumptions'!B21</f>
-        <v/>
-      </c>
-      <c r="H23" s="54">
-        <f>F13*1*D13</f>
-        <v/>
-      </c>
-      <c r="I23" s="54">
-        <f>B13+G13</f>
-        <v/>
-      </c>
-      <c r="J23" s="54">
-        <f>E13+H13</f>
-        <v/>
-      </c>
-      <c r="K23" s="54">
-        <f>I13-J13</f>
-        <v/>
-      </c>
-      <c r="L23" s="26">
-        <f>IFERROR(K13/I13,0)</f>
-        <v/>
-      </c>
-      <c r="M23" s="26">
-        <f>IFERROR((K13-'README &amp; Assumptions'!B53)/I13,0)</f>
-        <v/>
+      <c r="A23" s="95" t="inlineStr">
+        <is>
+          <t>Monthly Revenue</t>
+        </is>
+      </c>
+      <c r="B23" s="90" t="inlineStr">
+        <is>
+          <t>What user pays us per month for their subscription/PAYG plan</t>
+        </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="90" t="inlineStr">
-        <is>
-          <t>Cockpit (annual)</t>
-        </is>
-      </c>
-      <c r="B24" s="46">
-        <f>'README &amp; Assumptions'!B20</f>
-        <v/>
-      </c>
-      <c r="C24" s="49">
-        <f>'User Behavior'!D27</f>
-        <v/>
-      </c>
-      <c r="D24" s="46">
-        <f>'README &amp; Assumptions'!C31</f>
-        <v/>
-      </c>
-      <c r="E24" s="54">
-        <f>C14*D14</f>
-        <v/>
-      </c>
-      <c r="F24" s="81" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G24" s="54">
-        <f>F14*'README &amp; Assumptions'!B21</f>
-        <v/>
-      </c>
-      <c r="H24" s="54">
-        <f>F14*1*D14</f>
-        <v/>
-      </c>
-      <c r="I24" s="54">
-        <f>B14+G14</f>
-        <v/>
-      </c>
-      <c r="J24" s="54">
-        <f>E14+H14</f>
-        <v/>
-      </c>
-      <c r="K24" s="54">
-        <f>I14-J14</f>
-        <v/>
-      </c>
-      <c r="L24" s="26">
-        <f>IFERROR(K14/I14,0)</f>
-        <v/>
-      </c>
-      <c r="M24" s="26">
-        <f>IFERROR((K14-'README &amp; Assumptions'!B53)/I14,0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25"/>
+      <c r="A24" s="95" t="inlineStr">
+        <is>
+          <t>GB Consumed</t>
+        </is>
+      </c>
+      <c r="B24" s="90" t="inlineStr">
+        <is>
+          <t>How much data they actually USE (from Tab 2 per-tier rates, friction-adjusted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="95" t="inlineStr">
+        <is>
+          <t>Wholesale $/GB</t>
+        </is>
+      </c>
+      <c r="B25" s="90" t="inlineStr">
+        <is>
+          <t>What we pay Samurai per GB consumed (blended Tier-A/B/C cost)</t>
+        </is>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" s="39" t="inlineStr">
-        <is>
-          <t>⚠ Cockpit revenue here shows monthly equivalent ($24.92), not the annual $299 prepay. Cockpit ROI is best understood in Cockpit Logic tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27"/>
+      <c r="A26" s="95" t="inlineStr">
+        <is>
+          <t>eSIM COGS</t>
+        </is>
+      </c>
+      <c r="B26" s="90" t="inlineStr">
+        <is>
+          <t>GB consumed × wholesale $/GB = what we owe Samurai for this user</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="95" t="inlineStr">
+        <is>
+          <t>Refuel Revenue + COGS</t>
+        </is>
+      </c>
+      <c r="B27" s="90" t="inlineStr">
+        <is>
+          <t>Some % of users top up. They pay $4.99 per 1 GB, we pay ~$0.85-$1.40 wholesale.</t>
+        </is>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" s="94" t="inlineStr">
-        <is>
-          <t>2. HOW TO READ THIS TAB (Bite 2 — column-by-column)</t>
+      <c r="A28" s="95" t="inlineStr">
+        <is>
+          <t>Total Revenue / COGS</t>
+        </is>
+      </c>
+      <c r="B28" s="90" t="inlineStr">
+        <is>
+          <t>Sum of base + refuel</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="95" t="inlineStr">
         <is>
-          <t>Monthly Revenue</t>
+          <t>Gross Profit</t>
         </is>
       </c>
       <c r="B29" s="90" t="inlineStr">
         <is>
-          <t>What user pays us per month for their subscription/PAYG plan</t>
+          <t>Total Revenue - Total COGS (before operating costs)</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="95" t="inlineStr">
         <is>
-          <t>GB Consumed</t>
+          <t>Gross Margin %</t>
         </is>
       </c>
       <c r="B30" s="90" t="inlineStr">
         <is>
-          <t>How much data they actually USE (from Tab 2 per-tier rates, friction-adjusted)</t>
+          <t>Industry-standard profitability indicator. Target: 60-80%.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="95" t="inlineStr">
         <is>
+          <t>Net Margin (after OPEX)</t>
+        </is>
+      </c>
+      <c r="B31" s="90" t="inlineStr">
+        <is>
+          <t>Gross Profit minus $1.80/user OPEX (cloud, payments, support, SMS, hosting)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="94" t="inlineStr">
+        <is>
+          <t>3. SOURCES &amp; CONFIDENCE (Bite 5 — what feeds this tab)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="90" t="inlineStr">
+        <is>
+          <t>Retail prices</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="90" t="inlineStr">
+        <is>
+          <t>GB Consumed</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="90" t="inlineStr">
+        <is>
           <t>Wholesale $/GB</t>
         </is>
       </c>
-      <c r="B31" s="90" t="inlineStr">
-        <is>
-          <t>What we pay Samurai per GB consumed (blended Tier-A/B/C cost)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="95" t="inlineStr">
-        <is>
-          <t>eSIM COGS</t>
-        </is>
-      </c>
-      <c r="B32" s="90" t="inlineStr">
-        <is>
-          <t>GB consumed × wholesale $/GB = what we owe Samurai for this user</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="95" t="inlineStr">
-        <is>
-          <t>Refuel Revenue + COGS</t>
-        </is>
-      </c>
-      <c r="B33" s="90" t="inlineStr">
-        <is>
-          <t>Some % of users top up. They pay $4.99 per 1 GB, we pay ~$0.85-$1.40 wholesale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="95" t="inlineStr">
-        <is>
-          <t>Total Revenue / COGS</t>
-        </is>
-      </c>
-      <c r="B34" s="90" t="inlineStr">
-        <is>
-          <t>Sum of base + refuel</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="95" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B35" s="90" t="inlineStr">
-        <is>
-          <t>Total Revenue - Total COGS (before operating costs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="95" t="inlineStr">
-        <is>
-          <t>Gross Margin %</t>
-        </is>
-      </c>
-      <c r="B36" s="90" t="inlineStr">
-        <is>
-          <t>Industry-standard profitability indicator. Target: 60-80%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="95" t="inlineStr">
-        <is>
-          <t>Net Margin (after OPEX)</t>
-        </is>
-      </c>
-      <c r="B37" s="90" t="inlineStr">
-        <is>
-          <t>Gross Profit minus $1.80/user OPEX (cloud, payments, support, SMS, hosting)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38"/>
-    <row r="39"/>
+      <c r="B38" s="90" t="inlineStr">
+        <is>
+          <t>Real wholesale rate sheet, weighted by 75/20/5 country mix (updated 2026-06-01)</t>
+        </is>
+      </c>
+      <c r="C38" s="90" t="inlineStr">
+        <is>
+          <t>MEDIUM (mix is placeholder)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="90" t="inlineStr">
+        <is>
+          <t>Refuel attach %</t>
+        </is>
+      </c>
+      <c r="B39" s="90" t="inlineStr">
+        <is>
+          <t>MY ESTIMATE per tier (10-40%)</t>
+        </is>
+      </c>
+      <c r="C39" s="90" t="inlineStr">
+        <is>
+          <t>LOW (needs validation)</t>
+        </is>
+      </c>
+    </row>
     <row r="40">
-      <c r="A40" s="94" t="inlineStr">
-        <is>
-          <t>3. SOURCES &amp; CONFIDENCE (Bite 5 — what feeds this tab)</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="41" t="inlineStr">
-        <is>
-          <t>Component</t>
-        </is>
-      </c>
-      <c r="B41" s="41" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="C41" s="41" t="inlineStr">
-        <is>
-          <t>Confidence</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="90" t="inlineStr">
-        <is>
-          <t>Retail prices</t>
-        </is>
-      </c>
-      <c r="B42" s="90" t="inlineStr">
-        <is>
-          <t>Locked decisions 2026-06-01 (Tab 1 Section 2)</t>
-        </is>
-      </c>
-      <c r="C42" s="90" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
+      <c r="A40" s="90" t="inlineStr">
+        <is>
+          <t>OPEX $1.80/user</t>
+        </is>
+      </c>
+      <c r="B40" s="90" t="inlineStr">
+        <is>
+          <t>Tab 1 Section 5 — payment processing $1.20 + others</t>
+        </is>
+      </c>
+      <c r="C40" s="90" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42"/>
     <row r="43">
-      <c r="A43" s="90" t="inlineStr">
-        <is>
-          <t>GB Consumed</t>
-        </is>
-      </c>
-      <c r="B43" s="90" t="inlineStr">
-        <is>
-          <t>Per-tier rates from Tab 2 (40/45/54/33/60%)</t>
-        </is>
-      </c>
-      <c r="C43" s="90" t="inlineStr">
-        <is>
-          <t>MEDIUM (estimates)</t>
+      <c r="A43" s="94" t="inlineStr">
+        <is>
+          <t>4. VALIDATION QUEUE (open items)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="90" t="inlineStr">
-        <is>
-          <t>Wholesale $/GB</t>
-        </is>
-      </c>
-      <c r="B44" s="90" t="inlineStr">
-        <is>
-          <t>Real wholesale rate sheet, weighted by 75/20/5 country mix (updated 2026-06-01)</t>
-        </is>
-      </c>
-      <c r="C44" s="90" t="inlineStr">
-        <is>
-          <t>MEDIUM (mix is placeholder)</t>
+      <c r="A44" s="39" t="inlineStr">
+        <is>
+          <t>• Per-tier refuel attach rates (10/20/25/40/20/15%) — validate via app analytics post-launch</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="90" t="inlineStr">
-        <is>
-          <t>Refuel attach %</t>
-        </is>
-      </c>
-      <c r="B45" s="90" t="inlineStr">
-        <is>
-          <t>MY ESTIMATE per tier (10-40%)</t>
-        </is>
-      </c>
-      <c r="C45" s="90" t="inlineStr">
-        <is>
-          <t>LOW (needs validation)</t>
+      <c r="A45" s="39" t="inlineStr">
+        <is>
+          <t>• Wholesale country mix updated to 75/20/5 on 2026-06-01 (Emirates-realistic). Validate via 5-10 sample crew rosters.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="90" t="inlineStr">
-        <is>
-          <t>OPEX $1.80/user</t>
-        </is>
-      </c>
-      <c r="B46" s="90" t="inlineStr">
-        <is>
-          <t>Tab 1 Section 5 — payment processing $1.20 + others</t>
-        </is>
-      </c>
-      <c r="C46" s="90" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="94" t="inlineStr">
-        <is>
-          <t>4. VALIDATION QUEUE (open items)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="39" t="inlineStr">
-        <is>
-          <t>• Per-tier refuel attach rates (10/20/25/40/20/15%) — validate via app analytics post-launch</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="39" t="inlineStr">
-        <is>
-          <t>• Wholesale country mix updated to 75/20/5 on 2026-06-01 (Emirates-realistic). Validate via 5-10 sample crew rosters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="39" t="inlineStr">
+      <c r="A46" s="39" t="inlineStr">
         <is>
           <t>• Per-tier consumption rates inherited from Tab 2 (same validation as Tab 2)</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="39" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="39" t="inlineStr">
         <is>
           <t>• Sensitivity test: what happens if Premium consumption is 50% instead of 40%?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="D9:M9"/>
     <mergeCell ref="B23:M23"/>
     <mergeCell ref="A4:M4"/>
@@ -10794,12 +10433,14 @@
     <mergeCell ref="A40:M40"/>
     <mergeCell ref="D10:M10"/>
     <mergeCell ref="B24:M24"/>
+    <mergeCell ref="E17:H17"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="B20:M20"/>
     <mergeCell ref="D6:M6"/>
     <mergeCell ref="B26:M26"/>
     <mergeCell ref="A41:M41"/>
     <mergeCell ref="A16:M16"/>
+    <mergeCell ref="I17:M17"/>
     <mergeCell ref="B25:M25"/>
     <mergeCell ref="B22:M22"/>
     <mergeCell ref="A3:M3"/>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -9924,21 +9924,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
     <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
@@ -9952,125 +9952,383 @@
     <row r="2">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>PURPOSE: For each tier, compute revenue, COGS, refuel income, gross margin, and net margin (after OPEX). Single-user view.</t>
+          <t>PURPOSE: For each tier, compute revenue, COGS, gross margin, net margin — for ONE subscriber per month. The "PER-USER" math.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="39" t="inlineStr">
         <is>
-          <t>Pulls prices from README (rows 14-21), GB Consumed from Tab 2 (rows 21-28), blended wholesale cost from README C31, OPEX from README B53.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
-    <row r="5"/>
-    <row r="6"/>
-    <row r="7" ht="50" customHeight="1"/>
+          <t>Pulls prices from Tab 1 (rows 14-21), GB Consumed from Tab 2 (rows 21-27), blended wholesale from Tab 1 C31.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="121" t="inlineStr">
+        <is>
+          <t>GROUP 1 — INPUTS</t>
+        </is>
+      </c>
+      <c r="E5" s="122" t="inlineStr">
+        <is>
+          <t>GROUP 2 — eSIM MATH</t>
+        </is>
+      </c>
+      <c r="I5" s="123" t="inlineStr">
+        <is>
+          <t>GROUP 3 — PROFIT MATH</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="38" customHeight="1">
+      <c r="A6" s="124" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B6" s="124" t="inlineStr">
+        <is>
+          <t>Monthly Revenue</t>
+        </is>
+      </c>
+      <c r="C6" s="124" t="inlineStr">
+        <is>
+          <t>GB Consumed</t>
+        </is>
+      </c>
+      <c r="D6" s="124" t="inlineStr">
+        <is>
+          <t>Wholesale $/GB</t>
+        </is>
+      </c>
+      <c r="E6" s="125" t="inlineStr">
+        <is>
+          <t>eSIM COGS</t>
+        </is>
+      </c>
+      <c r="F6" s="125" t="inlineStr">
+        <is>
+          <t>Refuel Attach %</t>
+        </is>
+      </c>
+      <c r="G6" s="125" t="inlineStr">
+        <is>
+          <t>Refuel Revenue</t>
+        </is>
+      </c>
+      <c r="H6" s="125" t="inlineStr">
+        <is>
+          <t>Refuel COGS</t>
+        </is>
+      </c>
+      <c r="I6" s="126" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+      <c r="J6" s="126" t="inlineStr">
+        <is>
+          <t>Total COGS</t>
+        </is>
+      </c>
+      <c r="K6" s="126" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="L6" s="126" t="inlineStr">
+        <is>
+          <t>Gross Margin %</t>
+        </is>
+      </c>
+      <c r="M6" s="126" t="inlineStr">
+        <is>
+          <t>Net Margin (after OPEX)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="90" t="inlineStr">
+        <is>
+          <t>Economy (PAYG)</t>
+        </is>
+      </c>
+      <c r="B7" s="46">
+        <f>'README &amp; Assumptions'!B14</f>
+        <v/>
+      </c>
+      <c r="C7" s="49">
+        <f>'User Behavior'!D21</f>
+        <v/>
+      </c>
+      <c r="D7" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E7" s="54">
+        <f>C7*D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="54">
+        <f>F7*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H7" s="54">
+        <f>F7*1*D7</f>
+        <v/>
+      </c>
+      <c r="I7" s="54">
+        <f>B7+G7</f>
+        <v/>
+      </c>
+      <c r="J7" s="54">
+        <f>E7+H7</f>
+        <v/>
+      </c>
+      <c r="K7" s="54">
+        <f>I7-J7</f>
+        <v/>
+      </c>
+      <c r="L7" s="26">
+        <f>IFERROR(K7/I7,0)</f>
+        <v/>
+      </c>
+      <c r="M7" s="26">
+        <f>IFERROR((K7-'README &amp; Assumptions'!B53)/I7,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="8">
-      <c r="A8" s="94" t="inlineStr">
-        <is>
-          <t>1. PER-TIER UNIT ECONOMICS (Bites 2-4) — single subscriber per month</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+      <c r="A8" s="90" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B8" s="46">
+        <f>'README &amp; Assumptions'!B15</f>
+        <v/>
+      </c>
+      <c r="C8" s="49">
+        <f>'User Behavior'!D22</f>
+        <v/>
+      </c>
+      <c r="D8" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E8" s="54">
+        <f>C8*D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="81" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="54">
+        <f>F8*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H8" s="54">
+        <f>F8*1*D8</f>
+        <v/>
+      </c>
+      <c r="I8" s="54">
+        <f>B8+G8</f>
+        <v/>
+      </c>
+      <c r="J8" s="54">
+        <f>E8+H8</f>
+        <v/>
+      </c>
+      <c r="K8" s="54">
+        <f>I8-J8</f>
+        <v/>
+      </c>
+      <c r="L8" s="26">
+        <f>IFERROR(K8/I8,0)</f>
+        <v/>
+      </c>
+      <c r="M8" s="26">
+        <f>IFERROR((K8-'README &amp; Assumptions'!B53)/I8,0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="90" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B9" s="46">
+        <f>'README &amp; Assumptions'!B16</f>
+        <v/>
+      </c>
+      <c r="C9" s="49">
+        <f>'User Behavior'!D23</f>
+        <v/>
+      </c>
+      <c r="D9" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E9" s="54">
+        <f>C9*D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="81" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="54">
+        <f>F9*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H9" s="54">
+        <f>F9*1*D9</f>
+        <v/>
+      </c>
+      <c r="I9" s="54">
+        <f>B9+G9</f>
+        <v/>
+      </c>
+      <c r="J9" s="54">
+        <f>E9+H9</f>
+        <v/>
+      </c>
+      <c r="K9" s="54">
+        <f>I9-J9</f>
+        <v/>
+      </c>
+      <c r="L9" s="26">
+        <f>IFERROR(K9/I9,0)</f>
+        <v/>
+      </c>
+      <c r="M9" s="26">
+        <f>IFERROR((K9-'README &amp; Assumptions'!B53)/I9,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="121" t="inlineStr">
-        <is>
-          <t>GROUP 1 — INPUTS</t>
-        </is>
-      </c>
-      <c r="E10" s="122" t="inlineStr">
-        <is>
-          <t>GROUP 2 — eSIM MATH</t>
-        </is>
-      </c>
-      <c r="I10" s="123" t="inlineStr">
-        <is>
-          <t>GROUP 3 — PROFIT MATH</t>
-        </is>
+      <c r="A10" s="93" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B10" s="101">
+        <f>'README &amp; Assumptions'!B17</f>
+        <v/>
+      </c>
+      <c r="C10" s="102">
+        <f>'User Behavior'!D24</f>
+        <v/>
+      </c>
+      <c r="D10" s="101">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E10" s="59">
+        <f>C10*D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="103" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G10" s="59">
+        <f>F10*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H10" s="59">
+        <f>F10*1*D10</f>
+        <v/>
+      </c>
+      <c r="I10" s="59">
+        <f>B10+G10</f>
+        <v/>
+      </c>
+      <c r="J10" s="59">
+        <f>E10+H10</f>
+        <v/>
+      </c>
+      <c r="K10" s="59">
+        <f>I10-J10</f>
+        <v/>
+      </c>
+      <c r="L10" s="104">
+        <f>IFERROR(K10/I10,0)</f>
+        <v/>
+      </c>
+      <c r="M10" s="104">
+        <f>IFERROR((K10-'README &amp; Assumptions'!B53)/I10,0)</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="124" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B11" s="124" t="inlineStr">
-        <is>
-          <t>Monthly Revenue</t>
-        </is>
-      </c>
-      <c r="C11" s="124" t="inlineStr">
-        <is>
-          <t>GB Consumed</t>
-        </is>
-      </c>
-      <c r="D11" s="124" t="inlineStr">
-        <is>
-          <t>Wholesale $/GB</t>
-        </is>
-      </c>
-      <c r="E11" s="125" t="inlineStr">
-        <is>
-          <t>eSIM COGS</t>
-        </is>
-      </c>
-      <c r="F11" s="125" t="inlineStr">
-        <is>
-          <t>Refuel Attach %</t>
-        </is>
-      </c>
-      <c r="G11" s="125" t="inlineStr">
-        <is>
-          <t>Refuel Revenue</t>
-        </is>
-      </c>
-      <c r="H11" s="125" t="inlineStr">
-        <is>
-          <t>Refuel COGS</t>
-        </is>
-      </c>
-      <c r="I11" s="126" t="inlineStr">
-        <is>
-          <t>Total Revenue</t>
-        </is>
-      </c>
-      <c r="J11" s="126" t="inlineStr">
-        <is>
-          <t>Total COGS</t>
-        </is>
-      </c>
-      <c r="K11" s="126" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="L11" s="126" t="inlineStr">
-        <is>
-          <t>Gross Margin %</t>
-        </is>
-      </c>
-      <c r="M11" s="126" t="inlineStr">
-        <is>
-          <t>Net Margin (after OPEX)</t>
-        </is>
+      <c r="A11" s="90" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B11" s="46">
+        <f>'README &amp; Assumptions'!B18</f>
+        <v/>
+      </c>
+      <c r="C11" s="49">
+        <f>'User Behavior'!D25</f>
+        <v/>
+      </c>
+      <c r="D11" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E11" s="54">
+        <f>C11*D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="81" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="G11" s="54">
+        <f>F11*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H11" s="54">
+        <f>F11*1*D11</f>
+        <v/>
+      </c>
+      <c r="I11" s="54">
+        <f>B11+G11</f>
+        <v/>
+      </c>
+      <c r="J11" s="54">
+        <f>E11+H11</f>
+        <v/>
+      </c>
+      <c r="K11" s="54">
+        <f>I11-J11</f>
+        <v/>
+      </c>
+      <c r="L11" s="26">
+        <f>IFERROR(K11/I11,0)</f>
+        <v/>
+      </c>
+      <c r="M11" s="26">
+        <f>IFERROR((K11-'README &amp; Assumptions'!B53)/I11,0)</f>
+        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="90" t="inlineStr">
         <is>
-          <t>Economy (PAYG)</t>
+          <t>First Suite</t>
         </is>
       </c>
       <c r="B12" s="46">
-        <f>'README &amp; Assumptions'!B14</f>
+        <f>'README &amp; Assumptions'!B19</f>
         <v/>
       </c>
       <c r="C12" s="49">
-        <f>'User Behavior'!D21</f>
+        <f>'User Behavior'!D26</f>
         <v/>
       </c>
       <c r="D12" s="46">
@@ -10078,377 +10336,383 @@
         <v/>
       </c>
       <c r="E12" s="54">
-        <f>C8*D8</f>
+        <f>C12*D12</f>
         <v/>
       </c>
       <c r="F12" s="81" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G12" s="54">
-        <f>F8*'README &amp; Assumptions'!B21</f>
+        <f>F12*'README &amp; Assumptions'!B21</f>
         <v/>
       </c>
       <c r="H12" s="54">
-        <f>F8*1*D8</f>
+        <f>F12*1*D12</f>
         <v/>
       </c>
       <c r="I12" s="54">
-        <f>B8+G8</f>
+        <f>B12+G12</f>
         <v/>
       </c>
       <c r="J12" s="54">
-        <f>E8+H8</f>
+        <f>E12+H12</f>
         <v/>
       </c>
       <c r="K12" s="54">
-        <f>I8-J8</f>
+        <f>I12-J12</f>
         <v/>
       </c>
       <c r="L12" s="26">
-        <f>IFERROR(K8/I8,0)</f>
+        <f>IFERROR(K12/I12,0)</f>
         <v/>
       </c>
       <c r="M12" s="26">
-        <f>IFERROR((K8-'README &amp; Assumptions'!B53)/I8,0)</f>
+        <f>IFERROR((K12-'README &amp; Assumptions'!B53)/I12,0)</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="90" t="inlineStr">
         <is>
-          <t>Roster Bundle</t>
+          <t>Cockpit (annual)</t>
         </is>
       </c>
       <c r="B13" s="46">
-        <f>'README &amp; Assumptions'!B15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="90" t="inlineStr">
-        <is>
-          <t>Premium Economy</t>
-        </is>
-      </c>
-      <c r="B14" s="46">
-        <f>'README &amp; Assumptions'!B16</f>
+        <f>'README &amp; Assumptions'!B20</f>
+        <v/>
+      </c>
+      <c r="C13" s="49">
+        <f>'User Behavior'!D27</f>
+        <v/>
+      </c>
+      <c r="D13" s="46">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="E13" s="54">
+        <f>C13*D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="81" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G13" s="54">
+        <f>F13*'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="H13" s="54">
+        <f>F13*1*D13</f>
+        <v/>
+      </c>
+      <c r="I13" s="54">
+        <f>B13+G13</f>
+        <v/>
+      </c>
+      <c r="J13" s="54">
+        <f>E13+H13</f>
+        <v/>
+      </c>
+      <c r="K13" s="54">
+        <f>I13-J13</f>
+        <v/>
+      </c>
+      <c r="L13" s="26">
+        <f>IFERROR(K13/I13,0)</f>
+        <v/>
+      </c>
+      <c r="M13" s="26">
+        <f>IFERROR((K13-'README &amp; Assumptions'!B53)/I13,0)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="93" t="inlineStr">
-        <is>
-          <t>Business</t>
-        </is>
-      </c>
-      <c r="B15" s="101">
-        <f>'README &amp; Assumptions'!B17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="90" t="inlineStr">
-        <is>
-          <t>First</t>
-        </is>
-      </c>
-      <c r="B16" s="46">
-        <f>'README &amp; Assumptions'!B18</f>
-        <v/>
+      <c r="A15" s="39" t="inlineStr">
+        <is>
+          <t>⚠ Cockpit shows MONTHLY equivalent ($24.92), not annual prepay ($299). See Cockpit Logic tab.</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="90" t="inlineStr">
-        <is>
-          <t>First Suite</t>
-        </is>
-      </c>
-      <c r="B17" s="46">
-        <f>'README &amp; Assumptions'!B19</f>
-        <v/>
+      <c r="A17" s="94" t="inlineStr">
+        <is>
+          <t>HOW TO READ THIS TAB</t>
+        </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="90" t="inlineStr">
-        <is>
-          <t>Cockpit (annual)</t>
-        </is>
-      </c>
-      <c r="B18" s="46">
-        <f>'README &amp; Assumptions'!B20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19"/>
+      <c r="A18" s="95" t="inlineStr">
+        <is>
+          <t>Monthly Revenue (B)</t>
+        </is>
+      </c>
+      <c r="B18" s="90" t="inlineStr">
+        <is>
+          <t>What user pays us per month</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="95" t="inlineStr">
+        <is>
+          <t>GB Consumed (C)</t>
+        </is>
+      </c>
+      <c r="B19" s="90" t="inlineStr">
+        <is>
+          <t>Actual GB used — per-tier rate from Tab 2</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
-      <c r="A20" s="39" t="inlineStr">
-        <is>
-          <t>⚠ Cockpit revenue here shows monthly equivalent ($24.92), not the annual $299 prepay. Cockpit ROI is best understood in Cockpit Logic tab.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21"/>
+      <c r="A20" s="95" t="inlineStr">
+        <is>
+          <t>Wholesale $/GB (D)</t>
+        </is>
+      </c>
+      <c r="B20" s="90" t="inlineStr">
+        <is>
+          <t>Blended supplier rate ($1.34 at 75/20/5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="95" t="inlineStr">
+        <is>
+          <t>eSIM COGS (E)</t>
+        </is>
+      </c>
+      <c r="B21" s="90" t="inlineStr">
+        <is>
+          <t>C × D = what we owe supplier</t>
+        </is>
+      </c>
+    </row>
     <row r="22">
-      <c r="A22" s="94" t="inlineStr">
-        <is>
-          <t>2. HOW TO READ THIS TAB (Bite 2 — column-by-column)</t>
+      <c r="A22" s="95" t="inlineStr">
+        <is>
+          <t>Refuel Attach % (F)</t>
+        </is>
+      </c>
+      <c r="B22" s="90" t="inlineStr">
+        <is>
+          <t>% of users who buy a top-up</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="95" t="inlineStr">
         <is>
-          <t>Monthly Revenue</t>
+          <t>Refuel Revenue / COGS (G/H)</t>
         </is>
       </c>
       <c r="B23" s="90" t="inlineStr">
         <is>
-          <t>What user pays us per month for their subscription/PAYG plan</t>
+          <t>Top-up revenue + supplier cost</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="95" t="inlineStr">
         <is>
-          <t>GB Consumed</t>
+          <t>Total Revenue / COGS (I/J)</t>
         </is>
       </c>
       <c r="B24" s="90" t="inlineStr">
         <is>
-          <t>How much data they actually USE (from Tab 2 per-tier rates, friction-adjusted)</t>
+          <t>Base + refuel combined</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="95" t="inlineStr">
         <is>
-          <t>Wholesale $/GB</t>
+          <t>Gross Profit / Margin (K/L)</t>
         </is>
       </c>
       <c r="B25" s="90" t="inlineStr">
         <is>
-          <t>What we pay Samurai per GB consumed (blended Tier-A/B/C cost)</t>
+          <t>Revenue − COGS (before opex)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="95" t="inlineStr">
         <is>
-          <t>eSIM COGS</t>
+          <t>Net Margin (M)</t>
         </is>
       </c>
       <c r="B26" s="90" t="inlineStr">
         <is>
-          <t>GB consumed × wholesale $/GB = what we owe Samurai for this user</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="95" t="inlineStr">
-        <is>
-          <t>Refuel Revenue + COGS</t>
-        </is>
-      </c>
-      <c r="B27" s="90" t="inlineStr">
-        <is>
-          <t>Some % of users top up. They pay $4.99 per 1 GB, we pay ~$0.85-$1.40 wholesale.</t>
+          <t>After $1.80/user OPEX</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="95" t="inlineStr">
-        <is>
-          <t>Total Revenue / COGS</t>
-        </is>
-      </c>
-      <c r="B28" s="90" t="inlineStr">
-        <is>
-          <t>Sum of base + refuel</t>
+      <c r="A28" s="94" t="inlineStr">
+        <is>
+          <t>SOURCES &amp; CONFIDENCE</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="95" t="inlineStr">
-        <is>
-          <t>Gross Profit</t>
-        </is>
-      </c>
-      <c r="B29" s="90" t="inlineStr">
-        <is>
-          <t>Total Revenue - Total COGS (before operating costs)</t>
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>Component</t>
+        </is>
+      </c>
+      <c r="B29" s="41" t="inlineStr">
+        <is>
+          <t>Source</t>
+        </is>
+      </c>
+      <c r="C29" s="41" t="inlineStr">
+        <is>
+          <t>Confidence</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="95" t="inlineStr">
-        <is>
-          <t>Gross Margin %</t>
+      <c r="A30" s="90" t="inlineStr">
+        <is>
+          <t>Retail prices</t>
         </is>
       </c>
       <c r="B30" s="90" t="inlineStr">
         <is>
-          <t>Industry-standard profitability indicator. Target: 60-80%.</t>
+          <t>Locked decisions 2026-06-01</t>
+        </is>
+      </c>
+      <c r="C30" s="90" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="95" t="inlineStr">
-        <is>
-          <t>Net Margin (after OPEX)</t>
+      <c r="A31" s="90" t="inlineStr">
+        <is>
+          <t>GB Consumed</t>
         </is>
       </c>
       <c r="B31" s="90" t="inlineStr">
         <is>
-          <t>Gross Profit minus $1.80/user OPEX (cloud, payments, support, SMS, hosting)</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33"/>
+          <t>Per-tier rates from Tab 2</t>
+        </is>
+      </c>
+      <c r="C31" s="90" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="90" t="inlineStr">
+        <is>
+          <t>Wholesale $/GB</t>
+        </is>
+      </c>
+      <c r="B32" s="90" t="inlineStr">
+        <is>
+          <t>Real Samurai × 75/20/5 mix</t>
+        </is>
+      </c>
+      <c r="C32" s="90" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="90" t="inlineStr">
+        <is>
+          <t>Refuel attach %</t>
+        </is>
+      </c>
+      <c r="B33" s="90" t="inlineStr">
+        <is>
+          <t>MY ESTIMATE per tier</t>
+        </is>
+      </c>
+      <c r="C33" s="90" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
-      <c r="A34" s="94" t="inlineStr">
-        <is>
-          <t>3. SOURCES &amp; CONFIDENCE (Bite 5 — what feeds this tab)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="41" t="inlineStr">
-        <is>
-          <t>Component</t>
+      <c r="A34" s="90" t="inlineStr">
+        <is>
+          <t>OPEX $1.80/user</t>
+        </is>
+      </c>
+      <c r="B34" s="90" t="inlineStr">
+        <is>
+          <t>Tab 1 Section 5</t>
+        </is>
+      </c>
+      <c r="C34" s="90" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="90" t="inlineStr">
-        <is>
-          <t>Retail prices</t>
+      <c r="A36" s="94" t="inlineStr">
+        <is>
+          <t>VALIDATION QUEUE</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="90" t="inlineStr">
-        <is>
-          <t>GB Consumed</t>
+      <c r="A37" s="39" t="inlineStr">
+        <is>
+          <t>• Per-tier refuel attach rates — validate via app analytics post-launch</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="90" t="inlineStr">
-        <is>
-          <t>Wholesale $/GB</t>
-        </is>
-      </c>
-      <c r="B38" s="90" t="inlineStr">
-        <is>
-          <t>Real wholesale rate sheet, weighted by 75/20/5 country mix (updated 2026-06-01)</t>
-        </is>
-      </c>
-      <c r="C38" s="90" t="inlineStr">
-        <is>
-          <t>MEDIUM (mix is placeholder)</t>
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>• Wholesale country mix 75/20/5 — Akito to validate via crew rosters</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="90" t="inlineStr">
-        <is>
-          <t>Refuel attach %</t>
-        </is>
-      </c>
-      <c r="B39" s="90" t="inlineStr">
-        <is>
-          <t>MY ESTIMATE per tier (10-40%)</t>
-        </is>
-      </c>
-      <c r="C39" s="90" t="inlineStr">
-        <is>
-          <t>LOW (needs validation)</t>
+      <c r="A39" s="39" t="inlineStr">
+        <is>
+          <t>• Per-tier consumption rates inherited from Tab 2</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="90" t="inlineStr">
-        <is>
-          <t>OPEX $1.80/user</t>
-        </is>
-      </c>
-      <c r="B40" s="90" t="inlineStr">
-        <is>
-          <t>Tab 1 Section 5 — payment processing $1.20 + others</t>
-        </is>
-      </c>
-      <c r="C40" s="90" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43">
-      <c r="A43" s="94" t="inlineStr">
-        <is>
-          <t>4. VALIDATION QUEUE (open items)</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="39" t="inlineStr">
-        <is>
-          <t>• Per-tier refuel attach rates (10/20/25/40/20/15%) — validate via app analytics post-launch</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="39" t="inlineStr">
-        <is>
-          <t>• Wholesale country mix updated to 75/20/5 on 2026-06-01 (Emirates-realistic). Validate via 5-10 sample crew rosters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="39" t="inlineStr">
-        <is>
-          <t>• Per-tier consumption rates inherited from Tab 2 (same validation as Tab 2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="39" t="inlineStr">
-        <is>
-          <t>• Sensitivity test: what happens if Premium consumption is 50% instead of 40%?</t>
+      <c r="A40" s="39" t="inlineStr">
+        <is>
+          <t>• Sensitivity test: what if Premium consumption is 50% instead of 40%?</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="D9:M9"/>
+  <mergeCells count="20">
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="B23:M23"/>
-    <mergeCell ref="A4:M4"/>
-    <mergeCell ref="D8:M8"/>
-    <mergeCell ref="A43:M43"/>
+    <mergeCell ref="A38:M38"/>
     <mergeCell ref="B19:M19"/>
     <mergeCell ref="A40:M40"/>
-    <mergeCell ref="D10:M10"/>
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="A15:M15"/>
+    <mergeCell ref="E5:H5"/>
     <mergeCell ref="B24:M24"/>
-    <mergeCell ref="E17:H17"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="B20:M20"/>
-    <mergeCell ref="D6:M6"/>
     <mergeCell ref="B26:M26"/>
-    <mergeCell ref="A41:M41"/>
-    <mergeCell ref="A16:M16"/>
-    <mergeCell ref="I17:M17"/>
+    <mergeCell ref="I5:M5"/>
     <mergeCell ref="B25:M25"/>
+    <mergeCell ref="A37:M37"/>
     <mergeCell ref="B22:M22"/>
     <mergeCell ref="A3:M3"/>
-    <mergeCell ref="D7:M7"/>
-    <mergeCell ref="B27:M27"/>
+    <mergeCell ref="B18:M18"/>
     <mergeCell ref="B21:M21"/>
     <mergeCell ref="A2:M2"/>
-    <mergeCell ref="A42:M42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -4512,11 +4512,11 @@
         <v>100</v>
       </c>
       <c r="C5" s="24">
-        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D5" s="24">
-        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E5" s="25">
@@ -4528,7 +4528,7 @@
         <v/>
       </c>
       <c r="G5" s="27">
-        <f>B5*'README &amp; Assumptions'!B50</f>
+        <f>B5*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="H5" s="25">
@@ -4554,11 +4554,11 @@
         <v>1000</v>
       </c>
       <c r="C6" s="24">
-        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D6" s="24">
-        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E6" s="25">
@@ -4570,7 +4570,7 @@
         <v/>
       </c>
       <c r="G6" s="27">
-        <f>B6*'README &amp; Assumptions'!B50</f>
+        <f>B6*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="H6" s="25">
@@ -4596,11 +4596,11 @@
         <v>5000</v>
       </c>
       <c r="C7" s="24">
-        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D7" s="24">
-        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E7" s="25">
@@ -4612,7 +4612,7 @@
         <v/>
       </c>
       <c r="G7" s="27">
-        <f>B7*'README &amp; Assumptions'!B50</f>
+        <f>B7*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="H7" s="25">
@@ -4638,11 +4638,11 @@
         <v>20000</v>
       </c>
       <c r="C8" s="24">
-        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D8" s="24">
-        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E8" s="25">
@@ -4654,7 +4654,7 @@
         <v/>
       </c>
       <c r="G8" s="27">
-        <f>B8*'README &amp; Assumptions'!B50</f>
+        <f>B8*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="H8" s="25">
@@ -4855,11 +4855,11 @@
         </is>
       </c>
       <c r="B12" s="24">
-        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C12" s="24">
-        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)*B6</f>
+        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)*B6</f>
         <v/>
       </c>
       <c r="D12" s="24">
@@ -4867,7 +4867,7 @@
         <v/>
       </c>
       <c r="E12" s="25">
-        <f>B12-C12-D12-(1000*'README &amp; Assumptions'!B50)</f>
+        <f>B12-C12-D12-(1000*'README &amp; Assumptions'!B53)</f>
         <v/>
       </c>
       <c r="F12" s="17">
@@ -4886,11 +4886,11 @@
         </is>
       </c>
       <c r="B13" s="24">
-        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C13" s="24">
-        <f>1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*B7</f>
+        <f>1000*SUMPRODUCT('User Behavior'!B21:B27,'README &amp; Assumptions'!B36:B42)*'README &amp; Assumptions'!C31*B7</f>
         <v/>
       </c>
       <c r="D13" s="24">
@@ -4898,7 +4898,7 @@
         <v/>
       </c>
       <c r="E13" s="25">
-        <f>B13-C13-D13-(1000*'README &amp; Assumptions'!B50)</f>
+        <f>B13-C13-D13-(1000*'README &amp; Assumptions'!B53)</f>
         <v/>
       </c>
       <c r="F13" s="17">
@@ -4917,11 +4917,11 @@
         </is>
       </c>
       <c r="B14" s="24">
-        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C14" s="24">
-        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)*B8</f>
+        <f>1000*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)*B8</f>
         <v/>
       </c>
       <c r="D14" s="24">
@@ -4929,7 +4929,7 @@
         <v/>
       </c>
       <c r="E14" s="25">
-        <f>B14-C14-D14-(1000*'README &amp; Assumptions'!B50)</f>
+        <f>B14-C14-D14-(1000*'README &amp; Assumptions'!B53)</f>
         <v/>
       </c>
       <c r="F14" s="17">
@@ -5018,15 +5018,15 @@
         <v>50</v>
       </c>
       <c r="C5" s="24">
-        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D5" s="24">
-        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E5" s="24">
-        <f>B5*'README &amp; Assumptions'!B50</f>
+        <f>B5*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F5" s="25">
@@ -5048,15 +5048,15 @@
         <v>80</v>
       </c>
       <c r="C6" s="24">
-        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D6" s="24">
-        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E6" s="24">
-        <f>B6*'README &amp; Assumptions'!B50</f>
+        <f>B6*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F6" s="25">
@@ -5078,15 +5078,15 @@
         <v>130</v>
       </c>
       <c r="C7" s="24">
-        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D7" s="24">
-        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E7" s="24">
-        <f>B7*'README &amp; Assumptions'!B50</f>
+        <f>B7*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F7" s="25">
@@ -5108,15 +5108,15 @@
         <v>200</v>
       </c>
       <c r="C8" s="24">
-        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D8" s="24">
-        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E8" s="24">
-        <f>B8*'README &amp; Assumptions'!B50</f>
+        <f>B8*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F8" s="25">
@@ -5138,15 +5138,15 @@
         <v>300</v>
       </c>
       <c r="C9" s="24">
-        <f>B9*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B9*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D9" s="24">
-        <f>B9*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B9*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E9" s="24">
-        <f>B9*'README &amp; Assumptions'!B50</f>
+        <f>B9*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F9" s="25">
@@ -5168,15 +5168,15 @@
         <v>450</v>
       </c>
       <c r="C10" s="24">
-        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D10" s="24">
-        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E10" s="24">
-        <f>B10*'README &amp; Assumptions'!B50</f>
+        <f>B10*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F10" s="25">
@@ -5198,15 +5198,15 @@
         <v>650</v>
       </c>
       <c r="C11" s="24">
-        <f>B11*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B11*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D11" s="24">
-        <f>B11*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B11*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E11" s="24">
-        <f>B11*'README &amp; Assumptions'!B50</f>
+        <f>B11*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F11" s="25">
@@ -5228,15 +5228,15 @@
         <v>900</v>
       </c>
       <c r="C12" s="24">
-        <f>B12*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B12*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D12" s="24">
-        <f>B12*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B12*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E12" s="24">
-        <f>B12*'README &amp; Assumptions'!B50</f>
+        <f>B12*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F12" s="25">
@@ -5258,15 +5258,15 @@
         <v>1200</v>
       </c>
       <c r="C13" s="24">
-        <f>B13*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B13*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D13" s="24">
-        <f>B13*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B13*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E13" s="24">
-        <f>B13*'README &amp; Assumptions'!B50</f>
+        <f>B13*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F13" s="25">
@@ -5288,15 +5288,15 @@
         <v>1500</v>
       </c>
       <c r="C14" s="24">
-        <f>B14*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B14*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D14" s="24">
-        <f>B14*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B14*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E14" s="24">
-        <f>B14*'README &amp; Assumptions'!B50</f>
+        <f>B14*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F14" s="25">
@@ -5318,15 +5318,15 @@
         <v>1800</v>
       </c>
       <c r="C15" s="24">
-        <f>B15*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B15*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D15" s="24">
-        <f>B15*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B15*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E15" s="24">
-        <f>B15*'README &amp; Assumptions'!B50</f>
+        <f>B15*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F15" s="25">
@@ -5348,15 +5348,15 @@
         <v>2100</v>
       </c>
       <c r="C16" s="24">
-        <f>B16*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B16*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D16" s="24">
-        <f>B16*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B16*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E16" s="24">
-        <f>B16*'README &amp; Assumptions'!B50</f>
+        <f>B16*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F16" s="25">
@@ -5378,15 +5378,15 @@
         <v>2400</v>
       </c>
       <c r="C17" s="24">
-        <f>B17*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B17*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D17" s="24">
-        <f>B17*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B17*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E17" s="24">
-        <f>B17*'README &amp; Assumptions'!B50</f>
+        <f>B17*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F17" s="25">
@@ -5408,15 +5408,15 @@
         <v>2700</v>
       </c>
       <c r="C18" s="24">
-        <f>B18*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B18*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D18" s="24">
-        <f>B18*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B18*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E18" s="24">
-        <f>B18*'README &amp; Assumptions'!B50</f>
+        <f>B18*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F18" s="25">
@@ -5438,15 +5438,15 @@
         <v>3000</v>
       </c>
       <c r="C19" s="24">
-        <f>B19*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B19*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D19" s="24">
-        <f>B19*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B19*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E19" s="24">
-        <f>B19*'README &amp; Assumptions'!B50</f>
+        <f>B19*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F19" s="25">
@@ -5468,15 +5468,15 @@
         <v>3300</v>
       </c>
       <c r="C20" s="24">
-        <f>B20*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B20*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D20" s="24">
-        <f>B20*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B20*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E20" s="24">
-        <f>B20*'README &amp; Assumptions'!B50</f>
+        <f>B20*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F20" s="25">
@@ -5498,15 +5498,15 @@
         <v>3600</v>
       </c>
       <c r="C21" s="24">
-        <f>B21*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B21*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D21" s="24">
-        <f>B21*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B21*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E21" s="24">
-        <f>B21*'README &amp; Assumptions'!B50</f>
+        <f>B21*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F21" s="25">
@@ -5528,15 +5528,15 @@
         <v>3900</v>
       </c>
       <c r="C22" s="24">
-        <f>B22*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B22*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D22" s="24">
-        <f>B22*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B22*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E22" s="24">
-        <f>B22*'README &amp; Assumptions'!B50</f>
+        <f>B22*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F22" s="25">
@@ -5558,15 +5558,15 @@
         <v>4200</v>
       </c>
       <c r="C23" s="24">
-        <f>B23*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B23*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D23" s="24">
-        <f>B23*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B23*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E23" s="24">
-        <f>B23*'README &amp; Assumptions'!B50</f>
+        <f>B23*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F23" s="25">
@@ -5588,15 +5588,15 @@
         <v>4500</v>
       </c>
       <c r="C24" s="24">
-        <f>B24*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B24*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D24" s="24">
-        <f>B24*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B24*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E24" s="24">
-        <f>B24*'README &amp; Assumptions'!B50</f>
+        <f>B24*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F24" s="25">
@@ -5618,15 +5618,15 @@
         <v>4700</v>
       </c>
       <c r="C25" s="24">
-        <f>B25*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B25*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D25" s="24">
-        <f>B25*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B25*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E25" s="24">
-        <f>B25*'README &amp; Assumptions'!B50</f>
+        <f>B25*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F25" s="25">
@@ -5648,15 +5648,15 @@
         <v>4850</v>
       </c>
       <c r="C26" s="24">
-        <f>B26*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B26*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D26" s="24">
-        <f>B26*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B26*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E26" s="24">
-        <f>B26*'README &amp; Assumptions'!B50</f>
+        <f>B26*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F26" s="25">
@@ -5678,15 +5678,15 @@
         <v>4950</v>
       </c>
       <c r="C27" s="24">
-        <f>B27*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B27*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D27" s="24">
-        <f>B27*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B27*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E27" s="24">
-        <f>B27*'README &amp; Assumptions'!B50</f>
+        <f>B27*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F27" s="25">
@@ -5708,15 +5708,15 @@
         <v>5000</v>
       </c>
       <c r="C28" s="24">
-        <f>B28*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B28*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="D28" s="24">
-        <f>B28*SUMPRODUCT('Per-Tier Unit Economics'!E5:E11+'Per-Tier Unit Economics'!G5:G11+'Per-Tier Unit Economics'!H5:H11,'README &amp; Assumptions'!B34:B40)</f>
+        <f>B28*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="E28" s="24">
-        <f>B28*'README &amp; Assumptions'!B50</f>
+        <f>B28*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="F28" s="25">
@@ -5858,11 +5858,11 @@
         <v/>
       </c>
       <c r="G5" s="25">
-        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F5)-(1000*'README &amp; Assumptions'!B50)</f>
+        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42))-(1000*SUMPRODUCT('User Behavior'!B21:B27,'README &amp; Assumptions'!B36:B42)*'README &amp; Assumptions'!C31*F5)-(1000*'README &amp; Assumptions'!B53)</f>
         <v/>
       </c>
       <c r="H5" s="26">
-        <f>IFERROR(G5/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
+        <f>IFERROR(G5/(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)),0)</f>
         <v/>
       </c>
     </row>
@@ -5889,11 +5889,11 @@
         <v/>
       </c>
       <c r="G6" s="25">
-        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F6)-(1000*'README &amp; Assumptions'!B50)</f>
+        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42))-(1000*SUMPRODUCT('User Behavior'!B21:B27,'README &amp; Assumptions'!B36:B42)*'README &amp; Assumptions'!C31*F6)-(1000*'README &amp; Assumptions'!B53)</f>
         <v/>
       </c>
       <c r="H6" s="26">
-        <f>IFERROR(G6/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
+        <f>IFERROR(G6/(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)),0)</f>
         <v/>
       </c>
     </row>
@@ -5920,11 +5920,11 @@
         <v/>
       </c>
       <c r="G7" s="25">
-        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F7)-(1000*'README &amp; Assumptions'!B50)</f>
+        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42))-(1000*SUMPRODUCT('User Behavior'!B21:B27,'README &amp; Assumptions'!B36:B42)*'README &amp; Assumptions'!C31*F7)-(1000*'README &amp; Assumptions'!B53)</f>
         <v/>
       </c>
       <c r="H7" s="26">
-        <f>IFERROR(G7/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
+        <f>IFERROR(G7/(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)),0)</f>
         <v/>
       </c>
     </row>
@@ -5951,11 +5951,11 @@
         <v/>
       </c>
       <c r="G8" s="25">
-        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40))-(1000*SUMPRODUCT('User Behavior'!B17:B23,'README &amp; Assumptions'!B34:B40)*'README &amp; Assumptions'!C29*F8)-(1000*'README &amp; Assumptions'!B50)</f>
+        <f>(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42))-(1000*SUMPRODUCT('User Behavior'!B21:B27,'README &amp; Assumptions'!B36:B42)*'README &amp; Assumptions'!C31*F8)-(1000*'README &amp; Assumptions'!B53)</f>
         <v/>
       </c>
       <c r="H8" s="26">
-        <f>IFERROR(G8/(1000*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)),0)</f>
+        <f>IFERROR(G8/(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)),0)</f>
         <v/>
       </c>
     </row>
@@ -6231,7 +6231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6254,7 +6254,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>How much can we spend to acquire each tier? LTV:CAC &gt; 3 is investable, &gt; 5 is excellent.</t>
+          <t>How much can we spend to acquire each tier? LTV:CAC ratio + payback period.</t>
         </is>
       </c>
     </row>
@@ -6385,11 +6385,11 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>First Suite</t>
         </is>
       </c>
       <c r="B11" s="29" t="n">
-        <v>0.006</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C11" s="20">
         <f>IFERROR(1/B11,0)</f>
@@ -6397,18 +6397,18 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>Annual prepay = automatic 12-mo retention</t>
+          <t>Top of ladder — concierge + status badge</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Refuel (add-on)</t>
+          <t>Cockpit</t>
         </is>
       </c>
       <c r="B12" s="29" t="n">
-        <v>0.15</v>
+        <v>0.006</v>
       </c>
       <c r="C12" s="20">
         <f>IFERROR(1/B12,0)</f>
@@ -6416,218 +6416,222 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
+          <t>Annual prepay = automatic 12-mo retention</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Refuel (add-on)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C13">
+        <f>IFERROR(1/B13,0)</f>
+        <v/>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
           <t>Per-purchase, no subscription</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>CUSTOMER ACQUISITION COST (per-channel blended avg)</t>
-        </is>
-      </c>
+      <c r="A15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Channel</t>
-        </is>
-      </c>
-      <c r="B16" s="8" t="inlineStr">
-        <is>
-          <t>% of Acquisition</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>$ CAC</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
+          <t>CUSTOMER ACQUISITION COST (per-channel blended avg)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n"/>
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="9" t="inlineStr">
         <is>
-          <t>Organic / word-of-mouth</t>
-        </is>
-      </c>
-      <c r="B17" s="13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C17" s="28" t="n">
-        <v>0</v>
+          <t>Channel</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>% of Acquisition</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>$ CAC</t>
+        </is>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>Crew network referrals — free</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Referral bonus ($5 credit)</t>
+          <t>Organic / word-of-mouth</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="C18" s="28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Existing user refers</t>
+          <t>Crew network referrals — free</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Paid social (IG/TikTok)</t>
+          <t>Referral bonus ($5 credit)</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="C19" s="28" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Cold acquisition</t>
+          <t>Existing user refers</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
+          <t>Paid social (IG/TikTok)</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="C20" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D20" s="14" t="inlineStr">
+        <is>
+          <t>Cold acquisition</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>Influencer / crew creator</t>
         </is>
       </c>
-      <c r="B20" s="13" t="n">
+      <c r="B21" t="n">
         <v>0.1</v>
       </c>
-      <c r="C20" s="28" t="n">
+      <c r="C21" t="n">
         <v>8</v>
       </c>
-      <c r="D20" s="14" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Paid sponsorship to @crew_illust et al</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="9" t="n"/>
+      <c r="C22" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>BLENDED CAC</t>
         </is>
       </c>
-      <c r="C22" s="11">
-        <f>SUMPRODUCT(B17:B20,C17:C20)</f>
+      <c r="C23">
+        <f>SUMPRODUCT(B18:B21,C18:C21)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>LTV / CAC PER TIER (Gross Profit × Lifetime ÷ CAC)</t>
-        </is>
-      </c>
+      <c r="A25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B26" s="8" t="inlineStr">
-        <is>
-          <t>Gross Profit/mo</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>Lifetime (mo)</t>
-        </is>
-      </c>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>LTV</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="inlineStr">
-        <is>
-          <t>CAC</t>
-        </is>
-      </c>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>LTV:CAC</t>
-        </is>
-      </c>
-      <c r="G26" s="8" t="inlineStr">
-        <is>
-          <t>Payback (mo)</t>
-        </is>
-      </c>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>Verdict</t>
-        </is>
-      </c>
+          <t>LTV / CAC PER TIER (Gross Profit × Lifetime ÷ CAC)</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="n"/>
+      <c r="C26" s="8" t="n"/>
+      <c r="D26" s="8" t="n"/>
+      <c r="E26" s="8" t="n"/>
+      <c r="F26" s="8" t="n"/>
+      <c r="G26" s="8" t="n"/>
+      <c r="H26" s="8" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B27" s="21">
-        <f>'Per-Tier Unit Economics'!I5</f>
-        <v/>
-      </c>
-      <c r="C27" s="20">
-        <f>C6</f>
-        <v/>
-      </c>
-      <c r="D27" s="22">
-        <f>B27*C27</f>
-        <v/>
-      </c>
-      <c r="E27" s="21">
-        <f>$C$22</f>
-        <v/>
-      </c>
-      <c r="F27" s="30">
-        <f>IFERROR(D27/E27,0)</f>
-        <v/>
-      </c>
-      <c r="G27" s="20">
-        <f>IFERROR(E27/B27,0)</f>
-        <v/>
-      </c>
-      <c r="H27" s="9">
-        <f>IF(F27&gt;=5,"Excellent",IF(F27&gt;=3,"Investable",IF(F27&gt;=1,"Marginal","Loss")))</f>
-        <v/>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B27" s="21" t="inlineStr">
+        <is>
+          <t>Gross Profit/mo</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>Lifetime (mo)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>LTV</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="inlineStr">
+        <is>
+          <t>CAC</t>
+        </is>
+      </c>
+      <c r="F27" s="30" t="inlineStr">
+        <is>
+          <t>LTV:CAC</t>
+        </is>
+      </c>
+      <c r="G27" s="20" t="inlineStr">
+        <is>
+          <t>Payback (mo)</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Roster Bundle</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="B28" s="21">
-        <f>'Per-Tier Unit Economics'!I6</f>
+        <f>'Per-Tier Unit Economics'!K7</f>
         <v/>
       </c>
       <c r="C28" s="20">
-        <f>C7</f>
+        <f>C6</f>
         <v/>
       </c>
       <c r="D28" s="22">
@@ -6635,7 +6639,7 @@
         <v/>
       </c>
       <c r="E28" s="21">
-        <f>$C$22</f>
+        <f>$C$23</f>
         <v/>
       </c>
       <c r="F28" s="30">
@@ -6647,22 +6651,22 @@
         <v/>
       </c>
       <c r="H28" s="9">
-        <f>IF(F28&gt;=5,"Excellent",IF(F28&gt;=3,"Investable",IF(F28&gt;=1,"Marginal","Loss")))</f>
+        <f>IF(F28&gt;=5,"Excellent",IF(F28&gt;=3,"Investable",IF(F28&gt;=1,"Marginal","Unprofitable")))</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Premium Economy</t>
+          <t>Roster Bundle</t>
         </is>
       </c>
       <c r="B29" s="21">
-        <f>'Per-Tier Unit Economics'!I7</f>
+        <f>'Per-Tier Unit Economics'!K8</f>
         <v/>
       </c>
       <c r="C29" s="20">
-        <f>C8</f>
+        <f>C7</f>
         <v/>
       </c>
       <c r="D29" s="22">
@@ -6670,7 +6674,7 @@
         <v/>
       </c>
       <c r="E29" s="21">
-        <f>$C$22</f>
+        <f>$C$23</f>
         <v/>
       </c>
       <c r="F29" s="30">
@@ -6682,22 +6686,22 @@
         <v/>
       </c>
       <c r="H29" s="9">
-        <f>IF(F29&gt;=5,"Excellent",IF(F29&gt;=3,"Investable",IF(F29&gt;=1,"Marginal","Loss")))</f>
+        <f>IF(F29&gt;=5,"Excellent",IF(F29&gt;=3,"Investable",IF(F29&gt;=1,"Marginal","Unprofitable")))</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Premium Economy</t>
         </is>
       </c>
       <c r="B30" s="21">
-        <f>'Per-Tier Unit Economics'!I8</f>
+        <f>'Per-Tier Unit Economics'!K9</f>
         <v/>
       </c>
       <c r="C30" s="20">
-        <f>C9</f>
+        <f>C8</f>
         <v/>
       </c>
       <c r="D30" s="22">
@@ -6705,7 +6709,7 @@
         <v/>
       </c>
       <c r="E30" s="21">
-        <f>$C$22</f>
+        <f>$C$23</f>
         <v/>
       </c>
       <c r="F30" s="30">
@@ -6717,22 +6721,22 @@
         <v/>
       </c>
       <c r="H30" s="9">
-        <f>IF(F30&gt;=5,"Excellent",IF(F30&gt;=3,"Investable",IF(F30&gt;=1,"Marginal","Loss")))</f>
+        <f>IF(F30&gt;=5,"Excellent",IF(F30&gt;=3,"Investable",IF(F30&gt;=1,"Marginal","Unprofitable")))</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="9" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="B31" s="21">
-        <f>'Per-Tier Unit Economics'!I9</f>
+        <f>'Per-Tier Unit Economics'!K10</f>
         <v/>
       </c>
       <c r="C31" s="20">
-        <f>C10</f>
+        <f>C9</f>
         <v/>
       </c>
       <c r="D31" s="22">
@@ -6740,7 +6744,7 @@
         <v/>
       </c>
       <c r="E31" s="21">
-        <f>$C$22</f>
+        <f>$C$23</f>
         <v/>
       </c>
       <c r="F31" s="30">
@@ -6752,22 +6756,22 @@
         <v/>
       </c>
       <c r="H31" s="9">
-        <f>IF(F31&gt;=5,"Excellent",IF(F31&gt;=3,"Investable",IF(F31&gt;=1,"Marginal","Loss")))</f>
+        <f>IF(F31&gt;=5,"Excellent",IF(F31&gt;=3,"Investable",IF(F31&gt;=1,"Marginal","Unprofitable")))</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>First</t>
         </is>
       </c>
       <c r="B32" s="21">
-        <f>'Per-Tier Unit Economics'!I10</f>
+        <f>'Per-Tier Unit Economics'!K11</f>
         <v/>
       </c>
       <c r="C32" s="20">
-        <f>C11</f>
+        <f>C10</f>
         <v/>
       </c>
       <c r="D32" s="22">
@@ -6775,7 +6779,7 @@
         <v/>
       </c>
       <c r="E32" s="21">
-        <f>$C$22</f>
+        <f>$C$23</f>
         <v/>
       </c>
       <c r="F32" s="30">
@@ -6787,22 +6791,22 @@
         <v/>
       </c>
       <c r="H32" s="9">
-        <f>IF(F32&gt;=5,"Excellent",IF(F32&gt;=3,"Investable",IF(F32&gt;=1,"Marginal","Loss")))</f>
+        <f>IF(F32&gt;=5,"Excellent",IF(F32&gt;=3,"Investable",IF(F32&gt;=1,"Marginal","Unprofitable")))</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="9" t="inlineStr">
         <is>
-          <t>Refuel</t>
+          <t>First Suite</t>
         </is>
       </c>
       <c r="B33" s="21">
-        <f>'Per-Tier Unit Economics'!I11</f>
+        <f>'Per-Tier Unit Economics'!K12</f>
         <v/>
       </c>
       <c r="C33" s="20">
-        <f>C12</f>
+        <f>C11</f>
         <v/>
       </c>
       <c r="D33" s="22">
@@ -6810,7 +6814,7 @@
         <v/>
       </c>
       <c r="E33" s="21">
-        <f>$C$22</f>
+        <f>$C$23</f>
         <v/>
       </c>
       <c r="F33" s="30">
@@ -6822,7 +6826,77 @@
         <v/>
       </c>
       <c r="H33" s="9">
-        <f>IF(F33&gt;=5,"Excellent",IF(F33&gt;=3,"Investable",IF(F33&gt;=1,"Marginal","Loss")))</f>
+        <f>IF(F33&gt;=5,"Excellent",IF(F33&gt;=3,"Investable",IF(F33&gt;=1,"Marginal","Unprofitable")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>'Per-Tier Unit Economics'!K13</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>C12</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>B34*C34</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>$C$23</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>IFERROR(D34/E34,0)</f>
+        <v/>
+      </c>
+      <c r="G34">
+        <f>IFERROR(E34/B34,0)</f>
+        <v/>
+      </c>
+      <c r="H34">
+        <f>IF(F34&gt;=5,"Excellent",IF(F34&gt;=3,"Investable",IF(F34&gt;=1,"Marginal","Unprofitable")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Refuel</t>
+        </is>
+      </c>
+      <c r="B35">
+        <f>'README &amp; Assumptions'!B21-'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="C35">
+        <f>C13</f>
+        <v/>
+      </c>
+      <c r="D35">
+        <f>B35*C35</f>
+        <v/>
+      </c>
+      <c r="E35">
+        <f>$C$23</f>
+        <v/>
+      </c>
+      <c r="F35">
+        <f>IFERROR(D35/E35,0)</f>
+        <v/>
+      </c>
+      <c r="G35">
+        <f>IFERROR(E35/B35,0)</f>
+        <v/>
+      </c>
+      <c r="H35">
+        <f>IF(F35&gt;=5,"Excellent",IF(F35&gt;=3,"Investable",IF(F35&gt;=1,"Marginal","Unprofitable")))</f>
         <v/>
       </c>
     </row>
@@ -6837,7 +6911,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6912,11 +6986,11 @@
         <v>0.4</v>
       </c>
       <c r="E5" s="11">
-        <f>B5*'README &amp; Assumptions'!C25+C5*'README &amp; Assumptions'!C26+D5*'README &amp; Assumptions'!C27</f>
+        <f>B5*'README &amp; Assumptions'!C27+C5*'README &amp; Assumptions'!C28+D5*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
       <c r="F5" s="11">
-        <f>'README &amp; Assumptions'!C29-E5</f>
+        <f>'README &amp; Assumptions'!C31-E5</f>
         <v/>
       </c>
     </row>
@@ -6936,11 +7010,11 @@
         <v>0.05</v>
       </c>
       <c r="E6" s="11">
-        <f>B6*'README &amp; Assumptions'!C25+C6*'README &amp; Assumptions'!C26+D6*'README &amp; Assumptions'!C27</f>
+        <f>B6*'README &amp; Assumptions'!C27+C6*'README &amp; Assumptions'!C28+D6*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
       <c r="F6" s="11">
-        <f>'README &amp; Assumptions'!C29-E6</f>
+        <f>'README &amp; Assumptions'!C31-E6</f>
         <v/>
       </c>
     </row>
@@ -6960,11 +7034,11 @@
         <v>0.15</v>
       </c>
       <c r="E7" s="11">
-        <f>B7*'README &amp; Assumptions'!C25+C7*'README &amp; Assumptions'!C26+D7*'README &amp; Assumptions'!C27</f>
+        <f>B7*'README &amp; Assumptions'!C27+C7*'README &amp; Assumptions'!C28+D7*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
       <c r="F7" s="11">
-        <f>'README &amp; Assumptions'!C29-E7</f>
+        <f>'README &amp; Assumptions'!C31-E7</f>
         <v/>
       </c>
     </row>
@@ -6984,11 +7058,11 @@
         <v>0.15</v>
       </c>
       <c r="E8" s="11">
-        <f>B8*'README &amp; Assumptions'!C25+C8*'README &amp; Assumptions'!C26+D8*'README &amp; Assumptions'!C27</f>
+        <f>B8*'README &amp; Assumptions'!C27+C8*'README &amp; Assumptions'!C28+D8*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
       <c r="F8" s="11">
-        <f>'README &amp; Assumptions'!C29-E8</f>
+        <f>'README &amp; Assumptions'!C31-E8</f>
         <v/>
       </c>
     </row>
@@ -7008,59 +7082,83 @@
         <v>0.2</v>
       </c>
       <c r="E9" s="11">
-        <f>B9*'README &amp; Assumptions'!C25+C9*'README &amp; Assumptions'!C26+D9*'README &amp; Assumptions'!C27</f>
+        <f>B9*'README &amp; Assumptions'!C27+C9*'README &amp; Assumptions'!C28+D9*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
       <c r="F9" s="11">
-        <f>'README &amp; Assumptions'!C29-E9</f>
+        <f>'README &amp; Assumptions'!C31-E9</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>First Suite</t>
         </is>
       </c>
       <c r="B10" s="13" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.25</v>
+        <v>0.3</v>
       </c>
       <c r="D10" s="13" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="E10" s="11">
-        <f>B10*'README &amp; Assumptions'!C25+C10*'README &amp; Assumptions'!C26+D10*'README &amp; Assumptions'!C27</f>
+        <f>B10*'README &amp; Assumptions'!C27+C10*'README &amp; Assumptions'!C28+D10*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
       <c r="F10" s="11">
-        <f>'README &amp; Assumptions'!C29-E10</f>
+        <f>'README &amp; Assumptions'!C31-E10</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Refuel</t>
+          <t>Cockpit</t>
         </is>
       </c>
       <c r="B11" s="13" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>0.25</v>
       </c>
       <c r="D11" s="13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E11" s="11">
+        <f>B11*'README &amp; Assumptions'!C27+C11*'README &amp; Assumptions'!C28+D11*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+      <c r="F11" s="11">
+        <f>'README &amp; Assumptions'!C31-E11</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Refuel</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D12" t="n">
         <v>0.15</v>
       </c>
-      <c r="E11" s="11">
-        <f>B11*'README &amp; Assumptions'!C25+C11*'README &amp; Assumptions'!C26+D11*'README &amp; Assumptions'!C27</f>
-        <v/>
-      </c>
-      <c r="F11" s="11">
-        <f>'README &amp; Assumptions'!C29-E11</f>
+      <c r="E12">
+        <f>B12*'README &amp; Assumptions'!C27+C12*'README &amp; Assumptions'!C28+D12*'README &amp; Assumptions'!C29</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f>'README &amp; Assumptions'!C31-E12</f>
         <v/>
       </c>
     </row>
@@ -7120,11 +7218,11 @@
         </is>
       </c>
       <c r="B15" s="21">
-        <f>'Per-Tier Unit Economics'!B5</f>
+        <f>'Per-Tier Unit Economics'!B7</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>'Per-Tier Unit Economics'!C5</f>
+        <f>'Per-Tier Unit Economics'!C7</f>
         <v/>
       </c>
       <c r="D15" s="21">
@@ -7144,7 +7242,7 @@
         <v/>
       </c>
       <c r="H15" s="31">
-        <f>F15-'Per-Tier Unit Economics'!I5</f>
+        <f>F15-'Per-Tier Unit Economics'!K7</f>
         <v/>
       </c>
     </row>
@@ -7155,11 +7253,11 @@
         </is>
       </c>
       <c r="B16" s="21">
-        <f>'Per-Tier Unit Economics'!B6</f>
+        <f>'Per-Tier Unit Economics'!B8</f>
         <v/>
       </c>
       <c r="C16" s="18">
-        <f>'Per-Tier Unit Economics'!C6</f>
+        <f>'Per-Tier Unit Economics'!C8</f>
         <v/>
       </c>
       <c r="D16" s="21">
@@ -7179,7 +7277,7 @@
         <v/>
       </c>
       <c r="H16" s="31">
-        <f>F16-'Per-Tier Unit Economics'!I6</f>
+        <f>F16-'Per-Tier Unit Economics'!K8</f>
         <v/>
       </c>
     </row>
@@ -7190,11 +7288,11 @@
         </is>
       </c>
       <c r="B17" s="21">
-        <f>'Per-Tier Unit Economics'!B7</f>
+        <f>'Per-Tier Unit Economics'!B9</f>
         <v/>
       </c>
       <c r="C17" s="18">
-        <f>'Per-Tier Unit Economics'!C7</f>
+        <f>'Per-Tier Unit Economics'!C9</f>
         <v/>
       </c>
       <c r="D17" s="21">
@@ -7214,7 +7312,7 @@
         <v/>
       </c>
       <c r="H17" s="31">
-        <f>F17-'Per-Tier Unit Economics'!I7</f>
+        <f>F17-'Per-Tier Unit Economics'!K9</f>
         <v/>
       </c>
     </row>
@@ -7225,11 +7323,11 @@
         </is>
       </c>
       <c r="B18" s="21">
-        <f>'Per-Tier Unit Economics'!B8</f>
+        <f>'Per-Tier Unit Economics'!B10</f>
         <v/>
       </c>
       <c r="C18" s="18">
-        <f>'Per-Tier Unit Economics'!C8</f>
+        <f>'Per-Tier Unit Economics'!C10</f>
         <v/>
       </c>
       <c r="D18" s="21">
@@ -7249,7 +7347,7 @@
         <v/>
       </c>
       <c r="H18" s="31">
-        <f>F18-'Per-Tier Unit Economics'!I8</f>
+        <f>F18-'Per-Tier Unit Economics'!K10</f>
         <v/>
       </c>
     </row>
@@ -7260,11 +7358,11 @@
         </is>
       </c>
       <c r="B19" s="21">
-        <f>'Per-Tier Unit Economics'!B9</f>
+        <f>'Per-Tier Unit Economics'!B11</f>
         <v/>
       </c>
       <c r="C19" s="18">
-        <f>'Per-Tier Unit Economics'!C9</f>
+        <f>'Per-Tier Unit Economics'!C11</f>
         <v/>
       </c>
       <c r="D19" s="21">
@@ -7284,22 +7382,22 @@
         <v/>
       </c>
       <c r="H19" s="31">
-        <f>F19-'Per-Tier Unit Economics'!I9</f>
+        <f>F19-'Per-Tier Unit Economics'!K11</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>First Suite</t>
         </is>
       </c>
       <c r="B20" s="21">
-        <f>'Per-Tier Unit Economics'!B10</f>
+        <f>'Per-Tier Unit Economics'!B12</f>
         <v/>
       </c>
       <c r="C20" s="18">
-        <f>'Per-Tier Unit Economics'!C10</f>
+        <f>'Per-Tier Unit Economics'!C12</f>
         <v/>
       </c>
       <c r="D20" s="21">
@@ -7319,22 +7417,22 @@
         <v/>
       </c>
       <c r="H20" s="31">
-        <f>F20-'Per-Tier Unit Economics'!I10</f>
+        <f>F20-'Per-Tier Unit Economics'!K12</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Refuel</t>
+          <t>Cockpit</t>
         </is>
       </c>
       <c r="B21" s="21">
-        <f>'Per-Tier Unit Economics'!B11</f>
+        <f>'Per-Tier Unit Economics'!B13</f>
         <v/>
       </c>
       <c r="C21" s="18">
-        <f>'Per-Tier Unit Economics'!C11</f>
+        <f>'Per-Tier Unit Economics'!C13</f>
         <v/>
       </c>
       <c r="D21" s="21">
@@ -7354,7 +7452,41 @@
         <v/>
       </c>
       <c r="H21" s="31">
-        <f>F21-'Per-Tier Unit Economics'!I11</f>
+        <f>F21-'Per-Tier Unit Economics'!K13</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Refuel</t>
+        </is>
+      </c>
+      <c r="B22">
+        <f>'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <f>E12</f>
+        <v/>
+      </c>
+      <c r="E22">
+        <f>C22*D22</f>
+        <v/>
+      </c>
+      <c r="F22">
+        <f>B22-E22</f>
+        <v/>
+      </c>
+      <c r="G22">
+        <f>IFERROR(F22/B22,0)</f>
+        <v/>
+      </c>
+      <c r="H22">
+        <f>F22-('README &amp; Assumptions'!B21-'README &amp; Assumptions'!C31)</f>
         <v/>
       </c>
     </row>
@@ -7715,6 +7847,25 @@
           <t>First</t>
         </is>
       </c>
+      <c r="B25">
+        <f>'README &amp; Assumptions'!D18</f>
+        <v/>
+      </c>
+      <c r="C25" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D25">
+        <f>B25*C25</f>
+        <v/>
+      </c>
+      <c r="E25">
+        <f>(B25-D25)*'README &amp; Assumptions'!E18</f>
+        <v/>
+      </c>
+      <c r="F25">
+        <f>(B25-D25)*(1-'README &amp; Assumptions'!E18)</f>
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="90" t="inlineStr">
@@ -8226,7 +8377,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="16">
     <mergeCell ref="B53:F53"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A33:F33"/>
@@ -8242,7 +8393,6 @@
     <mergeCell ref="B50:F50"/>
     <mergeCell ref="A30:F30"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A25:F25"/>
     <mergeCell ref="B49:F49"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8336,7 +8486,7 @@
         <v/>
       </c>
       <c r="C6" s="19">
-        <f>'User Behavior'!C11</f>
+        <f>'User Behavior'!C21</f>
         <v/>
       </c>
       <c r="D6" s="20">
@@ -8352,7 +8502,7 @@
         <v/>
       </c>
       <c r="G6" s="22">
-        <f>F6*'README &amp; Assumptions'!C29</f>
+        <f>F6*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8367,7 +8517,7 @@
         <v/>
       </c>
       <c r="C7" s="19">
-        <f>'User Behavior'!C11</f>
+        <f>'User Behavior'!C22</f>
         <v/>
       </c>
       <c r="D7" s="20">
@@ -8383,7 +8533,7 @@
         <v/>
       </c>
       <c r="G7" s="22">
-        <f>F7*'README &amp; Assumptions'!C29</f>
+        <f>F7*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8398,7 +8548,7 @@
         <v/>
       </c>
       <c r="C8" s="19">
-        <f>'User Behavior'!C11</f>
+        <f>'User Behavior'!C23</f>
         <v/>
       </c>
       <c r="D8" s="20">
@@ -8414,7 +8564,7 @@
         <v/>
       </c>
       <c r="G8" s="22">
-        <f>F8*'README &amp; Assumptions'!C29</f>
+        <f>F8*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8429,7 +8579,7 @@
         <v/>
       </c>
       <c r="C9" s="19">
-        <f>'User Behavior'!C11</f>
+        <f>'User Behavior'!C24</f>
         <v/>
       </c>
       <c r="D9" s="20">
@@ -8445,7 +8595,7 @@
         <v/>
       </c>
       <c r="G9" s="22">
-        <f>F9*'README &amp; Assumptions'!C29</f>
+        <f>F9*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8460,7 +8610,7 @@
         <v/>
       </c>
       <c r="C10" s="19">
-        <f>'User Behavior'!C11</f>
+        <f>'User Behavior'!C25</f>
         <v/>
       </c>
       <c r="D10" s="20">
@@ -8476,14 +8626,14 @@
         <v/>
       </c>
       <c r="G10" s="22">
-        <f>F10*'README &amp; Assumptions'!C29</f>
+        <f>F10*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>First Suite</t>
         </is>
       </c>
       <c r="B11" s="18">
@@ -8491,7 +8641,7 @@
         <v/>
       </c>
       <c r="C11" s="19">
-        <f>'User Behavior'!C11</f>
+        <f>'User Behavior'!C26</f>
         <v/>
       </c>
       <c r="D11" s="20">
@@ -8507,14 +8657,14 @@
         <v/>
       </c>
       <c r="G11" s="22">
-        <f>F11*'README &amp; Assumptions'!C29</f>
+        <f>F11*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>Refuel</t>
+          <t>Cockpit</t>
         </is>
       </c>
       <c r="B12" s="18">
@@ -8522,7 +8672,7 @@
         <v/>
       </c>
       <c r="C12" s="19">
-        <f>'User Behavior'!C11</f>
+        <f>'User Behavior'!C27</f>
         <v/>
       </c>
       <c r="D12" s="20">
@@ -8538,21 +8688,52 @@
         <v/>
       </c>
       <c r="G12" s="22">
-        <f>F12*'README &amp; Assumptions'!C29</f>
+        <f>F12*'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Refuel</t>
+        </is>
+      </c>
+      <c r="B13">
+        <f>'README &amp; Assumptions'!D21</f>
+        <v/>
+      </c>
+      <c r="C13">
+        <f>'User Behavior'!C28</f>
+        <v/>
+      </c>
+      <c r="D13">
+        <f>B13*(1-C13)</f>
+        <v/>
+      </c>
+      <c r="E13">
+        <f>'README &amp; Assumptions'!E21</f>
+        <v/>
+      </c>
+      <c r="F13">
+        <f>D13*E13</f>
+        <v/>
+      </c>
+      <c r="G13">
+        <f>F13*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>CUMULATIVE LIABILITY OVER 12 MONTHS (at base 1,000 users, default mix)</t>
+          <t>CUMULATIVE LIABILITY OVER 12 MONTHS (at base 1,000 users, depending on mix)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Assumes 20%/mo redemption rate. Net accrual = carried - redeemed each month.</t>
+          <t>Assumes 20%/mo redemption rate. Net accrual = carried − redeemed.</t>
         </is>
       </c>
     </row>
@@ -8600,19 +8781,18 @@
         </is>
       </c>
       <c r="B19" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
-        <v/>
-      </c>
-      <c r="C19" s="20">
-        <f>0</f>
-        <v/>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
+        <v/>
+      </c>
+      <c r="C19" s="20" t="n">
+        <v>0</v>
       </c>
       <c r="D19" s="33">
         <f>B19-C19</f>
         <v/>
       </c>
       <c r="E19" s="25">
-        <f>D19*'README &amp; Assumptions'!C29</f>
+        <f>D19*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8623,7 +8803,7 @@
         </is>
       </c>
       <c r="B20" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C20" s="20">
@@ -8635,7 +8815,7 @@
         <v/>
       </c>
       <c r="E20" s="25">
-        <f>D20*'README &amp; Assumptions'!C29</f>
+        <f>D20*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8646,7 +8826,7 @@
         </is>
       </c>
       <c r="B21" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C21" s="20">
@@ -8658,7 +8838,7 @@
         <v/>
       </c>
       <c r="E21" s="25">
-        <f>D21*'README &amp; Assumptions'!C29</f>
+        <f>D21*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8669,7 +8849,7 @@
         </is>
       </c>
       <c r="B22" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C22" s="20">
@@ -8681,7 +8861,7 @@
         <v/>
       </c>
       <c r="E22" s="25">
-        <f>D22*'README &amp; Assumptions'!C29</f>
+        <f>D22*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8692,7 +8872,7 @@
         </is>
       </c>
       <c r="B23" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C23" s="20">
@@ -8704,7 +8884,7 @@
         <v/>
       </c>
       <c r="E23" s="25">
-        <f>D23*'README &amp; Assumptions'!C29</f>
+        <f>D23*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8715,7 +8895,7 @@
         </is>
       </c>
       <c r="B24" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C24" s="20">
@@ -8727,7 +8907,7 @@
         <v/>
       </c>
       <c r="E24" s="25">
-        <f>D24*'README &amp; Assumptions'!C29</f>
+        <f>D24*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8738,7 +8918,7 @@
         </is>
       </c>
       <c r="B25" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C25" s="20">
@@ -8750,7 +8930,7 @@
         <v/>
       </c>
       <c r="E25" s="25">
-        <f>D25*'README &amp; Assumptions'!C29</f>
+        <f>D25*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8761,7 +8941,7 @@
         </is>
       </c>
       <c r="B26" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C26" s="20">
@@ -8773,7 +8953,7 @@
         <v/>
       </c>
       <c r="E26" s="25">
-        <f>D26*'README &amp; Assumptions'!C29</f>
+        <f>D26*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8784,7 +8964,7 @@
         </is>
       </c>
       <c r="B27" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C27" s="20">
@@ -8796,7 +8976,7 @@
         <v/>
       </c>
       <c r="E27" s="25">
-        <f>D27*'README &amp; Assumptions'!C29</f>
+        <f>D27*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8807,7 +8987,7 @@
         </is>
       </c>
       <c r="B28" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C28" s="20">
@@ -8819,7 +8999,7 @@
         <v/>
       </c>
       <c r="E28" s="25">
-        <f>D28*'README &amp; Assumptions'!C29</f>
+        <f>D28*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8830,7 +9010,7 @@
         </is>
       </c>
       <c r="B29" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C29" s="20">
@@ -8842,7 +9022,7 @@
         <v/>
       </c>
       <c r="E29" s="25">
-        <f>D29*'README &amp; Assumptions'!C29</f>
+        <f>D29*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8853,7 +9033,7 @@
         </is>
       </c>
       <c r="B30" s="20">
-        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B34:B40)</f>
+        <f>1000*SUMPRODUCT(F6:F12,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
       <c r="C30" s="20">
@@ -8865,7 +9045,7 @@
         <v/>
       </c>
       <c r="E30" s="25">
-        <f>D30*'README &amp; Assumptions'!C29</f>
+        <f>D30*'README &amp; Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -8880,7 +9060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9131,7 +9311,7 @@
         <v>1000</v>
       </c>
       <c r="F16" s="25">
-        <f>E16*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)*12</f>
+        <f>E16*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)*12</f>
         <v/>
       </c>
     </row>
@@ -9156,7 +9336,7 @@
         <v>6000</v>
       </c>
       <c r="F17" s="25">
-        <f>E17*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)*12</f>
+        <f>E17*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)*12</f>
         <v/>
       </c>
     </row>
@@ -9181,7 +9361,7 @@
         <v>18000</v>
       </c>
       <c r="F18" s="25">
-        <f>E18*SUMPRODUCT('Per-Tier Unit Economics'!B5:B11+'Per-Tier Unit Economics'!F5:F11,'README &amp; Assumptions'!B34:B40)*12</f>
+        <f>E18*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)*12</f>
         <v/>
       </c>
     </row>
@@ -9243,15 +9423,15 @@
         </is>
       </c>
       <c r="B24" s="21">
-        <f>'Per-Tier Unit Economics'!B5</f>
+        <f>'Per-Tier Unit Economics'!B7</f>
         <v/>
       </c>
       <c r="C24" s="21">
-        <f>'Per-Tier Unit Economics'!E5</f>
+        <f>'Per-Tier Unit Economics'!E7</f>
         <v/>
       </c>
       <c r="D24" s="21">
-        <f>'README &amp; Assumptions'!B50</f>
+        <f>'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="E24" s="22">
@@ -9273,15 +9453,15 @@
         </is>
       </c>
       <c r="B25" s="21">
-        <f>'Per-Tier Unit Economics'!B6</f>
+        <f>'Per-Tier Unit Economics'!B8</f>
         <v/>
       </c>
       <c r="C25" s="21">
-        <f>'Per-Tier Unit Economics'!E6</f>
+        <f>'Per-Tier Unit Economics'!E8</f>
         <v/>
       </c>
       <c r="D25" s="21">
-        <f>'README &amp; Assumptions'!B50</f>
+        <f>'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="E25" s="22">
@@ -9303,15 +9483,15 @@
         </is>
       </c>
       <c r="B26" s="21">
-        <f>'Per-Tier Unit Economics'!B7</f>
+        <f>'Per-Tier Unit Economics'!B9</f>
         <v/>
       </c>
       <c r="C26" s="21">
-        <f>'Per-Tier Unit Economics'!E7</f>
+        <f>'Per-Tier Unit Economics'!E9</f>
         <v/>
       </c>
       <c r="D26" s="21">
-        <f>'README &amp; Assumptions'!B50</f>
+        <f>'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="E26" s="22">
@@ -9333,15 +9513,15 @@
         </is>
       </c>
       <c r="B27" s="21">
-        <f>'Per-Tier Unit Economics'!B8</f>
+        <f>'Per-Tier Unit Economics'!B10</f>
         <v/>
       </c>
       <c r="C27" s="21">
-        <f>'Per-Tier Unit Economics'!E8</f>
+        <f>'Per-Tier Unit Economics'!E10</f>
         <v/>
       </c>
       <c r="D27" s="21">
-        <f>'README &amp; Assumptions'!B50</f>
+        <f>'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="E27" s="22">
@@ -9363,15 +9543,15 @@
         </is>
       </c>
       <c r="B28" s="21">
-        <f>'Per-Tier Unit Economics'!B9</f>
+        <f>'Per-Tier Unit Economics'!B11</f>
         <v/>
       </c>
       <c r="C28" s="21">
-        <f>'Per-Tier Unit Economics'!E9</f>
+        <f>'Per-Tier Unit Economics'!E11</f>
         <v/>
       </c>
       <c r="D28" s="21">
-        <f>'README &amp; Assumptions'!B50</f>
+        <f>'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="E28" s="22">
@@ -9389,19 +9569,19 @@
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>First Suite</t>
         </is>
       </c>
       <c r="B29" s="21">
-        <f>'Per-Tier Unit Economics'!B10</f>
+        <f>'Per-Tier Unit Economics'!B12</f>
         <v/>
       </c>
       <c r="C29" s="21">
-        <f>'Per-Tier Unit Economics'!E10</f>
+        <f>'Per-Tier Unit Economics'!E12</f>
         <v/>
       </c>
       <c r="D29" s="21">
-        <f>'README &amp; Assumptions'!B50</f>
+        <f>'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="E29" s="22">
@@ -9409,7 +9589,7 @@
         <v/>
       </c>
       <c r="F29" s="10" t="n">
-        <v>24.99</v>
+        <v>45</v>
       </c>
       <c r="G29" s="35">
         <f>F29-E29</f>
@@ -9419,19 +9599,19 @@
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Refuel</t>
+          <t>Cockpit</t>
         </is>
       </c>
       <c r="B30" s="21">
-        <f>'Per-Tier Unit Economics'!B11</f>
+        <f>'Per-Tier Unit Economics'!B13</f>
         <v/>
       </c>
       <c r="C30" s="21">
-        <f>'Per-Tier Unit Economics'!E11</f>
+        <f>'Per-Tier Unit Economics'!E13</f>
         <v/>
       </c>
       <c r="D30" s="21">
-        <f>'README &amp; Assumptions'!B50</f>
+        <f>'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
       <c r="E30" s="22">
@@ -9439,10 +9619,40 @@
         <v/>
       </c>
       <c r="F30" s="10" t="n">
-        <v>5.99</v>
+        <v>24.99</v>
       </c>
       <c r="G30" s="35">
         <f>F30-E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Refuel</t>
+        </is>
+      </c>
+      <c r="B31">
+        <f>'README &amp; Assumptions'!B21</f>
+        <v/>
+      </c>
+      <c r="C31">
+        <f>'README &amp; Assumptions'!C31</f>
+        <v/>
+      </c>
+      <c r="D31">
+        <f>'README &amp; Assumptions'!B53</f>
+        <v/>
+      </c>
+      <c r="E31">
+        <f>C31+D31</f>
+        <v/>
+      </c>
+      <c r="F31" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="G31">
+        <f>F31-E31</f>
         <v/>
       </c>
     </row>
@@ -9513,11 +9723,11 @@
         <v>0.05</v>
       </c>
       <c r="B5" s="24">
-        <f>1000*5.99*A5</f>
+        <f>1000*'README &amp; Assumptions'!B21*A5</f>
         <v/>
       </c>
       <c r="C5" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A5</f>
+        <f>1000*'README &amp; Assumptions'!C31*A5</f>
         <v/>
       </c>
       <c r="D5" s="25">
@@ -9534,11 +9744,11 @@
         <v>0.1</v>
       </c>
       <c r="B6" s="24">
-        <f>1000*5.99*A6</f>
+        <f>1000*'README &amp; Assumptions'!B21*A6</f>
         <v/>
       </c>
       <c r="C6" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A6</f>
+        <f>1000*'README &amp; Assumptions'!C31*A6</f>
         <v/>
       </c>
       <c r="D6" s="25">
@@ -9555,11 +9765,11 @@
         <v>0.15</v>
       </c>
       <c r="B7" s="24">
-        <f>1000*5.99*A7</f>
+        <f>1000*'README &amp; Assumptions'!B21*A7</f>
         <v/>
       </c>
       <c r="C7" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A7</f>
+        <f>1000*'README &amp; Assumptions'!C31*A7</f>
         <v/>
       </c>
       <c r="D7" s="25">
@@ -9576,11 +9786,11 @@
         <v>0.2</v>
       </c>
       <c r="B8" s="24">
-        <f>1000*5.99*A8</f>
+        <f>1000*'README &amp; Assumptions'!B21*A8</f>
         <v/>
       </c>
       <c r="C8" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A8</f>
+        <f>1000*'README &amp; Assumptions'!C31*A8</f>
         <v/>
       </c>
       <c r="D8" s="25">
@@ -9597,11 +9807,11 @@
         <v>0.25</v>
       </c>
       <c r="B9" s="24">
-        <f>1000*5.99*A9</f>
+        <f>1000*'README &amp; Assumptions'!B21*A9</f>
         <v/>
       </c>
       <c r="C9" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A9</f>
+        <f>1000*'README &amp; Assumptions'!C31*A9</f>
         <v/>
       </c>
       <c r="D9" s="25">
@@ -9618,11 +9828,11 @@
         <v>0.3</v>
       </c>
       <c r="B10" s="24">
-        <f>1000*5.99*A10</f>
+        <f>1000*'README &amp; Assumptions'!B21*A10</f>
         <v/>
       </c>
       <c r="C10" s="24">
-        <f>1000*'README &amp; Assumptions'!C29*A10</f>
+        <f>1000*'README &amp; Assumptions'!C31*A10</f>
         <v/>
       </c>
       <c r="D10" s="25">
@@ -10787,11 +10997,11 @@
         </is>
       </c>
       <c r="B6" s="42" t="n">
-        <v>0.45</v>
+        <v>1.34</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Blended 30-day plan: HK/KR $0.26, UK $0.32, USA $0.35, JP $0.37, AU $0.43, UAE $1.00</t>
+          <t>Current Samurai actual blended (75/20/5 mix). Tier-A $0.85, Tier-B $1.40, Tier-C $8.50.</t>
         </is>
       </c>
     </row>
@@ -10855,7 +11065,7 @@
         </is>
       </c>
       <c r="B12" s="45">
-        <f>'User Behavior'!C11</f>
+        <f>'User Behavior'!C13</f>
         <v/>
       </c>
     </row>
@@ -10866,7 +11076,7 @@
         </is>
       </c>
       <c r="B13" s="45">
-        <f>'User Behavior'!D11</f>
+        <f>'User Behavior'!D14</f>
         <v/>
       </c>
     </row>
@@ -10877,7 +11087,7 @@
         </is>
       </c>
       <c r="B14" s="46">
-        <f>'README &amp; Assumptions'!B20</f>
+        <f>'README &amp; Assumptions'!B21</f>
         <v/>
       </c>
     </row>
@@ -11242,7 +11452,7 @@
     <row r="23">
       <c r="A23" s="48" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>First Suite</t>
         </is>
       </c>
       <c r="B23" s="49">
@@ -11294,6 +11504,61 @@
         <v/>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B24">
+        <f>'README &amp; Assumptions'!D20</f>
+        <v/>
+      </c>
+      <c r="C24">
+        <f>B24*$B$12</f>
+        <v/>
+      </c>
+      <c r="D24">
+        <f>C24*$B$9</f>
+        <v/>
+      </c>
+      <c r="E24">
+        <f>$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="F24">
+        <f>$B$13*1*$B$9</f>
+        <v/>
+      </c>
+      <c r="G24">
+        <f>D24+F24-E24</f>
+        <v/>
+      </c>
+      <c r="H24">
+        <f>G24</f>
+        <v/>
+      </c>
+      <c r="I24">
+        <f>G24/0.7</f>
+        <v/>
+      </c>
+      <c r="J24">
+        <f>G24/0.5</f>
+        <v/>
+      </c>
+      <c r="K24">
+        <f>G24/0.3</f>
+        <v/>
+      </c>
+      <c r="L24">
+        <f>'README &amp; Assumptions'!B20</f>
+        <v/>
+      </c>
+      <c r="M24">
+        <f>IFERROR((L24-G24)/L24,0)</f>
+        <v/>
+      </c>
+    </row>
     <row r="26">
       <c r="A26" s="40" t="inlineStr">
         <is>
@@ -11471,7 +11736,7 @@
     <row r="33">
       <c r="A33" s="48" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>First Suite</t>
         </is>
       </c>
       <c r="B33" s="46">
@@ -11495,6 +11760,33 @@
         <v/>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B34">
+        <f>'README &amp; Assumptions'!B20</f>
+        <v/>
+      </c>
+      <c r="C34">
+        <f>C24*$B$6+$B$13*1*$B$6-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="D34">
+        <f>C24*$B$7+$B$13*1*$B$7-$B$13*$B$14</f>
+        <v/>
+      </c>
+      <c r="E34">
+        <f>C34-D34</f>
+        <v/>
+      </c>
+      <c r="F34">
+        <f>E34*10000</f>
+        <v/>
+      </c>
+    </row>
     <row r="35">
       <c r="A35" s="43" t="inlineStr">
         <is>
@@ -11533,7 +11825,7 @@
     <row r="40">
       <c r="A40" s="39" t="inlineStr">
         <is>
-          <t>5. Negotiation summary at bottom: if you push Samurai from $0.45 to $0.30/GB, here is the per-user savings × 10K users.</t>
+          <t>5. Negotiation summary at bottom: if you push wholesale from $1.34 to $0.30/GB, here is the per-user savings × 10K users.</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -414,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="128">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -582,6 +582,7 @@
     <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="169" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1257,7 +1258,7 @@
         <v>4.99</v>
       </c>
       <c r="C21" s="11">
-        <f>B20*12</f>
+        <f>B21*12</f>
         <v/>
       </c>
       <c r="D21" s="12" t="n">
@@ -6911,7 +6912,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6938,6 +6939,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -7112,6 +7114,11 @@
       <c r="F10" s="11">
         <f>'README &amp; Assumptions'!C31-E10</f>
         <v/>
+      </c>
+      <c r="I10" s="92" t="inlineStr">
+        <is>
+          <t>⚠ Mix assumed same as First — update post-launch with real data</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -9365,6 +9372,7 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
@@ -9591,9 +9599,10 @@
       <c r="F29" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="G29" s="35">
-        <f>F29-E29</f>
-        <v/>
+      <c r="G29" s="127" t="inlineStr">
+        <is>
+          <t>⚠ PLACEHOLDER — Crew SIM has no First Suite tier. Akito to validate competitive price.</t>
+        </is>
       </c>
     </row>
     <row r="30">

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -37,7 +37,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="17">
+  <numFmts count="18">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -55,8 +55,9 @@
     <numFmt numFmtId="178" formatCode="#,##0&quot; users&quot;"/>
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0&quot; /mo&quot;"/>
     <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00&quot; /user/mo&quot;"/>
+    <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -250,6 +251,13 @@
       <color rgb="00D71921"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Helvetica Neue"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00D71921"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="19">
     <fill>
@@ -414,7 +422,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="131">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -583,6 +591,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="169" fontId="26" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="181" fontId="22" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4429,19 +4440,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4451,6 +4462,13 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>PURPOSE: Take Tab 3 per-user profit × user counts at different scales = total business P&amp;L. Answers "what does the business look like at N users?"</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -4671,7 +4689,260 @@
         <v/>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="94" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE — 1,000 users (the Base scenario explained step-by-step)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t>Step 1: Split 1,000 users by cabin tier (using locked mix %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B12" s="41" t="inlineStr">
+        <is>
+          <t>% of users</t>
+        </is>
+      </c>
+      <c r="C12" s="41" t="inlineStr">
+        <is>
+          <t># of users</t>
+        </is>
+      </c>
+      <c r="D12" s="41" t="inlineStr">
+        <is>
+          <t>Profit/user/mo</t>
+        </is>
+      </c>
+      <c r="E12" s="41" t="inlineStr">
+        <is>
+          <t>Total tier profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="90" t="inlineStr">
+        <is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="B13" s="57" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C13" s="71" t="n">
+        <v>500</v>
+      </c>
+      <c r="D13" s="54" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E13" s="86" t="n">
+        <v>1825</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="90" t="inlineStr">
+        <is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B14" s="57" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C14" s="71" t="n">
+        <v>180</v>
+      </c>
+      <c r="D14" s="54" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="E14" s="86" t="n">
+        <v>2448</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="90" t="inlineStr">
+        <is>
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B15" s="57" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="C15" s="71" t="n">
+        <v>130</v>
+      </c>
+      <c r="D15" s="54" t="n">
+        <v>13.35</v>
+      </c>
+      <c r="E15" s="86" t="n">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="90" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="B16" s="57" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C16" s="71" t="n">
+        <v>80</v>
+      </c>
+      <c r="D16" s="54" t="n">
+        <v>21.84</v>
+      </c>
+      <c r="E16" s="86" t="n">
+        <v>1747</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="90" t="inlineStr">
+        <is>
+          <t>First</t>
+        </is>
+      </c>
+      <c r="B17" s="57" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C17" s="71" t="n">
+        <v>30</v>
+      </c>
+      <c r="D17" s="54" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="E17" s="86" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="90" t="inlineStr">
+        <is>
+          <t>First Suite</t>
+        </is>
+      </c>
+      <c r="B18" s="57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C18" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="D18" s="54" t="n">
+        <v>33</v>
+      </c>
+      <c r="E18" s="86" t="n">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="90" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B19" s="57" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C19" s="71" t="n">
+        <v>30</v>
+      </c>
+      <c r="D19" s="54" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="E19" s="86" t="n">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="43" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C20" s="71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="39" t="inlineStr">
+        <is>
+          <t>Monthly Gross Profit →</t>
+        </is>
+      </c>
+      <c r="E20" s="87" t="n">
+        <v>9590</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t>Step 2: Subtract operating cost</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="90" t="inlineStr">
+        <is>
+          <t>Monthly Gross Profit</t>
+        </is>
+      </c>
+      <c r="B23" s="128" t="n">
+        <v>9590</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="90" t="inlineStr">
+        <is>
+          <t>OPEX (1,000 users × $1.80)</t>
+        </is>
+      </c>
+      <c r="B24" s="128" t="n">
+        <v>-1800</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="90" t="inlineStr">
+        <is>
+          <t>Monthly Net Profit</t>
+        </is>
+      </c>
+      <c r="B25" s="129" t="n">
+        <v>7790</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="90" t="inlineStr">
+        <is>
+          <t>Annual Net Profit</t>
+        </is>
+      </c>
+      <c r="B26" s="129" t="n">
+        <v>93480</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="130" t="inlineStr">
+        <is>
+          <t>Bottom line: 1,000 users → $93,480/year. Scale to 10,000 → ~$935K/year. Scale to 100K → ~$9.35M/year.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A11:J11"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6939,7 +7210,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
@@ -9372,7 +9642,6 @@
         <v/>
       </c>
     </row>
-    <row r="20"/>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -37,7 +37,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="18">
+  <numFmts count="19">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -56,6 +56,7 @@
     <numFmt numFmtId="179" formatCode="&quot;$&quot;#,##0&quot; /mo&quot;"/>
     <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00&quot; /user/mo&quot;"/>
     <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
+    <numFmt numFmtId="182" formatCode="0.0&quot; top-ups&quot;"/>
   </numFmts>
   <fonts count="36">
     <font>
@@ -422,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="131">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -594,6 +595,9 @@
     <xf numFmtId="181" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="181" fontId="22" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="182" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="182" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="174" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -10412,7 +10416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10538,15 +10542,15 @@
     <row r="7">
       <c r="A7" s="90" t="inlineStr">
         <is>
-          <t>Economy (PAYG)</t>
+          <t>Economy (PAYG realistic — 2.5×/mo)</t>
         </is>
       </c>
       <c r="B7" s="46">
-        <f>'README &amp; Assumptions'!B14</f>
+        <f>'README &amp; Assumptions'!B14*2.5</f>
         <v/>
       </c>
       <c r="C7" s="49">
-        <f>'User Behavior'!D21</f>
+        <f>'User Behavior'!D21*2.5</f>
         <v/>
       </c>
       <c r="D7" s="46">
@@ -11179,10 +11183,164 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="94" t="inlineStr">
+        <is>
+          <t>ECONOMY VARIANTS — what if a PAYG user buys different # of top-ups per month?</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="39" t="inlineStr">
+        <is>
+          <t>Same product ($4.99 per 1 GB), different user behavior. Light = 1 top-up (tried once). Average = 2.5 top-ups (the realistic Economy user — used in Row 7 above). Heavy = 4 top-ups (many layovers).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="41" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B45" s="41" t="inlineStr">
+        <is>
+          <t># Top-ups/mo</t>
+        </is>
+      </c>
+      <c r="C45" s="41" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D45" s="41" t="inlineStr">
+        <is>
+          <t>GB Consumed</t>
+        </is>
+      </c>
+      <c r="E45" s="41" t="inlineStr">
+        <is>
+          <t>COGS @ $1.34/GB</t>
+        </is>
+      </c>
+      <c r="F45" s="41" t="inlineStr">
+        <is>
+          <t>Gross Profit</t>
+        </is>
+      </c>
+      <c r="G45" s="41" t="inlineStr">
+        <is>
+          <t>Gross Margin</t>
+        </is>
+      </c>
+      <c r="H45" s="41" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="90" t="inlineStr">
+        <is>
+          <t>Trial (one-and-done)</t>
+        </is>
+      </c>
+      <c r="B46" s="131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="54" t="n">
+        <v>4.99</v>
+      </c>
+      <c r="D46" s="82" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="54" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="F46" s="54" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="G46" s="26" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="H46" s="39" t="inlineStr">
+        <is>
+          <t>User buys once, never returns. Pure single-tx profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="93" t="inlineStr">
+        <is>
+          <t>Realistic Economy (used in Row 7)</t>
+        </is>
+      </c>
+      <c r="B47" s="132" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C47" s="59" t="n">
+        <v>12.48</v>
+      </c>
+      <c r="D47" s="133" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E47" s="59" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F47" s="59" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="G47" s="104" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="H47" s="77" t="inlineStr">
+        <is>
+          <t>Typical PAYG crew member, 8-12 layovers, buys when needed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="90" t="inlineStr">
+        <is>
+          <t>Heavy Economy</t>
+        </is>
+      </c>
+      <c r="B48" s="131" t="n">
+        <v>4</v>
+      </c>
+      <c r="C48" s="54" t="n">
+        <v>19.96</v>
+      </c>
+      <c r="D48" s="82" t="n">
+        <v>4</v>
+      </c>
+      <c r="E48" s="54" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="F48" s="54" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="G48" s="26" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="H48" s="39" t="inlineStr">
+        <is>
+          <t>High-frequency Economy user. Candidate to upsell to subscription.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="92" t="inlineStr">
+        <is>
+          <t>ℹ Insight: Margin stays at 73% regardless of usage. But absolute profit scales linearly with frequency. Goal: get trial users to become realistic users (2.5×). The Heavy column shows our upsell ceiling before they should switch to subscription.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="23">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="B23:M23"/>
+    <mergeCell ref="A43:M43"/>
     <mergeCell ref="A38:M38"/>
     <mergeCell ref="B19:M19"/>
     <mergeCell ref="A40:M40"/>
@@ -11196,11 +11354,13 @@
     <mergeCell ref="I5:M5"/>
     <mergeCell ref="B25:M25"/>
     <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A50:M50"/>
     <mergeCell ref="B22:M22"/>
     <mergeCell ref="A3:M3"/>
     <mergeCell ref="B18:M18"/>
     <mergeCell ref="B21:M21"/>
     <mergeCell ref="A2:M2"/>
+    <mergeCell ref="A42:M42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -423,7 +423,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -598,6 +598,8 @@
     <xf numFmtId="182" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="182" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="174" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4444,7 +4446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4528,7 +4530,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Conservative</t>
+          <t>Beta (early testing)</t>
         </is>
       </c>
       <c r="B5" s="23" t="n">
@@ -4570,7 +4572,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Base</t>
+          <t>Soft Launch (Emirates seed)</t>
         </is>
       </c>
       <c r="B6" s="23" t="n">
@@ -4612,7 +4614,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Aggressive</t>
+          <t>Crew Network (Emirates + Etihad)</t>
         </is>
       </c>
       <c r="B7" s="23" t="n">
@@ -4654,7 +4656,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>Hockey Stick</t>
+          <t>Multi-Airline (+ JAL + ANA)</t>
         </is>
       </c>
       <c r="B8" s="23" t="n">
@@ -4693,165 +4695,212 @@
         <v/>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="43" t="inlineStr">
+        <is>
+          <t>Regional Scale</t>
+        </is>
+      </c>
+      <c r="B9" s="71" t="n">
+        <v>50000</v>
+      </c>
+      <c r="C9" s="86">
+        <f>B9*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
+        <v/>
+      </c>
+      <c r="D9" s="86">
+        <f>B9*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
+        <v/>
+      </c>
+      <c r="E9" s="86">
+        <f>C9-D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="26">
+        <f>IFERROR(E9/C9,0)</f>
+        <v/>
+      </c>
+      <c r="G9" s="86">
+        <f>B9*'README &amp; Assumptions'!B53</f>
+        <v/>
+      </c>
+      <c r="H9" s="86">
+        <f>E9-G9</f>
+        <v/>
+      </c>
+      <c r="I9" s="26">
+        <f>IFERROR(H9/C9,0)</f>
+        <v/>
+      </c>
+      <c r="J9" s="86">
+        <f>H9*12</f>
+        <v/>
+      </c>
+    </row>
     <row r="10">
-      <c r="A10" s="94" t="inlineStr">
+      <c r="A10" s="73" t="inlineStr">
+        <is>
+          <t>100K Target (full vision)</t>
+        </is>
+      </c>
+      <c r="B10" s="134" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C10" s="135">
+        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
+        <v/>
+      </c>
+      <c r="D10" s="135">
+        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
+        <v/>
+      </c>
+      <c r="E10" s="135">
+        <f>C10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="104">
+        <f>IFERROR(E10/C10,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="135">
+        <f>B10*'README &amp; Assumptions'!B53</f>
+        <v/>
+      </c>
+      <c r="H10" s="135">
+        <f>E10-G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="104">
+        <f>IFERROR(H10/C10,0)</f>
+        <v/>
+      </c>
+      <c r="J10" s="135">
+        <f>H10*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="94" t="inlineStr">
         <is>
           <t>WORKED EXAMPLE — 1,000 users (the Base scenario explained step-by-step)</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="43" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="43" t="inlineStr">
         <is>
           <t>Step 1: Split 1,000 users by cabin tier (using locked mix %)</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="41" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="41" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B12" s="41" t="inlineStr">
+      <c r="B14" s="41" t="inlineStr">
         <is>
           <t>% of users</t>
         </is>
       </c>
-      <c r="C12" s="41" t="inlineStr">
+      <c r="C14" s="41" t="inlineStr">
         <is>
           <t># of users</t>
         </is>
       </c>
-      <c r="D12" s="41" t="inlineStr">
+      <c r="D14" s="41" t="inlineStr">
         <is>
           <t>Profit/user/mo</t>
         </is>
       </c>
-      <c r="E12" s="41" t="inlineStr">
+      <c r="E14" s="41" t="inlineStr">
         <is>
           <t>Total tier profit</t>
         </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="90" t="inlineStr">
-        <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B13" s="57" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C13" s="71" t="n">
-        <v>500</v>
-      </c>
-      <c r="D13" s="54" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E13" s="86" t="n">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="90" t="inlineStr">
-        <is>
-          <t>Roster Bundle</t>
-        </is>
-      </c>
-      <c r="B14" s="57" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="C14" s="71" t="n">
-        <v>180</v>
-      </c>
-      <c r="D14" s="54" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="E14" s="86" t="n">
-        <v>2448</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="90" t="inlineStr">
         <is>
-          <t>Premium Economy</t>
+          <t>Economy</t>
         </is>
       </c>
       <c r="B15" s="57" t="n">
-        <v>0.13</v>
+        <v>0.5</v>
       </c>
       <c r="C15" s="71" t="n">
-        <v>130</v>
+        <v>500</v>
       </c>
       <c r="D15" s="54" t="n">
-        <v>13.35</v>
+        <v>3.65</v>
       </c>
       <c r="E15" s="86" t="n">
-        <v>1736</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="90" t="inlineStr">
         <is>
-          <t>Business</t>
+          <t>Roster Bundle</t>
         </is>
       </c>
       <c r="B16" s="57" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
       </c>
       <c r="C16" s="71" t="n">
-        <v>80</v>
+        <v>180</v>
       </c>
       <c r="D16" s="54" t="n">
-        <v>21.84</v>
+        <v>13.6</v>
       </c>
       <c r="E16" s="86" t="n">
-        <v>1747</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="90" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Premium Economy</t>
         </is>
       </c>
       <c r="B17" s="57" t="n">
-        <v>0.03</v>
+        <v>0.13</v>
       </c>
       <c r="C17" s="71" t="n">
-        <v>30</v>
+        <v>130</v>
       </c>
       <c r="D17" s="54" t="n">
-        <v>23.33</v>
+        <v>13.35</v>
       </c>
       <c r="E17" s="86" t="n">
-        <v>700</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="90" t="inlineStr">
         <is>
-          <t>First Suite</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="B18" s="57" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="C18" s="71" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="D18" s="54" t="n">
-        <v>33</v>
+        <v>21.84</v>
       </c>
       <c r="E18" s="86" t="n">
-        <v>660</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="90" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>First</t>
         </is>
       </c>
       <c r="B19" s="57" t="n">
@@ -4861,79 +4910,119 @@
         <v>30</v>
       </c>
       <c r="D19" s="54" t="n">
+        <v>23.33</v>
+      </c>
+      <c r="E19" s="86" t="n">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="90" t="inlineStr">
+        <is>
+          <t>First Suite</t>
+        </is>
+      </c>
+      <c r="B20" s="57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C20" s="71" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" s="54" t="n">
+        <v>33</v>
+      </c>
+      <c r="E20" s="86" t="n">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="90" t="inlineStr">
+        <is>
+          <t>Cockpit</t>
+        </is>
+      </c>
+      <c r="B21" s="57" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C21" s="71" t="n">
+        <v>30</v>
+      </c>
+      <c r="D21" s="54" t="n">
         <v>15.8</v>
       </c>
-      <c r="E19" s="86" t="n">
+      <c r="E21" s="86" t="n">
         <v>474</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="43" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="C20" s="71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D20" s="39" t="inlineStr">
-        <is>
-          <t>Monthly Gross Profit →</t>
-        </is>
-      </c>
-      <c r="E20" s="87" t="n">
-        <v>9590</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
         <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C22" s="71" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D22" s="39" t="inlineStr">
+        <is>
+          <t>Monthly Gross Profit →</t>
+        </is>
+      </c>
+      <c r="E22" s="87" t="n">
+        <v>9590</v>
+      </c>
+    </row>
+    <row r="23"/>
+    <row r="24">
+      <c r="A24" s="43" t="inlineStr">
+        <is>
           <t>Step 2: Subtract operating cost</t>
         </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="90" t="inlineStr">
-        <is>
-          <t>Monthly Gross Profit</t>
-        </is>
-      </c>
-      <c r="B23" s="128" t="n">
-        <v>9590</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="90" t="inlineStr">
-        <is>
-          <t>OPEX (1,000 users × $1.80)</t>
-        </is>
-      </c>
-      <c r="B24" s="128" t="n">
-        <v>-1800</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="90" t="inlineStr">
         <is>
-          <t>Monthly Net Profit</t>
-        </is>
-      </c>
-      <c r="B25" s="129" t="n">
-        <v>7790</v>
+          <t>Monthly Gross Profit</t>
+        </is>
+      </c>
+      <c r="B25" s="128" t="n">
+        <v>9590</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="90" t="inlineStr">
         <is>
+          <t>OPEX (1,000 users × $1.80)</t>
+        </is>
+      </c>
+      <c r="B26" s="128" t="n">
+        <v>-1800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="90" t="inlineStr">
+        <is>
+          <t>Monthly Net Profit</t>
+        </is>
+      </c>
+      <c r="B27" s="129" t="n">
+        <v>7790</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="90" t="inlineStr">
+        <is>
           <t>Annual Net Profit</t>
         </is>
       </c>
-      <c r="B26" s="129" t="n">
+      <c r="B28" s="129" t="n">
         <v>93480</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="130" t="inlineStr">
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" s="130" t="inlineStr">
         <is>
           <t>Bottom line: 1,000 users → $93,480/year. Scale to 10,000 → ~$935K/year. Scale to 100K → ~$9.35M/year.</t>
         </is>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -58,7 +58,7 @@
     <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
     <numFmt numFmtId="182" formatCode="0.0&quot; top-ups&quot;"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="39">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -259,8 +259,20 @@
       <color rgb="00D71921"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="19">
+  <fills count="23">
     <fill>
       <patternFill/>
     </fill>
@@ -352,6 +364,26 @@
         <fgColor rgb="005BAA82"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001a1a1a"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -423,7 +455,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="141">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -600,6 +632,11 @@
     <xf numFmtId="174" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4446,7 +4483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -4743,41 +4780,6 @@
           <t>100K Target (full vision)</t>
         </is>
       </c>
-      <c r="B10" s="134" t="n">
-        <v>100000</v>
-      </c>
-      <c r="C10" s="135">
-        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
-        <v/>
-      </c>
-      <c r="D10" s="135">
-        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
-        <v/>
-      </c>
-      <c r="E10" s="135">
-        <f>C10-D10</f>
-        <v/>
-      </c>
-      <c r="F10" s="104">
-        <f>IFERROR(E10/C10,0)</f>
-        <v/>
-      </c>
-      <c r="G10" s="135">
-        <f>B10*'README &amp; Assumptions'!B53</f>
-        <v/>
-      </c>
-      <c r="H10" s="135">
-        <f>E10-G10</f>
-        <v/>
-      </c>
-      <c r="I10" s="104">
-        <f>IFERROR(H10/C10,0)</f>
-        <v/>
-      </c>
-      <c r="J10" s="135">
-        <f>H10*12</f>
-        <v/>
-      </c>
     </row>
     <row r="11"/>
     <row r="12">
@@ -4960,19 +4962,7 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C22" s="71" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D22" s="39" t="inlineStr">
-        <is>
-          <t>Monthly Gross Profit →</t>
-        </is>
-      </c>
-      <c r="E22" s="87" t="n">
-        <v>9590</v>
-      </c>
-    </row>
-    <row r="23"/>
+    </row>
     <row r="24">
       <c r="A24" s="43" t="inlineStr">
         <is>
@@ -5016,11 +5006,7 @@
           <t>Annual Net Profit</t>
         </is>
       </c>
-      <c r="B28" s="129" t="n">
-        <v>93480</v>
-      </c>
-    </row>
-    <row r="29"/>
+    </row>
     <row r="30">
       <c r="A30" s="130" t="inlineStr">
         <is>
@@ -5046,15 +5032,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="65" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -5105,6 +5091,11 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="F5" s="136" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
@@ -5123,7 +5114,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Current model: COGS = consumed only, no upfront commitment</t>
+          <t>Current model assumption. Pay-per-order with wholesale supplier. NOT YET NEGOTIATED — pricing on price list but no contract signed.</t>
+        </is>
+      </c>
+      <c r="F6" s="137" t="inlineStr">
+        <is>
+          <t>UNCERTAIN — needs negotiation</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5140,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>10% discount but pre-buy 100% of pool, 15% breakage on unused inventory</t>
+          <t>FALLBACK if pay-per-order does not work. Pre-buy full pool, get 10% off. User confident this can be negotiated. 15% breakage on unused.</t>
+        </is>
+      </c>
+      <c r="F7" s="138" t="inlineStr">
+        <is>
+          <t>CONFIDENT — fallback</t>
         </is>
       </c>
     </row>
@@ -5165,7 +5166,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Bypass Samurai, save 40% but $5K/mo platform commitment</t>
+          <t>Bypass wholesale supplier, contract directly with upstream provider (eSIM Access or alternative). -40% estimate based on supplier margin analysis, NOT a real quote. Research in progress.</t>
+        </is>
+      </c>
+      <c r="F8" s="139" t="inlineStr">
+        <is>
+          <t>PENDING RESEARCH</t>
         </is>
       </c>
     </row>
@@ -5304,6 +5310,41 @@
       <c r="G14" s="25">
         <f>E14*12</f>
         <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="140" t="inlineStr">
+        <is>
+          <t>ACTION ITEMS (2026-06-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1. Negotiate Option A pay-per-order pricing with current wholesale supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2. If A fails: negotiate -10% bulk prepay terms with same supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3. Research direct SIM/eSIM upstream providers for Option C (in progress 2026-06-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>4. Get real quotes from direct providers to validate -40% assumption</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -6175,7 +6175,7 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
@@ -6244,7 +6244,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>Healthy SaaS (general travel — old base, upside)</t>
+          <t>🌴 Tourist Mix (light travel users — upside)</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
@@ -6275,7 +6275,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>Base (crew-skewed — new default)</t>
+          <t>✈️ Crew Standard (current base — realistic for cabin crew)</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
@@ -6306,7 +6306,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>Pure crew (power users dominate — downside)</t>
+          <t>🔥 Power Crew (heavy-fliers dominate — downside)</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
@@ -6337,7 +6337,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>High churn (bad acquisition)</t>
+          <t>💔 One-and-Done (bad acquisition, high churn)</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
@@ -6434,7 +6434,7 @@
     <row r="15">
       <c r="A15" s="90" t="inlineStr">
         <is>
-          <t>Pessimistic (low conversion)</t>
+          <t>🪤 PAYG Trap (most users stay on $4.99 Economy)</t>
         </is>
       </c>
       <c r="B15" s="57" t="n">
@@ -6470,7 +6470,7 @@
     <row r="16">
       <c r="A16" s="90" t="inlineStr">
         <is>
-          <t>Early-stage (months 1-6)</t>
+          <t>🚀 Launch Reality (Months 1-6, Economy-heavy)</t>
         </is>
       </c>
       <c r="B16" s="57" t="n">
@@ -6506,7 +6506,7 @@
     <row r="17">
       <c r="A17" s="93" t="inlineStr">
         <is>
-          <t>Base / current model</t>
+          <t>🎯 Steady State (CURRENT model — our default bet)</t>
         </is>
       </c>
       <c r="B17" s="56" t="n">
@@ -6542,7 +6542,7 @@
     <row r="18">
       <c r="A18" s="90" t="inlineStr">
         <is>
-          <t>Optimistic (high conversion)</t>
+          <t>📈 Ladder Climbers (strong subscription uptake)</t>
         </is>
       </c>
       <c r="B18" s="57" t="n">
@@ -6578,7 +6578,7 @@
     <row r="19">
       <c r="A19" s="90" t="inlineStr">
         <is>
-          <t>Subscription-heavy (year 2+)</t>
+          <t>👑 Mature Crew (Year 2+, subscriptions dominate)</t>
         </is>
       </c>
       <c r="B19" s="57" t="n">

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -58,7 +58,7 @@
     <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
     <numFmt numFmtId="182" formatCode="0.0&quot; top-ups&quot;"/>
   </numFmts>
-  <fonts count="39">
+  <fonts count="40">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -271,8 +271,12 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="007A5A10"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -384,6 +388,12 @@
         <fgColor rgb="001a1a1a"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFF00"/>
+        <bgColor rgb="00FFFF00"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -455,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="141">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -637,6 +647,16 @@
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="38" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="32" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="27" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -711,6 +731,31 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Balraj / Claude</author>
+  </authors>
+  <commentList>
+    <comment ref="C18" authorId="0" shapeId="0">
+      <text>
+        <t>PLACEHOLDER — no actual spend yet as of 2026-06-01. These fixed burn figures are estimates only. Update once real costs are tracked.</t>
+      </text>
+    </comment>
+    <comment ref="A26" authorId="0" shapeId="0">
+      <text>
+        <t>PLACEHOLDER — no actual spend yet as of 2026-06-01. These fixed burn figures are estimates only. Update once real costs are tracked.</t>
+      </text>
+    </comment>
+    <comment ref="C26" authorId="0" shapeId="0">
+      <text>
+        <t>PLACEHOLDER — no actual spend yet as of 2026-06-01. These fixed burn figures are estimates only. Update once real costs are tracked.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3471,7 +3516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -3800,7 +3845,7 @@
       <c r="B18" s="116" t="n">
         <v>0</v>
       </c>
-      <c r="C18" s="116" t="n">
+      <c r="C18" s="141" t="n">
         <v>10000</v>
       </c>
       <c r="D18" s="116" t="n">
@@ -3957,13 +4002,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="113" t="inlineStr">
+      <c r="A26" s="142" t="inlineStr">
         <is>
           <t>TOTAL fixed monthly burn (early)</t>
         </is>
       </c>
       <c r="B26" s="113" t="inlineStr"/>
-      <c r="C26" s="117">
+      <c r="C26" s="143">
         <f>SUM(C18:C24)</f>
         <v/>
       </c>
@@ -3992,86 +4037,78 @@
         </is>
       </c>
     </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="107" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="144" t="inlineStr">
+        <is>
+          <t>⚠️ PLACEHOLDER NOTICE</t>
+        </is>
+      </c>
+      <c r="B28" s="144" t="inlineStr">
+        <is>
+          <t>The "Early" fixed burn column (C) totalling ~$11,713/mo is a placeholder estimate. No actual expenses have been incurred as of 2026-06-01. Do not present this as real spend data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1"/>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="107" t="inlineStr">
         <is>
           <t>Section 3 — Variable scaling costs (marketing &amp; growth)</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="108" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="108" t="inlineStr">
         <is>
           <t>Cost line</t>
         </is>
       </c>
-      <c r="B30" s="108" t="inlineStr">
+      <c r="B31" s="108" t="inlineStr">
         <is>
           <t>Pre-launch</t>
         </is>
       </c>
-      <c r="C30" s="108" t="inlineStr">
+      <c r="C31" s="108" t="inlineStr">
         <is>
           <t>Early</t>
         </is>
       </c>
-      <c r="D30" s="108" t="inlineStr">
+      <c r="D31" s="108" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="E30" s="108" t="inlineStr">
+      <c r="E31" s="108" t="inlineStr">
         <is>
           <t>Notes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="109" t="inlineStr">
-        <is>
-          <t>Crew WhatsApp acquisition (Akito's network)</t>
-        </is>
-      </c>
-      <c r="B31" s="116" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="111" t="inlineStr">
-        <is>
-          <t>Free organic — the wedge</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="109" t="inlineStr">
         <is>
-          <t>Referral incentives ($5 credit per referral)</t>
+          <t>Crew WhatsApp acquisition (Akito's network)</t>
         </is>
       </c>
       <c r="B32" s="116" t="n">
         <v>0</v>
       </c>
       <c r="C32" s="116" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D32" s="116" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="E32" s="111" t="inlineStr">
         <is>
-          <t>Scale with user growth</t>
+          <t>Free organic — the wedge</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="109" t="inlineStr">
         <is>
-          <t>Paid social (Instagram crew creators)</t>
+          <t>Referral incentives ($5 credit per referral)</t>
         </is>
       </c>
       <c r="B33" s="116" t="n">
@@ -4081,43 +4118,43 @@
         <v>500</v>
       </c>
       <c r="D33" s="116" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="E33" s="111" t="inlineStr">
         <is>
-          <t>Phase 2 onwards</t>
+          <t>Scale with user growth</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="109" t="inlineStr">
         <is>
-          <t>Content marketing (Akito blog/JP content)</t>
+          <t>Paid social (Instagram crew creators)</t>
         </is>
       </c>
       <c r="B34" s="116" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="116" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D34" s="116" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="E34" s="111" t="inlineStr">
         <is>
-          <t>Time-based, no $ cost</t>
+          <t>Phase 2 onwards</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="109" t="inlineStr">
         <is>
-          <t>Beta crew gifts/swag</t>
+          <t>Content marketing (Akito blog/JP content)</t>
         </is>
       </c>
       <c r="B35" s="116" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="C35" s="116" t="n">
         <v>0</v>
@@ -4127,18 +4164,18 @@
       </c>
       <c r="E35" s="111" t="inlineStr">
         <is>
-          <t>One-time ($200) — placed in pre-launch column</t>
+          <t>Time-based, no $ cost</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="109" t="inlineStr">
         <is>
-          <t>Crew interview compensation</t>
+          <t>Beta crew gifts/swag</t>
         </is>
       </c>
       <c r="B36" s="116" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="C36" s="116" t="n">
         <v>0</v>
@@ -4148,14 +4185,14 @@
       </c>
       <c r="E36" s="111" t="inlineStr">
         <is>
-          <t>$50 × 20-30 crew, one-time — see Section 4</t>
+          <t>One-time ($200) — placed in pre-launch column</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="109" t="inlineStr">
         <is>
-          <t>Conferences / events</t>
+          <t>Crew interview compensation</t>
         </is>
       </c>
       <c r="B37" s="116" t="n">
@@ -4165,105 +4202,110 @@
         <v>0</v>
       </c>
       <c r="D37" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="111" t="inlineStr">
+        <is>
+          <t>$50 × 20-30 crew, one-time — see Section 4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="109" t="inlineStr">
+        <is>
+          <t>Conferences / events</t>
+        </is>
+      </c>
+      <c r="B38" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="116" t="n">
         <v>3000</v>
       </c>
-      <c r="E37" s="111" t="inlineStr">
+      <c r="E38" s="111" t="inlineStr">
         <is>
           <t>Year 2+ when we have product</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="113" t="inlineStr">
-        <is>
-          <t>TOTAL marketing (early stage)</t>
-        </is>
-      </c>
-      <c r="B38" s="113" t="inlineStr"/>
-      <c r="C38" s="117">
-        <f>SUM(C31:C37)</f>
-        <v/>
-      </c>
-      <c r="D38" s="113" t="inlineStr"/>
-      <c r="E38" s="115" t="inlineStr">
-        <is>
-          <t>(sum) — quoted $1,000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="113" t="inlineStr">
         <is>
+          <t>TOTAL marketing (early stage)</t>
+        </is>
+      </c>
+      <c r="B39" s="113" t="inlineStr"/>
+      <c r="C39" s="117">
+        <f>SUM(C31:C37)</f>
+        <v/>
+      </c>
+      <c r="D39" s="113" t="inlineStr"/>
+      <c r="E39" s="115" t="inlineStr">
+        <is>
+          <t>(sum) — quoted $1,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="113" t="inlineStr">
+        <is>
           <t>TOTAL marketing (growth stage)</t>
         </is>
       </c>
-      <c r="B39" s="113" t="inlineStr"/>
-      <c r="C39" s="113" t="inlineStr"/>
-      <c r="D39" s="117">
+      <c r="B40" s="113" t="inlineStr"/>
+      <c r="C40" s="113" t="inlineStr"/>
+      <c r="D40" s="117">
         <f>SUM(D31:D37)</f>
         <v/>
       </c>
-      <c r="E39" s="115" t="inlineStr">
+      <c r="E40" s="115" t="inlineStr">
         <is>
           <t>(sum) — quoted $10,000</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="26" customHeight="1">
-      <c r="A41" s="107" t="inlineStr">
+    <row r="41" ht="26" customHeight="1"/>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="107" t="inlineStr">
         <is>
           <t>Section 4 — One-time costs</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="108" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="108" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="B42" s="108" t="inlineStr">
+      <c r="B43" s="108" t="inlineStr">
         <is>
           <t>Amount</t>
         </is>
       </c>
-      <c r="C42" s="108" t="inlineStr">
+      <c r="C43" s="108" t="inlineStr">
         <is>
           <t>When</t>
         </is>
       </c>
-      <c r="D42" s="108" t="inlineStr"/>
-      <c r="E42" s="108" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="109" t="inlineStr">
-        <is>
-          <t>Delaware LLC filing</t>
-        </is>
-      </c>
-      <c r="B43" s="116" t="n">
-        <v>90</v>
-      </c>
-      <c r="C43" s="111" t="inlineStr">
-        <is>
-          <t>This week</t>
-        </is>
-      </c>
-      <c r="D43" s="109" t="inlineStr"/>
-      <c r="E43" s="109" t="inlineStr"/>
+      <c r="D43" s="108" t="inlineStr"/>
+      <c r="E43" s="108" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="109" t="inlineStr">
         <is>
-          <t>Trademark Class 35 search</t>
+          <t>Delaware LLC filing</t>
         </is>
       </c>
       <c r="B44" s="116" t="n">
-        <v>1500</v>
+        <v>90</v>
       </c>
       <c r="C44" s="111" t="inlineStr">
         <is>
-          <t>Before public launch</t>
+          <t>This week</t>
         </is>
       </c>
       <c r="D44" s="109" t="inlineStr"/>
@@ -4272,7 +4314,7 @@
     <row r="45">
       <c r="A45" s="109" t="inlineStr">
         <is>
-          <t>Trademark Class 9/38 filing</t>
+          <t>Trademark Class 35 search</t>
         </is>
       </c>
       <c r="B45" s="116" t="n">
@@ -4289,15 +4331,15 @@
     <row r="46">
       <c r="A46" s="109" t="inlineStr">
         <is>
-          <t>moonlight.ventures domain (5 years)</t>
+          <t>Trademark Class 9/38 filing</t>
         </is>
       </c>
       <c r="B46" s="116" t="n">
-        <v>125</v>
+        <v>1500</v>
       </c>
       <c r="C46" s="111" t="inlineStr">
         <is>
-          <t>This week</t>
+          <t>Before public launch</t>
         </is>
       </c>
       <c r="D46" s="109" t="inlineStr"/>
@@ -4306,15 +4348,15 @@
     <row r="47">
       <c r="A47" s="109" t="inlineStr">
         <is>
-          <t>Initial Apple Developer enrollment</t>
+          <t>moonlight.ventures domain (5 years)</t>
         </is>
       </c>
       <c r="B47" s="116" t="n">
-        <v>99</v>
+        <v>125</v>
       </c>
       <c r="C47" s="111" t="inlineStr">
         <is>
-          <t>LLC formation prereq</t>
+          <t>This week</t>
         </is>
       </c>
       <c r="D47" s="109" t="inlineStr"/>
@@ -4323,15 +4365,15 @@
     <row r="48">
       <c r="A48" s="109" t="inlineStr">
         <is>
-          <t>Mercury bank setup</t>
+          <t>Initial Apple Developer enrollment</t>
         </is>
       </c>
       <c r="B48" s="116" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="C48" s="111" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>LLC formation prereq</t>
         </is>
       </c>
       <c r="D48" s="109" t="inlineStr"/>
@@ -4340,7 +4382,7 @@
     <row r="49">
       <c r="A49" s="109" t="inlineStr">
         <is>
-          <t>Initial Samurai onboarding fees</t>
+          <t>Mercury bank setup</t>
         </is>
       </c>
       <c r="B49" s="116" t="n">
@@ -4348,52 +4390,59 @@
       </c>
       <c r="C49" s="111" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="D49" s="109" t="inlineStr"/>
       <c r="E49" s="109" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="113" t="inlineStr">
+      <c r="A50" s="109" t="inlineStr">
+        <is>
+          <t>Initial Samurai onboarding fees</t>
+        </is>
+      </c>
+      <c r="B50" s="116" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="111" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D50" s="109" t="inlineStr"/>
+      <c r="E50" s="109" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="113" t="inlineStr">
         <is>
           <t>TOTAL one-time</t>
         </is>
       </c>
-      <c r="B50" s="117">
+      <c r="B51" s="117">
         <f>SUM(B43:B49)</f>
         <v/>
       </c>
-      <c r="C50" s="115" t="inlineStr">
+      <c r="C51" s="115" t="inlineStr">
         <is>
           <t>(sum) — quoted $3,314</t>
         </is>
       </c>
-      <c r="D50" s="113" t="inlineStr"/>
-      <c r="E50" s="113" t="inlineStr"/>
-    </row>
-    <row r="52" ht="26" customHeight="1">
-      <c r="A52" s="107" t="inlineStr">
+      <c r="D51" s="113" t="inlineStr"/>
+      <c r="E51" s="113" t="inlineStr"/>
+    </row>
+    <row r="52" ht="26" customHeight="1"/>
+    <row r="53" ht="30" customHeight="1">
+      <c r="A53" s="107" t="inlineStr">
         <is>
           <t>Section 5 — Validation queue</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="108" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="108" t="inlineStr">
         <is>
           <t>Open validation item</t>
-        </is>
-      </c>
-      <c r="B53" s="118" t="n"/>
-      <c r="C53" s="118" t="n"/>
-      <c r="D53" s="118" t="n"/>
-      <c r="E53" s="119" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="112" t="inlineStr">
-        <is>
-          <t>☐  Validate Stripe payment processing actual rate post-launch</t>
         </is>
       </c>
       <c r="B54" s="118" t="n"/>
@@ -4404,7 +4453,7 @@
     <row r="55">
       <c r="A55" s="112" t="inlineStr">
         <is>
-          <t>☐  Validate customer support cost as we hire</t>
+          <t>☐  Validate Stripe payment processing actual rate post-launch</t>
         </is>
       </c>
       <c r="B55" s="118" t="n"/>
@@ -4415,7 +4464,7 @@
     <row r="56">
       <c r="A56" s="112" t="inlineStr">
         <is>
-          <t>☐  Validate refund cost from real data months 1-3</t>
+          <t>☐  Validate customer support cost as we hire</t>
         </is>
       </c>
       <c r="B56" s="118" t="n"/>
@@ -4426,7 +4475,7 @@
     <row r="57">
       <c r="A57" s="112" t="inlineStr">
         <is>
-          <t>☐  Validate FX fee impact on non-USD purchases</t>
+          <t>☐  Validate refund cost from real data months 1-3</t>
         </is>
       </c>
       <c r="B57" s="118" t="n"/>
@@ -4437,7 +4486,7 @@
     <row r="58">
       <c r="A58" s="112" t="inlineStr">
         <is>
-          <t>☐  Validate marketing CAC after first campaign</t>
+          <t>☐  Validate FX fee impact on non-USD purchases</t>
         </is>
       </c>
       <c r="B58" s="118" t="n"/>
@@ -4448,13 +4497,24 @@
     <row r="59">
       <c r="A59" s="112" t="inlineStr">
         <is>
-          <t>☐  Validate insurance quote (currently estimate)</t>
+          <t>☐  Validate marketing CAC after first campaign</t>
         </is>
       </c>
       <c r="B59" s="118" t="n"/>
       <c r="C59" s="118" t="n"/>
       <c r="D59" s="118" t="n"/>
       <c r="E59" s="119" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="112" t="inlineStr">
+        <is>
+          <t>☐  Validate insurance quote (currently estimate)</t>
+        </is>
+      </c>
+      <c r="B60" s="118" t="n"/>
+      <c r="C60" s="118" t="n"/>
+      <c r="D60" s="118" t="n"/>
+      <c r="E60" s="119" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="14">
@@ -4474,6 +4534,7 @@
     <mergeCell ref="A56:E56"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -58,7 +58,7 @@
     <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
     <numFmt numFmtId="182" formatCode="0.0&quot; top-ups&quot;"/>
   </numFmts>
-  <fonts count="40">
+  <fonts count="46">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -275,8 +275,33 @@
       <b val="1"/>
       <color rgb="007A5A10"/>
     </font>
+    <font>
+      <i val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C9A03B"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -394,6 +419,11 @@
         <bgColor rgb="00FFFF00"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FAF6F0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -465,7 +495,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -657,6 +687,28 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="36" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="44" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6233,17 +6285,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="55" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6301,11 +6355,16 @@
           <t>Net Margin %</t>
         </is>
       </c>
+      <c r="I4" s="136" t="inlineStr">
+        <is>
+          <t>What this means (user behavior)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>🌴 Tourist Mix (light travel users — upside)</t>
+          <t>🌴 Casual Travelers</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
@@ -6332,11 +6391,16 @@
         <f>IFERROR(G5/(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)),0)</f>
         <v/>
       </c>
+      <c r="I5" s="145" t="inlineStr">
+        <is>
+          <t>Non-crew leisure travelers who fly 2-4x/year for vacation. Light data use, not loyal. Acts like an Airalo customer, not a crew member.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>✈️ Crew Standard (current base — realistic for cabin crew)</t>
+          <t>✈️ Crew Standard</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
@@ -6363,11 +6427,16 @@
         <f>IFERROR(G6/(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)),0)</f>
         <v/>
       </c>
+      <c r="I6" s="145" t="inlineStr">
+        <is>
+          <t>Realistic crew mix. Most users are cabin crew flying 15-25 flights/month, mix of short-haul and long-haul. Current base assumption.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>🔥 Power Crew (heavy-fliers dominate — downside)</t>
+          <t>🔥 Power Crew</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
@@ -6394,11 +6463,16 @@
         <f>IFERROR(G7/(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)),0)</f>
         <v/>
       </c>
+      <c r="I7" s="145" t="inlineStr">
+        <is>
+          <t>Heavy-flier dominance. Long-haul pursers, senior crew on multi-leg pairings. They consume nearly all the pool every month.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>💔 One-and-Done (bad acquisition, high churn)</t>
+          <t>💔 One-and-Done</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
@@ -6425,6 +6499,11 @@
         <f>IFERROR(G8/(1000*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)),0)</f>
         <v/>
       </c>
+      <c r="I8" s="145" t="inlineStr">
+        <is>
+          <t>High churn (30% of users disappear after one trip). Typical if we accidentally market to casual vacationers instead of working crew.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="40" t="inlineStr">
@@ -6486,9 +6565,9 @@
           <t>Blended ARPU</t>
         </is>
       </c>
-      <c r="J14" s="41" t="inlineStr">
-        <is>
-          <t>Notes</t>
+      <c r="J14" s="136" t="inlineStr">
+        <is>
+          <t>What this means (who is buying what)</t>
         </is>
       </c>
     </row>
@@ -6522,9 +6601,9 @@
       <c r="I15" s="54" t="n">
         <v>15.1679</v>
       </c>
-      <c r="J15" s="39" t="inlineStr">
-        <is>
-          <t>Most users stay PAYG. Worst case for ARPU.</t>
+      <c r="J15" s="146" t="inlineStr">
+        <is>
+          <t>🪤 70% of users stuck on Economy PAYG ($4.99). They never upgrade to a subscription. Worst case for ARPU. Conversion funnel is broken.</t>
         </is>
       </c>
     </row>
@@ -6558,9 +6637,9 @@
       <c r="I16" s="54" t="n">
         <v>14.55265</v>
       </c>
-      <c r="J16" s="39" t="inlineStr">
-        <is>
-          <t>Realistic launch period — heavy Economy mix.</t>
+      <c r="J16" s="146" t="inlineStr">
+        <is>
+          <t>🚀 Months 1-6 reality — 80% of new signups land on Economy, only 20% commit to subscription. Honest launch period before social proof kicks in.</t>
         </is>
       </c>
     </row>
@@ -6594,9 +6673,9 @@
       <c r="I17" s="59" t="n">
         <v>17.516</v>
       </c>
-      <c r="J17" s="77" t="inlineStr">
-        <is>
-          <t>Steady-state guess. CURRENT MODEL.</t>
+      <c r="J17" s="147" t="inlineStr">
+        <is>
+          <t>🎯 Our base case. Half of users buy Economy/PAYG, half spread across Roster + Premium + Business + First. Steady-state assumption.</t>
         </is>
       </c>
     </row>
@@ -6630,9 +6709,9 @@
       <c r="I18" s="54" t="n">
         <v>20.3392</v>
       </c>
-      <c r="J18" s="39" t="inlineStr">
-        <is>
-          <t>Strong subscription uptake.</t>
+      <c r="J18" s="146" t="inlineStr">
+        <is>
+          <t>📈 Strong conversion. Only 35% stay on Economy, the rest climb the ladder. Achievable if we nudge upgrades aggressively in onboarding.</t>
         </is>
       </c>
     </row>
@@ -6666,9 +6745,9 @@
       <c r="I19" s="54" t="n">
         <v>21.4755</v>
       </c>
-      <c r="J19" s="39" t="inlineStr">
-        <is>
-          <t>Mature population after Cockpit/First grow.</t>
+      <c r="J19" s="146" t="inlineStr">
+        <is>
+          <t>👑 Mature population (Year 2+). Most users are now on subscription tiers. Cockpit annual and First/Suite are growing. Best ARPU case.</t>
         </is>
       </c>
     </row>
@@ -6681,6 +6760,344 @@
       <c r="I21" s="94" t="inlineStr">
         <is>
           <t>$14.55 – $21.48</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="148" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE — 100 users in TWO worlds</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="149" t="inlineStr">
+        <is>
+          <t>Same 100 users, same supplier costs. The ONLY difference is which tier they pick.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="150" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B26" s="150" t="inlineStr">
+        <is>
+          <t>🚀 Launch Reality
+(80% on Economy)</t>
+        </is>
+      </c>
+      <c r="C26" s="150" t="inlineStr">
+        <is>
+          <t>Per-user net</t>
+        </is>
+      </c>
+      <c r="D26" s="150" t="inlineStr">
+        <is>
+          <t>Total / mo</t>
+        </is>
+      </c>
+      <c r="E26" s="150" t="inlineStr">
+        <is>
+          <t>📈 Ladder Climbers
+(35% on Economy)</t>
+        </is>
+      </c>
+      <c r="F26" s="150" t="inlineStr">
+        <is>
+          <t>Per-user net</t>
+        </is>
+      </c>
+      <c r="G26" s="150" t="inlineStr">
+        <is>
+          <t>Total / mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Economy ($4.99/$12.48 realistic)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>80</v>
+      </c>
+      <c r="C27" s="54" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="D27" s="54">
+        <f>B27*C27</f>
+        <v/>
+      </c>
+      <c r="E27" t="n">
+        <v>35</v>
+      </c>
+      <c r="F27" s="54" t="n">
+        <v>9.130000000000001</v>
+      </c>
+      <c r="G27" s="54">
+        <f>E27*F27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Roster Bundle ($19.95)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>10</v>
+      </c>
+      <c r="C28" s="54" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="D28" s="54">
+        <f>B28*C28</f>
+        <v/>
+      </c>
+      <c r="E28" t="n">
+        <v>22</v>
+      </c>
+      <c r="F28" s="54" t="n">
+        <v>13.62</v>
+      </c>
+      <c r="G28" s="54">
+        <f>E28*F28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Premium Economy ($17.99)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>5</v>
+      </c>
+      <c r="C29" s="54" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="D29" s="54">
+        <f>B29*C29</f>
+        <v/>
+      </c>
+      <c r="E29" t="n">
+        <v>18</v>
+      </c>
+      <c r="F29" s="54" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="G29" s="54">
+        <f>E29*F29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Business ($29.99)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3</v>
+      </c>
+      <c r="C30" s="54" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="D30" s="54">
+        <f>B30*C30</f>
+        <v/>
+      </c>
+      <c r="E30" t="n">
+        <v>12</v>
+      </c>
+      <c r="F30" s="54" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="G30" s="54">
+        <f>E30*F30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>First ($39.99)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" s="54" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="D31" s="54">
+        <f>B31*C31</f>
+        <v/>
+      </c>
+      <c r="E31" t="n">
+        <v>5</v>
+      </c>
+      <c r="F31" s="54" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="G31" s="54">
+        <f>E31*F31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>First Suite ($49.99)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="54" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="D32" s="54">
+        <f>B32*C32</f>
+        <v/>
+      </c>
+      <c r="E32" t="n">
+        <v>3</v>
+      </c>
+      <c r="F32" s="54" t="n">
+        <v>33.03</v>
+      </c>
+      <c r="G32" s="54">
+        <f>E32*F32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cockpit ($24.92 mo equiv)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" s="54" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="D33" s="54">
+        <f>B33*C33</f>
+        <v/>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" s="54" t="n">
+        <v>15.82</v>
+      </c>
+      <c r="G33" s="54">
+        <f>E33*F33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="151" t="inlineStr">
+        <is>
+          <t>TOTAL (100 users)</t>
+        </is>
+      </c>
+      <c r="B34" s="151">
+        <f>SUM(B27:B33)</f>
+        <v/>
+      </c>
+      <c r="D34" s="152">
+        <f>SUM(D27:D33)</f>
+        <v/>
+      </c>
+      <c r="E34" s="151">
+        <f>SUM(E27:E33)</f>
+        <v/>
+      </c>
+      <c r="G34" s="152">
+        <f>SUM(G27:G33)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="153" t="inlineStr">
+        <is>
+          <t>Blended net per user/mo</t>
+        </is>
+      </c>
+      <c r="D35" s="154">
+        <f>D34/B34</f>
+        <v/>
+      </c>
+      <c r="G35" s="154">
+        <f>G34/E34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="149" t="inlineStr">
+        <is>
+          <t>The lift from converting Economy → subscription:</t>
+        </is>
+      </c>
+      <c r="G36" s="155">
+        <f>(G34-D34)/D34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="156" t="inlineStr">
+        <is>
+          <t>AT 5,000 USERS (Month 24 target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>🚀 Launch Reality at 5K users (monthly)</t>
+        </is>
+      </c>
+      <c r="D39" s="86">
+        <f>D35*5000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>📈 Ladder Climbers at 5K users (monthly)</t>
+        </is>
+      </c>
+      <c r="D40" s="86">
+        <f>G35*5000</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="153" t="inlineStr">
+        <is>
+          <t>Annual difference (Ladder Climbers vs Launch Reality)</t>
+        </is>
+      </c>
+      <c r="D41" s="157">
+        <f>(D40-D39)*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="158" t="inlineStr">
+        <is>
+          <t>THE BOTTOM LINE: Getting users to climb the ladder is the #1 profit lever. Same supplier costs, +37% revenue.</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -58,7 +58,7 @@
     <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
     <numFmt numFmtId="182" formatCode="0.0&quot; top-ups&quot;"/>
   </numFmts>
-  <fonts count="46">
+  <fonts count="47">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -300,8 +300,12 @@
       <i val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="26">
     <fill>
       <patternFill/>
     </fill>
@@ -424,6 +428,11 @@
         <fgColor rgb="00FAF6F0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -495,7 +504,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -709,6 +718,15 @@
     <xf numFmtId="0" fontId="44" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="176" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="45" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7115,13 +7133,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H35"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
@@ -7327,9 +7345,9 @@
       <c r="A15" s="3" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>CUSTOMER ACQUISITION COST (per-channel blended avg)</t>
+      <c r="A16" s="159" t="inlineStr">
+        <is>
+          <t>CUSTOMER ACQUISITION COST — LAUNCH REALITY (word-of-mouth only)</t>
         </is>
       </c>
       <c r="B16" s="8" t="n"/>
@@ -7359,74 +7377,74 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>Organic / word-of-mouth</t>
+      <c r="A18" s="160" t="inlineStr">
+        <is>
+          <t>Organic / crew word-of-mouth</t>
         </is>
       </c>
       <c r="B18" s="13" t="n">
-        <v>0.5</v>
+        <v>0.85</v>
       </c>
       <c r="C18" s="28" t="n">
         <v>0</v>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
-          <t>Crew network referrals — free</t>
+          <t>Cabin crew layover chat, group chats, social proof — 100% free</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>Referral bonus ($5 credit)</t>
+      <c r="A19" s="160" t="inlineStr">
+        <is>
+          <t>Referral bonus ($5 credit per referrer)</t>
         </is>
       </c>
       <c r="B19" s="13" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="C19" s="28" t="n">
         <v>5</v>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
-          <t>Existing user refers</t>
+          <t>Existing user refers a colleague — paid in credit, not cash</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>Paid social (IG/TikTok)</t>
+      <c r="A20" s="161" t="inlineStr">
+        <is>
+          <t>Paid social (FUTURE — NOT IN LAUNCH PLAN)</t>
         </is>
       </c>
       <c r="B20" s="13" t="n">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="C20" s="28" t="n">
         <v>12</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
-          <t>Cold acquisition</t>
+          <t>⚠️ Set to 0% — no paid ads at launch per founder decision</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Influencer / crew creator</t>
+      <c r="A21" s="162" t="inlineStr">
+        <is>
+          <t>Influencer / crew creator (FUTURE — NOT IN LAUNCH PLAN)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
         <v>8</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Paid sponsorship to @crew_illust et al</t>
+          <t>⚠️ Set to 0% — Harikai partnership is asset swap, not paid CAC</t>
         </is>
       </c>
     </row>
@@ -7435,14 +7453,19 @@
       <c r="C22" s="11" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>BLENDED CAC</t>
-        </is>
-      </c>
-      <c r="C23">
+      <c r="A23" s="153" t="inlineStr">
+        <is>
+          <t>BLENDED CAC (Launch Reality)</t>
+        </is>
+      </c>
+      <c r="C23" s="154">
         <f>SUMPRODUCT(B18:B21,C18:C21)</f>
         <v/>
+      </c>
+      <c r="D23" s="149" t="inlineStr">
+        <is>
+          <t>At launch: 85% organic + 15% referral = ~$0.75/user. Will rise when paid channels open.</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -7782,6 +7805,154 @@
       <c r="H35">
         <f>IF(F35&gt;=5,"Excellent",IF(F35&gt;=3,"Investable",IF(F35&gt;=1,"Marginal","Unprofitable")))</f>
         <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="156" t="inlineStr">
+        <is>
+          <t>ECONOMY CHURN PRESSURE-TEST (industry sees 30-40% for trial-style tiers)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="136" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B46" s="136" t="inlineStr">
+        <is>
+          <t>Monthly Churn</t>
+        </is>
+      </c>
+      <c r="C46" s="136" t="inlineStr">
+        <is>
+          <t>Avg Lifetime (mo)</t>
+        </is>
+      </c>
+      <c r="D46" s="136" t="inlineStr">
+        <is>
+          <t>LTV</t>
+        </is>
+      </c>
+      <c r="E46" s="136" t="inlineStr">
+        <is>
+          <t>CAC</t>
+        </is>
+      </c>
+      <c r="F46" s="136" t="inlineStr">
+        <is>
+          <t>LTV:CAC</t>
+        </is>
+      </c>
+      <c r="G46" s="136" t="inlineStr">
+        <is>
+          <t>Verdict</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Optimistic — current assumption</t>
+        </is>
+      </c>
+      <c r="B47" s="26" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="C47" s="163">
+        <f>1/B47</f>
+        <v/>
+      </c>
+      <c r="D47" s="54">
+        <f>B28*C47</f>
+        <v/>
+      </c>
+      <c r="E47" s="54">
+        <f>$C$23</f>
+        <v/>
+      </c>
+      <c r="F47" s="164">
+        <f>D47/E47</f>
+        <v/>
+      </c>
+      <c r="G47">
+        <f>IF(F47&gt;=5,"Excellent",IF(F47&gt;=3,"Investable",IF(F47&gt;=1,"Marginal","Unprofitable")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Realistic — travel-eSIM industry avg</t>
+        </is>
+      </c>
+      <c r="B48" s="26" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C48" s="163">
+        <f>1/B48</f>
+        <v/>
+      </c>
+      <c r="D48" s="54">
+        <f>B28*C48</f>
+        <v/>
+      </c>
+      <c r="E48" s="54">
+        <f>$C$23</f>
+        <v/>
+      </c>
+      <c r="F48" s="164">
+        <f>D48/E48</f>
+        <v/>
+      </c>
+      <c r="G48">
+        <f>IF(F48&gt;=5,"Excellent",IF(F48&gt;=3,"Investable",IF(F48&gt;=1,"Marginal","Unprofitable")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Pessimistic — pure trial users</t>
+        </is>
+      </c>
+      <c r="B49" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C49" s="163">
+        <f>1/B49</f>
+        <v/>
+      </c>
+      <c r="D49" s="54">
+        <f>B28*C49</f>
+        <v/>
+      </c>
+      <c r="E49" s="54">
+        <f>$C$23</f>
+        <v/>
+      </c>
+      <c r="F49" s="164">
+        <f>D49/E49</f>
+        <v/>
+      </c>
+      <c r="G49">
+        <f>IF(F49&gt;=5,"Excellent",IF(F49&gt;=3,"Investable",IF(F49&gt;=1,"Marginal","Unprofitable")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="165" t="inlineStr">
+        <is>
+          <t>INSIGHT: Even at the WORST Economy churn (40%), LTV:CAC stays excellent because our $0.75 CAC is so low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="149" t="inlineStr">
+        <is>
+          <t>The risk is NOT unit economics — it is whether word-of-mouth alone can scale fast enough to reach 5K users in 24 months.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -58,7 +58,7 @@
     <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
     <numFmt numFmtId="182" formatCode="0.0&quot; top-ups&quot;"/>
   </numFmts>
-  <fonts count="47">
+  <fonts count="48">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -304,6 +304,10 @@
       <b val="1"/>
       <i val="1"/>
     </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00C9A03B"/>
+    </font>
   </fonts>
   <fills count="26">
     <fill>
@@ -504,7 +508,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="170">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -727,6 +731,10 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="46" fillId="24" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="4" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="47" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7304,21 +7312,22 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="166" t="inlineStr">
         <is>
           <t>Cockpit</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
-        <v>0.006</v>
-      </c>
-      <c r="C12" s="20">
-        <f>IFERROR(1/B12,0)</f>
-        <v/>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>Annual prepay = automatic 12-mo retention</t>
+      <c r="B12" s="167" t="inlineStr">
+        <is>
+          <t>Annual prepay</t>
+        </is>
+      </c>
+      <c r="C12" s="168" t="n">
+        <v>36</v>
+      </c>
+      <c r="D12" s="169" t="inlineStr">
+        <is>
+          <t>ANNUAL PREPAY: Year 1 forced retention (0% churn). After Year 1: ~70% renew. Realistic avg lifetime = ~36 months (3 years). Cannot use monthly churn formula.</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -58,7 +58,7 @@
     <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
     <numFmt numFmtId="182" formatCode="0.0&quot; top-ups&quot;"/>
   </numFmts>
-  <fonts count="48">
+  <fonts count="50">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -308,6 +308,14 @@
       <i val="1"/>
       <color rgb="00C9A03B"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00888888"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00888888"/>
+    </font>
   </fonts>
   <fills count="26">
     <fill>
@@ -508,7 +516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="170">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -735,6 +743,22 @@
     <xf numFmtId="165" fontId="4" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="47" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -7141,7 +7165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -7961,6 +7985,112 @@
       <c r="A52" s="149" t="inlineStr">
         <is>
           <t>The risk is NOT unit economics — it is whether word-of-mouth alone can scale fast enough to reach 5K users in 24 months.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="148" t="inlineStr">
+        <is>
+          <t>PAYBACK PERIOD — explained simply (the lemonade analogy)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="30" customHeight="1">
+      <c r="A57" s="151" t="inlineStr">
+        <is>
+          <t>The plain-English question:</t>
+        </is>
+      </c>
+      <c r="B57" s="170" t="inlineStr">
+        <is>
+          <t>"How long does a new user need to stay a paying customer before they have earned back the cost we spent to acquire them?"</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
+      <c r="A59" s="151" t="inlineStr">
+        <is>
+          <t>Lemonade stand example:</t>
+        </is>
+      </c>
+      <c r="B59" s="171" t="inlineStr">
+        <is>
+          <t>You spend $5 on posters to attract a customer. Each lemonade they buy earns you $2 profit. After 3 lemonades ($6 cumulative), you have paid back the $5 poster cost. Every lemonade after that = pure profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="151" t="inlineStr">
+        <is>
+          <t>For Peanut (Premium tier example):</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Cost to acquire a Premium user (blended CAC)</t>
+        </is>
+      </c>
+      <c r="B62" s="54">
+        <f>$C$23</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Profit from a Premium user per month</t>
+        </is>
+      </c>
+      <c r="B63" s="54">
+        <f>'Per-Tier Unit Economics'!K9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Payback period (months)</t>
+        </is>
+      </c>
+      <c r="B64" s="172">
+        <f>B62/B63</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Payback period (days)</t>
+        </is>
+      </c>
+      <c r="B65" s="173">
+        <f>B64*30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
+      <c r="A67" s="174" t="inlineStr">
+        <is>
+          <t>TAKEAWAY:</t>
+        </is>
+      </c>
+      <c r="B67" s="175" t="inlineStr">
+        <is>
+          <t>A Premium user pays us back the $0.75 referral cost in under 2 days. Every day after that, they are pure profit. This is why our low-CAC + high-contribution model is so strong — we are never "underwater" on a user for long.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="30" customHeight="1">
+      <c r="A68" s="176" t="inlineStr">
+        <is>
+          <t>Compare to a typical startup:</t>
+        </is>
+      </c>
+      <c r="B68" s="177" t="inlineStr">
+        <is>
+          <t>Company spends $50 on Facebook ads per user, earns $5/mo profit. Payback = 10 months. They are underwater for nearly a year. Most startups die in that gap.</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -4501,7 +4501,7 @@
     <row r="50">
       <c r="A50" s="109" t="inlineStr">
         <is>
-          <t>Initial Samurai onboarding fees</t>
+          <t>Initial wholesale supplier onboarding fees</t>
         </is>
       </c>
       <c r="B50" s="116" t="n">
@@ -5217,7 +5217,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Compare current Samurai pay-per-order vs. bulk-prepay vs. eSIM Access direct at 1,000 users.</t>
+          <t>Compare current wholesale supplier pay-per-order vs. bulk-prepay vs. eSIM Access direct at 1,000 users.</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>A. Samurai pay-per-order</t>
+          <t>A. wholesale supplier pay-per-order</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
@@ -5289,7 +5289,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>B. Samurai bulk prepay -10%</t>
+          <t>B. wholesale supplier bulk prepay -10%</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
@@ -5385,7 +5385,7 @@
     <row r="12">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>A. Samurai pay-per-order</t>
+          <t>A. wholesale supplier pay-per-order</t>
         </is>
       </c>
       <c r="B12" s="24">
@@ -5416,7 +5416,7 @@
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>B. Samurai bulk prepay -10%</t>
+          <t>B. wholesale supplier bulk prepay -10%</t>
         </is>
       </c>
       <c r="B13" s="24">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Samurai Markup (assumed)</t>
+          <t>wholesale supplier Markup (assumed)</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Stay with Samurai (no leverage yet)</t>
+          <t>Stay with wholesale supplier (no leverage yet)</t>
         </is>
       </c>
     </row>
@@ -12023,7 +12023,7 @@
       </c>
       <c r="B32" s="90" t="inlineStr">
         <is>
-          <t>Real Samurai × 75/20/5 mix</t>
+          <t>Real wholesale supplier × 75/20/5 mix</t>
         </is>
       </c>
       <c r="C32" s="90" t="inlineStr">
@@ -12311,7 +12311,7 @@
     <row r="1">
       <c r="A1" s="38" t="inlineStr">
         <is>
-          <t>Pricing Simulator — what should we charge given Samurai wholesale costs?</t>
+          <t>Pricing Simulator — what should we charge given our wholesale supplier costs?</t>
         </is>
       </c>
     </row>
@@ -12349,7 +12349,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Samurai actual (from rate sheet)</t>
+          <t>wholesale supplier actual (from rate sheet)</t>
         </is>
       </c>
       <c r="B6" s="42" t="n">
@@ -12357,14 +12357,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Current Samurai actual blended (75/20/5 mix). Tier-A $0.85, Tier-B $1.40, Tier-C $8.50.</t>
+          <t>Current wholesale supplier actual blended (75/20/5 mix). Tier-A $0.85, Tier-B $1.40, Tier-C $8.50.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Samurai target (after negotiation)</t>
+          <t>wholesale supplier target (after negotiation)</t>
         </is>
       </c>
       <c r="B7" s="42" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>What we ask Samurai to come down to — basis for negotiation</t>
+          <t>What we ask wholesale supplier to come down to — basis for negotiation</t>
         </is>
       </c>
     </row>
@@ -12935,12 +12935,12 @@
       </c>
       <c r="C27" s="41" t="inlineStr">
         <is>
-          <t>COGS @ Samurai actual</t>
+          <t>COGS @ wholesale supplier actual</t>
         </is>
       </c>
       <c r="D27" s="41" t="inlineStr">
         <is>
-          <t>COGS @ Samurai target</t>
+          <t>COGS @ wholesale supplier target</t>
         </is>
       </c>
       <c r="E27" s="41" t="inlineStr">
@@ -13239,6 +13239,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
@@ -13314,7 +13315,7 @@
       </c>
       <c r="B10" s="48" t="inlineStr">
         <is>
-          <t>Flat worldwide — all Samurai eSIM countries</t>
+          <t>Flat worldwide — all wholesale supplier eSIM countries</t>
         </is>
       </c>
     </row>
@@ -13342,10 +13343,11 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="40" t="inlineStr">
         <is>
-          <t>2. WHOLESALE COST FLOOR (Samurai actual rate sheet)</t>
+          <t>2. WHOLESALE COST FLOOR (wholesale supplier actual rate sheet)</t>
         </is>
       </c>
     </row>
@@ -13623,6 +13625,8 @@
         <v>-1.005344021376086</v>
       </c>
     </row>
+    <row r="27"/>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="40" t="inlineStr">
         <is>
@@ -13782,6 +13786,8 @@
         </is>
       </c>
     </row>
+    <row r="36"/>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="40" t="inlineStr">
         <is>
@@ -13849,6 +13855,7 @@
         </is>
       </c>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="40" t="inlineStr">
         <is>
@@ -13870,6 +13877,7 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
     <row r="49">
       <c r="A49" s="39" t="inlineStr">
         <is>
@@ -13898,6 +13906,7 @@
         </is>
       </c>
     </row>
+    <row r="53"/>
     <row r="54">
       <c r="A54" s="40" t="inlineStr">
         <is>
@@ -14042,6 +14051,7 @@
         <v/>
       </c>
     </row>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="40" t="inlineStr">
         <is>
@@ -14118,6 +14128,7 @@
         <v/>
       </c>
     </row>
+    <row r="76"/>
     <row r="77">
       <c r="A77" s="40" t="inlineStr">
         <is>
@@ -14128,7 +14139,7 @@
     <row r="78">
       <c r="A78" s="39" t="inlineStr">
         <is>
-          <t>• Wholesale costs: Samurai-Wifi-Wholesale-CNY.xlsx (rate sheet, sampled 2026-05-31). CNY → USD at 7.2.</t>
+          <t>• Wholesale costs: wholesale-rate-sheet.xlsx (rate sheet, sampled 2026-05-31). CNY → USD at 7.2.</t>
         </is>
       </c>
     </row>
@@ -14232,6 +14243,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
@@ -14331,10 +14343,11 @@
       </c>
       <c r="B12" s="64" t="inlineStr">
         <is>
-          <t>Same Samurai eSIM catalog as Economy</t>
-        </is>
-      </c>
-    </row>
+          <t>Same wholesale supplier eSIM catalog as Economy</t>
+        </is>
+      </c>
+    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="40" t="inlineStr">
         <is>
@@ -14350,7 +14363,7 @@
       </c>
       <c r="B15" s="41" t="inlineStr">
         <is>
-          <t>Samurai cost</t>
+          <t>wholesale supplier cost</t>
         </is>
       </c>
       <c r="C15" s="41" t="inlineStr">
@@ -14521,6 +14534,7 @@
         <v/>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" s="40" t="inlineStr">
         <is>
@@ -14663,6 +14677,8 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="40" t="inlineStr">
         <is>
@@ -14812,6 +14828,8 @@
         </is>
       </c>
     </row>
+    <row r="39"/>
+    <row r="40"/>
     <row r="41">
       <c r="A41" s="40" t="inlineStr">
         <is>
@@ -14851,7 +14869,7 @@
       </c>
       <c r="B44" s="64" t="inlineStr">
         <is>
-          <t>We know in advance which SIMs to buy from Samurai → bulk-prepay negotiating leverage.</t>
+          <t>We know in advance which SIMs to buy from wholesale supplier → bulk-prepay negotiating leverage.</t>
         </is>
       </c>
     </row>
@@ -14891,6 +14909,8 @@
         </is>
       </c>
     </row>
+    <row r="48"/>
+    <row r="49"/>
     <row r="50">
       <c r="A50" s="40" t="inlineStr">
         <is>
@@ -15003,6 +15023,7 @@
         <v/>
       </c>
     </row>
+    <row r="60"/>
     <row r="61">
       <c r="A61" s="40" t="inlineStr">
         <is>
@@ -15070,6 +15091,8 @@
         </is>
       </c>
     </row>
+    <row r="67"/>
+    <row r="68"/>
     <row r="69">
       <c r="A69" s="40" t="inlineStr">
         <is>
@@ -15080,7 +15103,7 @@
     <row r="70">
       <c r="A70" s="39" t="inlineStr">
         <is>
-          <t>• Wholesale costs: Samurai-Wifi-Wholesale-CNY.xlsx (1 GB / 2-day plans, sampled 2026-05-31).</t>
+          <t>• Wholesale costs: wholesale-rate-sheet.xlsx (1 GB / 2-day plans, sampled 2026-05-31).</t>
         </is>
       </c>
     </row>
@@ -15386,7 +15409,7 @@
     <row r="20">
       <c r="A20" s="48" t="inlineStr">
         <is>
-          <t>Wholesale cost / GB (blended Samurai)</t>
+          <t>Wholesale cost / GB (blended wholesale supplier)</t>
         </is>
       </c>
       <c r="B20" s="54" t="n">

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -516,7 +516,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="178">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -759,6 +759,13 @@
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="42" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="43" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4649,7 +4656,7 @@
   <dimension ref="A1:J30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -4736,15 +4743,15 @@
       <c r="B5" s="23" t="n">
         <v>100</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="178">
         <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="178">
         <f>B5*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="179">
         <f>C5-D5</f>
         <v/>
       </c>
@@ -4752,11 +4759,11 @@
         <f>IFERROR(E5/C5,0)</f>
         <v/>
       </c>
-      <c r="G5" s="27">
+      <c r="G5" s="86">
         <f>B5*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="179">
         <f>E5-G5</f>
         <v/>
       </c>
@@ -4764,7 +4771,7 @@
         <f>IFERROR(H5/C5,0)</f>
         <v/>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="179">
         <f>H5*12</f>
         <v/>
       </c>
@@ -4778,15 +4785,15 @@
       <c r="B6" s="23" t="n">
         <v>1000</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="178">
         <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="178">
         <f>B6*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="179">
         <f>C6-D6</f>
         <v/>
       </c>
@@ -4794,11 +4801,11 @@
         <f>IFERROR(E6/C6,0)</f>
         <v/>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="86">
         <f>B6*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="179">
         <f>E6-G6</f>
         <v/>
       </c>
@@ -4806,7 +4813,7 @@
         <f>IFERROR(H6/C6,0)</f>
         <v/>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="179">
         <f>H6*12</f>
         <v/>
       </c>
@@ -4820,15 +4827,15 @@
       <c r="B7" s="23" t="n">
         <v>5000</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="178">
         <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="178">
         <f>B7*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="179">
         <f>C7-D7</f>
         <v/>
       </c>
@@ -4836,11 +4843,11 @@
         <f>IFERROR(E7/C7,0)</f>
         <v/>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="86">
         <f>B7*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="179">
         <f>E7-G7</f>
         <v/>
       </c>
@@ -4848,7 +4855,7 @@
         <f>IFERROR(H7/C7,0)</f>
         <v/>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="179">
         <f>H7*12</f>
         <v/>
       </c>
@@ -4862,15 +4869,15 @@
       <c r="B8" s="23" t="n">
         <v>20000</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="178">
         <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="178">
         <f>B8*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
         <v/>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="179">
         <f>C8-D8</f>
         <v/>
       </c>
@@ -4878,11 +4885,11 @@
         <f>IFERROR(E8/C8,0)</f>
         <v/>
       </c>
-      <c r="G8" s="27">
+      <c r="G8" s="86">
         <f>B8*'README &amp; Assumptions'!B53</f>
         <v/>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="179">
         <f>E8-G8</f>
         <v/>
       </c>
@@ -4890,7 +4897,7 @@
         <f>IFERROR(H8/C8,0)</f>
         <v/>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="179">
         <f>H8*12</f>
         <v/>
       </c>
@@ -4943,8 +4950,49 @@
           <t>100K Target (full vision)</t>
         </is>
       </c>
-    </row>
-    <row r="11"/>
+      <c r="B10" t="n">
+        <v>100000</v>
+      </c>
+      <c r="C10" s="86">
+        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!I7:I13,'README &amp; Assumptions'!B36:B42)</f>
+        <v/>
+      </c>
+      <c r="D10" s="86">
+        <f>B10*SUMPRODUCT('Per-Tier Unit Economics'!J7:J13,'README &amp; Assumptions'!B36:B42)</f>
+        <v/>
+      </c>
+      <c r="E10" s="86">
+        <f>C10-D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="26">
+        <f>IFERROR(E10/C10,0)</f>
+        <v/>
+      </c>
+      <c r="G10" s="86">
+        <f>B10*'README &amp; Assumptions'!B53</f>
+        <v/>
+      </c>
+      <c r="H10" s="86">
+        <f>E10-G10</f>
+        <v/>
+      </c>
+      <c r="I10" s="26">
+        <f>IFERROR(H10/C10,0)</f>
+        <v/>
+      </c>
+      <c r="J10" s="86">
+        <f>H10*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="180" t="inlineStr">
+        <is>
+          <t>NOTE: OPEX columns above use $1.80/user placeholder. Real OPEX = $0 today (no spend yet).</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" s="94" t="inlineStr">
         <is>
@@ -4998,11 +5046,13 @@
       <c r="C15" s="71" t="n">
         <v>500</v>
       </c>
-      <c r="D15" s="54" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E15" s="86" t="n">
-        <v>1825</v>
+      <c r="D15" s="54">
+        <f>'Per-Tier Unit Economics'!K7</f>
+        <v/>
+      </c>
+      <c r="E15" s="54">
+        <f>C15*D15</f>
+        <v/>
       </c>
     </row>
     <row r="16">
@@ -5017,11 +5067,13 @@
       <c r="C16" s="71" t="n">
         <v>180</v>
       </c>
-      <c r="D16" s="54" t="n">
-        <v>13.6</v>
-      </c>
-      <c r="E16" s="86" t="n">
-        <v>2448</v>
+      <c r="D16" s="54">
+        <f>'Per-Tier Unit Economics'!K8</f>
+        <v/>
+      </c>
+      <c r="E16" s="54">
+        <f>C16*D16</f>
+        <v/>
       </c>
     </row>
     <row r="17">
@@ -5036,11 +5088,13 @@
       <c r="C17" s="71" t="n">
         <v>130</v>
       </c>
-      <c r="D17" s="54" t="n">
-        <v>13.35</v>
-      </c>
-      <c r="E17" s="86" t="n">
-        <v>1736</v>
+      <c r="D17" s="54">
+        <f>'Per-Tier Unit Economics'!K9</f>
+        <v/>
+      </c>
+      <c r="E17" s="54">
+        <f>C17*D17</f>
+        <v/>
       </c>
     </row>
     <row r="18">
@@ -5055,11 +5109,13 @@
       <c r="C18" s="71" t="n">
         <v>80</v>
       </c>
-      <c r="D18" s="54" t="n">
-        <v>21.84</v>
-      </c>
-      <c r="E18" s="86" t="n">
-        <v>1747</v>
+      <c r="D18" s="54">
+        <f>'Per-Tier Unit Economics'!K10</f>
+        <v/>
+      </c>
+      <c r="E18" s="54">
+        <f>C18*D18</f>
+        <v/>
       </c>
     </row>
     <row r="19">
@@ -5074,11 +5130,13 @@
       <c r="C19" s="71" t="n">
         <v>30</v>
       </c>
-      <c r="D19" s="54" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="E19" s="86" t="n">
-        <v>700</v>
+      <c r="D19" s="54">
+        <f>'Per-Tier Unit Economics'!K11</f>
+        <v/>
+      </c>
+      <c r="E19" s="54">
+        <f>C19*D19</f>
+        <v/>
       </c>
     </row>
     <row r="20">
@@ -5093,11 +5151,13 @@
       <c r="C20" s="71" t="n">
         <v>20</v>
       </c>
-      <c r="D20" s="54" t="n">
-        <v>33</v>
-      </c>
-      <c r="E20" s="86" t="n">
-        <v>660</v>
+      <c r="D20" s="54">
+        <f>'Per-Tier Unit Economics'!K12</f>
+        <v/>
+      </c>
+      <c r="E20" s="54">
+        <f>C20*D20</f>
+        <v/>
       </c>
     </row>
     <row r="21">
@@ -5112,18 +5172,24 @@
       <c r="C21" s="71" t="n">
         <v>30</v>
       </c>
-      <c r="D21" s="54" t="n">
-        <v>15.8</v>
-      </c>
-      <c r="E21" s="86" t="n">
-        <v>474</v>
+      <c r="D21" s="54">
+        <f>'Per-Tier Unit Economics'!K13</f>
+        <v/>
+      </c>
+      <c r="E21" s="54">
+        <f>C21*D21</f>
+        <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="43" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
+      <c r="A22" s="151" t="inlineStr">
+        <is>
+          <t>TOTAL Monthly Gross Profit (1,000 users)</t>
+        </is>
+      </c>
+      <c r="E22" s="154">
+        <f>SUM(E15:E21)</f>
+        <v/>
       </c>
     </row>
     <row r="24">
@@ -5139,51 +5205,64 @@
           <t>Monthly Gross Profit</t>
         </is>
       </c>
-      <c r="B25" s="128" t="n">
-        <v>9590</v>
+      <c r="B25" s="54">
+        <f>E22</f>
+        <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="90" t="inlineStr">
-        <is>
-          <t>OPEX (1,000 users × $1.80)</t>
-        </is>
-      </c>
-      <c r="B26" s="128" t="n">
+      <c r="A26" s="181" t="inlineStr">
+        <is>
+          <t>OPEX placeholder ($1.80/user) — NO real spend yet as of 2026-06-02</t>
+        </is>
+      </c>
+      <c r="B26" s="182" t="n">
         <v>-1800</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="90" t="inlineStr">
         <is>
-          <t>Monthly Net Profit</t>
-        </is>
-      </c>
-      <c r="B27" s="129" t="n">
-        <v>7790</v>
+          <t>Monthly Net Profit (after placeholder OPEX)</t>
+        </is>
+      </c>
+      <c r="B27" s="183">
+        <f>B25+B26</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="90" t="inlineStr">
         <is>
-          <t>Annual Net Profit</t>
-        </is>
+          <t>Annual Net Profit (placeholder OPEX baseline)</t>
+        </is>
+      </c>
+      <c r="B28" s="154">
+        <f>B27*12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Monthly Net at $0 OPEX (LAUNCH REALITY today)</t>
+        </is>
+      </c>
+      <c r="B29" s="184">
+        <f>B25</f>
+        <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="130" t="inlineStr">
-        <is>
-          <t>Bottom line: 1,000 users → $93,480/year. Scale to 10,000 → ~$935K/year. Scale to 100K → ~$9.35M/year.</t>
+      <c r="A30" s="165" t="inlineStr">
+        <is>
+          <t>BOTTOM LINE: 1,000 users → ~$149,748/yr gross (at $0 real OPEX). Scale to 10K → ~$1.50M/yr. Scale to 100K → ~$15M/yr.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A22:J22"/>
+  <mergeCells count="1">
     <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A11:J11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13239,7 +13318,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
@@ -13343,7 +13421,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="40" t="inlineStr">
         <is>
@@ -13625,8 +13702,6 @@
         <v>-1.005344021376086</v>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="40" t="inlineStr">
         <is>
@@ -13786,8 +13861,6 @@
         </is>
       </c>
     </row>
-    <row r="36"/>
-    <row r="37"/>
     <row r="38">
       <c r="A38" s="40" t="inlineStr">
         <is>
@@ -13855,7 +13928,6 @@
         </is>
       </c>
     </row>
-    <row r="44"/>
     <row r="45">
       <c r="A45" s="40" t="inlineStr">
         <is>
@@ -13877,7 +13949,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
     <row r="49">
       <c r="A49" s="39" t="inlineStr">
         <is>
@@ -13906,7 +13977,6 @@
         </is>
       </c>
     </row>
-    <row r="53"/>
     <row r="54">
       <c r="A54" s="40" t="inlineStr">
         <is>
@@ -14051,7 +14121,6 @@
         <v/>
       </c>
     </row>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="40" t="inlineStr">
         <is>
@@ -14128,7 +14197,6 @@
         <v/>
       </c>
     </row>
-    <row r="76"/>
     <row r="77">
       <c r="A77" s="40" t="inlineStr">
         <is>
@@ -14243,7 +14311,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="40" t="inlineStr">
         <is>
@@ -14347,7 +14414,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="40" t="inlineStr">
         <is>
@@ -14534,7 +14600,6 @@
         <v/>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="40" t="inlineStr">
         <is>
@@ -14677,8 +14742,6 @@
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31"/>
     <row r="32">
       <c r="A32" s="40" t="inlineStr">
         <is>
@@ -14828,8 +14891,6 @@
         </is>
       </c>
     </row>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="40" t="inlineStr">
         <is>
@@ -14909,8 +14970,6 @@
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49"/>
     <row r="50">
       <c r="A50" s="40" t="inlineStr">
         <is>
@@ -15023,7 +15082,6 @@
         <v/>
       </c>
     </row>
-    <row r="60"/>
     <row r="61">
       <c r="A61" s="40" t="inlineStr">
         <is>
@@ -15091,8 +15149,6 @@
         </is>
       </c>
     </row>
-    <row r="67"/>
-    <row r="68"/>
     <row r="69">
       <c r="A69" s="40" t="inlineStr">
         <is>

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -58,7 +58,7 @@
     <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
     <numFmt numFmtId="182" formatCode="0.0&quot; top-ups&quot;"/>
   </numFmts>
-  <fonts count="50">
+  <fonts count="52">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -316,6 +316,15 @@
       <i val="1"/>
       <color rgb="00888888"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00D71921"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="14"/>
+    </font>
   </fonts>
   <fills count="26">
     <fill>
@@ -516,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="185">
+  <cellXfs count="190">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -766,6 +775,11 @@
     <xf numFmtId="173" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="42" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="43" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1159,12 +1173,12 @@
   <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1594,54 +1608,144 @@
         <v/>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="148" t="inlineStr">
+        <is>
+          <t>GEO MIX SCENARIOS — side-by-side comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="136" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B33" s="136" t="inlineStr">
+        <is>
+          <t>Tier-A %</t>
+        </is>
+      </c>
+      <c r="C33" s="136" t="inlineStr">
+        <is>
+          <t>Tier-B %</t>
+        </is>
+      </c>
+      <c r="D33" s="136" t="inlineStr">
+        <is>
+          <t>Tier-C %</t>
+        </is>
+      </c>
+      <c r="E33" s="136" t="inlineStr">
+        <is>
+          <t>Blended $/GB</t>
+        </is>
+      </c>
+      <c r="F33" s="136" t="inlineStr">
+        <is>
+          <t>Source / rationale</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>CABIN-CLASS MIX (% of paying users in each tier)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="inlineStr">
-        <is>
-          <t>Tier</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>% Users</t>
+          <t>Optimistic (CURRENT MODEL)</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="C34" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D34" s="26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E34" s="185">
+        <f>B34*0.85+C34*1.40+D34*8.50</f>
+        <v/>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Original assumption — Emirates-crew skewed Asia</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="186" t="inlineStr">
+        <is>
+          <t>REALISTIC (layover-weighted from EK route data)</t>
+        </is>
+      </c>
+      <c r="B35" s="187" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D35" s="26" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E35" s="154">
+        <f>B35*0.85+C35*1.40+D35*8.50</f>
+        <v/>
+      </c>
+      <c r="F35" s="145" t="inlineStr">
+        <is>
+          <t>EK layover xlsx + DXB route data 2026-05-24. Excludes turnarounds (Mumbai-style 1-3h ground time). Weights Tier-C longer (24-48h vs 24h).</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="9" t="inlineStr">
         <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B36" s="13" t="n">
-        <v>0.5</v>
+          <t>Pessimistic (heavy US-Europe crew)</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C36" s="26" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D36" s="26" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E36" s="188">
+        <f>B36*0.85+C36*1.40+D36*8.50</f>
+        <v/>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>If real crew skew toward long-haul US/Cruise routes</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
-        <is>
-          <t>Roster Bundle</t>
-        </is>
-      </c>
+      <c r="A37" s="9" t="inlineStr"/>
       <c r="B37" s="13" t="n">
         <v>0.18</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Premium Economy</t>
+      <c r="A38" s="151" t="inlineStr">
+        <is>
+          <t>ACTIVE blended $/GB used by model</t>
         </is>
       </c>
       <c r="B38" s="13" t="n">
         <v>0.13</v>
       </c>
+      <c r="E38" s="189">
+        <f>E34</f>
+        <v/>
+      </c>
+      <c r="F38" s="180" t="inlineStr">
+        <is>
+          <t>← change to =E35 (REALISTIC) or =E36 (PESSIMISTIC) to flip the model</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="9" t="inlineStr">
@@ -1654,9 +1758,9 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>First</t>
+      <c r="A40" s="153" t="inlineStr">
+        <is>
+          <t>COGS IMPACT — Premium user (4 GB consumed)</t>
         </is>
       </c>
       <c r="B40" s="13" t="n">
@@ -1666,7 +1770,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>First Suite</t>
+          <t>At Optimistic $1.34/GB → COGS = $5.36 → Net contribution $13.36 (70% margin)</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1676,7 +1780,7 @@
     <row r="42">
       <c r="A42" s="9" t="inlineStr">
         <is>
-          <t>Cockpit</t>
+          <t>At Realistic $2.60/GB → COGS = $10.40 → Net contribution $7.59 (42% margin)</t>
         </is>
       </c>
       <c r="B42" s="13" t="n">
@@ -1686,11 +1790,18 @@
     <row r="43">
       <c r="A43" s="9" t="inlineStr">
         <is>
-          <t>Refuel attach</t>
+          <t>At Pessimistic $3.84/GB → COGS = $15.36 → Net contribution $2.63 (15% margin)</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
         <v>0.3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="165" t="inlineStr">
+        <is>
+          <t>AKITO ASK: Pull 5-10 crew "last 3 months layover destinations" (not turnarounds) to validate which scenario is real.</t>
+        </is>
       </c>
     </row>
     <row r="46">

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -37,7 +37,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="19">
+  <numFmts count="20">
     <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
@@ -57,6 +57,7 @@
     <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00&quot; /user/mo&quot;"/>
     <numFmt numFmtId="181" formatCode="&quot;$&quot;#,##0;[Red](&quot;$&quot;#,##0)"/>
     <numFmt numFmtId="182" formatCode="0.0&quot; top-ups&quot;"/>
+    <numFmt numFmtId="183" formatCode="0.00&quot; GB&quot;"/>
   </numFmts>
   <fonts count="52">
     <font>
@@ -525,7 +526,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="190">
+  <cellXfs count="194">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -780,6 +781,12 @@
     <xf numFmtId="165" fontId="7" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="173" fontId="51" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="183" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="173" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8304,8 +8311,8 @@
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8353,6 +8360,16 @@
           <t>Margin vs Default</t>
         </is>
       </c>
+      <c r="G4" s="136" t="inlineStr">
+        <is>
+          <t>GB Consumed/mo</t>
+        </is>
+      </c>
+      <c r="H4" s="136" t="inlineStr">
+        <is>
+          <t>Monthly Wholesale Cost ($)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
@@ -8373,8 +8390,16 @@
         <f>B5*'README &amp; Assumptions'!C27+C5*'README &amp; Assumptions'!C28+D5*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="190">
         <f>'README &amp; Assumptions'!C31-E5</f>
+        <v/>
+      </c>
+      <c r="G5" s="191">
+        <f>'User Behavior'!D21*2.5</f>
+        <v/>
+      </c>
+      <c r="H5" s="54">
+        <f>G5*E5</f>
         <v/>
       </c>
     </row>
@@ -8397,8 +8422,16 @@
         <f>B6*'README &amp; Assumptions'!C27+C6*'README &amp; Assumptions'!C28+D6*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="F6" s="11">
+      <c r="F6" s="190">
         <f>'README &amp; Assumptions'!C31-E6</f>
+        <v/>
+      </c>
+      <c r="G6" s="191">
+        <f>'User Behavior'!D22</f>
+        <v/>
+      </c>
+      <c r="H6" s="54">
+        <f>G6*E6</f>
         <v/>
       </c>
     </row>
@@ -8421,8 +8454,16 @@
         <f>B7*'README &amp; Assumptions'!C27+C7*'README &amp; Assumptions'!C28+D7*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="190">
         <f>'README &amp; Assumptions'!C31-E7</f>
+        <v/>
+      </c>
+      <c r="G7" s="191">
+        <f>'User Behavior'!D23</f>
+        <v/>
+      </c>
+      <c r="H7" s="54">
+        <f>G7*E7</f>
         <v/>
       </c>
     </row>
@@ -8445,8 +8486,16 @@
         <f>B8*'README &amp; Assumptions'!C27+C8*'README &amp; Assumptions'!C28+D8*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="190">
         <f>'README &amp; Assumptions'!C31-E8</f>
+        <v/>
+      </c>
+      <c r="G8" s="191">
+        <f>'User Behavior'!D24</f>
+        <v/>
+      </c>
+      <c r="H8" s="54">
+        <f>G8*E8</f>
         <v/>
       </c>
     </row>
@@ -8469,8 +8518,16 @@
         <f>B9*'README &amp; Assumptions'!C27+C9*'README &amp; Assumptions'!C28+D9*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="190">
         <f>'README &amp; Assumptions'!C31-E9</f>
+        <v/>
+      </c>
+      <c r="G9" s="191">
+        <f>'User Behavior'!D25</f>
+        <v/>
+      </c>
+      <c r="H9" s="54">
+        <f>G9*E9</f>
         <v/>
       </c>
     </row>
@@ -8493,8 +8550,16 @@
         <f>B10*'README &amp; Assumptions'!C27+C10*'README &amp; Assumptions'!C28+D10*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="190">
         <f>'README &amp; Assumptions'!C31-E10</f>
+        <v/>
+      </c>
+      <c r="G10" s="191">
+        <f>'User Behavior'!D26</f>
+        <v/>
+      </c>
+      <c r="H10" s="54">
+        <f>G10*E10</f>
         <v/>
       </c>
       <c r="I10" s="92" t="inlineStr">
@@ -8522,8 +8587,16 @@
         <f>B11*'README &amp; Assumptions'!C27+C11*'README &amp; Assumptions'!C28+D11*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="190">
         <f>'README &amp; Assumptions'!C31-E11</f>
+        <v/>
+      </c>
+      <c r="G11" s="191">
+        <f>'User Behavior'!D27</f>
+        <v/>
+      </c>
+      <c r="H11" s="54">
+        <f>G11*E11</f>
         <v/>
       </c>
     </row>
@@ -8546,22 +8619,29 @@
         <f>B12*'README &amp; Assumptions'!C27+C12*'README &amp; Assumptions'!C28+D12*'README &amp; Assumptions'!C29</f>
         <v/>
       </c>
-      <c r="F12">
+      <c r="F12" s="54">
         <f>'README &amp; Assumptions'!C31-E12</f>
         <v/>
       </c>
+      <c r="G12" s="191" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="54">
+        <f>G12*E12</f>
+        <v/>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>REVISED PER-TIER GROSS MARGIN (with tier-specific geo mix)</t>
+      <c r="A13" s="180" t="inlineStr">
+        <is>
+          <t>NOTE: Column G = GB consumed per user per month (verified from User Behavior tab). Column H = GB × effective $/GB = what we actually pay supplier for one user.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>Tier</t>
+      <c r="A14" s="192" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE — Maya (Economy) vs Yuki (Roster Bundle):</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
@@ -8603,31 +8683,34 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>Economy</t>
-        </is>
-      </c>
-      <c r="B15" s="21">
-        <f>'Per-Tier Unit Economics'!B7</f>
-        <v/>
-      </c>
-      <c r="C15" s="18">
-        <f>'Per-Tier Unit Economics'!C7</f>
-        <v/>
-      </c>
-      <c r="D15" s="21">
-        <f>E5</f>
-        <v/>
-      </c>
-      <c r="E15" s="11">
-        <f>C15*D15</f>
-        <v/>
-      </c>
-      <c r="F15" s="22">
-        <f>B15-E15</f>
-        <v/>
-      </c>
-      <c r="G15" s="17">
-        <f>IFERROR(F15/B15,0)</f>
+          <t>MAYA buys 2.5 GB. 40% in Tier-C (USA/Vegas).</t>
+        </is>
+      </c>
+      <c r="B15" s="21" t="inlineStr">
+        <is>
+          <t>Cost to us:</t>
+        </is>
+      </c>
+      <c r="C15" s="193">
+        <f>G5*E5</f>
+        <v/>
+      </c>
+      <c r="D15" s="21" t="inlineStr">
+        <is>
+          <t>Revenue:</t>
+        </is>
+      </c>
+      <c r="E15" s="190">
+        <f>'Per-Tier Unit Economics'!I7</f>
+        <v/>
+      </c>
+      <c r="F15" s="22" t="inlineStr">
+        <is>
+          <t>Net:</t>
+        </is>
+      </c>
+      <c r="G15" s="188">
+        <f>E15-C15</f>
         <v/>
       </c>
       <c r="H15" s="31">
@@ -8638,31 +8721,34 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>Roster Bundle</t>
-        </is>
-      </c>
-      <c r="B16" s="21">
-        <f>'Per-Tier Unit Economics'!B8</f>
-        <v/>
-      </c>
-      <c r="C16" s="18">
-        <f>'Per-Tier Unit Economics'!C8</f>
-        <v/>
-      </c>
-      <c r="D16" s="21">
-        <f>E6</f>
-        <v/>
-      </c>
-      <c r="E16" s="11">
-        <f>C16*D16</f>
-        <v/>
-      </c>
-      <c r="F16" s="22">
-        <f>B16-E16</f>
-        <v/>
-      </c>
-      <c r="G16" s="17">
-        <f>IFERROR(F16/B16,0)</f>
+          <t>YUKI buys 5 GB. 70% in Tier-A (Mumbai/Bangkok).</t>
+        </is>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Cost to us:</t>
+        </is>
+      </c>
+      <c r="C16" s="193">
+        <f>G6*E6</f>
+        <v/>
+      </c>
+      <c r="D16" s="21" t="inlineStr">
+        <is>
+          <t>Revenue:</t>
+        </is>
+      </c>
+      <c r="E16" s="190">
+        <f>'Per-Tier Unit Economics'!I8</f>
+        <v/>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>Net:</t>
+        </is>
+      </c>
+      <c r="G16" s="185">
+        <f>E16-C16</f>
         <v/>
       </c>
       <c r="H16" s="31">
@@ -8671,9 +8757,9 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>Premium Economy</t>
+      <c r="A17" s="180" t="inlineStr">
+        <is>
+          <t>Same data world, very different profit per user — because of WHERE they roam.</t>
         </is>
       </c>
       <c r="B17" s="21">

--- a/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
+++ b/docs/downloads/Peanut-eSIM-PL-Model-2026-05-31.xlsx
@@ -327,7 +327,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="26">
+  <fills count="27">
     <fill>
       <patternFill/>
     </fill>
@@ -455,6 +455,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C9A03B"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="6">
     <border>
@@ -526,7 +531,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="194">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -787,6 +792,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="173" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="26" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="183" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="173" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="50" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -8302,10 +8314,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
@@ -8632,49 +8644,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="180" t="inlineStr">
-        <is>
-          <t>NOTE: Column G = GB consumed per user per month (verified from User Behavior tab). Column H = GB × effective $/GB = what we actually pay supplier for one user.</t>
+      <c r="A13" s="148" t="inlineStr">
+        <is>
+          <t>REVISED PER-TIER GROSS MARGIN (with tier-specific geo mix)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="192" t="inlineStr">
-        <is>
-          <t>WORKED EXAMPLE — Maya (Economy) vs Yuki (Roster Bundle):</t>
-        </is>
-      </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="A14" s="194" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="B14" s="194" t="inlineStr">
         <is>
           <t>Monthly Revenue</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="194" t="inlineStr">
         <is>
           <t>GB Consumed</t>
         </is>
       </c>
-      <c r="D14" s="8" t="inlineStr">
+      <c r="D14" s="194" t="inlineStr">
         <is>
           <t>Effective $/GB</t>
         </is>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="E14" s="194" t="inlineStr">
         <is>
           <t>Adjusted COGS</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="194" t="inlineStr">
         <is>
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="G14" s="194" t="inlineStr">
         <is>
           <t>Margin %</t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="H14" s="194" t="inlineStr">
         <is>
           <t>vs Default</t>
         </is>
@@ -8683,37 +8695,34 @@
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>MAYA buys 2.5 GB. 40% in Tier-C (USA/Vegas).</t>
-        </is>
-      </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>Cost to us:</t>
-        </is>
-      </c>
-      <c r="C15" s="193">
-        <f>G5*E5</f>
-        <v/>
-      </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>Revenue:</t>
-        </is>
+          <t>Economy</t>
+        </is>
+      </c>
+      <c r="B15" s="193">
+        <f>'Per-Tier Unit Economics'!B7</f>
+        <v/>
+      </c>
+      <c r="C15" s="195">
+        <f>'Per-Tier Unit Economics'!C7</f>
+        <v/>
+      </c>
+      <c r="D15" s="193">
+        <f>E5</f>
+        <v/>
       </c>
       <c r="E15" s="190">
-        <f>'Per-Tier Unit Economics'!I7</f>
-        <v/>
-      </c>
-      <c r="F15" s="22" t="inlineStr">
-        <is>
-          <t>Net:</t>
-        </is>
-      </c>
-      <c r="G15" s="188">
-        <f>E15-C15</f>
-        <v/>
-      </c>
-      <c r="H15" s="31">
+        <f>C15*D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="196">
+        <f>B15-E15</f>
+        <v/>
+      </c>
+      <c r="G15" s="197">
+        <f>IFERROR(F15/B15,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="190">
         <f>F15-'Per-Tier Unit Economics'!K7</f>
         <v/>
       </c>
@@ -8721,37 +8730,34 @@
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>YUKI buys 5 GB. 70% in Tier-A (Mumbai/Bangkok).</t>
-        </is>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>Cost to us:</t>
-        </is>
-      </c>
-      <c r="C16" s="193">
-        <f>G6*E6</f>
-        <v/>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>Revenue:</t>
-        </is>
+          <t>Roster Bundle</t>
+        </is>
+      </c>
+      <c r="B16" s="193">
+        <f>'Per-Tier Unit Economics'!B8</f>
+        <v/>
+      </c>
+      <c r="C16" s="195">
+        <f>'Per-Tier Unit Economics'!C8</f>
+        <v/>
+      </c>
+      <c r="D16" s="193">
+        <f>E6</f>
+        <v/>
       </c>
       <c r="E16" s="190">
-        <f>'Per-Tier Unit Economics'!I8</f>
-        <v/>
-      </c>
-      <c r="F16" s="22" t="inlineStr">
-        <is>
-          <t>Net:</t>
-        </is>
-      </c>
-      <c r="G16" s="185">
-        <f>E16-C16</f>
-        <v/>
-      </c>
-      <c r="H16" s="31">
+        <f>C16*D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="196">
+        <f>B16-E16</f>
+        <v/>
+      </c>
+      <c r="G16" s="155">
+        <f>IFERROR(F16/B16,0)</f>
+        <v/>
+      </c>
+      <c r="H16" s="190">
         <f>F16-'Per-Tier Unit Economics'!K8</f>
         <v/>
       </c>
@@ -8759,26 +8765,26 @@
     <row r="17">
       <c r="A17" s="180" t="inlineStr">
         <is>
-          <t>Same data world, very different profit per user — because of WHERE they roam.</t>
-        </is>
-      </c>
-      <c r="B17" s="21">
+          <t>Premium Economy</t>
+        </is>
+      </c>
+      <c r="B17" s="193">
         <f>'Per-Tier Unit Economics'!B9</f>
         <v/>
       </c>
-      <c r="C17" s="18">
+      <c r="C17" s="195">
         <f>'Per-Tier Unit Economics'!C9</f>
         <v/>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="193">
         <f>E7</f>
         <v/>
       </c>
-      <c r="E17" s="11">
+      <c r="E17" s="190">
         <f>C17*D17</f>
         <v/>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="196">
         <f>B17-E17</f>
         <v/>
       </c>
@@ -8786,7 +8792,7 @@
         <f>IFERROR(F17/B17,0)</f>
         <v/>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="190">
         <f>F17-'Per-Tier Unit Economics'!K9</f>
         <v/>
       </c>
@@ -8797,23 +8803,23 @@
           <t>Business</t>
         </is>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="193">
         <f>'Per-Tier Unit Economics'!B10</f>
         <v/>
       </c>
-      <c r="C18" s="18">
+      <c r="C18" s="195">
         <f>'Per-Tier Unit Economics'!C10</f>
         <v/>
       </c>
-      <c r="D18" s="21">
+      <c r="D18" s="193">
         <f>E8</f>
         <v/>
       </c>
-      <c r="E18" s="11">
+      <c r="E18" s="190">
         <f>C18*D18</f>
         <v/>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="196">
         <f>B18-E18</f>
         <v/>
       </c>
@@ -8821,7 +8827,7 @@
         <f>IFERROR(F18/B18,0)</f>
         <v/>
       </c>
-      <c r="H18" s="31">
+      <c r="H18" s="190">
         <f>F18-'Per-Tier Unit Economics'!K10</f>
         <v/>
       </c>
@@ -8832,23 +8838,23 @@
           <t>First</t>
         </is>
       </c>
-      <c r="B19" s="21">
+      <c r="B19" s="193">
         <f>'Per-Tier Unit Economics'!B11</f>
         <v/>
       </c>
-      <c r="C19" s="18">
+      <c r="C19" s="195">
         <f>'Per-Tier Unit Economics'!C11</f>
         <v/>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="193">
         <f>E9</f>
         <v/>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="190">
         <f>C19*D19</f>
         <v/>
       </c>
-      <c r="F19" s="22">
+      <c r="F19" s="196">
         <f>B19-E19</f>
         <v/>
       </c>
@@ -8856,7 +8862,7 @@
         <f>IFERROR(F19/B19,0)</f>
         <v/>
       </c>
-      <c r="H19" s="31">
+      <c r="H19" s="190">
         <f>F19-'Per-Tier Unit Economics'!K11</f>
         <v/>
       </c>
@@ -8867,23 +8873,23 @@
           <t>First Suite</t>
         </is>
       </c>
-      <c r="B20" s="21">
+      <c r="B20" s="193">
         <f>'Per-Tier Unit Economics'!B12</f>
         <v/>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="195">
         <f>'Per-Tier Unit Economics'!C12</f>
         <v/>
       </c>
-      <c r="D20" s="21">
+      <c r="D20" s="193">
         <f>E10</f>
         <v/>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="190">
         <f>C20*D20</f>
         <v/>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="196">
         <f>B20-E20</f>
         <v/>
       </c>
@@ -8891,7 +8897,7 @@
         <f>IFERROR(F20/B20,0)</f>
         <v/>
       </c>
-      <c r="H20" s="31">
+      <c r="H20" s="190">
         <f>F20-'Per-Tier Unit Economics'!K12</f>
         <v/>
       </c>
@@ -8902,23 +8908,23 @@
           <t>Cockpit</t>
         </is>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="193">
         <f>'Per-Tier Unit Economics'!B13</f>
         <v/>
       </c>
-      <c r="C21" s="18">
+      <c r="C21" s="195">
         <f>'Per-Tier Unit Economics'!C13</f>
         <v/>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="193">
         <f>E11</f>
         <v/>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="190">
         <f>C21*D21</f>
         <v/>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="196">
         <f>B21-E21</f>
         <v/>
       </c>
@@ -8926,7 +8932,7 @@
         <f>IFERROR(F21/B21,0)</f>
         <v/>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="190">
         <f>F21-'Per-Tier Unit Economics'!K13</f>
         <v/>
       </c>
@@ -8937,32 +8943,128 @@
           <t>Refuel</t>
         </is>
       </c>
-      <c r="B22">
+      <c r="B22" s="54">
         <f>'README &amp; Assumptions'!B21</f>
         <v/>
       </c>
-      <c r="C22" t="n">
+      <c r="C22" s="191" t="n">
         <v>1</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="54">
         <f>E12</f>
         <v/>
       </c>
-      <c r="E22">
+      <c r="E22" s="54">
         <f>C22*D22</f>
         <v/>
       </c>
-      <c r="F22">
+      <c r="F22" s="54">
         <f>B22-E22</f>
         <v/>
       </c>
-      <c r="G22">
+      <c r="G22" s="26">
         <f>IFERROR(F22/B22,0)</f>
         <v/>
       </c>
-      <c r="H22">
+      <c r="H22" s="54">
         <f>F22-('README &amp; Assumptions'!B21-'README &amp; Assumptions'!C31)</f>
         <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="198" t="inlineStr">
+        <is>
+          <t>WORKED EXAMPLE — Maya (Economy) vs Yuki (Roster Bundle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="149" t="inlineStr">
+        <is>
+          <t>Same eSIM service. Different user. Different profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>MAYA buys 2.5 GB (Economy PAYG). 40% used in Tier-C (USA/Vegas).</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Cost to us:</t>
+        </is>
+      </c>
+      <c r="C26" s="54">
+        <f>G5*E5</f>
+        <v/>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Revenue:</t>
+        </is>
+      </c>
+      <c r="E26" s="54">
+        <f>'Per-Tier Unit Economics'!I7</f>
+        <v/>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Net:</t>
+        </is>
+      </c>
+      <c r="G26" s="188">
+        <f>E26-C26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>YUKI buys 5 GB (Roster Bundle). 70% used in Tier-A (Mumbai/Bangkok).</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Cost to us:</t>
+        </is>
+      </c>
+      <c r="C27" s="54">
+        <f>G6*E6</f>
+        <v/>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Revenue:</t>
+        </is>
+      </c>
+      <c r="E27" s="54">
+        <f>'Per-Tier Unit Economics'!I8</f>
+        <v/>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Net:</t>
+        </is>
+      </c>
+      <c r="G27" s="185">
+        <f>E27-C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="180" t="inlineStr">
+        <is>
+          <t>Same supplier costs. Yuki uses 2x the data. But Yuki delivers 5.7x more profit — because of WHERE she roams.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="180" t="inlineStr">
+        <is>
+          <t>NOTE: Column G in Section 1 = GB consumed per user per month. Column H = monthly wholesale cost = GB x effective $/GB.</t>
+        </is>
       </c>
     </row>
   </sheetData>
